--- a/nickname_song.xlsx
+++ b/nickname_song.xlsx
@@ -1,10 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ClashConfig\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="25600" windowHeight="10480"/>
+    <workbookView windowWidth="25600" windowHeight="9880"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -27,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1396" uniqueCount="1386">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1397" uniqueCount="1387">
   <si>
     <t>Id</t>
   </si>
@@ -3671,6 +3676,9 @@
   </si>
   <si>
     <t>遥之彼方,遥彼方,羊叫</t>
+  </si>
+  <si>
+    <t>纯白思念</t>
   </si>
   <si>
     <t>“Say cheese!!!!!”</t>
@@ -4333,7 +4341,7 @@
     <t>Choco Typhooooon!!</t>
   </si>
   <si>
-    <t>台风</t>
+    <t>台风,巧可台风,巧克台风,typ</t>
   </si>
   <si>
     <t>dokidoki,dkdk,ksar约会曲,演都不演了,心跳心跳约会,心动心动约会</t>
@@ -4442,14 +4450,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="28">
-    <font>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
+  <fonts count="25">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -4617,20 +4618,8 @@
     <font>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="Segoe UI Symbol"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="1"/>
       <name val="Yu Gothic"/>
       <charset val="128"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
@@ -4948,28 +4937,31 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -4978,125 +4970,122 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="49">
@@ -5481,7 +5470,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C723"/>
+  <dimension ref="A1:C724"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="10.7" customWidth="1"/>
@@ -12098,174 +12087,174 @@
     </row>
     <row r="604" spans="1:3">
       <c r="A604">
-        <v>646</v>
-      </c>
-      <c r="B604" t="s">
+        <v>645</v>
+      </c>
+      <c r="C604" s="1" t="s">
         <v>1190</v>
-      </c>
-      <c r="C604" t="s">
-        <v>1191</v>
       </c>
     </row>
     <row r="605" spans="1:3">
       <c r="A605">
-        <v>647</v>
-      </c>
-      <c r="C605" s="1" t="s">
+        <v>646</v>
+      </c>
+      <c r="B605" t="s">
+        <v>1191</v>
+      </c>
+      <c r="C605" t="s">
         <v>1192</v>
       </c>
     </row>
     <row r="606" spans="1:3">
       <c r="A606">
-        <v>649</v>
-      </c>
-      <c r="B606" t="s">
+        <v>647</v>
+      </c>
+      <c r="C606" s="1" t="s">
         <v>1193</v>
-      </c>
-      <c r="C606" t="s">
-        <v>1194</v>
       </c>
     </row>
     <row r="607" spans="1:3">
       <c r="A607">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="B607" t="s">
+        <v>1194</v>
+      </c>
+      <c r="C607" t="s">
         <v>1195</v>
-      </c>
-      <c r="C607" s="1" t="s">
-        <v>1196</v>
       </c>
     </row>
     <row r="608" spans="1:3">
       <c r="A608">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="B608" t="s">
+        <v>1196</v>
+      </c>
+      <c r="C608" s="1" t="s">
         <v>1197</v>
-      </c>
-      <c r="C608" t="s">
-        <v>1198</v>
       </c>
     </row>
     <row r="609" spans="1:3">
       <c r="A609">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="B609" t="s">
+        <v>1198</v>
+      </c>
+      <c r="C609" t="s">
         <v>1199</v>
-      </c>
-      <c r="C609" t="s">
-        <v>1200</v>
       </c>
     </row>
     <row r="610" spans="1:3">
       <c r="A610">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="B610" t="s">
+        <v>1200</v>
+      </c>
+      <c r="C610" t="s">
         <v>1201</v>
-      </c>
-      <c r="C610" t="s">
-        <v>1202</v>
       </c>
     </row>
     <row r="611" spans="1:3">
       <c r="A611">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="B611" t="s">
+        <v>1202</v>
+      </c>
+      <c r="C611" t="s">
         <v>1203</v>
-      </c>
-      <c r="C611" t="s">
-        <v>1204</v>
       </c>
     </row>
     <row r="612" spans="1:3">
       <c r="A612">
-        <v>657</v>
-      </c>
-      <c r="C612" s="1" t="s">
+        <v>655</v>
+      </c>
+      <c r="B612" t="s">
+        <v>1204</v>
+      </c>
+      <c r="C612" t="s">
         <v>1205</v>
       </c>
     </row>
     <row r="613" spans="1:3">
       <c r="A613">
-        <v>659</v>
-      </c>
-      <c r="B613" t="s">
+        <v>657</v>
+      </c>
+      <c r="C613" s="1" t="s">
         <v>1206</v>
-      </c>
-      <c r="C613" t="s">
-        <v>1207</v>
       </c>
     </row>
     <row r="614" spans="1:3">
       <c r="A614">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="B614" t="s">
+        <v>1207</v>
+      </c>
+      <c r="C614" t="s">
         <v>1208</v>
-      </c>
-      <c r="C614" t="s">
-        <v>1209</v>
       </c>
     </row>
     <row r="615" spans="1:3">
       <c r="A615">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="B615" t="s">
+        <v>1209</v>
+      </c>
+      <c r="C615" t="s">
         <v>1210</v>
-      </c>
-      <c r="C615" t="s">
-        <v>1211</v>
       </c>
     </row>
     <row r="616" spans="1:3">
       <c r="A616">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="B616" t="s">
+        <v>1211</v>
+      </c>
+      <c r="C616" t="s">
         <v>1212</v>
-      </c>
-      <c r="C616" t="s">
-        <v>1213</v>
       </c>
     </row>
     <row r="617" spans="1:3">
       <c r="A617">
-        <v>667</v>
+        <v>663</v>
       </c>
       <c r="B617" t="s">
+        <v>1213</v>
+      </c>
+      <c r="C617" t="s">
         <v>1214</v>
-      </c>
-      <c r="C617" t="s">
-        <v>1215</v>
       </c>
     </row>
     <row r="618" spans="1:3">
       <c r="A618">
-        <v>669</v>
-      </c>
-      <c r="C618" s="1" t="s">
+        <v>667</v>
+      </c>
+      <c r="B618" t="s">
+        <v>1215</v>
+      </c>
+      <c r="C618" t="s">
         <v>1216</v>
       </c>
     </row>
     <row r="619" spans="1:3">
       <c r="A619">
-        <v>670</v>
-      </c>
-      <c r="B619" t="s">
+        <v>669</v>
+      </c>
+      <c r="C619" s="1" t="s">
         <v>1217</v>
-      </c>
-      <c r="C619" s="1" t="s">
-        <v>1218</v>
       </c>
     </row>
     <row r="620" spans="1:3">
       <c r="A620">
-        <v>672</v>
+        <v>670</v>
+      </c>
+      <c r="B620" t="s">
+        <v>1218</v>
       </c>
       <c r="C620" s="1" t="s">
         <v>1219</v>
@@ -12273,183 +12262,183 @@
     </row>
     <row r="621" spans="1:3">
       <c r="A621">
-        <v>673</v>
-      </c>
-      <c r="B621" t="s">
+        <v>672</v>
+      </c>
+      <c r="C621" s="1" t="s">
         <v>1220</v>
-      </c>
-      <c r="C621" t="s">
-        <v>1221</v>
       </c>
     </row>
     <row r="622" spans="1:3">
       <c r="A622">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="B622" t="s">
+        <v>1221</v>
+      </c>
+      <c r="C622" t="s">
         <v>1222</v>
-      </c>
-      <c r="C622" t="s">
-        <v>1223</v>
       </c>
     </row>
     <row r="623" spans="1:3">
       <c r="A623">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="B623" t="s">
+        <v>1223</v>
+      </c>
+      <c r="C623" t="s">
         <v>1224</v>
-      </c>
-      <c r="C623" t="s">
-        <v>1225</v>
       </c>
     </row>
     <row r="624" spans="1:3">
       <c r="A624">
-        <v>680</v>
+        <v>675</v>
       </c>
       <c r="B624" t="s">
+        <v>1225</v>
+      </c>
+      <c r="C624" t="s">
         <v>1226</v>
-      </c>
-      <c r="C624" t="s">
-        <v>1227</v>
       </c>
     </row>
     <row r="625" spans="1:3">
       <c r="A625">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="B625" t="s">
+        <v>1227</v>
+      </c>
+      <c r="C625" t="s">
         <v>1228</v>
-      </c>
-      <c r="C625" t="s">
-        <v>1229</v>
       </c>
     </row>
     <row r="626" spans="1:3">
       <c r="A626">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="B626" t="s">
+        <v>1229</v>
+      </c>
+      <c r="C626" t="s">
         <v>1230</v>
-      </c>
-      <c r="C626" s="1" t="s">
-        <v>1231</v>
       </c>
     </row>
     <row r="627" spans="1:3">
       <c r="A627">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="B627" t="s">
+        <v>1231</v>
+      </c>
+      <c r="C627" s="1" t="s">
         <v>1232</v>
-      </c>
-      <c r="C627" t="s">
-        <v>1233</v>
       </c>
     </row>
     <row r="628" spans="1:3">
       <c r="A628">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B628" t="s">
+        <v>1233</v>
+      </c>
+      <c r="C628" t="s">
         <v>1234</v>
-      </c>
-      <c r="C628" t="s">
-        <v>1235</v>
       </c>
     </row>
     <row r="629" spans="1:3">
       <c r="A629">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="B629" t="s">
+        <v>1235</v>
+      </c>
+      <c r="C629" t="s">
         <v>1236</v>
-      </c>
-      <c r="C629" t="s">
-        <v>1237</v>
       </c>
     </row>
     <row r="630" spans="1:3">
       <c r="A630">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="B630" t="s">
+        <v>1237</v>
+      </c>
+      <c r="C630" t="s">
         <v>1238</v>
-      </c>
-      <c r="C630" t="s">
-        <v>1239</v>
       </c>
     </row>
     <row r="631" spans="1:3">
       <c r="A631">
-        <v>689</v>
+        <v>686</v>
       </c>
       <c r="B631" t="s">
+        <v>1239</v>
+      </c>
+      <c r="C631" t="s">
         <v>1240</v>
-      </c>
-      <c r="C631" t="s">
-        <v>1241</v>
       </c>
     </row>
     <row r="632" spans="1:3">
       <c r="A632">
-        <v>697</v>
+        <v>689</v>
       </c>
       <c r="B632" t="s">
+        <v>1241</v>
+      </c>
+      <c r="C632" t="s">
         <v>1242</v>
-      </c>
-      <c r="C632" s="1" t="s">
-        <v>1243</v>
       </c>
     </row>
     <row r="633" spans="1:3">
       <c r="A633">
-        <v>701</v>
+        <v>697</v>
       </c>
       <c r="B633" t="s">
+        <v>1243</v>
+      </c>
+      <c r="C633" s="1" t="s">
         <v>1244</v>
-      </c>
-      <c r="C633" t="s">
-        <v>1245</v>
       </c>
     </row>
     <row r="634" spans="1:3">
       <c r="A634">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="B634" t="s">
+        <v>1245</v>
+      </c>
+      <c r="C634" t="s">
         <v>1246</v>
-      </c>
-      <c r="C634" t="s">
-        <v>1247</v>
       </c>
     </row>
     <row r="635" spans="1:3">
       <c r="A635">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="B635" t="s">
+        <v>1247</v>
+      </c>
+      <c r="C635" t="s">
         <v>1248</v>
-      </c>
-      <c r="C635" s="1" t="s">
-        <v>1249</v>
       </c>
     </row>
     <row r="636" spans="1:3">
       <c r="A636">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="B636" t="s">
+        <v>1249</v>
+      </c>
+      <c r="C636" s="1" t="s">
         <v>1250</v>
-      </c>
-      <c r="C636" s="1" t="s">
-        <v>1251</v>
       </c>
     </row>
     <row r="637" spans="1:3">
       <c r="A637">
-        <v>707</v>
+        <v>705</v>
+      </c>
+      <c r="B637" t="s">
+        <v>1251</v>
       </c>
       <c r="C637" s="1" t="s">
         <v>1252</v>
@@ -12457,7 +12446,7 @@
     </row>
     <row r="638" spans="1:3">
       <c r="A638">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="C638" s="1" t="s">
         <v>1253</v>
@@ -12465,51 +12454,51 @@
     </row>
     <row r="639" spans="1:3">
       <c r="A639">
-        <v>710</v>
-      </c>
-      <c r="B639" t="s">
+        <v>708</v>
+      </c>
+      <c r="C639" s="1" t="s">
         <v>1254</v>
-      </c>
-      <c r="C639" s="1" t="s">
-        <v>1255</v>
       </c>
     </row>
     <row r="640" spans="1:3">
       <c r="A640">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="B640" t="s">
+        <v>1255</v>
+      </c>
+      <c r="C640" s="1" t="s">
         <v>1256</v>
-      </c>
-      <c r="C640" t="s">
-        <v>1257</v>
       </c>
     </row>
     <row r="641" spans="1:3">
       <c r="A641">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="B641" t="s">
+        <v>1257</v>
+      </c>
+      <c r="C641" t="s">
         <v>1258</v>
-      </c>
-      <c r="C641" s="1" t="s">
-        <v>1259</v>
       </c>
     </row>
     <row r="642" spans="1:3">
       <c r="A642">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="B642" t="s">
+        <v>1259</v>
+      </c>
+      <c r="C642" s="1" t="s">
         <v>1260</v>
-      </c>
-      <c r="C642" s="1" t="s">
-        <v>1261</v>
       </c>
     </row>
     <row r="643" spans="1:3">
       <c r="A643">
-        <v>715</v>
+        <v>714</v>
+      </c>
+      <c r="B643" t="s">
+        <v>1261</v>
       </c>
       <c r="C643" s="1" t="s">
         <v>1262</v>
@@ -12517,7 +12506,7 @@
     </row>
     <row r="644" spans="1:3">
       <c r="A644">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="C644" s="1" t="s">
         <v>1263</v>
@@ -12525,158 +12514,158 @@
     </row>
     <row r="645" spans="1:3">
       <c r="A645">
-        <v>717</v>
-      </c>
-      <c r="B645" t="s">
+        <v>716</v>
+      </c>
+      <c r="C645" s="1" t="s">
         <v>1264</v>
-      </c>
-      <c r="C645" s="1" t="s">
-        <v>1265</v>
       </c>
     </row>
     <row r="646" spans="1:3">
       <c r="A646">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="B646" t="s">
+        <v>1265</v>
+      </c>
+      <c r="C646" s="1" t="s">
         <v>1266</v>
-      </c>
-      <c r="C646" t="s">
-        <v>1267</v>
       </c>
     </row>
     <row r="647" spans="1:3">
       <c r="A647">
+        <v>718</v>
+      </c>
+      <c r="B647" t="s">
+        <v>1267</v>
+      </c>
+      <c r="C647" t="s">
+        <v>1268</v>
+      </c>
+    </row>
+    <row r="648" spans="1:3">
+      <c r="A648">
         <v>719</v>
       </c>
-      <c r="B647" t="s">
-        <v>1268</v>
-      </c>
-      <c r="C647" t="s">
+      <c r="B648" t="s">
         <v>1269</v>
       </c>
-    </row>
-    <row r="648" ht="20" spans="1:3">
-      <c r="A648">
+      <c r="C648" t="s">
+        <v>1270</v>
+      </c>
+    </row>
+    <row r="649" ht="20" spans="1:3">
+      <c r="A649">
         <v>721</v>
       </c>
-      <c r="B648" t="s">
-        <v>1270</v>
-      </c>
-      <c r="C648" t="s">
+      <c r="B649" t="s">
         <v>1271</v>
       </c>
-    </row>
-    <row r="649" spans="1:3">
-      <c r="A649">
-        <v>722</v>
-      </c>
-      <c r="B649" t="s">
+      <c r="C649" t="s">
         <v>1272</v>
-      </c>
-      <c r="C649" t="s">
-        <v>1273</v>
       </c>
     </row>
     <row r="650" spans="1:3">
       <c r="A650">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="B650" t="s">
+        <v>1273</v>
+      </c>
+      <c r="C650" t="s">
         <v>1274</v>
-      </c>
-      <c r="C650" t="s">
-        <v>1275</v>
       </c>
     </row>
     <row r="651" spans="1:3">
       <c r="A651">
-        <v>724</v>
-      </c>
-      <c r="C651" s="1" t="s">
+        <v>723</v>
+      </c>
+      <c r="B651" t="s">
+        <v>1275</v>
+      </c>
+      <c r="C651" t="s">
         <v>1276</v>
       </c>
     </row>
     <row r="652" spans="1:3">
       <c r="A652">
-        <v>725</v>
-      </c>
-      <c r="B652" s="3" t="s">
+        <v>724</v>
+      </c>
+      <c r="C652" s="1" t="s">
         <v>1277</v>
-      </c>
-      <c r="C652" t="s">
-        <v>1278</v>
       </c>
     </row>
     <row r="653" spans="1:3">
       <c r="A653">
-        <v>726</v>
-      </c>
-      <c r="B653" t="s">
+        <v>725</v>
+      </c>
+      <c r="B653" s="3" t="s">
+        <v>1278</v>
+      </c>
+      <c r="C653" t="s">
         <v>1279</v>
-      </c>
-      <c r="C653" t="s">
-        <v>1280</v>
       </c>
     </row>
     <row r="654" spans="1:3">
       <c r="A654">
+        <v>726</v>
+      </c>
+      <c r="B654" t="s">
+        <v>1280</v>
+      </c>
+      <c r="C654" t="s">
+        <v>1281</v>
+      </c>
+    </row>
+    <row r="655" spans="1:3">
+      <c r="A655">
         <v>727</v>
       </c>
-      <c r="B654" t="s">
-        <v>1281</v>
-      </c>
-      <c r="C654" s="1" t="s">
+      <c r="B655" t="s">
         <v>1282</v>
       </c>
-    </row>
-    <row r="655" ht="20" spans="1:3">
-      <c r="A655">
-        <v>728</v>
-      </c>
-      <c r="B655" t="s">
+      <c r="C655" s="1" t="s">
         <v>1283</v>
-      </c>
-      <c r="C655" s="1" t="s">
-        <v>1284</v>
       </c>
     </row>
     <row r="656" ht="20" spans="1:3">
       <c r="A656">
+        <v>728</v>
+      </c>
+      <c r="B656" t="s">
+        <v>1284</v>
+      </c>
+      <c r="C656" s="1" t="s">
+        <v>1285</v>
+      </c>
+    </row>
+    <row r="657" ht="20" spans="1:3">
+      <c r="A657">
         <v>729</v>
       </c>
-      <c r="B656" t="s">
-        <v>1285</v>
-      </c>
-      <c r="C656" s="1" t="s">
+      <c r="B657" t="s">
         <v>1286</v>
       </c>
-    </row>
-    <row r="657" spans="1:3">
-      <c r="A657">
-        <v>730</v>
-      </c>
-      <c r="B657" t="s">
+      <c r="C657" s="1" t="s">
         <v>1287</v>
-      </c>
-      <c r="C657" s="1" t="s">
-        <v>1288</v>
       </c>
     </row>
     <row r="658" spans="1:3">
       <c r="A658">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="B658" t="s">
+        <v>1288</v>
+      </c>
+      <c r="C658" s="1" t="s">
         <v>1289</v>
-      </c>
-      <c r="C658" s="1" t="s">
-        <v>1290</v>
       </c>
     </row>
     <row r="659" spans="1:3">
       <c r="A659">
-        <v>732</v>
+        <v>731</v>
+      </c>
+      <c r="B659" t="s">
+        <v>1290</v>
       </c>
       <c r="C659" s="1" t="s">
         <v>1291</v>
@@ -12684,200 +12673,199 @@
     </row>
     <row r="660" spans="1:3">
       <c r="A660">
-        <v>733</v>
-      </c>
-      <c r="B660" t="s">
+        <v>732</v>
+      </c>
+      <c r="C660" s="1" t="s">
         <v>1292</v>
-      </c>
-      <c r="C660" t="s">
-        <v>1293</v>
       </c>
     </row>
     <row r="661" spans="1:3">
       <c r="A661">
-        <v>734</v>
-      </c>
-      <c r="C661" s="1" t="s">
+        <v>733</v>
+      </c>
+      <c r="B661" t="s">
+        <v>1293</v>
+      </c>
+      <c r="C661" t="s">
         <v>1294</v>
       </c>
     </row>
     <row r="662" spans="1:3">
       <c r="A662">
-        <v>735</v>
-      </c>
-      <c r="B662" s="1" t="s">
+        <v>734</v>
+      </c>
+      <c r="C662" s="1" t="s">
         <v>1295</v>
-      </c>
-      <c r="C662" s="1" t="s">
-        <v>1296</v>
       </c>
     </row>
     <row r="663" spans="1:3">
       <c r="A663">
-        <v>736</v>
-      </c>
-      <c r="B663" t="s">
+        <v>735</v>
+      </c>
+      <c r="B663" s="1" t="s">
+        <v>1296</v>
+      </c>
+      <c r="C663" s="1" t="s">
         <v>1297</v>
-      </c>
-      <c r="C663" s="1" t="s">
-        <v>1298</v>
       </c>
     </row>
     <row r="664" spans="1:3">
       <c r="A664">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="B664" t="s">
+        <v>1298</v>
+      </c>
+      <c r="C664" s="1" t="s">
         <v>1299</v>
-      </c>
-      <c r="C664" s="1" t="s">
-        <v>1300</v>
       </c>
     </row>
     <row r="665" spans="1:3">
       <c r="A665">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="B665" t="s">
+        <v>1300</v>
+      </c>
+      <c r="C665" s="1" t="s">
         <v>1301</v>
-      </c>
-      <c r="C665" t="s">
-        <v>1302</v>
       </c>
     </row>
     <row r="666" spans="1:3">
       <c r="A666">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="B666" t="s">
+        <v>1302</v>
+      </c>
+      <c r="C666" t="s">
         <v>1303</v>
-      </c>
-      <c r="C666" t="s">
-        <v>1304</v>
       </c>
     </row>
     <row r="667" spans="1:3">
       <c r="A667">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="B667" t="s">
+        <v>1304</v>
+      </c>
+      <c r="C667" t="s">
         <v>1305</v>
-      </c>
-      <c r="C667" t="s">
-        <v>1306</v>
       </c>
     </row>
     <row r="668" spans="1:3">
       <c r="A668">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="B668" t="s">
+        <v>1306</v>
+      </c>
+      <c r="C668" t="s">
         <v>1307</v>
-      </c>
-      <c r="C668" s="1" t="s">
-        <v>1308</v>
       </c>
     </row>
     <row r="669" spans="1:3">
       <c r="A669">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="B669" t="s">
+        <v>1308</v>
+      </c>
+      <c r="C669" s="1" t="s">
         <v>1309</v>
-      </c>
-      <c r="C669" s="1" t="s">
-        <v>1310</v>
       </c>
     </row>
     <row r="670" spans="1:3">
       <c r="A670">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="B670" t="s">
+        <v>1310</v>
+      </c>
+      <c r="C670" s="1" t="s">
         <v>1311</v>
-      </c>
-      <c r="C670" s="1" t="s">
-        <v>1312</v>
       </c>
     </row>
     <row r="671" spans="1:3">
       <c r="A671">
+        <v>743</v>
+      </c>
+      <c r="B671" t="s">
+        <v>1312</v>
+      </c>
+      <c r="C671" s="1" t="s">
+        <v>1313</v>
+      </c>
+    </row>
+    <row r="672" spans="1:3">
+      <c r="A672">
         <v>744</v>
       </c>
-      <c r="B671" t="s">
-        <v>1313</v>
-      </c>
-      <c r="C671" t="s">
+      <c r="B672" t="s">
         <v>1314</v>
       </c>
-    </row>
-    <row r="672" ht="20" spans="1:3">
-      <c r="A672">
+      <c r="C672" t="s">
+        <v>1315</v>
+      </c>
+    </row>
+    <row r="673" ht="20" spans="1:3">
+      <c r="A673">
         <v>745</v>
       </c>
-      <c r="B672" s="2" t="s">
-        <v>1315</v>
-      </c>
-      <c r="C672" t="s">
+      <c r="B673" s="2" t="s">
         <v>1316</v>
       </c>
-    </row>
-    <row r="673" spans="1:3">
-      <c r="A673">
-        <v>746</v>
-      </c>
-      <c r="B673" s="2" t="s">
+      <c r="C673" t="s">
         <v>1317</v>
-      </c>
-      <c r="C673" t="s">
-        <v>1318</v>
       </c>
     </row>
     <row r="674" spans="1:3">
       <c r="A674">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="B674" s="2" t="s">
+        <v>1318</v>
+      </c>
+      <c r="C674" t="s">
         <v>1319</v>
-      </c>
-      <c r="C674" s="1" t="s">
-        <v>1320</v>
       </c>
     </row>
     <row r="675" spans="1:3">
       <c r="A675">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="B675" s="2" t="s">
+        <v>1320</v>
+      </c>
+      <c r="C675" s="1" t="s">
         <v>1321</v>
-      </c>
-      <c r="C675" t="s">
-        <v>1322</v>
       </c>
     </row>
     <row r="676" spans="1:3">
       <c r="A676">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="B676" s="2" t="s">
+        <v>1322</v>
+      </c>
+      <c r="C676" t="s">
         <v>1323</v>
-      </c>
-      <c r="C676" t="s">
-        <v>1324</v>
       </c>
     </row>
     <row r="677" spans="1:3">
       <c r="A677">
-        <v>750</v>
-      </c>
-      <c r="B677" s="2"/>
-      <c r="C677" s="1" t="s">
+        <v>749</v>
+      </c>
+      <c r="B677" s="2" t="s">
+        <v>1324</v>
+      </c>
+      <c r="C677" t="s">
         <v>1325</v>
       </c>
     </row>
     <row r="678" spans="1:3">
       <c r="A678">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="B678" s="2"/>
       <c r="C678" s="1" t="s">
@@ -12886,199 +12874,199 @@
     </row>
     <row r="679" spans="1:3">
       <c r="A679">
-        <v>753</v>
-      </c>
-      <c r="B679" s="2" t="s">
+        <v>751</v>
+      </c>
+      <c r="B679" s="2"/>
+      <c r="C679" s="1" t="s">
         <v>1327</v>
-      </c>
-      <c r="C679" t="s">
-        <v>1328</v>
       </c>
     </row>
     <row r="680" spans="1:3">
       <c r="A680">
-        <v>755</v>
+        <v>753</v>
       </c>
       <c r="B680" s="2" t="s">
+        <v>1328</v>
+      </c>
+      <c r="C680" t="s">
         <v>1329</v>
-      </c>
-      <c r="C680" s="1" t="s">
-        <v>1330</v>
       </c>
     </row>
     <row r="681" spans="1:3">
       <c r="A681">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="B681" s="2" t="s">
+        <v>1330</v>
+      </c>
+      <c r="C681" s="1" t="s">
         <v>1331</v>
-      </c>
-      <c r="C681" s="1" t="s">
-        <v>1332</v>
       </c>
     </row>
     <row r="682" spans="1:3">
       <c r="A682">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="B682" s="2" t="s">
+        <v>1332</v>
+      </c>
+      <c r="C682" s="1" t="s">
         <v>1333</v>
-      </c>
-      <c r="C682" s="1" t="s">
-        <v>1334</v>
       </c>
     </row>
     <row r="683" spans="1:3">
       <c r="A683">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="B683" s="2" t="s">
+        <v>1334</v>
+      </c>
+      <c r="C683" s="1" t="s">
         <v>1335</v>
-      </c>
-      <c r="C683" s="1" t="s">
-        <v>1336</v>
       </c>
     </row>
     <row r="684" spans="1:3">
       <c r="A684">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="B684" s="2" t="s">
+        <v>1336</v>
+      </c>
+      <c r="C684" s="1" t="s">
         <v>1337</v>
-      </c>
-      <c r="C684" s="1" t="s">
-        <v>1338</v>
       </c>
     </row>
     <row r="685" spans="1:3">
       <c r="A685">
+        <v>759</v>
+      </c>
+      <c r="B685" s="2" t="s">
+        <v>1338</v>
+      </c>
+      <c r="C685" s="1" t="s">
+        <v>1339</v>
+      </c>
+    </row>
+    <row r="686" spans="1:3">
+      <c r="A686">
         <v>760</v>
       </c>
-      <c r="B685" s="2" t="s">
-        <v>1339</v>
-      </c>
-      <c r="C685" s="1" t="s">
+      <c r="B686" s="2" t="s">
         <v>1340</v>
       </c>
-    </row>
-    <row r="686" ht="20" spans="1:3">
-      <c r="A686">
+      <c r="C686" s="1" t="s">
+        <v>1341</v>
+      </c>
+    </row>
+    <row r="687" ht="20" spans="1:3">
+      <c r="A687">
         <v>761</v>
       </c>
-      <c r="B686" s="2" t="s">
-        <v>1341</v>
-      </c>
-      <c r="C686" s="1" t="s">
+      <c r="B687" s="2" t="s">
         <v>1342</v>
       </c>
-    </row>
-    <row r="687" ht="17.5" spans="1:3">
-      <c r="A687">
-        <v>762</v>
-      </c>
-      <c r="B687" s="2" t="s">
+      <c r="C687" s="1" t="s">
         <v>1343</v>
-      </c>
-      <c r="C687" s="1" t="s">
-        <v>1344</v>
       </c>
     </row>
     <row r="688" ht="17.5" spans="1:3">
       <c r="A688">
+        <v>762</v>
+      </c>
+      <c r="B688" s="2" t="s">
+        <v>1344</v>
+      </c>
+      <c r="C688" s="1" t="s">
+        <v>1345</v>
+      </c>
+    </row>
+    <row r="689" ht="17.5" spans="1:3">
+      <c r="A689">
         <v>763</v>
       </c>
-      <c r="B688" s="2" t="s">
-        <v>1345</v>
-      </c>
-      <c r="C688" s="1" t="s">
+      <c r="B689" s="2" t="s">
         <v>1346</v>
       </c>
-    </row>
-    <row r="689" spans="1:3">
-      <c r="A689">
-        <v>764</v>
-      </c>
-      <c r="B689" s="2" t="s">
+      <c r="C689" s="1" t="s">
         <v>1347</v>
-      </c>
-      <c r="C689" s="1" t="s">
-        <v>1348</v>
       </c>
     </row>
     <row r="690" spans="1:3">
       <c r="A690">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="B690" s="2" t="s">
+        <v>1348</v>
+      </c>
+      <c r="C690" s="1" t="s">
         <v>1349</v>
-      </c>
-      <c r="C690" s="1" t="s">
-        <v>1350</v>
       </c>
     </row>
     <row r="691" spans="1:3">
       <c r="A691">
-        <v>766</v>
-      </c>
-      <c r="B691" s="2"/>
+        <v>765</v>
+      </c>
+      <c r="B691" s="2" t="s">
+        <v>1350</v>
+      </c>
       <c r="C691" s="1" t="s">
         <v>1351</v>
       </c>
     </row>
     <row r="692" spans="1:3">
       <c r="A692">
-        <v>767</v>
-      </c>
-      <c r="B692" s="2" t="s">
+        <v>766</v>
+      </c>
+      <c r="B692" s="2"/>
+      <c r="C692" s="1" t="s">
         <v>1352</v>
-      </c>
-      <c r="C692" t="s">
-        <v>1353</v>
       </c>
     </row>
     <row r="693" spans="1:3">
       <c r="A693">
-        <v>768</v>
-      </c>
-      <c r="B693" s="2"/>
-      <c r="C693" s="1" t="s">
+        <v>767</v>
+      </c>
+      <c r="B693" s="2" t="s">
+        <v>1353</v>
+      </c>
+      <c r="C693" t="s">
         <v>1354</v>
       </c>
     </row>
     <row r="694" spans="1:3">
       <c r="A694">
-        <v>769</v>
-      </c>
-      <c r="B694" s="2" t="s">
+        <v>768</v>
+      </c>
+      <c r="B694" s="2"/>
+      <c r="C694" s="1" t="s">
         <v>1355</v>
-      </c>
-      <c r="C694" t="s">
-        <v>1356</v>
       </c>
     </row>
     <row r="695" spans="1:3">
       <c r="A695">
-        <v>772</v>
+        <v>769</v>
       </c>
       <c r="B695" s="2" t="s">
+        <v>1356</v>
+      </c>
+      <c r="C695" t="s">
         <v>1357</v>
-      </c>
-      <c r="C695" s="1" t="s">
-        <v>1358</v>
       </c>
     </row>
     <row r="696" spans="1:3">
       <c r="A696">
-        <v>773</v>
-      </c>
-      <c r="B696" s="2"/>
+        <v>772</v>
+      </c>
+      <c r="B696" s="2" t="s">
+        <v>1358</v>
+      </c>
       <c r="C696" s="1" t="s">
         <v>1359</v>
       </c>
     </row>
     <row r="697" spans="1:3">
       <c r="A697">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="B697" s="2"/>
       <c r="C697" s="1" t="s">
@@ -13087,7 +13075,7 @@
     </row>
     <row r="698" spans="1:3">
       <c r="A698">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="B698" s="2"/>
       <c r="C698" s="1" t="s">
@@ -13096,7 +13084,7 @@
     </row>
     <row r="699" spans="1:3">
       <c r="A699">
-        <v>779</v>
+        <v>776</v>
       </c>
       <c r="B699" s="2"/>
       <c r="C699" s="1" t="s">
@@ -13105,7 +13093,7 @@
     </row>
     <row r="700" spans="1:3">
       <c r="A700">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="B700" s="2"/>
       <c r="C700" s="1" t="s">
@@ -13114,7 +13102,7 @@
     </row>
     <row r="701" spans="1:3">
       <c r="A701">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="B701" s="2"/>
       <c r="C701" s="1" t="s">
@@ -13123,7 +13111,7 @@
     </row>
     <row r="702" spans="1:3">
       <c r="A702">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="B702" s="2"/>
       <c r="C702" s="1" t="s">
@@ -13132,7 +13120,7 @@
     </row>
     <row r="703" spans="1:3">
       <c r="A703">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="B703" s="2"/>
       <c r="C703" s="1" t="s">
@@ -13141,7 +13129,7 @@
     </row>
     <row r="704" spans="1:3">
       <c r="A704">
-        <v>784</v>
+        <v>782</v>
       </c>
       <c r="B704" s="2"/>
       <c r="C704" s="1" t="s">
@@ -13150,15 +13138,16 @@
     </row>
     <row r="705" spans="1:3">
       <c r="A705">
-        <v>785</v>
-      </c>
+        <v>784</v>
+      </c>
+      <c r="B705" s="2"/>
       <c r="C705" s="1" t="s">
         <v>1368</v>
       </c>
     </row>
     <row r="706" spans="1:3">
       <c r="A706">
-        <v>787</v>
+        <v>785</v>
       </c>
       <c r="C706" s="1" t="s">
         <v>1369</v>
@@ -13166,7 +13155,7 @@
     </row>
     <row r="707" spans="1:3">
       <c r="A707">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C707" s="1" t="s">
         <v>1370</v>
@@ -13174,7 +13163,7 @@
     </row>
     <row r="708" spans="1:3">
       <c r="A708">
-        <v>790</v>
+        <v>788</v>
       </c>
       <c r="C708" s="1" t="s">
         <v>1371</v>
@@ -13182,7 +13171,7 @@
     </row>
     <row r="709" spans="1:3">
       <c r="A709">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="C709" s="1" t="s">
         <v>1372</v>
@@ -13190,7 +13179,7 @@
     </row>
     <row r="710" spans="1:3">
       <c r="A710">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="C710" s="1" t="s">
         <v>1373</v>
@@ -13198,7 +13187,7 @@
     </row>
     <row r="711" spans="1:3">
       <c r="A711">
-        <v>794</v>
+        <v>792</v>
       </c>
       <c r="C711" s="1" t="s">
         <v>1374</v>
@@ -13206,7 +13195,7 @@
     </row>
     <row r="712" spans="1:3">
       <c r="A712">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="C712" s="1" t="s">
         <v>1375</v>
@@ -13214,7 +13203,7 @@
     </row>
     <row r="713" spans="1:3">
       <c r="A713">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="C713" s="1" t="s">
         <v>1376</v>
@@ -13222,7 +13211,7 @@
     </row>
     <row r="714" spans="1:3">
       <c r="A714">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="C714" s="1" t="s">
         <v>1377</v>
@@ -13230,7 +13219,7 @@
     </row>
     <row r="715" spans="1:3">
       <c r="A715">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="C715" s="1" t="s">
         <v>1378</v>
@@ -13238,7 +13227,7 @@
     </row>
     <row r="716" spans="1:3">
       <c r="A716">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="C716" s="1" t="s">
         <v>1379</v>
@@ -13246,7 +13235,7 @@
     </row>
     <row r="717" spans="1:3">
       <c r="A717">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="C717" s="1" t="s">
         <v>1380</v>
@@ -13254,21 +13243,21 @@
     </row>
     <row r="718" spans="1:3">
       <c r="A718">
-        <v>801</v>
-      </c>
-      <c r="C718" s="1"/>
+        <v>800</v>
+      </c>
+      <c r="C718" s="1" t="s">
+        <v>1381</v>
+      </c>
     </row>
     <row r="719" spans="1:3">
       <c r="A719">
+        <v>801</v>
+      </c>
+      <c r="C719" s="1"/>
+    </row>
+    <row r="720" spans="1:3">
+      <c r="A720">
         <v>802</v>
-      </c>
-      <c r="C719" s="1" t="s">
-        <v>1381</v>
-      </c>
-    </row>
-    <row r="720" ht="16.2" customHeight="1" spans="1:3">
-      <c r="A720">
-        <v>803</v>
       </c>
       <c r="C720" s="1" t="s">
         <v>1382</v>
@@ -13276,32 +13265,40 @@
     </row>
     <row r="721" ht="16.2" customHeight="1" spans="1:3">
       <c r="A721">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="C721" s="1" t="s">
         <v>1383</v>
       </c>
     </row>
-    <row r="722" spans="1:3">
+    <row r="722" ht="16.2" customHeight="1" spans="1:3">
       <c r="A722">
-        <v>10001</v>
-      </c>
-      <c r="B722" t="s">
+        <v>804</v>
+      </c>
+      <c r="C722" s="1" t="s">
         <v>1384</v>
-      </c>
-      <c r="C722" s="1" t="s">
-        <v>1385</v>
       </c>
     </row>
     <row r="723" spans="1:3">
       <c r="A723">
+        <v>10001</v>
+      </c>
+      <c r="B723" t="s">
+        <v>1385</v>
+      </c>
+      <c r="C723" s="1" t="s">
+        <v>1386</v>
+      </c>
+    </row>
+    <row r="724" spans="1:3">
+      <c r="A724">
         <v>10003</v>
       </c>
-      <c r="B723" t="s">
-        <v>1355</v>
-      </c>
-      <c r="C723" t="s">
+      <c r="B724" t="s">
         <v>1356</v>
+      </c>
+      <c r="C724" t="s">
+        <v>1357</v>
       </c>
     </row>
   </sheetData>
@@ -13309,7 +13306,7 @@
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="A77:B77 A78:C78 A243:B243 A244:C246 A600 A334:B334 A335:C337 A91:B91 A92:C92 A200:B200 A201:C207 A589:B589 A190:B190 A191:C197 A472:B472 A429:B429 A430:C431 A332:B332 A333:C333 A158:B158 A159:C161 A220:B220 A221:C223 A399:B399 A400:C400 A110:B110 A111:C112 A178:B178 A179:C180 A318:B319 A320:C326 A63:B64 A65:C69 A483:B484 A485:C486 A17:B18 A19:C19 A441:B441 A442:C446 A181:B182 A183:C189 A142:B142 A143:C144 A83:B83 A84:C84 A361:B361 A362:C373 A198:B198 A199:C199 A599:C599 A97:B97 A98:C98 A342:B342 A343:C344 A210:B211 A212:C219 A152:B152 A153:C153 A254:B254 A255:C256 A56:B58 A525:B525 A526:C529 A271:B271 A272:C278 A130:B130 A131:C132 A530:B531 A224:B224 A225:C228 A467:B467 A468:C468 A294:B296 A338:B339 A340:C341 A113:B114 A607:B607 A426:C428 A621:B622 A392 A393:C398 A390:B390 A391:C391 A167:B167 A168:C169 A285:B286 A487:B487 A488:C498 A421:B423 A208:B208 A209:C209 A313:B313 A314:C314 A133:B133 A134:C141 A595:B595 A617:B617 A474:B474 A536:B538 A279:B280 A374:B374 A375:C376 A406 C412:C413 A412:A413 A414:C417 A499:B500 A23:B23 A24:C27 A569:B572 A587:B587 A590:C590 A611:C611 A170:B170 A171:C177 A38:B39 A30:B31 A85:B85 A86:C90 A473 A475:C476 A349:B349 A350:C350 A463:B465 A353:B353 A354:C360 A598:B598 A604:B604 A608:C609 A43:B43 A44:C50 A297:C306 A327 A328:C331 A385:B386 A387:C389 A407:B407 A408:C411 A477:B477 A478:C479 A555:B557 A565:B565 A15:B15 A16:C16 A40:C42 A99:B99 A100:C106 A455:B456 A469:B469 A470:C471 A521:B522 A523:C524 A451:B453 A379:B381 A384:C384 A383:B383 A382:C382 A602:C602 A8:B8 A9:C11 A71 A128:B128 A129:C129 A154:B154 A155:C157 A59:C62 A107:B107 A108:C109 A229:B230 A231:C233 A250:B251 A252:C253 A260:B260 A261:C267 A268:B268 A269:C270 A281:C284 A401:B402 A403:C405 A425:B425 A432:B432 A433:C440 A447:B447 A448:C448 A466:C466 A505:B507 A511:C512 A509:B510 A508:C508 A539:C539 A550:B551 A552:C552 A449:B449 A450:C450 A580:B580 A582:C582 A2:B6 A12:B13 A14:C14 A424:C424 A454:C454 A501:C502 A513:B515 A576:B578 A624:B624 A532:C535 A517:B519 A520:C520 A480:B480 A481:C482 A150:B150 A151:C151 A503 A504:C504 A79:B79 A80:C82 A418:B419 A287:C293 A115:C117 A118:B118 A119:C119 A420:C420 A20:B20 A21:C22 A615:C615 A566 A567:C568 A573:C573 A7:C7 A257:B257 A258:C259 A629:C631 A377:B377 A378:C378 A162:B162 A163:C166 A70:B70 A72:C76 A51:B51 A52:C52 A345:B345 A346:C348 A553:B553 A554:C554 A93:B94 A516:C516 A457:C458 A53:B54 A307:B307 A308:C312 A579:C579 A28:B28 A29:C29 A558:C564 A55:C55 A540:B540 A541:C549 A145:B145 A146:C149 A95:C96 A234:B234 A248:C249 A247:B247 A235:C242 A626:B626 A459:B459 A460:C462 A574:B574 A575 A594:C594 A351:B351 A352:C352 A316:C317 A315:B315 A722:B722 A120:B120 A121:C127 A1:C1 A37:C37 A36:B36 A32:C35" numberStoredAsText="1"/>
+    <ignoredError sqref="A32:C35 A36:B36 A37:C37 A1:C1 A121:C127 A120:B120 A723:B723 A315:B315 A316:C317 A352:C352 A351:B351 A594:C594 A575 A574:B574 A460:C462 A459:B459 A627:B627 A235:C242 A247:B247 A248:C249 A234:B234 A95:C96 A146:C149 A145:B145 A541:C549 A540:B540 A55:C55 A558:C564 A29:C29 A28:B28 A579:C579 A308:C312 A307:B307 A53:B54 A457:C458 A516:C516 A93:B94 A554:C554 A553:B553 A346:C348 A345:B345 A52:C52 A51:B51 A72:C76 A70:B70 A163:C166 A162:B162 A378:C378 A377:B377 A630:C632 A258:C259 A257:B257 A7:C7 A573:C573 A567:C568 A566 A616:C616 A21:C22 A20:B20 A420:C420 A119:C119 A118:B118 A115:C117 A287:C293 A418:B419 A80:C82 A79:B79 A504:C504 A503 A151:C151 A150:B150 A481:C482 A480:B480 A520:C520 A517:B519 A532:C535 A625:B625 A576:B578 A513:B515 A501:C502 A454:C454 A424:C424 A14:C14 A12:B13 A2:B6 A582:C582 A580:B580 A450:C450 A449:B449 A552:C552 A550:B551 A539:C539 A508:C508 A509:B510 A511:C512 A505:B507 A466:C466 A448:C448 A447:B447 A433:C440 A432:B432 A425:B425 A403:C405 A401:B402 A281:C284 A269:C270 A268:B268 A261:C267 A260:B260 A252:C253 A250:B251 A231:C233 A229:B230 A108:C109 A107:B107 A59:C62 A155:C157 A154:B154 A129:C129 A128:B128 A71 A9:C11 A8:B8 A602:C602 A382:C382 A383:B383 A384:C384 A379:B381 A451:B453 A523:C524 A521:B522 A470:C471 A469:B469 A455:B456 A100:C106 A99:B99 A40:C42 A16:C16 A15:B15 A565:B565 A555:B557 A478:C479 A477:B477 A408:C411 A407:B407 A387:C389 A385:B386 A328:C331 A327 A297:C306 A44:C50 A43:B43 A609:C610 A605:B605 A598:B598 A354:C360 A353:B353 A463:B465 A350:C350 A349:B349 A475:C476 A473 A86:C90 A85:B85 A30:B31 A38:B39 A171:C177 A170:B170 A612:C612 A590:C590 A587:B587 A569:B572 A24:C27 A23:B23 A499:B500 A414:C417 A412:A413 C412:C413 A406 A375:C376 A374:B374 A279:B280 A536:B538 A474:B474 A618:B618 A595:B595 A134:C141 A133:B133 A314:C314 A313:B313 A209:C209 A208:B208 A421:B423 A488:C498 A487:B487 A285:B286 A168:C169 A167:B167 A391:C391 A390:B390 A393:C398 A392 A622:B623 A426:C428 A608:B608 A113:B114 A340:C341 A338:B339 A294:B296 A468:C468 A467:B467 A225:C228 A224:B224 A530:B531 A131:C132 A130:B130 A272:C278 A271:B271 A526:C529 A525:B525 A56:B58 A255:C256 A254:B254 A153:C153 A152:B152 A212:C219 A210:B211 A343:C344 A342:B342 A98:C98 A97:B97 A599:C599 A199:C199 A198:B198 A362:C373 A361:B361 A84:C84 A83:B83 A143:C144 A142:B142 A183:C189 A181:B182 A442:C446 A441:B441 A19:C19 A17:B18 A485:C486 A483:B484 A65:C69 A63:B64 A320:C326 A318:B319 A179:C180 A178:B178 A111:C112 A110:B110 A400:C400 A399:B399 A221:C223 A220:B220 A159:C161 A158:B158 A333:C333 A332:B332 A430:C431 A429:B429 A472:B472 A191:C197 A190:B190 A589:B589 A201:C207 A200:B200 A92:C92 A91:B91 A335:C337 A334:B334 A600 A244:C246 A243:B243 A78:C78 A77:B77" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/nickname_song.xlsx
+++ b/nickname_song.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Coding\Tsugu-Backend\config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DBC9796-341B-4683-841A-702A936DB9B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0C8B657-974B-4F68-9323-E90BEB8A1E70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2124" yWindow="1536" windowWidth="23040" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -740,9 +740,6 @@
   </si>
   <si>
     <t>二重の虹(ダブル レインボウ)</t>
-  </si>
-  <si>
-    <t>二重虹,ppp2章,二重之虹,俩彩虹,两彩虹,双彩虹</t>
   </si>
   <si>
     <t>ふわふわ☆ゆめいろサンドイッチ</t>
@@ -4501,6 +4498,10 @@
   </si>
   <si>
     <t>哦！劲敌,哦对手,劲敌</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>二重虹,ppp2章,二重之虹,俩彩虹,两彩虹,双彩虹,双重彩虹</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -6102,7 +6103,7 @@
         <v>213</v>
       </c>
       <c r="C107" s="3" t="s">
-        <v>1393</v>
+        <v>1392</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.25">
@@ -6178,8 +6179,8 @@
       <c r="B114" t="s">
         <v>226</v>
       </c>
-      <c r="C114" t="s">
-        <v>227</v>
+      <c r="C114" s="3" t="s">
+        <v>1402</v>
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.25">
@@ -6187,10 +6188,10 @@
         <v>123</v>
       </c>
       <c r="B115" t="s">
+        <v>227</v>
+      </c>
+      <c r="C115" t="s">
         <v>228</v>
-      </c>
-      <c r="C115" t="s">
-        <v>229</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.25">
@@ -6198,10 +6199,10 @@
         <v>124</v>
       </c>
       <c r="B116" t="s">
+        <v>229</v>
+      </c>
+      <c r="C116" t="s">
         <v>230</v>
-      </c>
-      <c r="C116" t="s">
-        <v>231</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.25">
@@ -6209,10 +6210,10 @@
         <v>125</v>
       </c>
       <c r="B117" t="s">
+        <v>231</v>
+      </c>
+      <c r="C117" t="s">
         <v>232</v>
-      </c>
-      <c r="C117" t="s">
-        <v>233</v>
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.25">
@@ -6220,10 +6221,10 @@
         <v>126</v>
       </c>
       <c r="B118" t="s">
+        <v>233</v>
+      </c>
+      <c r="C118" t="s">
         <v>234</v>
-      </c>
-      <c r="C118" t="s">
-        <v>235</v>
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.25">
@@ -6231,10 +6232,10 @@
         <v>127</v>
       </c>
       <c r="B119" t="s">
+        <v>235</v>
+      </c>
+      <c r="C119" t="s">
         <v>236</v>
-      </c>
-      <c r="C119" t="s">
-        <v>237</v>
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.25">
@@ -6242,10 +6243,10 @@
         <v>128</v>
       </c>
       <c r="B120" t="s">
+        <v>237</v>
+      </c>
+      <c r="C120" t="s">
         <v>238</v>
-      </c>
-      <c r="C120" t="s">
-        <v>239</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.25">
@@ -6253,10 +6254,10 @@
         <v>129</v>
       </c>
       <c r="B121" t="s">
+        <v>239</v>
+      </c>
+      <c r="C121" t="s">
         <v>240</v>
-      </c>
-      <c r="C121" t="s">
-        <v>241</v>
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.25">
@@ -6264,10 +6265,10 @@
         <v>130</v>
       </c>
       <c r="B122" t="s">
+        <v>241</v>
+      </c>
+      <c r="C122" t="s">
         <v>242</v>
-      </c>
-      <c r="C122" t="s">
-        <v>243</v>
       </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.25">
@@ -6275,10 +6276,10 @@
         <v>131</v>
       </c>
       <c r="B123" t="s">
+        <v>243</v>
+      </c>
+      <c r="C123" t="s">
         <v>244</v>
-      </c>
-      <c r="C123" t="s">
-        <v>245</v>
       </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.25">
@@ -6286,10 +6287,10 @@
         <v>132</v>
       </c>
       <c r="B124" t="s">
+        <v>245</v>
+      </c>
+      <c r="C124" t="s">
         <v>246</v>
-      </c>
-      <c r="C124" t="s">
-        <v>247</v>
       </c>
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.25">
@@ -6297,10 +6298,10 @@
         <v>133</v>
       </c>
       <c r="B125" t="s">
+        <v>247</v>
+      </c>
+      <c r="C125" t="s">
         <v>248</v>
-      </c>
-      <c r="C125" t="s">
-        <v>249</v>
       </c>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.25">
@@ -6308,10 +6309,10 @@
         <v>134</v>
       </c>
       <c r="B126" t="s">
+        <v>249</v>
+      </c>
+      <c r="C126" t="s">
         <v>250</v>
-      </c>
-      <c r="C126" t="s">
-        <v>251</v>
       </c>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.25">
@@ -6319,10 +6320,10 @@
         <v>135</v>
       </c>
       <c r="B127" t="s">
+        <v>251</v>
+      </c>
+      <c r="C127" t="s">
         <v>252</v>
-      </c>
-      <c r="C127" t="s">
-        <v>253</v>
       </c>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.25">
@@ -6330,10 +6331,10 @@
         <v>136</v>
       </c>
       <c r="B128" t="s">
+        <v>253</v>
+      </c>
+      <c r="C128" t="s">
         <v>254</v>
-      </c>
-      <c r="C128" t="s">
-        <v>255</v>
       </c>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.25">
@@ -6341,10 +6342,10 @@
         <v>137</v>
       </c>
       <c r="B129" t="s">
+        <v>255</v>
+      </c>
+      <c r="C129" t="s">
         <v>256</v>
-      </c>
-      <c r="C129" t="s">
-        <v>257</v>
       </c>
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.25">
@@ -6352,10 +6353,10 @@
         <v>138</v>
       </c>
       <c r="B130" t="s">
+        <v>257</v>
+      </c>
+      <c r="C130" t="s">
         <v>258</v>
-      </c>
-      <c r="C130" t="s">
-        <v>259</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.25">
@@ -6363,10 +6364,10 @@
         <v>139</v>
       </c>
       <c r="B131" t="s">
+        <v>259</v>
+      </c>
+      <c r="C131" t="s">
         <v>260</v>
-      </c>
-      <c r="C131" t="s">
-        <v>261</v>
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.25">
@@ -6374,10 +6375,10 @@
         <v>140</v>
       </c>
       <c r="B132" t="s">
+        <v>261</v>
+      </c>
+      <c r="C132" t="s">
         <v>262</v>
-      </c>
-      <c r="C132" t="s">
-        <v>263</v>
       </c>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.25">
@@ -6385,10 +6386,10 @@
         <v>141</v>
       </c>
       <c r="B133" t="s">
+        <v>263</v>
+      </c>
+      <c r="C133" t="s">
         <v>264</v>
-      </c>
-      <c r="C133" t="s">
-        <v>265</v>
       </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.25">
@@ -6396,10 +6397,10 @@
         <v>142</v>
       </c>
       <c r="B134" t="s">
+        <v>265</v>
+      </c>
+      <c r="C134" t="s">
         <v>266</v>
-      </c>
-      <c r="C134" t="s">
-        <v>267</v>
       </c>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.25">
@@ -6407,10 +6408,10 @@
         <v>143</v>
       </c>
       <c r="B135" t="s">
+        <v>267</v>
+      </c>
+      <c r="C135" t="s">
         <v>268</v>
-      </c>
-      <c r="C135" t="s">
-        <v>269</v>
       </c>
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.25">
@@ -6418,10 +6419,10 @@
         <v>144</v>
       </c>
       <c r="B136" t="s">
+        <v>269</v>
+      </c>
+      <c r="C136" t="s">
         <v>270</v>
-      </c>
-      <c r="C136" t="s">
-        <v>271</v>
       </c>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.25">
@@ -6429,10 +6430,10 @@
         <v>145</v>
       </c>
       <c r="B137" t="s">
+        <v>271</v>
+      </c>
+      <c r="C137" t="s">
         <v>272</v>
-      </c>
-      <c r="C137" t="s">
-        <v>273</v>
       </c>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.25">
@@ -6440,10 +6441,10 @@
         <v>146</v>
       </c>
       <c r="B138" t="s">
+        <v>273</v>
+      </c>
+      <c r="C138" t="s">
         <v>274</v>
-      </c>
-      <c r="C138" t="s">
-        <v>275</v>
       </c>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.25">
@@ -6451,10 +6452,10 @@
         <v>147</v>
       </c>
       <c r="B139" t="s">
+        <v>275</v>
+      </c>
+      <c r="C139" t="s">
         <v>276</v>
-      </c>
-      <c r="C139" t="s">
-        <v>277</v>
       </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.25">
@@ -6462,10 +6463,10 @@
         <v>148</v>
       </c>
       <c r="B140" t="s">
+        <v>277</v>
+      </c>
+      <c r="C140" t="s">
         <v>278</v>
-      </c>
-      <c r="C140" t="s">
-        <v>279</v>
       </c>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.25">
@@ -6473,10 +6474,10 @@
         <v>149</v>
       </c>
       <c r="B141" t="s">
+        <v>279</v>
+      </c>
+      <c r="C141" t="s">
         <v>280</v>
-      </c>
-      <c r="C141" t="s">
-        <v>281</v>
       </c>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.25">
@@ -6484,10 +6485,10 @@
         <v>150</v>
       </c>
       <c r="B142" t="s">
+        <v>281</v>
+      </c>
+      <c r="C142" t="s">
         <v>282</v>
-      </c>
-      <c r="C142" t="s">
-        <v>283</v>
       </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.25">
@@ -6495,10 +6496,10 @@
         <v>151</v>
       </c>
       <c r="B143" t="s">
+        <v>283</v>
+      </c>
+      <c r="C143" t="s">
         <v>284</v>
-      </c>
-      <c r="C143" t="s">
-        <v>285</v>
       </c>
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.25">
@@ -6506,10 +6507,10 @@
         <v>152</v>
       </c>
       <c r="B144" t="s">
+        <v>285</v>
+      </c>
+      <c r="C144" t="s">
         <v>286</v>
-      </c>
-      <c r="C144" t="s">
-        <v>287</v>
       </c>
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.25">
@@ -6517,10 +6518,10 @@
         <v>153</v>
       </c>
       <c r="B145" t="s">
+        <v>287</v>
+      </c>
+      <c r="C145" t="s">
         <v>288</v>
-      </c>
-      <c r="C145" t="s">
-        <v>289</v>
       </c>
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.25">
@@ -6528,10 +6529,10 @@
         <v>154</v>
       </c>
       <c r="B146" t="s">
+        <v>289</v>
+      </c>
+      <c r="C146" t="s">
         <v>290</v>
-      </c>
-      <c r="C146" t="s">
-        <v>291</v>
       </c>
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.25">
@@ -6539,10 +6540,10 @@
         <v>155</v>
       </c>
       <c r="B147" t="s">
+        <v>291</v>
+      </c>
+      <c r="C147" t="s">
         <v>292</v>
-      </c>
-      <c r="C147" t="s">
-        <v>293</v>
       </c>
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.25">
@@ -6550,10 +6551,10 @@
         <v>156</v>
       </c>
       <c r="B148" t="s">
+        <v>293</v>
+      </c>
+      <c r="C148" t="s">
         <v>294</v>
-      </c>
-      <c r="C148" t="s">
-        <v>295</v>
       </c>
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.25">
@@ -6561,10 +6562,10 @@
         <v>157</v>
       </c>
       <c r="B149" t="s">
+        <v>295</v>
+      </c>
+      <c r="C149" t="s">
         <v>296</v>
-      </c>
-      <c r="C149" t="s">
-        <v>297</v>
       </c>
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.25">
@@ -6572,10 +6573,10 @@
         <v>158</v>
       </c>
       <c r="B150" t="s">
+        <v>297</v>
+      </c>
+      <c r="C150" t="s">
         <v>298</v>
-      </c>
-      <c r="C150" t="s">
-        <v>299</v>
       </c>
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.25">
@@ -6583,10 +6584,10 @@
         <v>159</v>
       </c>
       <c r="B151" t="s">
+        <v>299</v>
+      </c>
+      <c r="C151" t="s">
         <v>300</v>
-      </c>
-      <c r="C151" t="s">
-        <v>301</v>
       </c>
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.25">
@@ -6594,10 +6595,10 @@
         <v>160</v>
       </c>
       <c r="B152" t="s">
+        <v>301</v>
+      </c>
+      <c r="C152" t="s">
         <v>302</v>
-      </c>
-      <c r="C152" t="s">
-        <v>303</v>
       </c>
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.25">
@@ -6605,10 +6606,10 @@
         <v>161</v>
       </c>
       <c r="B153" t="s">
+        <v>303</v>
+      </c>
+      <c r="C153" t="s">
         <v>304</v>
-      </c>
-      <c r="C153" t="s">
-        <v>305</v>
       </c>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.25">
@@ -6616,10 +6617,10 @@
         <v>162</v>
       </c>
       <c r="B154" t="s">
+        <v>305</v>
+      </c>
+      <c r="C154" t="s">
         <v>306</v>
-      </c>
-      <c r="C154" t="s">
-        <v>307</v>
       </c>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.25">
@@ -6627,10 +6628,10 @@
         <v>163</v>
       </c>
       <c r="B155" t="s">
+        <v>307</v>
+      </c>
+      <c r="C155" t="s">
         <v>308</v>
-      </c>
-      <c r="C155" t="s">
-        <v>309</v>
       </c>
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.25">
@@ -6638,10 +6639,10 @@
         <v>164</v>
       </c>
       <c r="B156" t="s">
+        <v>309</v>
+      </c>
+      <c r="C156" t="s">
         <v>310</v>
-      </c>
-      <c r="C156" t="s">
-        <v>311</v>
       </c>
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.25">
@@ -6649,10 +6650,10 @@
         <v>165</v>
       </c>
       <c r="B157" t="s">
+        <v>311</v>
+      </c>
+      <c r="C157" t="s">
         <v>312</v>
-      </c>
-      <c r="C157" t="s">
-        <v>313</v>
       </c>
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.25">
@@ -6660,10 +6661,10 @@
         <v>166</v>
       </c>
       <c r="B158" t="s">
+        <v>313</v>
+      </c>
+      <c r="C158" t="s">
         <v>314</v>
-      </c>
-      <c r="C158" t="s">
-        <v>315</v>
       </c>
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.25">
@@ -6671,10 +6672,10 @@
         <v>167</v>
       </c>
       <c r="B159" t="s">
+        <v>315</v>
+      </c>
+      <c r="C159" t="s">
         <v>316</v>
-      </c>
-      <c r="C159" t="s">
-        <v>317</v>
       </c>
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.25">
@@ -6682,10 +6683,10 @@
         <v>168</v>
       </c>
       <c r="B160" t="s">
+        <v>317</v>
+      </c>
+      <c r="C160" t="s">
         <v>318</v>
-      </c>
-      <c r="C160" t="s">
-        <v>319</v>
       </c>
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.25">
@@ -6693,10 +6694,10 @@
         <v>169</v>
       </c>
       <c r="B161" t="s">
+        <v>319</v>
+      </c>
+      <c r="C161" t="s">
         <v>320</v>
-      </c>
-      <c r="C161" t="s">
-        <v>321</v>
       </c>
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.25">
@@ -6704,10 +6705,10 @@
         <v>170</v>
       </c>
       <c r="B162" t="s">
+        <v>321</v>
+      </c>
+      <c r="C162" t="s">
         <v>322</v>
-      </c>
-      <c r="C162" t="s">
-        <v>323</v>
       </c>
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.25">
@@ -6715,10 +6716,10 @@
         <v>171</v>
       </c>
       <c r="B163" t="s">
+        <v>323</v>
+      </c>
+      <c r="C163" t="s">
         <v>324</v>
-      </c>
-      <c r="C163" t="s">
-        <v>325</v>
       </c>
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.25">
@@ -6726,10 +6727,10 @@
         <v>172</v>
       </c>
       <c r="B164" t="s">
+        <v>325</v>
+      </c>
+      <c r="C164" t="s">
         <v>326</v>
-      </c>
-      <c r="C164" t="s">
-        <v>327</v>
       </c>
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.25">
@@ -6737,10 +6738,10 @@
         <v>173</v>
       </c>
       <c r="B165" t="s">
+        <v>327</v>
+      </c>
+      <c r="C165" t="s">
         <v>328</v>
-      </c>
-      <c r="C165" t="s">
-        <v>329</v>
       </c>
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.25">
@@ -6748,10 +6749,10 @@
         <v>174</v>
       </c>
       <c r="B166" t="s">
+        <v>329</v>
+      </c>
+      <c r="C166" t="s">
         <v>330</v>
-      </c>
-      <c r="C166" t="s">
-        <v>331</v>
       </c>
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.25">
@@ -6759,10 +6760,10 @@
         <v>175</v>
       </c>
       <c r="B167" t="s">
+        <v>331</v>
+      </c>
+      <c r="C167" t="s">
         <v>332</v>
-      </c>
-      <c r="C167" t="s">
-        <v>333</v>
       </c>
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.25">
@@ -6770,10 +6771,10 @@
         <v>176</v>
       </c>
       <c r="B168" t="s">
+        <v>333</v>
+      </c>
+      <c r="C168" t="s">
         <v>334</v>
-      </c>
-      <c r="C168" t="s">
-        <v>335</v>
       </c>
     </row>
     <row r="169" spans="1:3" x14ac:dyDescent="0.25">
@@ -6781,10 +6782,10 @@
         <v>177</v>
       </c>
       <c r="B169" t="s">
+        <v>335</v>
+      </c>
+      <c r="C169" t="s">
         <v>336</v>
-      </c>
-      <c r="C169" t="s">
-        <v>337</v>
       </c>
     </row>
     <row r="170" spans="1:3" x14ac:dyDescent="0.25">
@@ -6792,10 +6793,10 @@
         <v>178</v>
       </c>
       <c r="B170" t="s">
+        <v>337</v>
+      </c>
+      <c r="C170" t="s">
         <v>338</v>
-      </c>
-      <c r="C170" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="171" spans="1:3" x14ac:dyDescent="0.25">
@@ -6803,10 +6804,10 @@
         <v>179</v>
       </c>
       <c r="B171" t="s">
+        <v>339</v>
+      </c>
+      <c r="C171" t="s">
         <v>340</v>
-      </c>
-      <c r="C171" t="s">
-        <v>341</v>
       </c>
     </row>
     <row r="172" spans="1:3" x14ac:dyDescent="0.25">
@@ -6814,10 +6815,10 @@
         <v>180</v>
       </c>
       <c r="B172" t="s">
+        <v>341</v>
+      </c>
+      <c r="C172" t="s">
         <v>342</v>
-      </c>
-      <c r="C172" t="s">
-        <v>343</v>
       </c>
     </row>
     <row r="173" spans="1:3" x14ac:dyDescent="0.25">
@@ -6825,10 +6826,10 @@
         <v>181</v>
       </c>
       <c r="B173" t="s">
+        <v>343</v>
+      </c>
+      <c r="C173" t="s">
         <v>344</v>
-      </c>
-      <c r="C173" t="s">
-        <v>345</v>
       </c>
     </row>
     <row r="174" spans="1:3" x14ac:dyDescent="0.25">
@@ -6836,10 +6837,10 @@
         <v>182</v>
       </c>
       <c r="B174" t="s">
+        <v>345</v>
+      </c>
+      <c r="C174" t="s">
         <v>346</v>
-      </c>
-      <c r="C174" t="s">
-        <v>347</v>
       </c>
     </row>
     <row r="175" spans="1:3" x14ac:dyDescent="0.25">
@@ -6847,10 +6848,10 @@
         <v>183</v>
       </c>
       <c r="B175" t="s">
+        <v>347</v>
+      </c>
+      <c r="C175" t="s">
         <v>348</v>
-      </c>
-      <c r="C175" t="s">
-        <v>349</v>
       </c>
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.25">
@@ -6858,10 +6859,10 @@
         <v>184</v>
       </c>
       <c r="B176" t="s">
+        <v>349</v>
+      </c>
+      <c r="C176" t="s">
         <v>350</v>
-      </c>
-      <c r="C176" t="s">
-        <v>351</v>
       </c>
     </row>
     <row r="177" spans="1:3" x14ac:dyDescent="0.25">
@@ -6869,10 +6870,10 @@
         <v>185</v>
       </c>
       <c r="B177" t="s">
+        <v>351</v>
+      </c>
+      <c r="C177" t="s">
         <v>352</v>
-      </c>
-      <c r="C177" t="s">
-        <v>353</v>
       </c>
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.25">
@@ -6880,10 +6881,10 @@
         <v>186</v>
       </c>
       <c r="B178" t="s">
+        <v>353</v>
+      </c>
+      <c r="C178" t="s">
         <v>354</v>
-      </c>
-      <c r="C178" t="s">
-        <v>355</v>
       </c>
     </row>
     <row r="179" spans="1:3" x14ac:dyDescent="0.25">
@@ -6891,10 +6892,10 @@
         <v>187</v>
       </c>
       <c r="B179" t="s">
+        <v>355</v>
+      </c>
+      <c r="C179" t="s">
         <v>356</v>
-      </c>
-      <c r="C179" t="s">
-        <v>357</v>
       </c>
     </row>
     <row r="180" spans="1:3" x14ac:dyDescent="0.25">
@@ -6902,10 +6903,10 @@
         <v>188</v>
       </c>
       <c r="B180" t="s">
+        <v>357</v>
+      </c>
+      <c r="C180" t="s">
         <v>358</v>
-      </c>
-      <c r="C180" t="s">
-        <v>359</v>
       </c>
     </row>
     <row r="181" spans="1:3" x14ac:dyDescent="0.25">
@@ -6913,10 +6914,10 @@
         <v>189</v>
       </c>
       <c r="B181" t="s">
+        <v>359</v>
+      </c>
+      <c r="C181" t="s">
         <v>360</v>
-      </c>
-      <c r="C181" t="s">
-        <v>361</v>
       </c>
     </row>
     <row r="182" spans="1:3" x14ac:dyDescent="0.25">
@@ -6924,10 +6925,10 @@
         <v>190</v>
       </c>
       <c r="B182" t="s">
+        <v>361</v>
+      </c>
+      <c r="C182" t="s">
         <v>362</v>
-      </c>
-      <c r="C182" t="s">
-        <v>363</v>
       </c>
     </row>
     <row r="183" spans="1:3" x14ac:dyDescent="0.25">
@@ -6935,10 +6936,10 @@
         <v>191</v>
       </c>
       <c r="B183" t="s">
+        <v>363</v>
+      </c>
+      <c r="C183" t="s">
         <v>364</v>
-      </c>
-      <c r="C183" t="s">
-        <v>365</v>
       </c>
     </row>
     <row r="184" spans="1:3" x14ac:dyDescent="0.25">
@@ -6946,10 +6947,10 @@
         <v>192</v>
       </c>
       <c r="B184" t="s">
+        <v>365</v>
+      </c>
+      <c r="C184" t="s">
         <v>366</v>
-      </c>
-      <c r="C184" t="s">
-        <v>367</v>
       </c>
     </row>
     <row r="185" spans="1:3" x14ac:dyDescent="0.25">
@@ -6957,10 +6958,10 @@
         <v>193</v>
       </c>
       <c r="B185" t="s">
+        <v>367</v>
+      </c>
+      <c r="C185" t="s">
         <v>368</v>
-      </c>
-      <c r="C185" t="s">
-        <v>369</v>
       </c>
     </row>
     <row r="186" spans="1:3" x14ac:dyDescent="0.25">
@@ -6968,10 +6969,10 @@
         <v>194</v>
       </c>
       <c r="B186" t="s">
+        <v>369</v>
+      </c>
+      <c r="C186" t="s">
         <v>370</v>
-      </c>
-      <c r="C186" t="s">
-        <v>371</v>
       </c>
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.25">
@@ -6979,10 +6980,10 @@
         <v>195</v>
       </c>
       <c r="B187" t="s">
+        <v>371</v>
+      </c>
+      <c r="C187" t="s">
         <v>372</v>
-      </c>
-      <c r="C187" t="s">
-        <v>373</v>
       </c>
     </row>
     <row r="188" spans="1:3" x14ac:dyDescent="0.25">
@@ -6990,10 +6991,10 @@
         <v>196</v>
       </c>
       <c r="B188" t="s">
+        <v>373</v>
+      </c>
+      <c r="C188" t="s">
         <v>374</v>
-      </c>
-      <c r="C188" t="s">
-        <v>375</v>
       </c>
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.25">
@@ -7001,10 +7002,10 @@
         <v>197</v>
       </c>
       <c r="B189" t="s">
+        <v>375</v>
+      </c>
+      <c r="C189" t="s">
         <v>376</v>
-      </c>
-      <c r="C189" t="s">
-        <v>377</v>
       </c>
     </row>
     <row r="190" spans="1:3" x14ac:dyDescent="0.25">
@@ -7012,10 +7013,10 @@
         <v>198</v>
       </c>
       <c r="B190" t="s">
+        <v>377</v>
+      </c>
+      <c r="C190" t="s">
         <v>378</v>
-      </c>
-      <c r="C190" t="s">
-        <v>379</v>
       </c>
     </row>
     <row r="191" spans="1:3" x14ac:dyDescent="0.25">
@@ -7023,10 +7024,10 @@
         <v>199</v>
       </c>
       <c r="B191" t="s">
+        <v>379</v>
+      </c>
+      <c r="C191" t="s">
         <v>380</v>
-      </c>
-      <c r="C191" t="s">
-        <v>381</v>
       </c>
     </row>
     <row r="192" spans="1:3" x14ac:dyDescent="0.25">
@@ -7034,10 +7035,10 @@
         <v>200</v>
       </c>
       <c r="B192" t="s">
+        <v>381</v>
+      </c>
+      <c r="C192" t="s">
         <v>382</v>
-      </c>
-      <c r="C192" t="s">
-        <v>383</v>
       </c>
     </row>
     <row r="193" spans="1:3" x14ac:dyDescent="0.25">
@@ -7045,10 +7046,10 @@
         <v>201</v>
       </c>
       <c r="B193" t="s">
+        <v>383</v>
+      </c>
+      <c r="C193" t="s">
         <v>384</v>
-      </c>
-      <c r="C193" t="s">
-        <v>385</v>
       </c>
     </row>
     <row r="194" spans="1:3" x14ac:dyDescent="0.25">
@@ -7056,10 +7057,10 @@
         <v>202</v>
       </c>
       <c r="B194" t="s">
+        <v>385</v>
+      </c>
+      <c r="C194" t="s">
         <v>386</v>
-      </c>
-      <c r="C194" t="s">
-        <v>387</v>
       </c>
     </row>
     <row r="195" spans="1:3" x14ac:dyDescent="0.25">
@@ -7067,10 +7068,10 @@
         <v>203</v>
       </c>
       <c r="B195" t="s">
+        <v>387</v>
+      </c>
+      <c r="C195" t="s">
         <v>388</v>
-      </c>
-      <c r="C195" t="s">
-        <v>389</v>
       </c>
     </row>
     <row r="196" spans="1:3" x14ac:dyDescent="0.25">
@@ -7078,10 +7079,10 @@
         <v>204</v>
       </c>
       <c r="B196" t="s">
+        <v>389</v>
+      </c>
+      <c r="C196" t="s">
         <v>390</v>
-      </c>
-      <c r="C196" t="s">
-        <v>391</v>
       </c>
     </row>
     <row r="197" spans="1:3" x14ac:dyDescent="0.25">
@@ -7089,10 +7090,10 @@
         <v>205</v>
       </c>
       <c r="B197" t="s">
+        <v>391</v>
+      </c>
+      <c r="C197" t="s">
         <v>392</v>
-      </c>
-      <c r="C197" t="s">
-        <v>393</v>
       </c>
     </row>
     <row r="198" spans="1:3" x14ac:dyDescent="0.25">
@@ -7100,10 +7101,10 @@
         <v>206</v>
       </c>
       <c r="B198" t="s">
+        <v>393</v>
+      </c>
+      <c r="C198" t="s">
         <v>394</v>
-      </c>
-      <c r="C198" t="s">
-        <v>395</v>
       </c>
     </row>
     <row r="199" spans="1:3" x14ac:dyDescent="0.25">
@@ -7111,10 +7112,10 @@
         <v>207</v>
       </c>
       <c r="B199" t="s">
+        <v>395</v>
+      </c>
+      <c r="C199" t="s">
         <v>396</v>
-      </c>
-      <c r="C199" t="s">
-        <v>397</v>
       </c>
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.25">
@@ -7122,10 +7123,10 @@
         <v>208</v>
       </c>
       <c r="B200" t="s">
+        <v>397</v>
+      </c>
+      <c r="C200" t="s">
         <v>398</v>
-      </c>
-      <c r="C200" t="s">
-        <v>399</v>
       </c>
     </row>
     <row r="201" spans="1:3" x14ac:dyDescent="0.25">
@@ -7133,10 +7134,10 @@
         <v>209</v>
       </c>
       <c r="B201" t="s">
+        <v>399</v>
+      </c>
+      <c r="C201" t="s">
         <v>400</v>
-      </c>
-      <c r="C201" t="s">
-        <v>401</v>
       </c>
     </row>
     <row r="202" spans="1:3" x14ac:dyDescent="0.25">
@@ -7144,10 +7145,10 @@
         <v>210</v>
       </c>
       <c r="B202" t="s">
+        <v>401</v>
+      </c>
+      <c r="C202" t="s">
         <v>402</v>
-      </c>
-      <c r="C202" t="s">
-        <v>403</v>
       </c>
     </row>
     <row r="203" spans="1:3" x14ac:dyDescent="0.25">
@@ -7155,10 +7156,10 @@
         <v>211</v>
       </c>
       <c r="B203" t="s">
+        <v>403</v>
+      </c>
+      <c r="C203" t="s">
         <v>404</v>
-      </c>
-      <c r="C203" t="s">
-        <v>405</v>
       </c>
     </row>
     <row r="204" spans="1:3" x14ac:dyDescent="0.25">
@@ -7166,10 +7167,10 @@
         <v>212</v>
       </c>
       <c r="B204" t="s">
+        <v>405</v>
+      </c>
+      <c r="C204" t="s">
         <v>406</v>
-      </c>
-      <c r="C204" t="s">
-        <v>407</v>
       </c>
     </row>
     <row r="205" spans="1:3" x14ac:dyDescent="0.25">
@@ -7177,10 +7178,10 @@
         <v>213</v>
       </c>
       <c r="B205" t="s">
+        <v>407</v>
+      </c>
+      <c r="C205" t="s">
         <v>408</v>
-      </c>
-      <c r="C205" t="s">
-        <v>409</v>
       </c>
     </row>
     <row r="206" spans="1:3" x14ac:dyDescent="0.25">
@@ -7188,10 +7189,10 @@
         <v>214</v>
       </c>
       <c r="B206" t="s">
+        <v>409</v>
+      </c>
+      <c r="C206" t="s">
         <v>410</v>
-      </c>
-      <c r="C206" t="s">
-        <v>411</v>
       </c>
     </row>
     <row r="207" spans="1:3" x14ac:dyDescent="0.25">
@@ -7199,10 +7200,10 @@
         <v>215</v>
       </c>
       <c r="B207" t="s">
+        <v>411</v>
+      </c>
+      <c r="C207" t="s">
         <v>412</v>
-      </c>
-      <c r="C207" t="s">
-        <v>413</v>
       </c>
     </row>
     <row r="208" spans="1:3" x14ac:dyDescent="0.25">
@@ -7210,10 +7211,10 @@
         <v>217</v>
       </c>
       <c r="B208" t="s">
+        <v>413</v>
+      </c>
+      <c r="C208" t="s">
         <v>414</v>
-      </c>
-      <c r="C208" t="s">
-        <v>415</v>
       </c>
     </row>
     <row r="209" spans="1:3" x14ac:dyDescent="0.25">
@@ -7221,10 +7222,10 @@
         <v>218</v>
       </c>
       <c r="B209" t="s">
+        <v>415</v>
+      </c>
+      <c r="C209" t="s">
         <v>416</v>
-      </c>
-      <c r="C209" t="s">
-        <v>417</v>
       </c>
     </row>
     <row r="210" spans="1:3" x14ac:dyDescent="0.25">
@@ -7232,10 +7233,10 @@
         <v>219</v>
       </c>
       <c r="B210" t="s">
+        <v>417</v>
+      </c>
+      <c r="C210" t="s">
         <v>418</v>
-      </c>
-      <c r="C210" t="s">
-        <v>419</v>
       </c>
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.25">
@@ -7243,10 +7244,10 @@
         <v>220</v>
       </c>
       <c r="B211" t="s">
+        <v>419</v>
+      </c>
+      <c r="C211" t="s">
         <v>420</v>
-      </c>
-      <c r="C211" t="s">
-        <v>421</v>
       </c>
     </row>
     <row r="212" spans="1:3" x14ac:dyDescent="0.25">
@@ -7254,10 +7255,10 @@
         <v>221</v>
       </c>
       <c r="B212" t="s">
+        <v>421</v>
+      </c>
+      <c r="C212" t="s">
         <v>422</v>
-      </c>
-      <c r="C212" t="s">
-        <v>423</v>
       </c>
     </row>
     <row r="213" spans="1:3" x14ac:dyDescent="0.25">
@@ -7265,10 +7266,10 @@
         <v>222</v>
       </c>
       <c r="B213" t="s">
+        <v>423</v>
+      </c>
+      <c r="C213" t="s">
         <v>424</v>
-      </c>
-      <c r="C213" t="s">
-        <v>425</v>
       </c>
     </row>
     <row r="214" spans="1:3" x14ac:dyDescent="0.25">
@@ -7276,10 +7277,10 @@
         <v>223</v>
       </c>
       <c r="B214" t="s">
+        <v>425</v>
+      </c>
+      <c r="C214" t="s">
         <v>426</v>
-      </c>
-      <c r="C214" t="s">
-        <v>427</v>
       </c>
     </row>
     <row r="215" spans="1:3" x14ac:dyDescent="0.25">
@@ -7287,10 +7288,10 @@
         <v>224</v>
       </c>
       <c r="B215" t="s">
+        <v>427</v>
+      </c>
+      <c r="C215" t="s">
         <v>428</v>
-      </c>
-      <c r="C215" t="s">
-        <v>429</v>
       </c>
     </row>
     <row r="216" spans="1:3" x14ac:dyDescent="0.25">
@@ -7298,10 +7299,10 @@
         <v>225</v>
       </c>
       <c r="B216" t="s">
+        <v>429</v>
+      </c>
+      <c r="C216" t="s">
         <v>430</v>
-      </c>
-      <c r="C216" t="s">
-        <v>431</v>
       </c>
     </row>
     <row r="217" spans="1:3" x14ac:dyDescent="0.25">
@@ -7309,10 +7310,10 @@
         <v>226</v>
       </c>
       <c r="B217" t="s">
+        <v>431</v>
+      </c>
+      <c r="C217" t="s">
         <v>432</v>
-      </c>
-      <c r="C217" t="s">
-        <v>433</v>
       </c>
     </row>
     <row r="218" spans="1:3" x14ac:dyDescent="0.25">
@@ -7320,10 +7321,10 @@
         <v>227</v>
       </c>
       <c r="B218" t="s">
+        <v>433</v>
+      </c>
+      <c r="C218" t="s">
         <v>434</v>
-      </c>
-      <c r="C218" t="s">
-        <v>435</v>
       </c>
     </row>
     <row r="219" spans="1:3" x14ac:dyDescent="0.25">
@@ -7331,10 +7332,10 @@
         <v>228</v>
       </c>
       <c r="B219" t="s">
+        <v>435</v>
+      </c>
+      <c r="C219" t="s">
         <v>436</v>
-      </c>
-      <c r="C219" t="s">
-        <v>437</v>
       </c>
     </row>
     <row r="220" spans="1:3" x14ac:dyDescent="0.25">
@@ -7342,10 +7343,10 @@
         <v>229</v>
       </c>
       <c r="B220" t="s">
+        <v>437</v>
+      </c>
+      <c r="C220" t="s">
         <v>438</v>
-      </c>
-      <c r="C220" t="s">
-        <v>439</v>
       </c>
     </row>
     <row r="221" spans="1:3" x14ac:dyDescent="0.25">
@@ -7353,10 +7354,10 @@
         <v>230</v>
       </c>
       <c r="B221" t="s">
+        <v>439</v>
+      </c>
+      <c r="C221" t="s">
         <v>440</v>
-      </c>
-      <c r="C221" t="s">
-        <v>441</v>
       </c>
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.25">
@@ -7364,10 +7365,10 @@
         <v>231</v>
       </c>
       <c r="B222" t="s">
+        <v>441</v>
+      </c>
+      <c r="C222" t="s">
         <v>442</v>
-      </c>
-      <c r="C222" t="s">
-        <v>443</v>
       </c>
     </row>
     <row r="223" spans="1:3" x14ac:dyDescent="0.25">
@@ -7375,10 +7376,10 @@
         <v>232</v>
       </c>
       <c r="B223" t="s">
+        <v>443</v>
+      </c>
+      <c r="C223" t="s">
         <v>444</v>
-      </c>
-      <c r="C223" t="s">
-        <v>445</v>
       </c>
     </row>
     <row r="224" spans="1:3" x14ac:dyDescent="0.25">
@@ -7386,10 +7387,10 @@
         <v>233</v>
       </c>
       <c r="B224" t="s">
+        <v>445</v>
+      </c>
+      <c r="C224" t="s">
         <v>446</v>
-      </c>
-      <c r="C224" t="s">
-        <v>447</v>
       </c>
     </row>
     <row r="225" spans="1:3" x14ac:dyDescent="0.25">
@@ -7397,10 +7398,10 @@
         <v>234</v>
       </c>
       <c r="B225" t="s">
+        <v>447</v>
+      </c>
+      <c r="C225" t="s">
         <v>448</v>
-      </c>
-      <c r="C225" t="s">
-        <v>449</v>
       </c>
     </row>
     <row r="226" spans="1:3" x14ac:dyDescent="0.25">
@@ -7408,10 +7409,10 @@
         <v>235</v>
       </c>
       <c r="B226" t="s">
+        <v>449</v>
+      </c>
+      <c r="C226" t="s">
         <v>450</v>
-      </c>
-      <c r="C226" t="s">
-        <v>451</v>
       </c>
     </row>
     <row r="227" spans="1:3" x14ac:dyDescent="0.25">
@@ -7419,10 +7420,10 @@
         <v>236</v>
       </c>
       <c r="B227" t="s">
+        <v>451</v>
+      </c>
+      <c r="C227" t="s">
         <v>452</v>
-      </c>
-      <c r="C227" t="s">
-        <v>453</v>
       </c>
     </row>
     <row r="228" spans="1:3" x14ac:dyDescent="0.25">
@@ -7430,10 +7431,10 @@
         <v>237</v>
       </c>
       <c r="B228" t="s">
+        <v>453</v>
+      </c>
+      <c r="C228" t="s">
         <v>454</v>
-      </c>
-      <c r="C228" t="s">
-        <v>455</v>
       </c>
     </row>
     <row r="229" spans="1:3" x14ac:dyDescent="0.25">
@@ -7441,10 +7442,10 @@
         <v>238</v>
       </c>
       <c r="B229" t="s">
+        <v>455</v>
+      </c>
+      <c r="C229" t="s">
         <v>456</v>
-      </c>
-      <c r="C229" t="s">
-        <v>457</v>
       </c>
     </row>
     <row r="230" spans="1:3" x14ac:dyDescent="0.25">
@@ -7452,10 +7453,10 @@
         <v>239</v>
       </c>
       <c r="B230" t="s">
+        <v>457</v>
+      </c>
+      <c r="C230" t="s">
         <v>458</v>
-      </c>
-      <c r="C230" t="s">
-        <v>459</v>
       </c>
     </row>
     <row r="231" spans="1:3" x14ac:dyDescent="0.25">
@@ -7463,10 +7464,10 @@
         <v>240</v>
       </c>
       <c r="B231" t="s">
+        <v>459</v>
+      </c>
+      <c r="C231" t="s">
         <v>460</v>
-      </c>
-      <c r="C231" t="s">
-        <v>461</v>
       </c>
     </row>
     <row r="232" spans="1:3" x14ac:dyDescent="0.25">
@@ -7474,10 +7475,10 @@
         <v>241</v>
       </c>
       <c r="B232" t="s">
+        <v>461</v>
+      </c>
+      <c r="C232" t="s">
         <v>462</v>
-      </c>
-      <c r="C232" t="s">
-        <v>463</v>
       </c>
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.25">
@@ -7485,10 +7486,10 @@
         <v>242</v>
       </c>
       <c r="B233" t="s">
+        <v>463</v>
+      </c>
+      <c r="C233" t="s">
         <v>464</v>
-      </c>
-      <c r="C233" t="s">
-        <v>465</v>
       </c>
     </row>
     <row r="234" spans="1:3" x14ac:dyDescent="0.25">
@@ -7496,10 +7497,10 @@
         <v>243</v>
       </c>
       <c r="B234" t="s">
+        <v>465</v>
+      </c>
+      <c r="C234" t="s">
         <v>466</v>
-      </c>
-      <c r="C234" t="s">
-        <v>467</v>
       </c>
     </row>
     <row r="235" spans="1:3" x14ac:dyDescent="0.25">
@@ -7507,10 +7508,10 @@
         <v>244</v>
       </c>
       <c r="B235" t="s">
+        <v>467</v>
+      </c>
+      <c r="C235" t="s">
         <v>468</v>
-      </c>
-      <c r="C235" t="s">
-        <v>469</v>
       </c>
     </row>
     <row r="236" spans="1:3" x14ac:dyDescent="0.25">
@@ -7518,10 +7519,10 @@
         <v>245</v>
       </c>
       <c r="B236" t="s">
+        <v>469</v>
+      </c>
+      <c r="C236" t="s">
         <v>470</v>
-      </c>
-      <c r="C236" t="s">
-        <v>471</v>
       </c>
     </row>
     <row r="237" spans="1:3" x14ac:dyDescent="0.25">
@@ -7529,10 +7530,10 @@
         <v>246</v>
       </c>
       <c r="B237" t="s">
+        <v>471</v>
+      </c>
+      <c r="C237" t="s">
         <v>472</v>
-      </c>
-      <c r="C237" t="s">
-        <v>473</v>
       </c>
     </row>
     <row r="238" spans="1:3" x14ac:dyDescent="0.25">
@@ -7540,10 +7541,10 @@
         <v>247</v>
       </c>
       <c r="B238" t="s">
+        <v>473</v>
+      </c>
+      <c r="C238" t="s">
         <v>474</v>
-      </c>
-      <c r="C238" t="s">
-        <v>475</v>
       </c>
     </row>
     <row r="239" spans="1:3" x14ac:dyDescent="0.25">
@@ -7551,10 +7552,10 @@
         <v>248</v>
       </c>
       <c r="B239" t="s">
+        <v>475</v>
+      </c>
+      <c r="C239" t="s">
         <v>476</v>
-      </c>
-      <c r="C239" t="s">
-        <v>477</v>
       </c>
     </row>
     <row r="240" spans="1:3" x14ac:dyDescent="0.25">
@@ -7562,10 +7563,10 @@
         <v>249</v>
       </c>
       <c r="B240" t="s">
+        <v>477</v>
+      </c>
+      <c r="C240" t="s">
         <v>478</v>
-      </c>
-      <c r="C240" t="s">
-        <v>479</v>
       </c>
     </row>
     <row r="241" spans="1:3" x14ac:dyDescent="0.25">
@@ -7573,10 +7574,10 @@
         <v>250</v>
       </c>
       <c r="B241" t="s">
+        <v>479</v>
+      </c>
+      <c r="C241" t="s">
         <v>480</v>
-      </c>
-      <c r="C241" t="s">
-        <v>481</v>
       </c>
     </row>
     <row r="242" spans="1:3" x14ac:dyDescent="0.25">
@@ -7584,10 +7585,10 @@
         <v>251</v>
       </c>
       <c r="B242" t="s">
+        <v>481</v>
+      </c>
+      <c r="C242" t="s">
         <v>482</v>
-      </c>
-      <c r="C242" t="s">
-        <v>483</v>
       </c>
     </row>
     <row r="243" spans="1:3" x14ac:dyDescent="0.25">
@@ -7595,10 +7596,10 @@
         <v>252</v>
       </c>
       <c r="B243" t="s">
+        <v>483</v>
+      </c>
+      <c r="C243" t="s">
         <v>484</v>
-      </c>
-      <c r="C243" t="s">
-        <v>485</v>
       </c>
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.25">
@@ -7606,10 +7607,10 @@
         <v>253</v>
       </c>
       <c r="B244" t="s">
+        <v>485</v>
+      </c>
+      <c r="C244" t="s">
         <v>486</v>
-      </c>
-      <c r="C244" t="s">
-        <v>487</v>
       </c>
     </row>
     <row r="245" spans="1:3" x14ac:dyDescent="0.25">
@@ -7617,10 +7618,10 @@
         <v>254</v>
       </c>
       <c r="B245" t="s">
+        <v>487</v>
+      </c>
+      <c r="C245" t="s">
         <v>488</v>
-      </c>
-      <c r="C245" t="s">
-        <v>489</v>
       </c>
     </row>
     <row r="246" spans="1:3" x14ac:dyDescent="0.25">
@@ -7628,10 +7629,10 @@
         <v>255</v>
       </c>
       <c r="B246" t="s">
+        <v>489</v>
+      </c>
+      <c r="C246" t="s">
         <v>490</v>
-      </c>
-      <c r="C246" t="s">
-        <v>491</v>
       </c>
     </row>
     <row r="247" spans="1:3" x14ac:dyDescent="0.25">
@@ -7639,10 +7640,10 @@
         <v>256</v>
       </c>
       <c r="B247" t="s">
+        <v>491</v>
+      </c>
+      <c r="C247" t="s">
         <v>492</v>
-      </c>
-      <c r="C247" t="s">
-        <v>493</v>
       </c>
     </row>
     <row r="248" spans="1:3" x14ac:dyDescent="0.25">
@@ -7650,10 +7651,10 @@
         <v>257</v>
       </c>
       <c r="B248" t="s">
+        <v>493</v>
+      </c>
+      <c r="C248" t="s">
         <v>494</v>
-      </c>
-      <c r="C248" t="s">
-        <v>495</v>
       </c>
     </row>
     <row r="249" spans="1:3" x14ac:dyDescent="0.25">
@@ -7661,10 +7662,10 @@
         <v>258</v>
       </c>
       <c r="B249" t="s">
+        <v>495</v>
+      </c>
+      <c r="C249" t="s">
         <v>496</v>
-      </c>
-      <c r="C249" t="s">
-        <v>497</v>
       </c>
     </row>
     <row r="250" spans="1:3" x14ac:dyDescent="0.25">
@@ -7672,10 +7673,10 @@
         <v>259</v>
       </c>
       <c r="B250" t="s">
+        <v>497</v>
+      </c>
+      <c r="C250" t="s">
         <v>498</v>
-      </c>
-      <c r="C250" t="s">
-        <v>499</v>
       </c>
     </row>
     <row r="251" spans="1:3" x14ac:dyDescent="0.25">
@@ -7683,10 +7684,10 @@
         <v>260</v>
       </c>
       <c r="B251" t="s">
+        <v>499</v>
+      </c>
+      <c r="C251" t="s">
         <v>500</v>
-      </c>
-      <c r="C251" t="s">
-        <v>501</v>
       </c>
     </row>
     <row r="252" spans="1:3" x14ac:dyDescent="0.25">
@@ -7694,10 +7695,10 @@
         <v>261</v>
       </c>
       <c r="B252" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="C252" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="253" spans="1:3" x14ac:dyDescent="0.25">
@@ -7705,10 +7706,10 @@
         <v>262</v>
       </c>
       <c r="B253" t="s">
+        <v>502</v>
+      </c>
+      <c r="C253" t="s">
         <v>503</v>
-      </c>
-      <c r="C253" t="s">
-        <v>504</v>
       </c>
     </row>
     <row r="254" spans="1:3" x14ac:dyDescent="0.25">
@@ -7716,10 +7717,10 @@
         <v>263</v>
       </c>
       <c r="B254" t="s">
+        <v>504</v>
+      </c>
+      <c r="C254" t="s">
         <v>505</v>
-      </c>
-      <c r="C254" t="s">
-        <v>506</v>
       </c>
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.25">
@@ -7727,10 +7728,10 @@
         <v>264</v>
       </c>
       <c r="B255" t="s">
+        <v>506</v>
+      </c>
+      <c r="C255" t="s">
         <v>507</v>
-      </c>
-      <c r="C255" t="s">
-        <v>508</v>
       </c>
     </row>
     <row r="256" spans="1:3" x14ac:dyDescent="0.25">
@@ -7738,10 +7739,10 @@
         <v>265</v>
       </c>
       <c r="B256" t="s">
+        <v>508</v>
+      </c>
+      <c r="C256" t="s">
         <v>509</v>
-      </c>
-      <c r="C256" t="s">
-        <v>510</v>
       </c>
     </row>
     <row r="257" spans="1:3" x14ac:dyDescent="0.25">
@@ -7749,10 +7750,10 @@
         <v>266</v>
       </c>
       <c r="B257" t="s">
+        <v>510</v>
+      </c>
+      <c r="C257" t="s">
         <v>511</v>
-      </c>
-      <c r="C257" t="s">
-        <v>512</v>
       </c>
     </row>
     <row r="258" spans="1:3" x14ac:dyDescent="0.25">
@@ -7760,10 +7761,10 @@
         <v>267</v>
       </c>
       <c r="B258" t="s">
+        <v>512</v>
+      </c>
+      <c r="C258" t="s">
         <v>513</v>
-      </c>
-      <c r="C258" t="s">
-        <v>514</v>
       </c>
     </row>
     <row r="259" spans="1:3" x14ac:dyDescent="0.25">
@@ -7771,10 +7772,10 @@
         <v>268</v>
       </c>
       <c r="B259" t="s">
+        <v>514</v>
+      </c>
+      <c r="C259" t="s">
         <v>515</v>
-      </c>
-      <c r="C259" t="s">
-        <v>516</v>
       </c>
     </row>
     <row r="260" spans="1:3" x14ac:dyDescent="0.25">
@@ -7782,10 +7783,10 @@
         <v>269</v>
       </c>
       <c r="B260" t="s">
+        <v>516</v>
+      </c>
+      <c r="C260" t="s">
         <v>517</v>
-      </c>
-      <c r="C260" t="s">
-        <v>518</v>
       </c>
     </row>
     <row r="261" spans="1:3" x14ac:dyDescent="0.25">
@@ -7793,10 +7794,10 @@
         <v>270</v>
       </c>
       <c r="B261" t="s">
+        <v>518</v>
+      </c>
+      <c r="C261" t="s">
         <v>519</v>
-      </c>
-      <c r="C261" t="s">
-        <v>520</v>
       </c>
     </row>
     <row r="262" spans="1:3" x14ac:dyDescent="0.25">
@@ -7804,10 +7805,10 @@
         <v>271</v>
       </c>
       <c r="B262" t="s">
+        <v>520</v>
+      </c>
+      <c r="C262" t="s">
         <v>521</v>
-      </c>
-      <c r="C262" t="s">
-        <v>522</v>
       </c>
     </row>
     <row r="263" spans="1:3" x14ac:dyDescent="0.25">
@@ -7815,10 +7816,10 @@
         <v>272</v>
       </c>
       <c r="B263" t="s">
+        <v>522</v>
+      </c>
+      <c r="C263" t="s">
         <v>523</v>
-      </c>
-      <c r="C263" t="s">
-        <v>524</v>
       </c>
     </row>
     <row r="264" spans="1:3" x14ac:dyDescent="0.25">
@@ -7826,10 +7827,10 @@
         <v>274</v>
       </c>
       <c r="B264" t="s">
+        <v>524</v>
+      </c>
+      <c r="C264" t="s">
         <v>525</v>
-      </c>
-      <c r="C264" t="s">
-        <v>526</v>
       </c>
     </row>
     <row r="265" spans="1:3" x14ac:dyDescent="0.25">
@@ -7837,10 +7838,10 @@
         <v>275</v>
       </c>
       <c r="B265" t="s">
+        <v>526</v>
+      </c>
+      <c r="C265" t="s">
         <v>527</v>
-      </c>
-      <c r="C265" t="s">
-        <v>528</v>
       </c>
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.25">
@@ -7848,10 +7849,10 @@
         <v>276</v>
       </c>
       <c r="B266" t="s">
+        <v>528</v>
+      </c>
+      <c r="C266" t="s">
         <v>529</v>
-      </c>
-      <c r="C266" t="s">
-        <v>530</v>
       </c>
     </row>
     <row r="267" spans="1:3" x14ac:dyDescent="0.25">
@@ -7859,10 +7860,10 @@
         <v>277</v>
       </c>
       <c r="B267" t="s">
+        <v>530</v>
+      </c>
+      <c r="C267" t="s">
         <v>531</v>
-      </c>
-      <c r="C267" t="s">
-        <v>532</v>
       </c>
     </row>
     <row r="268" spans="1:3" x14ac:dyDescent="0.25">
@@ -7870,10 +7871,10 @@
         <v>278</v>
       </c>
       <c r="B268" t="s">
+        <v>532</v>
+      </c>
+      <c r="C268" t="s">
         <v>533</v>
-      </c>
-      <c r="C268" t="s">
-        <v>534</v>
       </c>
     </row>
     <row r="269" spans="1:3" x14ac:dyDescent="0.25">
@@ -7881,10 +7882,10 @@
         <v>279</v>
       </c>
       <c r="B269" t="s">
+        <v>534</v>
+      </c>
+      <c r="C269" t="s">
         <v>535</v>
-      </c>
-      <c r="C269" t="s">
-        <v>536</v>
       </c>
     </row>
     <row r="270" spans="1:3" x14ac:dyDescent="0.25">
@@ -7892,10 +7893,10 @@
         <v>280</v>
       </c>
       <c r="B270" t="s">
+        <v>536</v>
+      </c>
+      <c r="C270" t="s">
         <v>537</v>
-      </c>
-      <c r="C270" t="s">
-        <v>538</v>
       </c>
     </row>
     <row r="271" spans="1:3" x14ac:dyDescent="0.25">
@@ -7903,10 +7904,10 @@
         <v>281</v>
       </c>
       <c r="B271" t="s">
+        <v>538</v>
+      </c>
+      <c r="C271" t="s">
         <v>539</v>
-      </c>
-      <c r="C271" t="s">
-        <v>540</v>
       </c>
     </row>
     <row r="272" spans="1:3" x14ac:dyDescent="0.25">
@@ -7914,10 +7915,10 @@
         <v>282</v>
       </c>
       <c r="B272" t="s">
+        <v>540</v>
+      </c>
+      <c r="C272" t="s">
         <v>541</v>
-      </c>
-      <c r="C272" t="s">
-        <v>542</v>
       </c>
     </row>
     <row r="273" spans="1:3" x14ac:dyDescent="0.25">
@@ -7925,10 +7926,10 @@
         <v>283</v>
       </c>
       <c r="B273" t="s">
+        <v>542</v>
+      </c>
+      <c r="C273" t="s">
         <v>543</v>
-      </c>
-      <c r="C273" t="s">
-        <v>544</v>
       </c>
     </row>
     <row r="274" spans="1:3" x14ac:dyDescent="0.25">
@@ -7936,10 +7937,10 @@
         <v>284</v>
       </c>
       <c r="B274" t="s">
+        <v>544</v>
+      </c>
+      <c r="C274" t="s">
         <v>545</v>
-      </c>
-      <c r="C274" t="s">
-        <v>546</v>
       </c>
     </row>
     <row r="275" spans="1:3" x14ac:dyDescent="0.25">
@@ -7947,10 +7948,10 @@
         <v>285</v>
       </c>
       <c r="B275" t="s">
+        <v>546</v>
+      </c>
+      <c r="C275" t="s">
         <v>547</v>
-      </c>
-      <c r="C275" t="s">
-        <v>548</v>
       </c>
     </row>
     <row r="276" spans="1:3" x14ac:dyDescent="0.25">
@@ -7958,10 +7959,10 @@
         <v>286</v>
       </c>
       <c r="B276" t="s">
+        <v>548</v>
+      </c>
+      <c r="C276" t="s">
         <v>549</v>
-      </c>
-      <c r="C276" t="s">
-        <v>550</v>
       </c>
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.25">
@@ -7969,10 +7970,10 @@
         <v>287</v>
       </c>
       <c r="B277" t="s">
+        <v>550</v>
+      </c>
+      <c r="C277" t="s">
         <v>551</v>
-      </c>
-      <c r="C277" t="s">
-        <v>552</v>
       </c>
     </row>
     <row r="278" spans="1:3" x14ac:dyDescent="0.25">
@@ -7980,10 +7981,10 @@
         <v>288</v>
       </c>
       <c r="B278" t="s">
+        <v>552</v>
+      </c>
+      <c r="C278" t="s">
         <v>553</v>
-      </c>
-      <c r="C278" t="s">
-        <v>554</v>
       </c>
     </row>
     <row r="279" spans="1:3" x14ac:dyDescent="0.25">
@@ -7991,10 +7992,10 @@
         <v>289</v>
       </c>
       <c r="B279" t="s">
+        <v>554</v>
+      </c>
+      <c r="C279" t="s">
         <v>555</v>
-      </c>
-      <c r="C279" t="s">
-        <v>556</v>
       </c>
     </row>
     <row r="280" spans="1:3" x14ac:dyDescent="0.25">
@@ -8002,10 +8003,10 @@
         <v>290</v>
       </c>
       <c r="B280" t="s">
+        <v>556</v>
+      </c>
+      <c r="C280" t="s">
         <v>557</v>
-      </c>
-      <c r="C280" t="s">
-        <v>558</v>
       </c>
     </row>
     <row r="281" spans="1:3" x14ac:dyDescent="0.25">
@@ -8013,10 +8014,10 @@
         <v>291</v>
       </c>
       <c r="B281" t="s">
+        <v>558</v>
+      </c>
+      <c r="C281" t="s">
         <v>559</v>
-      </c>
-      <c r="C281" t="s">
-        <v>560</v>
       </c>
     </row>
     <row r="282" spans="1:3" x14ac:dyDescent="0.25">
@@ -8024,10 +8025,10 @@
         <v>292</v>
       </c>
       <c r="B282" t="s">
+        <v>560</v>
+      </c>
+      <c r="C282" t="s">
         <v>561</v>
-      </c>
-      <c r="C282" t="s">
-        <v>562</v>
       </c>
     </row>
     <row r="283" spans="1:3" x14ac:dyDescent="0.25">
@@ -8035,10 +8036,10 @@
         <v>293</v>
       </c>
       <c r="B283" t="s">
+        <v>562</v>
+      </c>
+      <c r="C283" t="s">
         <v>563</v>
-      </c>
-      <c r="C283" t="s">
-        <v>564</v>
       </c>
     </row>
     <row r="284" spans="1:3" x14ac:dyDescent="0.25">
@@ -8046,10 +8047,10 @@
         <v>294</v>
       </c>
       <c r="B284" t="s">
+        <v>564</v>
+      </c>
+      <c r="C284" t="s">
         <v>565</v>
-      </c>
-      <c r="C284" t="s">
-        <v>566</v>
       </c>
     </row>
     <row r="285" spans="1:3" x14ac:dyDescent="0.25">
@@ -8057,10 +8058,10 @@
         <v>295</v>
       </c>
       <c r="B285" t="s">
+        <v>566</v>
+      </c>
+      <c r="C285" t="s">
         <v>567</v>
-      </c>
-      <c r="C285" t="s">
-        <v>568</v>
       </c>
     </row>
     <row r="286" spans="1:3" x14ac:dyDescent="0.25">
@@ -8068,10 +8069,10 @@
         <v>296</v>
       </c>
       <c r="B286" t="s">
+        <v>568</v>
+      </c>
+      <c r="C286" t="s">
         <v>569</v>
-      </c>
-      <c r="C286" t="s">
-        <v>570</v>
       </c>
     </row>
     <row r="287" spans="1:3" x14ac:dyDescent="0.25">
@@ -8079,10 +8080,10 @@
         <v>297</v>
       </c>
       <c r="B287" t="s">
+        <v>570</v>
+      </c>
+      <c r="C287" t="s">
         <v>571</v>
-      </c>
-      <c r="C287" t="s">
-        <v>572</v>
       </c>
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.25">
@@ -8090,10 +8091,10 @@
         <v>298</v>
       </c>
       <c r="B288" t="s">
+        <v>572</v>
+      </c>
+      <c r="C288" t="s">
         <v>573</v>
-      </c>
-      <c r="C288" t="s">
-        <v>574</v>
       </c>
     </row>
     <row r="289" spans="1:3" x14ac:dyDescent="0.25">
@@ -8101,10 +8102,10 @@
         <v>299</v>
       </c>
       <c r="B289" t="s">
+        <v>574</v>
+      </c>
+      <c r="C289" t="s">
         <v>575</v>
-      </c>
-      <c r="C289" t="s">
-        <v>576</v>
       </c>
     </row>
     <row r="290" spans="1:3" x14ac:dyDescent="0.25">
@@ -8112,10 +8113,10 @@
         <v>300</v>
       </c>
       <c r="B290" t="s">
+        <v>576</v>
+      </c>
+      <c r="C290" t="s">
         <v>577</v>
-      </c>
-      <c r="C290" t="s">
-        <v>578</v>
       </c>
     </row>
     <row r="291" spans="1:3" x14ac:dyDescent="0.25">
@@ -8123,10 +8124,10 @@
         <v>301</v>
       </c>
       <c r="B291" t="s">
+        <v>578</v>
+      </c>
+      <c r="C291" t="s">
         <v>579</v>
-      </c>
-      <c r="C291" t="s">
-        <v>580</v>
       </c>
     </row>
     <row r="292" spans="1:3" x14ac:dyDescent="0.25">
@@ -8134,10 +8135,10 @@
         <v>302</v>
       </c>
       <c r="B292" t="s">
+        <v>580</v>
+      </c>
+      <c r="C292" t="s">
         <v>581</v>
-      </c>
-      <c r="C292" t="s">
-        <v>582</v>
       </c>
     </row>
     <row r="293" spans="1:3" x14ac:dyDescent="0.25">
@@ -8145,10 +8146,10 @@
         <v>303</v>
       </c>
       <c r="B293" t="s">
+        <v>582</v>
+      </c>
+      <c r="C293" t="s">
         <v>583</v>
-      </c>
-      <c r="C293" t="s">
-        <v>584</v>
       </c>
     </row>
     <row r="294" spans="1:3" x14ac:dyDescent="0.25">
@@ -8156,10 +8157,10 @@
         <v>304</v>
       </c>
       <c r="B294" t="s">
+        <v>584</v>
+      </c>
+      <c r="C294" t="s">
         <v>585</v>
-      </c>
-      <c r="C294" t="s">
-        <v>586</v>
       </c>
     </row>
     <row r="295" spans="1:3" x14ac:dyDescent="0.25">
@@ -8167,10 +8168,10 @@
         <v>305</v>
       </c>
       <c r="B295" t="s">
+        <v>586</v>
+      </c>
+      <c r="C295" t="s">
         <v>587</v>
-      </c>
-      <c r="C295" t="s">
-        <v>588</v>
       </c>
     </row>
     <row r="296" spans="1:3" x14ac:dyDescent="0.25">
@@ -8178,10 +8179,10 @@
         <v>306</v>
       </c>
       <c r="B296" t="s">
+        <v>588</v>
+      </c>
+      <c r="C296" t="s">
         <v>589</v>
-      </c>
-      <c r="C296" t="s">
-        <v>590</v>
       </c>
     </row>
     <row r="297" spans="1:3" x14ac:dyDescent="0.25">
@@ -8189,10 +8190,10 @@
         <v>307</v>
       </c>
       <c r="B297" t="s">
+        <v>590</v>
+      </c>
+      <c r="C297" t="s">
         <v>591</v>
-      </c>
-      <c r="C297" t="s">
-        <v>592</v>
       </c>
     </row>
     <row r="298" spans="1:3" x14ac:dyDescent="0.25">
@@ -8200,10 +8201,10 @@
         <v>308</v>
       </c>
       <c r="B298" t="s">
+        <v>592</v>
+      </c>
+      <c r="C298" t="s">
         <v>593</v>
-      </c>
-      <c r="C298" t="s">
-        <v>594</v>
       </c>
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.25">
@@ -8211,10 +8212,10 @@
         <v>309</v>
       </c>
       <c r="B299" t="s">
+        <v>594</v>
+      </c>
+      <c r="C299" t="s">
         <v>595</v>
-      </c>
-      <c r="C299" t="s">
-        <v>596</v>
       </c>
     </row>
     <row r="300" spans="1:3" x14ac:dyDescent="0.25">
@@ -8222,10 +8223,10 @@
         <v>310</v>
       </c>
       <c r="B300" t="s">
+        <v>596</v>
+      </c>
+      <c r="C300" t="s">
         <v>597</v>
-      </c>
-      <c r="C300" t="s">
-        <v>598</v>
       </c>
     </row>
     <row r="301" spans="1:3" x14ac:dyDescent="0.25">
@@ -8233,10 +8234,10 @@
         <v>311</v>
       </c>
       <c r="B301" t="s">
+        <v>598</v>
+      </c>
+      <c r="C301" t="s">
         <v>599</v>
-      </c>
-      <c r="C301" t="s">
-        <v>600</v>
       </c>
     </row>
     <row r="302" spans="1:3" x14ac:dyDescent="0.25">
@@ -8244,10 +8245,10 @@
         <v>312</v>
       </c>
       <c r="B302" t="s">
+        <v>600</v>
+      </c>
+      <c r="C302" t="s">
         <v>601</v>
-      </c>
-      <c r="C302" t="s">
-        <v>602</v>
       </c>
     </row>
     <row r="303" spans="1:3" x14ac:dyDescent="0.25">
@@ -8255,10 +8256,10 @@
         <v>313</v>
       </c>
       <c r="B303" t="s">
+        <v>602</v>
+      </c>
+      <c r="C303" t="s">
         <v>603</v>
-      </c>
-      <c r="C303" t="s">
-        <v>604</v>
       </c>
     </row>
     <row r="304" spans="1:3" x14ac:dyDescent="0.25">
@@ -8266,10 +8267,10 @@
         <v>314</v>
       </c>
       <c r="B304" t="s">
+        <v>604</v>
+      </c>
+      <c r="C304" t="s">
         <v>605</v>
-      </c>
-      <c r="C304" t="s">
-        <v>606</v>
       </c>
     </row>
     <row r="305" spans="1:3" x14ac:dyDescent="0.25">
@@ -8277,10 +8278,10 @@
         <v>315</v>
       </c>
       <c r="B305" t="s">
+        <v>606</v>
+      </c>
+      <c r="C305" t="s">
         <v>607</v>
-      </c>
-      <c r="C305" t="s">
-        <v>608</v>
       </c>
     </row>
     <row r="306" spans="1:3" x14ac:dyDescent="0.25">
@@ -8288,10 +8289,10 @@
         <v>316</v>
       </c>
       <c r="B306" t="s">
+        <v>608</v>
+      </c>
+      <c r="C306" t="s">
         <v>609</v>
-      </c>
-      <c r="C306" t="s">
-        <v>610</v>
       </c>
     </row>
     <row r="307" spans="1:3" x14ac:dyDescent="0.25">
@@ -8299,10 +8300,10 @@
         <v>317</v>
       </c>
       <c r="B307" t="s">
+        <v>610</v>
+      </c>
+      <c r="C307" t="s">
         <v>611</v>
-      </c>
-      <c r="C307" t="s">
-        <v>612</v>
       </c>
     </row>
     <row r="308" spans="1:3" x14ac:dyDescent="0.25">
@@ -8310,10 +8311,10 @@
         <v>318</v>
       </c>
       <c r="B308" t="s">
+        <v>612</v>
+      </c>
+      <c r="C308" t="s">
         <v>613</v>
-      </c>
-      <c r="C308" t="s">
-        <v>614</v>
       </c>
     </row>
     <row r="309" spans="1:3" x14ac:dyDescent="0.25">
@@ -8321,10 +8322,10 @@
         <v>319</v>
       </c>
       <c r="B309" t="s">
+        <v>614</v>
+      </c>
+      <c r="C309" t="s">
         <v>615</v>
-      </c>
-      <c r="C309" t="s">
-        <v>616</v>
       </c>
     </row>
     <row r="310" spans="1:3" x14ac:dyDescent="0.25">
@@ -8332,10 +8333,10 @@
         <v>320</v>
       </c>
       <c r="B310" t="s">
+        <v>616</v>
+      </c>
+      <c r="C310" t="s">
         <v>617</v>
-      </c>
-      <c r="C310" t="s">
-        <v>618</v>
       </c>
     </row>
     <row r="311" spans="1:3" x14ac:dyDescent="0.25">
@@ -8343,10 +8344,10 @@
         <v>321</v>
       </c>
       <c r="B311" t="s">
+        <v>618</v>
+      </c>
+      <c r="C311" t="s">
         <v>619</v>
-      </c>
-      <c r="C311" t="s">
-        <v>620</v>
       </c>
     </row>
     <row r="312" spans="1:3" x14ac:dyDescent="0.25">
@@ -8354,10 +8355,10 @@
         <v>322</v>
       </c>
       <c r="B312" t="s">
+        <v>620</v>
+      </c>
+      <c r="C312" t="s">
         <v>621</v>
-      </c>
-      <c r="C312" t="s">
-        <v>622</v>
       </c>
     </row>
     <row r="313" spans="1:3" x14ac:dyDescent="0.25">
@@ -8365,10 +8366,10 @@
         <v>323</v>
       </c>
       <c r="B313" t="s">
+        <v>622</v>
+      </c>
+      <c r="C313" t="s">
         <v>623</v>
-      </c>
-      <c r="C313" t="s">
-        <v>624</v>
       </c>
     </row>
     <row r="314" spans="1:3" x14ac:dyDescent="0.25">
@@ -8376,10 +8377,10 @@
         <v>324</v>
       </c>
       <c r="B314" t="s">
+        <v>624</v>
+      </c>
+      <c r="C314" t="s">
         <v>625</v>
-      </c>
-      <c r="C314" t="s">
-        <v>626</v>
       </c>
     </row>
     <row r="315" spans="1:3" x14ac:dyDescent="0.25">
@@ -8387,10 +8388,10 @@
         <v>325</v>
       </c>
       <c r="B315" t="s">
+        <v>626</v>
+      </c>
+      <c r="C315" t="s">
         <v>627</v>
-      </c>
-      <c r="C315" t="s">
-        <v>628</v>
       </c>
     </row>
     <row r="316" spans="1:3" x14ac:dyDescent="0.25">
@@ -8398,10 +8399,10 @@
         <v>326</v>
       </c>
       <c r="B316" t="s">
+        <v>628</v>
+      </c>
+      <c r="C316" t="s">
         <v>629</v>
-      </c>
-      <c r="C316" t="s">
-        <v>630</v>
       </c>
     </row>
     <row r="317" spans="1:3" x14ac:dyDescent="0.25">
@@ -8409,10 +8410,10 @@
         <v>327</v>
       </c>
       <c r="B317" t="s">
+        <v>630</v>
+      </c>
+      <c r="C317" t="s">
         <v>631</v>
-      </c>
-      <c r="C317" t="s">
-        <v>632</v>
       </c>
     </row>
     <row r="318" spans="1:3" x14ac:dyDescent="0.25">
@@ -8420,10 +8421,10 @@
         <v>328</v>
       </c>
       <c r="B318" t="s">
+        <v>632</v>
+      </c>
+      <c r="C318" t="s">
         <v>633</v>
-      </c>
-      <c r="C318" t="s">
-        <v>634</v>
       </c>
     </row>
     <row r="319" spans="1:3" x14ac:dyDescent="0.25">
@@ -8431,10 +8432,10 @@
         <v>329</v>
       </c>
       <c r="B319" t="s">
+        <v>634</v>
+      </c>
+      <c r="C319" t="s">
         <v>635</v>
-      </c>
-      <c r="C319" t="s">
-        <v>636</v>
       </c>
     </row>
     <row r="320" spans="1:3" x14ac:dyDescent="0.25">
@@ -8442,10 +8443,10 @@
         <v>330</v>
       </c>
       <c r="B320" t="s">
+        <v>636</v>
+      </c>
+      <c r="C320" t="s">
         <v>637</v>
-      </c>
-      <c r="C320" t="s">
-        <v>638</v>
       </c>
     </row>
     <row r="321" spans="1:3" x14ac:dyDescent="0.25">
@@ -8453,10 +8454,10 @@
         <v>331</v>
       </c>
       <c r="B321" t="s">
+        <v>638</v>
+      </c>
+      <c r="C321" t="s">
         <v>639</v>
-      </c>
-      <c r="C321" t="s">
-        <v>640</v>
       </c>
     </row>
     <row r="322" spans="1:3" x14ac:dyDescent="0.25">
@@ -8464,10 +8465,10 @@
         <v>332</v>
       </c>
       <c r="B322" t="s">
+        <v>640</v>
+      </c>
+      <c r="C322" t="s">
         <v>641</v>
-      </c>
-      <c r="C322" t="s">
-        <v>642</v>
       </c>
     </row>
     <row r="323" spans="1:3" x14ac:dyDescent="0.25">
@@ -8475,10 +8476,10 @@
         <v>333</v>
       </c>
       <c r="B323" t="s">
+        <v>642</v>
+      </c>
+      <c r="C323" t="s">
         <v>643</v>
-      </c>
-      <c r="C323" t="s">
-        <v>644</v>
       </c>
     </row>
     <row r="324" spans="1:3" x14ac:dyDescent="0.25">
@@ -8486,10 +8487,10 @@
         <v>334</v>
       </c>
       <c r="B324" t="s">
+        <v>644</v>
+      </c>
+      <c r="C324" t="s">
         <v>645</v>
-      </c>
-      <c r="C324" t="s">
-        <v>646</v>
       </c>
     </row>
     <row r="325" spans="1:3" x14ac:dyDescent="0.25">
@@ -8497,10 +8498,10 @@
         <v>335</v>
       </c>
       <c r="B325" t="s">
+        <v>646</v>
+      </c>
+      <c r="C325" t="s">
         <v>647</v>
-      </c>
-      <c r="C325" t="s">
-        <v>648</v>
       </c>
     </row>
     <row r="326" spans="1:3" x14ac:dyDescent="0.25">
@@ -8508,10 +8509,10 @@
         <v>336</v>
       </c>
       <c r="B326" t="s">
+        <v>648</v>
+      </c>
+      <c r="C326" t="s">
         <v>649</v>
-      </c>
-      <c r="C326" t="s">
-        <v>650</v>
       </c>
     </row>
     <row r="327" spans="1:3" x14ac:dyDescent="0.25">
@@ -8519,10 +8520,10 @@
         <v>337</v>
       </c>
       <c r="B327" t="s">
+        <v>650</v>
+      </c>
+      <c r="C327" t="s">
         <v>651</v>
-      </c>
-      <c r="C327" t="s">
-        <v>652</v>
       </c>
     </row>
     <row r="328" spans="1:3" x14ac:dyDescent="0.25">
@@ -8530,10 +8531,10 @@
         <v>338</v>
       </c>
       <c r="B328" t="s">
+        <v>652</v>
+      </c>
+      <c r="C328" t="s">
         <v>653</v>
-      </c>
-      <c r="C328" t="s">
-        <v>654</v>
       </c>
     </row>
     <row r="329" spans="1:3" x14ac:dyDescent="0.25">
@@ -8541,10 +8542,10 @@
         <v>339</v>
       </c>
       <c r="B329" t="s">
+        <v>654</v>
+      </c>
+      <c r="C329" t="s">
         <v>655</v>
-      </c>
-      <c r="C329" t="s">
-        <v>656</v>
       </c>
     </row>
     <row r="330" spans="1:3" x14ac:dyDescent="0.25">
@@ -8552,10 +8553,10 @@
         <v>340</v>
       </c>
       <c r="B330" t="s">
+        <v>656</v>
+      </c>
+      <c r="C330" t="s">
         <v>657</v>
-      </c>
-      <c r="C330" t="s">
-        <v>658</v>
       </c>
     </row>
     <row r="331" spans="1:3" x14ac:dyDescent="0.25">
@@ -8563,10 +8564,10 @@
         <v>341</v>
       </c>
       <c r="B331" t="s">
+        <v>658</v>
+      </c>
+      <c r="C331" t="s">
         <v>659</v>
-      </c>
-      <c r="C331" t="s">
-        <v>660</v>
       </c>
     </row>
     <row r="332" spans="1:3" x14ac:dyDescent="0.25">
@@ -8574,10 +8575,10 @@
         <v>342</v>
       </c>
       <c r="B332" t="s">
+        <v>660</v>
+      </c>
+      <c r="C332" t="s">
         <v>661</v>
-      </c>
-      <c r="C332" t="s">
-        <v>662</v>
       </c>
     </row>
     <row r="333" spans="1:3" x14ac:dyDescent="0.25">
@@ -8585,10 +8586,10 @@
         <v>343</v>
       </c>
       <c r="B333" t="s">
+        <v>662</v>
+      </c>
+      <c r="C333" t="s">
         <v>663</v>
-      </c>
-      <c r="C333" t="s">
-        <v>664</v>
       </c>
     </row>
     <row r="334" spans="1:3" x14ac:dyDescent="0.25">
@@ -8596,10 +8597,10 @@
         <v>344</v>
       </c>
       <c r="B334" t="s">
+        <v>664</v>
+      </c>
+      <c r="C334" t="s">
         <v>665</v>
-      </c>
-      <c r="C334" t="s">
-        <v>666</v>
       </c>
     </row>
     <row r="335" spans="1:3" x14ac:dyDescent="0.25">
@@ -8607,10 +8608,10 @@
         <v>345</v>
       </c>
       <c r="B335" t="s">
+        <v>666</v>
+      </c>
+      <c r="C335" t="s">
         <v>667</v>
-      </c>
-      <c r="C335" t="s">
-        <v>668</v>
       </c>
     </row>
     <row r="336" spans="1:3" x14ac:dyDescent="0.25">
@@ -8618,10 +8619,10 @@
         <v>346</v>
       </c>
       <c r="B336" t="s">
+        <v>668</v>
+      </c>
+      <c r="C336" t="s">
         <v>669</v>
-      </c>
-      <c r="C336" t="s">
-        <v>670</v>
       </c>
     </row>
     <row r="337" spans="1:3" x14ac:dyDescent="0.25">
@@ -8629,10 +8630,10 @@
         <v>347</v>
       </c>
       <c r="B337" t="s">
+        <v>670</v>
+      </c>
+      <c r="C337" t="s">
         <v>671</v>
-      </c>
-      <c r="C337" t="s">
-        <v>672</v>
       </c>
     </row>
     <row r="338" spans="1:3" x14ac:dyDescent="0.25">
@@ -8640,10 +8641,10 @@
         <v>348</v>
       </c>
       <c r="B338" t="s">
+        <v>672</v>
+      </c>
+      <c r="C338" t="s">
         <v>673</v>
-      </c>
-      <c r="C338" t="s">
-        <v>674</v>
       </c>
     </row>
     <row r="339" spans="1:3" x14ac:dyDescent="0.25">
@@ -8651,10 +8652,10 @@
         <v>349</v>
       </c>
       <c r="B339" t="s">
+        <v>674</v>
+      </c>
+      <c r="C339" t="s">
         <v>675</v>
-      </c>
-      <c r="C339" t="s">
-        <v>676</v>
       </c>
     </row>
     <row r="340" spans="1:3" x14ac:dyDescent="0.25">
@@ -8662,10 +8663,10 @@
         <v>350</v>
       </c>
       <c r="B340" t="s">
+        <v>676</v>
+      </c>
+      <c r="C340" t="s">
         <v>677</v>
-      </c>
-      <c r="C340" t="s">
-        <v>678</v>
       </c>
     </row>
     <row r="341" spans="1:3" x14ac:dyDescent="0.25">
@@ -8673,10 +8674,10 @@
         <v>351</v>
       </c>
       <c r="B341" t="s">
+        <v>678</v>
+      </c>
+      <c r="C341" t="s">
         <v>679</v>
-      </c>
-      <c r="C341" t="s">
-        <v>680</v>
       </c>
     </row>
     <row r="342" spans="1:3" x14ac:dyDescent="0.25">
@@ -8684,10 +8685,10 @@
         <v>352</v>
       </c>
       <c r="B342" t="s">
+        <v>680</v>
+      </c>
+      <c r="C342" t="s">
         <v>681</v>
-      </c>
-      <c r="C342" t="s">
-        <v>682</v>
       </c>
     </row>
     <row r="343" spans="1:3" x14ac:dyDescent="0.25">
@@ -8695,10 +8696,10 @@
         <v>353</v>
       </c>
       <c r="B343" t="s">
+        <v>682</v>
+      </c>
+      <c r="C343" t="s">
         <v>683</v>
-      </c>
-      <c r="C343" t="s">
-        <v>684</v>
       </c>
     </row>
     <row r="344" spans="1:3" x14ac:dyDescent="0.25">
@@ -8706,10 +8707,10 @@
         <v>354</v>
       </c>
       <c r="B344" t="s">
+        <v>684</v>
+      </c>
+      <c r="C344" t="s">
         <v>685</v>
-      </c>
-      <c r="C344" t="s">
-        <v>686</v>
       </c>
     </row>
     <row r="345" spans="1:3" x14ac:dyDescent="0.25">
@@ -8717,10 +8718,10 @@
         <v>355</v>
       </c>
       <c r="B345" t="s">
+        <v>686</v>
+      </c>
+      <c r="C345" t="s">
         <v>687</v>
-      </c>
-      <c r="C345" t="s">
-        <v>688</v>
       </c>
     </row>
     <row r="346" spans="1:3" x14ac:dyDescent="0.25">
@@ -8728,10 +8729,10 @@
         <v>356</v>
       </c>
       <c r="B346" t="s">
+        <v>688</v>
+      </c>
+      <c r="C346" t="s">
         <v>689</v>
-      </c>
-      <c r="C346" t="s">
-        <v>690</v>
       </c>
     </row>
     <row r="347" spans="1:3" x14ac:dyDescent="0.25">
@@ -8739,10 +8740,10 @@
         <v>357</v>
       </c>
       <c r="B347" t="s">
+        <v>690</v>
+      </c>
+      <c r="C347" t="s">
         <v>691</v>
-      </c>
-      <c r="C347" t="s">
-        <v>692</v>
       </c>
     </row>
     <row r="348" spans="1:3" x14ac:dyDescent="0.25">
@@ -8750,10 +8751,10 @@
         <v>358</v>
       </c>
       <c r="B348" t="s">
+        <v>692</v>
+      </c>
+      <c r="C348" t="s">
         <v>693</v>
-      </c>
-      <c r="C348" t="s">
-        <v>694</v>
       </c>
     </row>
     <row r="349" spans="1:3" x14ac:dyDescent="0.25">
@@ -8761,10 +8762,10 @@
         <v>359</v>
       </c>
       <c r="B349" t="s">
+        <v>694</v>
+      </c>
+      <c r="C349" t="s">
         <v>695</v>
-      </c>
-      <c r="C349" t="s">
-        <v>696</v>
       </c>
     </row>
     <row r="350" spans="1:3" x14ac:dyDescent="0.25">
@@ -8772,10 +8773,10 @@
         <v>360</v>
       </c>
       <c r="B350" t="s">
+        <v>696</v>
+      </c>
+      <c r="C350" t="s">
         <v>697</v>
-      </c>
-      <c r="C350" t="s">
-        <v>698</v>
       </c>
     </row>
     <row r="351" spans="1:3" x14ac:dyDescent="0.25">
@@ -8783,10 +8784,10 @@
         <v>361</v>
       </c>
       <c r="B351" t="s">
+        <v>698</v>
+      </c>
+      <c r="C351" t="s">
         <v>699</v>
-      </c>
-      <c r="C351" t="s">
-        <v>700</v>
       </c>
     </row>
     <row r="352" spans="1:3" x14ac:dyDescent="0.25">
@@ -8794,10 +8795,10 @@
         <v>362</v>
       </c>
       <c r="B352" t="s">
+        <v>700</v>
+      </c>
+      <c r="C352" t="s">
         <v>701</v>
-      </c>
-      <c r="C352" t="s">
-        <v>702</v>
       </c>
     </row>
     <row r="353" spans="1:3" x14ac:dyDescent="0.25">
@@ -8805,10 +8806,10 @@
         <v>363</v>
       </c>
       <c r="B353" t="s">
+        <v>702</v>
+      </c>
+      <c r="C353" t="s">
         <v>703</v>
-      </c>
-      <c r="C353" t="s">
-        <v>704</v>
       </c>
     </row>
     <row r="354" spans="1:3" x14ac:dyDescent="0.25">
@@ -8816,10 +8817,10 @@
         <v>364</v>
       </c>
       <c r="B354" t="s">
+        <v>704</v>
+      </c>
+      <c r="C354" t="s">
         <v>705</v>
-      </c>
-      <c r="C354" t="s">
-        <v>706</v>
       </c>
     </row>
     <row r="355" spans="1:3" x14ac:dyDescent="0.25">
@@ -8827,10 +8828,10 @@
         <v>365</v>
       </c>
       <c r="B355" t="s">
+        <v>706</v>
+      </c>
+      <c r="C355" t="s">
         <v>707</v>
-      </c>
-      <c r="C355" t="s">
-        <v>708</v>
       </c>
     </row>
     <row r="356" spans="1:3" x14ac:dyDescent="0.25">
@@ -8838,10 +8839,10 @@
         <v>366</v>
       </c>
       <c r="B356" t="s">
+        <v>708</v>
+      </c>
+      <c r="C356" t="s">
         <v>709</v>
-      </c>
-      <c r="C356" t="s">
-        <v>710</v>
       </c>
     </row>
     <row r="357" spans="1:3" x14ac:dyDescent="0.25">
@@ -8849,10 +8850,10 @@
         <v>367</v>
       </c>
       <c r="B357" t="s">
+        <v>710</v>
+      </c>
+      <c r="C357" t="s">
         <v>711</v>
-      </c>
-      <c r="C357" t="s">
-        <v>712</v>
       </c>
     </row>
     <row r="358" spans="1:3" x14ac:dyDescent="0.25">
@@ -8860,10 +8861,10 @@
         <v>368</v>
       </c>
       <c r="B358" t="s">
+        <v>712</v>
+      </c>
+      <c r="C358" t="s">
         <v>713</v>
-      </c>
-      <c r="C358" t="s">
-        <v>714</v>
       </c>
     </row>
     <row r="359" spans="1:3" x14ac:dyDescent="0.25">
@@ -8871,10 +8872,10 @@
         <v>369</v>
       </c>
       <c r="B359" t="s">
+        <v>714</v>
+      </c>
+      <c r="C359" t="s">
         <v>715</v>
-      </c>
-      <c r="C359" t="s">
-        <v>716</v>
       </c>
     </row>
     <row r="360" spans="1:3" x14ac:dyDescent="0.25">
@@ -8882,10 +8883,10 @@
         <v>370</v>
       </c>
       <c r="B360" t="s">
+        <v>716</v>
+      </c>
+      <c r="C360" t="s">
         <v>717</v>
-      </c>
-      <c r="C360" t="s">
-        <v>718</v>
       </c>
     </row>
     <row r="361" spans="1:3" x14ac:dyDescent="0.25">
@@ -8893,10 +8894,10 @@
         <v>371</v>
       </c>
       <c r="B361" t="s">
+        <v>718</v>
+      </c>
+      <c r="C361" t="s">
         <v>719</v>
-      </c>
-      <c r="C361" t="s">
-        <v>720</v>
       </c>
     </row>
     <row r="362" spans="1:3" x14ac:dyDescent="0.25">
@@ -8904,10 +8905,10 @@
         <v>372</v>
       </c>
       <c r="B362" t="s">
+        <v>720</v>
+      </c>
+      <c r="C362" t="s">
         <v>721</v>
-      </c>
-      <c r="C362" t="s">
-        <v>722</v>
       </c>
     </row>
     <row r="363" spans="1:3" x14ac:dyDescent="0.25">
@@ -8915,10 +8916,10 @@
         <v>373</v>
       </c>
       <c r="B363" t="s">
+        <v>722</v>
+      </c>
+      <c r="C363" t="s">
         <v>723</v>
-      </c>
-      <c r="C363" t="s">
-        <v>724</v>
       </c>
     </row>
     <row r="364" spans="1:3" x14ac:dyDescent="0.25">
@@ -8926,10 +8927,10 @@
         <v>374</v>
       </c>
       <c r="B364" t="s">
+        <v>724</v>
+      </c>
+      <c r="C364" t="s">
         <v>725</v>
-      </c>
-      <c r="C364" t="s">
-        <v>726</v>
       </c>
     </row>
     <row r="365" spans="1:3" x14ac:dyDescent="0.25">
@@ -8937,10 +8938,10 @@
         <v>375</v>
       </c>
       <c r="B365" t="s">
+        <v>726</v>
+      </c>
+      <c r="C365" t="s">
         <v>727</v>
-      </c>
-      <c r="C365" t="s">
-        <v>728</v>
       </c>
     </row>
     <row r="366" spans="1:3" x14ac:dyDescent="0.25">
@@ -8948,10 +8949,10 @@
         <v>376</v>
       </c>
       <c r="B366" t="s">
+        <v>728</v>
+      </c>
+      <c r="C366" t="s">
         <v>729</v>
-      </c>
-      <c r="C366" t="s">
-        <v>730</v>
       </c>
     </row>
     <row r="367" spans="1:3" x14ac:dyDescent="0.25">
@@ -8959,10 +8960,10 @@
         <v>377</v>
       </c>
       <c r="B367" t="s">
+        <v>730</v>
+      </c>
+      <c r="C367" t="s">
         <v>731</v>
-      </c>
-      <c r="C367" t="s">
-        <v>732</v>
       </c>
     </row>
     <row r="368" spans="1:3" x14ac:dyDescent="0.25">
@@ -8970,10 +8971,10 @@
         <v>378</v>
       </c>
       <c r="B368" t="s">
+        <v>732</v>
+      </c>
+      <c r="C368" t="s">
         <v>733</v>
-      </c>
-      <c r="C368" t="s">
-        <v>734</v>
       </c>
     </row>
     <row r="369" spans="1:3" x14ac:dyDescent="0.25">
@@ -8981,10 +8982,10 @@
         <v>379</v>
       </c>
       <c r="B369" t="s">
+        <v>734</v>
+      </c>
+      <c r="C369" t="s">
         <v>735</v>
-      </c>
-      <c r="C369" t="s">
-        <v>736</v>
       </c>
     </row>
     <row r="370" spans="1:3" x14ac:dyDescent="0.25">
@@ -8992,10 +8993,10 @@
         <v>380</v>
       </c>
       <c r="B370" t="s">
+        <v>736</v>
+      </c>
+      <c r="C370" t="s">
         <v>737</v>
-      </c>
-      <c r="C370" t="s">
-        <v>738</v>
       </c>
     </row>
     <row r="371" spans="1:3" x14ac:dyDescent="0.25">
@@ -9003,10 +9004,10 @@
         <v>381</v>
       </c>
       <c r="B371" t="s">
+        <v>738</v>
+      </c>
+      <c r="C371" t="s">
         <v>739</v>
-      </c>
-      <c r="C371" t="s">
-        <v>740</v>
       </c>
     </row>
     <row r="372" spans="1:3" x14ac:dyDescent="0.25">
@@ -9014,10 +9015,10 @@
         <v>382</v>
       </c>
       <c r="B372" t="s">
+        <v>740</v>
+      </c>
+      <c r="C372" t="s">
         <v>741</v>
-      </c>
-      <c r="C372" t="s">
-        <v>742</v>
       </c>
     </row>
     <row r="373" spans="1:3" x14ac:dyDescent="0.25">
@@ -9025,10 +9026,10 @@
         <v>383</v>
       </c>
       <c r="B373" t="s">
+        <v>742</v>
+      </c>
+      <c r="C373" t="s">
         <v>743</v>
-      </c>
-      <c r="C373" t="s">
-        <v>744</v>
       </c>
     </row>
     <row r="374" spans="1:3" x14ac:dyDescent="0.25">
@@ -9036,10 +9037,10 @@
         <v>384</v>
       </c>
       <c r="B374" t="s">
+        <v>744</v>
+      </c>
+      <c r="C374" t="s">
         <v>745</v>
-      </c>
-      <c r="C374" t="s">
-        <v>746</v>
       </c>
     </row>
     <row r="375" spans="1:3" x14ac:dyDescent="0.25">
@@ -9047,10 +9048,10 @@
         <v>385</v>
       </c>
       <c r="B375" t="s">
+        <v>746</v>
+      </c>
+      <c r="C375" t="s">
         <v>747</v>
-      </c>
-      <c r="C375" t="s">
-        <v>748</v>
       </c>
     </row>
     <row r="376" spans="1:3" x14ac:dyDescent="0.25">
@@ -9058,10 +9059,10 @@
         <v>386</v>
       </c>
       <c r="B376" t="s">
+        <v>748</v>
+      </c>
+      <c r="C376" t="s">
         <v>749</v>
-      </c>
-      <c r="C376" t="s">
-        <v>750</v>
       </c>
     </row>
     <row r="377" spans="1:3" x14ac:dyDescent="0.25">
@@ -9069,10 +9070,10 @@
         <v>387</v>
       </c>
       <c r="B377" t="s">
+        <v>750</v>
+      </c>
+      <c r="C377" t="s">
         <v>751</v>
-      </c>
-      <c r="C377" t="s">
-        <v>752</v>
       </c>
     </row>
     <row r="378" spans="1:3" x14ac:dyDescent="0.25">
@@ -9080,10 +9081,10 @@
         <v>388</v>
       </c>
       <c r="B378" t="s">
+        <v>752</v>
+      </c>
+      <c r="C378" t="s">
         <v>753</v>
-      </c>
-      <c r="C378" t="s">
-        <v>754</v>
       </c>
     </row>
     <row r="379" spans="1:3" x14ac:dyDescent="0.25">
@@ -9091,10 +9092,10 @@
         <v>389</v>
       </c>
       <c r="B379" t="s">
+        <v>754</v>
+      </c>
+      <c r="C379" t="s">
         <v>755</v>
-      </c>
-      <c r="C379" t="s">
-        <v>756</v>
       </c>
     </row>
     <row r="380" spans="1:3" x14ac:dyDescent="0.25">
@@ -9102,10 +9103,10 @@
         <v>390</v>
       </c>
       <c r="B380" t="s">
+        <v>756</v>
+      </c>
+      <c r="C380" t="s">
         <v>757</v>
-      </c>
-      <c r="C380" t="s">
-        <v>758</v>
       </c>
     </row>
     <row r="381" spans="1:3" x14ac:dyDescent="0.25">
@@ -9113,10 +9114,10 @@
         <v>391</v>
       </c>
       <c r="B381" t="s">
+        <v>758</v>
+      </c>
+      <c r="C381" t="s">
         <v>759</v>
-      </c>
-      <c r="C381" t="s">
-        <v>760</v>
       </c>
     </row>
     <row r="382" spans="1:3" x14ac:dyDescent="0.25">
@@ -9124,10 +9125,10 @@
         <v>392</v>
       </c>
       <c r="B382" t="s">
+        <v>760</v>
+      </c>
+      <c r="C382" t="s">
         <v>761</v>
-      </c>
-      <c r="C382" t="s">
-        <v>762</v>
       </c>
     </row>
     <row r="383" spans="1:3" x14ac:dyDescent="0.25">
@@ -9135,10 +9136,10 @@
         <v>393</v>
       </c>
       <c r="B383" t="s">
+        <v>762</v>
+      </c>
+      <c r="C383" t="s">
         <v>763</v>
-      </c>
-      <c r="C383" t="s">
-        <v>764</v>
       </c>
     </row>
     <row r="384" spans="1:3" x14ac:dyDescent="0.25">
@@ -9146,10 +9147,10 @@
         <v>394</v>
       </c>
       <c r="B384" t="s">
+        <v>764</v>
+      </c>
+      <c r="C384" t="s">
         <v>765</v>
-      </c>
-      <c r="C384" t="s">
-        <v>766</v>
       </c>
     </row>
     <row r="385" spans="1:3" x14ac:dyDescent="0.25">
@@ -9157,10 +9158,10 @@
         <v>395</v>
       </c>
       <c r="B385" t="s">
+        <v>766</v>
+      </c>
+      <c r="C385" t="s">
         <v>767</v>
-      </c>
-      <c r="C385" t="s">
-        <v>768</v>
       </c>
     </row>
     <row r="386" spans="1:3" x14ac:dyDescent="0.25">
@@ -9168,10 +9169,10 @@
         <v>396</v>
       </c>
       <c r="B386" t="s">
+        <v>768</v>
+      </c>
+      <c r="C386" t="s">
         <v>769</v>
-      </c>
-      <c r="C386" t="s">
-        <v>770</v>
       </c>
     </row>
     <row r="387" spans="1:3" x14ac:dyDescent="0.25">
@@ -9179,10 +9180,10 @@
         <v>397</v>
       </c>
       <c r="B387" t="s">
+        <v>770</v>
+      </c>
+      <c r="C387" t="s">
         <v>771</v>
-      </c>
-      <c r="C387" t="s">
-        <v>772</v>
       </c>
     </row>
     <row r="388" spans="1:3" x14ac:dyDescent="0.25">
@@ -9190,10 +9191,10 @@
         <v>398</v>
       </c>
       <c r="B388" t="s">
+        <v>772</v>
+      </c>
+      <c r="C388" t="s">
         <v>773</v>
-      </c>
-      <c r="C388" t="s">
-        <v>774</v>
       </c>
     </row>
     <row r="389" spans="1:3" x14ac:dyDescent="0.25">
@@ -9201,10 +9202,10 @@
         <v>399</v>
       </c>
       <c r="B389" t="s">
+        <v>774</v>
+      </c>
+      <c r="C389" t="s">
         <v>775</v>
-      </c>
-      <c r="C389" t="s">
-        <v>776</v>
       </c>
     </row>
     <row r="390" spans="1:3" x14ac:dyDescent="0.25">
@@ -9212,10 +9213,10 @@
         <v>400</v>
       </c>
       <c r="B390" t="s">
+        <v>776</v>
+      </c>
+      <c r="C390" t="s">
         <v>777</v>
-      </c>
-      <c r="C390" t="s">
-        <v>778</v>
       </c>
     </row>
     <row r="391" spans="1:3" x14ac:dyDescent="0.25">
@@ -9223,10 +9224,10 @@
         <v>401</v>
       </c>
       <c r="B391" t="s">
+        <v>778</v>
+      </c>
+      <c r="C391" t="s">
         <v>779</v>
-      </c>
-      <c r="C391" t="s">
-        <v>780</v>
       </c>
     </row>
     <row r="392" spans="1:3" ht="19.2" x14ac:dyDescent="0.45">
@@ -9234,10 +9235,10 @@
         <v>402</v>
       </c>
       <c r="B392" t="s">
+        <v>780</v>
+      </c>
+      <c r="C392" t="s">
         <v>781</v>
-      </c>
-      <c r="C392" t="s">
-        <v>782</v>
       </c>
     </row>
     <row r="393" spans="1:3" x14ac:dyDescent="0.25">
@@ -9245,10 +9246,10 @@
         <v>403</v>
       </c>
       <c r="B393" t="s">
+        <v>782</v>
+      </c>
+      <c r="C393" t="s">
         <v>783</v>
-      </c>
-      <c r="C393" t="s">
-        <v>784</v>
       </c>
     </row>
     <row r="394" spans="1:3" x14ac:dyDescent="0.25">
@@ -9256,10 +9257,10 @@
         <v>404</v>
       </c>
       <c r="B394" t="s">
+        <v>784</v>
+      </c>
+      <c r="C394" t="s">
         <v>785</v>
-      </c>
-      <c r="C394" t="s">
-        <v>786</v>
       </c>
     </row>
     <row r="395" spans="1:3" x14ac:dyDescent="0.25">
@@ -9267,10 +9268,10 @@
         <v>405</v>
       </c>
       <c r="B395" t="s">
+        <v>786</v>
+      </c>
+      <c r="C395" t="s">
         <v>787</v>
-      </c>
-      <c r="C395" t="s">
-        <v>788</v>
       </c>
     </row>
     <row r="396" spans="1:3" x14ac:dyDescent="0.25">
@@ -9278,10 +9279,10 @@
         <v>406</v>
       </c>
       <c r="B396" t="s">
+        <v>788</v>
+      </c>
+      <c r="C396" t="s">
         <v>789</v>
-      </c>
-      <c r="C396" t="s">
-        <v>790</v>
       </c>
     </row>
     <row r="397" spans="1:3" x14ac:dyDescent="0.25">
@@ -9289,10 +9290,10 @@
         <v>407</v>
       </c>
       <c r="B397" t="s">
+        <v>790</v>
+      </c>
+      <c r="C397" t="s">
         <v>791</v>
-      </c>
-      <c r="C397" t="s">
-        <v>792</v>
       </c>
     </row>
     <row r="398" spans="1:3" x14ac:dyDescent="0.25">
@@ -9300,10 +9301,10 @@
         <v>408</v>
       </c>
       <c r="B398" t="s">
+        <v>792</v>
+      </c>
+      <c r="C398" t="s">
         <v>793</v>
-      </c>
-      <c r="C398" t="s">
-        <v>794</v>
       </c>
     </row>
     <row r="399" spans="1:3" x14ac:dyDescent="0.25">
@@ -9311,10 +9312,10 @@
         <v>409</v>
       </c>
       <c r="B399" t="s">
+        <v>794</v>
+      </c>
+      <c r="C399" t="s">
         <v>795</v>
-      </c>
-      <c r="C399" t="s">
-        <v>796</v>
       </c>
     </row>
     <row r="400" spans="1:3" x14ac:dyDescent="0.25">
@@ -9322,10 +9323,10 @@
         <v>410</v>
       </c>
       <c r="B400" t="s">
+        <v>796</v>
+      </c>
+      <c r="C400" t="s">
         <v>797</v>
-      </c>
-      <c r="C400" t="s">
-        <v>798</v>
       </c>
     </row>
     <row r="401" spans="1:3" x14ac:dyDescent="0.25">
@@ -9333,10 +9334,10 @@
         <v>411</v>
       </c>
       <c r="B401" t="s">
+        <v>798</v>
+      </c>
+      <c r="C401" t="s">
         <v>799</v>
-      </c>
-      <c r="C401" t="s">
-        <v>800</v>
       </c>
     </row>
     <row r="402" spans="1:3" x14ac:dyDescent="0.25">
@@ -9344,10 +9345,10 @@
         <v>412</v>
       </c>
       <c r="B402" t="s">
+        <v>800</v>
+      </c>
+      <c r="C402" t="s">
         <v>801</v>
-      </c>
-      <c r="C402" t="s">
-        <v>802</v>
       </c>
     </row>
     <row r="403" spans="1:3" x14ac:dyDescent="0.25">
@@ -9355,10 +9356,10 @@
         <v>413</v>
       </c>
       <c r="B403" t="s">
+        <v>802</v>
+      </c>
+      <c r="C403" t="s">
         <v>803</v>
-      </c>
-      <c r="C403" t="s">
-        <v>804</v>
       </c>
     </row>
     <row r="404" spans="1:3" x14ac:dyDescent="0.25">
@@ -9366,10 +9367,10 @@
         <v>414</v>
       </c>
       <c r="B404" t="s">
+        <v>804</v>
+      </c>
+      <c r="C404" t="s">
         <v>805</v>
-      </c>
-      <c r="C404" t="s">
-        <v>806</v>
       </c>
     </row>
     <row r="405" spans="1:3" x14ac:dyDescent="0.25">
@@ -9377,10 +9378,10 @@
         <v>415</v>
       </c>
       <c r="B405" t="s">
+        <v>806</v>
+      </c>
+      <c r="C405" t="s">
         <v>807</v>
-      </c>
-      <c r="C405" t="s">
-        <v>808</v>
       </c>
     </row>
     <row r="406" spans="1:3" x14ac:dyDescent="0.25">
@@ -9388,10 +9389,10 @@
         <v>416</v>
       </c>
       <c r="B406" t="s">
+        <v>808</v>
+      </c>
+      <c r="C406" t="s">
         <v>809</v>
-      </c>
-      <c r="C406" t="s">
-        <v>810</v>
       </c>
     </row>
     <row r="407" spans="1:3" x14ac:dyDescent="0.25">
@@ -9399,10 +9400,10 @@
         <v>417</v>
       </c>
       <c r="B407" t="s">
+        <v>810</v>
+      </c>
+      <c r="C407" t="s">
         <v>811</v>
-      </c>
-      <c r="C407" t="s">
-        <v>812</v>
       </c>
     </row>
     <row r="408" spans="1:3" x14ac:dyDescent="0.25">
@@ -9410,10 +9411,10 @@
         <v>418</v>
       </c>
       <c r="B408" t="s">
+        <v>812</v>
+      </c>
+      <c r="C408" t="s">
         <v>813</v>
-      </c>
-      <c r="C408" t="s">
-        <v>814</v>
       </c>
     </row>
     <row r="409" spans="1:3" x14ac:dyDescent="0.25">
@@ -9421,10 +9422,10 @@
         <v>419</v>
       </c>
       <c r="B409" t="s">
+        <v>814</v>
+      </c>
+      <c r="C409" t="s">
         <v>815</v>
-      </c>
-      <c r="C409" t="s">
-        <v>816</v>
       </c>
     </row>
     <row r="410" spans="1:3" x14ac:dyDescent="0.25">
@@ -9432,10 +9433,10 @@
         <v>420</v>
       </c>
       <c r="B410" t="s">
+        <v>816</v>
+      </c>
+      <c r="C410" t="s">
         <v>817</v>
-      </c>
-      <c r="C410" t="s">
-        <v>818</v>
       </c>
     </row>
     <row r="411" spans="1:3" x14ac:dyDescent="0.25">
@@ -9443,10 +9444,10 @@
         <v>421</v>
       </c>
       <c r="B411" t="s">
+        <v>818</v>
+      </c>
+      <c r="C411" t="s">
         <v>819</v>
-      </c>
-      <c r="C411" t="s">
-        <v>820</v>
       </c>
     </row>
     <row r="412" spans="1:3" x14ac:dyDescent="0.25">
@@ -9454,10 +9455,10 @@
         <v>422</v>
       </c>
       <c r="B412" t="s">
+        <v>820</v>
+      </c>
+      <c r="C412" t="s">
         <v>821</v>
-      </c>
-      <c r="C412" t="s">
-        <v>822</v>
       </c>
     </row>
     <row r="413" spans="1:3" x14ac:dyDescent="0.25">
@@ -9465,10 +9466,10 @@
         <v>423</v>
       </c>
       <c r="B413" t="s">
+        <v>822</v>
+      </c>
+      <c r="C413" t="s">
         <v>823</v>
-      </c>
-      <c r="C413" t="s">
-        <v>824</v>
       </c>
     </row>
     <row r="414" spans="1:3" x14ac:dyDescent="0.25">
@@ -9476,10 +9477,10 @@
         <v>424</v>
       </c>
       <c r="B414" t="s">
+        <v>824</v>
+      </c>
+      <c r="C414" t="s">
         <v>825</v>
-      </c>
-      <c r="C414" t="s">
-        <v>826</v>
       </c>
     </row>
     <row r="415" spans="1:3" x14ac:dyDescent="0.25">
@@ -9487,10 +9488,10 @@
         <v>425</v>
       </c>
       <c r="B415" t="s">
+        <v>826</v>
+      </c>
+      <c r="C415" t="s">
         <v>827</v>
-      </c>
-      <c r="C415" t="s">
-        <v>828</v>
       </c>
     </row>
     <row r="416" spans="1:3" x14ac:dyDescent="0.25">
@@ -9498,10 +9499,10 @@
         <v>426</v>
       </c>
       <c r="B416" t="s">
+        <v>828</v>
+      </c>
+      <c r="C416" t="s">
         <v>829</v>
-      </c>
-      <c r="C416" t="s">
-        <v>830</v>
       </c>
     </row>
     <row r="417" spans="1:3" x14ac:dyDescent="0.25">
@@ -9509,10 +9510,10 @@
         <v>427</v>
       </c>
       <c r="B417" t="s">
+        <v>830</v>
+      </c>
+      <c r="C417" t="s">
         <v>831</v>
-      </c>
-      <c r="C417" t="s">
-        <v>832</v>
       </c>
     </row>
     <row r="418" spans="1:3" x14ac:dyDescent="0.25">
@@ -9520,10 +9521,10 @@
         <v>428</v>
       </c>
       <c r="B418" t="s">
+        <v>832</v>
+      </c>
+      <c r="C418" t="s">
         <v>833</v>
-      </c>
-      <c r="C418" t="s">
-        <v>834</v>
       </c>
     </row>
     <row r="419" spans="1:3" x14ac:dyDescent="0.25">
@@ -9531,10 +9532,10 @@
         <v>429</v>
       </c>
       <c r="B419" t="s">
+        <v>834</v>
+      </c>
+      <c r="C419" t="s">
         <v>835</v>
-      </c>
-      <c r="C419" t="s">
-        <v>836</v>
       </c>
     </row>
     <row r="420" spans="1:3" x14ac:dyDescent="0.25">
@@ -9542,10 +9543,10 @@
         <v>430</v>
       </c>
       <c r="B420" t="s">
+        <v>836</v>
+      </c>
+      <c r="C420" t="s">
         <v>837</v>
-      </c>
-      <c r="C420" t="s">
-        <v>838</v>
       </c>
     </row>
     <row r="421" spans="1:3" x14ac:dyDescent="0.25">
@@ -9553,10 +9554,10 @@
         <v>431</v>
       </c>
       <c r="B421" t="s">
+        <v>838</v>
+      </c>
+      <c r="C421" t="s">
         <v>839</v>
-      </c>
-      <c r="C421" t="s">
-        <v>840</v>
       </c>
     </row>
     <row r="422" spans="1:3" x14ac:dyDescent="0.25">
@@ -9564,10 +9565,10 @@
         <v>432</v>
       </c>
       <c r="B422" t="s">
+        <v>840</v>
+      </c>
+      <c r="C422" t="s">
         <v>841</v>
-      </c>
-      <c r="C422" t="s">
-        <v>842</v>
       </c>
     </row>
     <row r="423" spans="1:3" x14ac:dyDescent="0.25">
@@ -9575,10 +9576,10 @@
         <v>433</v>
       </c>
       <c r="B423" t="s">
+        <v>842</v>
+      </c>
+      <c r="C423" t="s">
         <v>843</v>
-      </c>
-      <c r="C423" t="s">
-        <v>844</v>
       </c>
     </row>
     <row r="424" spans="1:3" x14ac:dyDescent="0.25">
@@ -9586,10 +9587,10 @@
         <v>434</v>
       </c>
       <c r="B424" t="s">
+        <v>844</v>
+      </c>
+      <c r="C424" t="s">
         <v>845</v>
-      </c>
-      <c r="C424" t="s">
-        <v>846</v>
       </c>
     </row>
     <row r="425" spans="1:3" x14ac:dyDescent="0.25">
@@ -9597,10 +9598,10 @@
         <v>435</v>
       </c>
       <c r="B425" t="s">
+        <v>846</v>
+      </c>
+      <c r="C425" t="s">
         <v>847</v>
-      </c>
-      <c r="C425" t="s">
-        <v>848</v>
       </c>
     </row>
     <row r="426" spans="1:3" x14ac:dyDescent="0.25">
@@ -9608,10 +9609,10 @@
         <v>436</v>
       </c>
       <c r="B426" t="s">
+        <v>848</v>
+      </c>
+      <c r="C426" t="s">
         <v>849</v>
-      </c>
-      <c r="C426" t="s">
-        <v>850</v>
       </c>
     </row>
     <row r="427" spans="1:3" x14ac:dyDescent="0.25">
@@ -9619,10 +9620,10 @@
         <v>437</v>
       </c>
       <c r="B427" t="s">
+        <v>850</v>
+      </c>
+      <c r="C427" t="s">
         <v>851</v>
-      </c>
-      <c r="C427" t="s">
-        <v>852</v>
       </c>
     </row>
     <row r="428" spans="1:3" x14ac:dyDescent="0.25">
@@ -9630,10 +9631,10 @@
         <v>438</v>
       </c>
       <c r="B428" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="C428" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
     </row>
     <row r="429" spans="1:3" x14ac:dyDescent="0.25">
@@ -9641,10 +9642,10 @@
         <v>439</v>
       </c>
       <c r="B429" t="s">
+        <v>853</v>
+      </c>
+      <c r="C429" t="s">
         <v>854</v>
-      </c>
-      <c r="C429" t="s">
-        <v>855</v>
       </c>
     </row>
     <row r="430" spans="1:3" x14ac:dyDescent="0.25">
@@ -9652,10 +9653,10 @@
         <v>440</v>
       </c>
       <c r="B430" t="s">
+        <v>855</v>
+      </c>
+      <c r="C430" t="s">
         <v>856</v>
-      </c>
-      <c r="C430" t="s">
-        <v>857</v>
       </c>
     </row>
     <row r="431" spans="1:3" x14ac:dyDescent="0.25">
@@ -9663,10 +9664,10 @@
         <v>441</v>
       </c>
       <c r="B431" t="s">
+        <v>857</v>
+      </c>
+      <c r="C431" t="s">
         <v>858</v>
-      </c>
-      <c r="C431" t="s">
-        <v>859</v>
       </c>
     </row>
     <row r="432" spans="1:3" x14ac:dyDescent="0.25">
@@ -9674,10 +9675,10 @@
         <v>442</v>
       </c>
       <c r="B432" t="s">
+        <v>859</v>
+      </c>
+      <c r="C432" t="s">
         <v>860</v>
-      </c>
-      <c r="C432" t="s">
-        <v>861</v>
       </c>
     </row>
     <row r="433" spans="1:3" x14ac:dyDescent="0.25">
@@ -9685,10 +9686,10 @@
         <v>443</v>
       </c>
       <c r="B433" t="s">
+        <v>861</v>
+      </c>
+      <c r="C433" t="s">
         <v>862</v>
-      </c>
-      <c r="C433" t="s">
-        <v>863</v>
       </c>
     </row>
     <row r="434" spans="1:3" x14ac:dyDescent="0.25">
@@ -9696,10 +9697,10 @@
         <v>444</v>
       </c>
       <c r="B434" t="s">
+        <v>863</v>
+      </c>
+      <c r="C434" t="s">
         <v>864</v>
-      </c>
-      <c r="C434" t="s">
-        <v>865</v>
       </c>
     </row>
     <row r="435" spans="1:3" x14ac:dyDescent="0.25">
@@ -9707,10 +9708,10 @@
         <v>445</v>
       </c>
       <c r="B435" t="s">
+        <v>865</v>
+      </c>
+      <c r="C435" t="s">
         <v>866</v>
-      </c>
-      <c r="C435" t="s">
-        <v>867</v>
       </c>
     </row>
     <row r="436" spans="1:3" x14ac:dyDescent="0.25">
@@ -9718,10 +9719,10 @@
         <v>446</v>
       </c>
       <c r="B436" t="s">
+        <v>867</v>
+      </c>
+      <c r="C436" t="s">
         <v>868</v>
-      </c>
-      <c r="C436" t="s">
-        <v>869</v>
       </c>
     </row>
     <row r="437" spans="1:3" x14ac:dyDescent="0.25">
@@ -9729,10 +9730,10 @@
         <v>447</v>
       </c>
       <c r="B437" t="s">
+        <v>869</v>
+      </c>
+      <c r="C437" t="s">
         <v>870</v>
-      </c>
-      <c r="C437" t="s">
-        <v>871</v>
       </c>
     </row>
     <row r="438" spans="1:3" x14ac:dyDescent="0.25">
@@ -9740,10 +9741,10 @@
         <v>448</v>
       </c>
       <c r="B438" t="s">
+        <v>871</v>
+      </c>
+      <c r="C438" t="s">
         <v>872</v>
-      </c>
-      <c r="C438" t="s">
-        <v>873</v>
       </c>
     </row>
     <row r="439" spans="1:3" x14ac:dyDescent="0.25">
@@ -9751,10 +9752,10 @@
         <v>449</v>
       </c>
       <c r="B439" t="s">
+        <v>873</v>
+      </c>
+      <c r="C439" t="s">
         <v>874</v>
-      </c>
-      <c r="C439" t="s">
-        <v>875</v>
       </c>
     </row>
     <row r="440" spans="1:3" x14ac:dyDescent="0.25">
@@ -9762,10 +9763,10 @@
         <v>450</v>
       </c>
       <c r="B440" t="s">
+        <v>875</v>
+      </c>
+      <c r="C440" t="s">
         <v>876</v>
-      </c>
-      <c r="C440" t="s">
-        <v>877</v>
       </c>
     </row>
     <row r="441" spans="1:3" x14ac:dyDescent="0.25">
@@ -9773,10 +9774,10 @@
         <v>451</v>
       </c>
       <c r="B441" t="s">
+        <v>877</v>
+      </c>
+      <c r="C441" t="s">
         <v>878</v>
-      </c>
-      <c r="C441" t="s">
-        <v>879</v>
       </c>
     </row>
     <row r="442" spans="1:3" x14ac:dyDescent="0.25">
@@ -9784,10 +9785,10 @@
         <v>452</v>
       </c>
       <c r="B442" t="s">
+        <v>879</v>
+      </c>
+      <c r="C442" t="s">
         <v>880</v>
-      </c>
-      <c r="C442" t="s">
-        <v>881</v>
       </c>
     </row>
     <row r="443" spans="1:3" x14ac:dyDescent="0.25">
@@ -9795,10 +9796,10 @@
         <v>453</v>
       </c>
       <c r="B443" t="s">
+        <v>881</v>
+      </c>
+      <c r="C443" t="s">
         <v>882</v>
-      </c>
-      <c r="C443" t="s">
-        <v>883</v>
       </c>
     </row>
     <row r="444" spans="1:3" x14ac:dyDescent="0.25">
@@ -9806,10 +9807,10 @@
         <v>455</v>
       </c>
       <c r="B444" t="s">
+        <v>883</v>
+      </c>
+      <c r="C444" t="s">
         <v>884</v>
-      </c>
-      <c r="C444" t="s">
-        <v>885</v>
       </c>
     </row>
     <row r="445" spans="1:3" x14ac:dyDescent="0.25">
@@ -9817,10 +9818,10 @@
         <v>456</v>
       </c>
       <c r="B445" t="s">
+        <v>885</v>
+      </c>
+      <c r="C445" t="s">
         <v>886</v>
-      </c>
-      <c r="C445" t="s">
-        <v>887</v>
       </c>
     </row>
     <row r="446" spans="1:3" x14ac:dyDescent="0.25">
@@ -9828,10 +9829,10 @@
         <v>457</v>
       </c>
       <c r="B446" t="s">
+        <v>887</v>
+      </c>
+      <c r="C446" t="s">
         <v>888</v>
-      </c>
-      <c r="C446" t="s">
-        <v>889</v>
       </c>
     </row>
     <row r="447" spans="1:3" x14ac:dyDescent="0.25">
@@ -9839,10 +9840,10 @@
         <v>458</v>
       </c>
       <c r="B447" t="s">
+        <v>889</v>
+      </c>
+      <c r="C447" t="s">
         <v>890</v>
-      </c>
-      <c r="C447" t="s">
-        <v>891</v>
       </c>
     </row>
     <row r="448" spans="1:3" x14ac:dyDescent="0.25">
@@ -9850,10 +9851,10 @@
         <v>459</v>
       </c>
       <c r="B448" t="s">
+        <v>891</v>
+      </c>
+      <c r="C448" t="s">
         <v>892</v>
-      </c>
-      <c r="C448" t="s">
-        <v>893</v>
       </c>
     </row>
     <row r="449" spans="1:3" x14ac:dyDescent="0.25">
@@ -9861,10 +9862,10 @@
         <v>460</v>
       </c>
       <c r="B449" t="s">
+        <v>893</v>
+      </c>
+      <c r="C449" t="s">
         <v>894</v>
-      </c>
-      <c r="C449" t="s">
-        <v>895</v>
       </c>
     </row>
     <row r="450" spans="1:3" x14ac:dyDescent="0.25">
@@ -9872,10 +9873,10 @@
         <v>461</v>
       </c>
       <c r="B450" t="s">
+        <v>895</v>
+      </c>
+      <c r="C450" t="s">
         <v>896</v>
-      </c>
-      <c r="C450" t="s">
-        <v>897</v>
       </c>
     </row>
     <row r="451" spans="1:3" x14ac:dyDescent="0.25">
@@ -9883,10 +9884,10 @@
         <v>462</v>
       </c>
       <c r="B451" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="C451" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
     </row>
     <row r="452" spans="1:3" x14ac:dyDescent="0.25">
@@ -9894,10 +9895,10 @@
         <v>463</v>
       </c>
       <c r="B452" t="s">
+        <v>898</v>
+      </c>
+      <c r="C452" t="s">
         <v>899</v>
-      </c>
-      <c r="C452" t="s">
-        <v>900</v>
       </c>
     </row>
     <row r="453" spans="1:3" x14ac:dyDescent="0.25">
@@ -9905,10 +9906,10 @@
         <v>464</v>
       </c>
       <c r="B453" t="s">
+        <v>900</v>
+      </c>
+      <c r="C453" t="s">
         <v>901</v>
-      </c>
-      <c r="C453" t="s">
-        <v>902</v>
       </c>
     </row>
     <row r="454" spans="1:3" x14ac:dyDescent="0.25">
@@ -9916,10 +9917,10 @@
         <v>465</v>
       </c>
       <c r="B454" t="s">
+        <v>902</v>
+      </c>
+      <c r="C454" t="s">
         <v>903</v>
-      </c>
-      <c r="C454" t="s">
-        <v>904</v>
       </c>
     </row>
     <row r="455" spans="1:3" x14ac:dyDescent="0.25">
@@ -9927,10 +9928,10 @@
         <v>466</v>
       </c>
       <c r="B455" t="s">
+        <v>904</v>
+      </c>
+      <c r="C455" t="s">
         <v>905</v>
-      </c>
-      <c r="C455" t="s">
-        <v>906</v>
       </c>
     </row>
     <row r="456" spans="1:3" x14ac:dyDescent="0.25">
@@ -9938,10 +9939,10 @@
         <v>467</v>
       </c>
       <c r="B456" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="C456" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
     </row>
     <row r="457" spans="1:3" x14ac:dyDescent="0.25">
@@ -9949,10 +9950,10 @@
         <v>468</v>
       </c>
       <c r="B457" t="s">
+        <v>907</v>
+      </c>
+      <c r="C457" t="s">
         <v>908</v>
-      </c>
-      <c r="C457" t="s">
-        <v>909</v>
       </c>
     </row>
     <row r="458" spans="1:3" x14ac:dyDescent="0.25">
@@ -9960,10 +9961,10 @@
         <v>469</v>
       </c>
       <c r="B458" t="s">
+        <v>909</v>
+      </c>
+      <c r="C458" t="s">
         <v>910</v>
-      </c>
-      <c r="C458" t="s">
-        <v>911</v>
       </c>
     </row>
     <row r="459" spans="1:3" x14ac:dyDescent="0.25">
@@ -9971,10 +9972,10 @@
         <v>470</v>
       </c>
       <c r="B459" t="s">
+        <v>911</v>
+      </c>
+      <c r="C459" t="s">
         <v>912</v>
-      </c>
-      <c r="C459" t="s">
-        <v>913</v>
       </c>
     </row>
     <row r="460" spans="1:3" x14ac:dyDescent="0.25">
@@ -9982,7 +9983,7 @@
         <v>471</v>
       </c>
       <c r="B460" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
     </row>
     <row r="461" spans="1:3" x14ac:dyDescent="0.25">
@@ -9990,10 +9991,10 @@
         <v>472</v>
       </c>
       <c r="B461" t="s">
+        <v>914</v>
+      </c>
+      <c r="C461" t="s">
         <v>915</v>
-      </c>
-      <c r="C461" t="s">
-        <v>916</v>
       </c>
     </row>
     <row r="462" spans="1:3" x14ac:dyDescent="0.25">
@@ -10001,10 +10002,10 @@
         <v>473</v>
       </c>
       <c r="B462" t="s">
+        <v>916</v>
+      </c>
+      <c r="C462" t="s">
         <v>917</v>
-      </c>
-      <c r="C462" t="s">
-        <v>918</v>
       </c>
     </row>
     <row r="463" spans="1:3" x14ac:dyDescent="0.25">
@@ -10012,10 +10013,10 @@
         <v>474</v>
       </c>
       <c r="B463" t="s">
+        <v>918</v>
+      </c>
+      <c r="C463" t="s">
         <v>919</v>
-      </c>
-      <c r="C463" t="s">
-        <v>920</v>
       </c>
     </row>
     <row r="464" spans="1:3" x14ac:dyDescent="0.25">
@@ -10023,10 +10024,10 @@
         <v>475</v>
       </c>
       <c r="B464" t="s">
+        <v>920</v>
+      </c>
+      <c r="C464" t="s">
         <v>921</v>
-      </c>
-      <c r="C464" t="s">
-        <v>922</v>
       </c>
     </row>
     <row r="465" spans="1:3" x14ac:dyDescent="0.25">
@@ -10034,10 +10035,10 @@
         <v>476</v>
       </c>
       <c r="B465" t="s">
+        <v>922</v>
+      </c>
+      <c r="C465" t="s">
         <v>923</v>
-      </c>
-      <c r="C465" t="s">
-        <v>924</v>
       </c>
     </row>
     <row r="466" spans="1:3" x14ac:dyDescent="0.25">
@@ -10045,10 +10046,10 @@
         <v>477</v>
       </c>
       <c r="B466" t="s">
+        <v>924</v>
+      </c>
+      <c r="C466" t="s">
         <v>925</v>
-      </c>
-      <c r="C466" t="s">
-        <v>926</v>
       </c>
     </row>
     <row r="467" spans="1:3" x14ac:dyDescent="0.25">
@@ -10056,10 +10057,10 @@
         <v>478</v>
       </c>
       <c r="B467" t="s">
+        <v>926</v>
+      </c>
+      <c r="C467" t="s">
         <v>927</v>
-      </c>
-      <c r="C467" t="s">
-        <v>928</v>
       </c>
     </row>
     <row r="468" spans="1:3" x14ac:dyDescent="0.25">
@@ -10067,10 +10068,10 @@
         <v>479</v>
       </c>
       <c r="B468" t="s">
+        <v>928</v>
+      </c>
+      <c r="C468" t="s">
         <v>929</v>
-      </c>
-      <c r="C468" t="s">
-        <v>930</v>
       </c>
     </row>
     <row r="469" spans="1:3" x14ac:dyDescent="0.25">
@@ -10078,10 +10079,10 @@
         <v>480</v>
       </c>
       <c r="B469" t="s">
+        <v>930</v>
+      </c>
+      <c r="C469" t="s">
         <v>931</v>
-      </c>
-      <c r="C469" t="s">
-        <v>932</v>
       </c>
     </row>
     <row r="470" spans="1:3" x14ac:dyDescent="0.25">
@@ -10089,10 +10090,10 @@
         <v>481</v>
       </c>
       <c r="B470" t="s">
+        <v>932</v>
+      </c>
+      <c r="C470" t="s">
         <v>933</v>
-      </c>
-      <c r="C470" t="s">
-        <v>934</v>
       </c>
     </row>
     <row r="471" spans="1:3" x14ac:dyDescent="0.25">
@@ -10100,10 +10101,10 @@
         <v>482</v>
       </c>
       <c r="B471" t="s">
+        <v>934</v>
+      </c>
+      <c r="C471" t="s">
         <v>935</v>
-      </c>
-      <c r="C471" t="s">
-        <v>936</v>
       </c>
     </row>
     <row r="472" spans="1:3" x14ac:dyDescent="0.25">
@@ -10111,10 +10112,10 @@
         <v>483</v>
       </c>
       <c r="B472" t="s">
+        <v>936</v>
+      </c>
+      <c r="C472" t="s">
         <v>937</v>
-      </c>
-      <c r="C472" t="s">
-        <v>938</v>
       </c>
     </row>
     <row r="473" spans="1:3" ht="19.2" x14ac:dyDescent="0.45">
@@ -10122,10 +10123,10 @@
         <v>484</v>
       </c>
       <c r="B473" t="s">
+        <v>938</v>
+      </c>
+      <c r="C473" t="s">
         <v>939</v>
-      </c>
-      <c r="C473" t="s">
-        <v>940</v>
       </c>
     </row>
     <row r="474" spans="1:3" x14ac:dyDescent="0.25">
@@ -10133,10 +10134,10 @@
         <v>485</v>
       </c>
       <c r="B474" t="s">
+        <v>940</v>
+      </c>
+      <c r="C474" t="s">
         <v>941</v>
-      </c>
-      <c r="C474" t="s">
-        <v>942</v>
       </c>
     </row>
     <row r="475" spans="1:3" x14ac:dyDescent="0.25">
@@ -10144,10 +10145,10 @@
         <v>486</v>
       </c>
       <c r="B475" t="s">
+        <v>942</v>
+      </c>
+      <c r="C475" t="s">
         <v>943</v>
-      </c>
-      <c r="C475" t="s">
-        <v>944</v>
       </c>
     </row>
     <row r="476" spans="1:3" x14ac:dyDescent="0.25">
@@ -10155,10 +10156,10 @@
         <v>487</v>
       </c>
       <c r="B476" t="s">
+        <v>944</v>
+      </c>
+      <c r="C476" t="s">
         <v>945</v>
-      </c>
-      <c r="C476" t="s">
-        <v>946</v>
       </c>
     </row>
     <row r="477" spans="1:3" x14ac:dyDescent="0.25">
@@ -10166,10 +10167,10 @@
         <v>488</v>
       </c>
       <c r="B477" t="s">
+        <v>946</v>
+      </c>
+      <c r="C477" t="s">
         <v>947</v>
-      </c>
-      <c r="C477" t="s">
-        <v>948</v>
       </c>
     </row>
     <row r="478" spans="1:3" x14ac:dyDescent="0.25">
@@ -10177,10 +10178,10 @@
         <v>489</v>
       </c>
       <c r="B478" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="C478" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
     </row>
     <row r="479" spans="1:3" x14ac:dyDescent="0.25">
@@ -10188,10 +10189,10 @@
         <v>490</v>
       </c>
       <c r="B479" t="s">
+        <v>949</v>
+      </c>
+      <c r="C479" t="s">
         <v>950</v>
-      </c>
-      <c r="C479" t="s">
-        <v>951</v>
       </c>
     </row>
     <row r="480" spans="1:3" x14ac:dyDescent="0.25">
@@ -10199,10 +10200,10 @@
         <v>491</v>
       </c>
       <c r="B480" t="s">
+        <v>951</v>
+      </c>
+      <c r="C480" t="s">
         <v>952</v>
-      </c>
-      <c r="C480" t="s">
-        <v>953</v>
       </c>
     </row>
     <row r="481" spans="1:3" x14ac:dyDescent="0.25">
@@ -10210,10 +10211,10 @@
         <v>492</v>
       </c>
       <c r="B481" t="s">
+        <v>953</v>
+      </c>
+      <c r="C481" t="s">
         <v>954</v>
-      </c>
-      <c r="C481" t="s">
-        <v>955</v>
       </c>
     </row>
     <row r="482" spans="1:3" x14ac:dyDescent="0.25">
@@ -10221,10 +10222,10 @@
         <v>493</v>
       </c>
       <c r="B482" t="s">
+        <v>955</v>
+      </c>
+      <c r="C482" t="s">
         <v>956</v>
-      </c>
-      <c r="C482" t="s">
-        <v>957</v>
       </c>
     </row>
     <row r="483" spans="1:3" x14ac:dyDescent="0.25">
@@ -10232,10 +10233,10 @@
         <v>494</v>
       </c>
       <c r="B483" t="s">
+        <v>957</v>
+      </c>
+      <c r="C483" t="s">
         <v>958</v>
-      </c>
-      <c r="C483" t="s">
-        <v>959</v>
       </c>
     </row>
     <row r="484" spans="1:3" x14ac:dyDescent="0.25">
@@ -10243,10 +10244,10 @@
         <v>496</v>
       </c>
       <c r="B484" t="s">
+        <v>959</v>
+      </c>
+      <c r="C484" t="s">
         <v>960</v>
-      </c>
-      <c r="C484" t="s">
-        <v>961</v>
       </c>
     </row>
     <row r="485" spans="1:3" x14ac:dyDescent="0.25">
@@ -10254,10 +10255,10 @@
         <v>497</v>
       </c>
       <c r="B485" t="s">
+        <v>961</v>
+      </c>
+      <c r="C485" t="s">
         <v>962</v>
-      </c>
-      <c r="C485" t="s">
-        <v>963</v>
       </c>
     </row>
     <row r="486" spans="1:3" x14ac:dyDescent="0.25">
@@ -10265,10 +10266,10 @@
         <v>498</v>
       </c>
       <c r="B486" t="s">
+        <v>963</v>
+      </c>
+      <c r="C486" t="s">
         <v>964</v>
-      </c>
-      <c r="C486" t="s">
-        <v>965</v>
       </c>
     </row>
     <row r="487" spans="1:3" x14ac:dyDescent="0.25">
@@ -10276,10 +10277,10 @@
         <v>499</v>
       </c>
       <c r="B487" t="s">
+        <v>965</v>
+      </c>
+      <c r="C487" t="s">
         <v>966</v>
-      </c>
-      <c r="C487" t="s">
-        <v>967</v>
       </c>
     </row>
     <row r="488" spans="1:3" x14ac:dyDescent="0.25">
@@ -10287,10 +10288,10 @@
         <v>500</v>
       </c>
       <c r="B488" t="s">
+        <v>967</v>
+      </c>
+      <c r="C488" t="s">
         <v>968</v>
-      </c>
-      <c r="C488" t="s">
-        <v>969</v>
       </c>
     </row>
     <row r="489" spans="1:3" x14ac:dyDescent="0.25">
@@ -10298,10 +10299,10 @@
         <v>501</v>
       </c>
       <c r="B489" t="s">
+        <v>969</v>
+      </c>
+      <c r="C489" t="s">
         <v>970</v>
-      </c>
-      <c r="C489" t="s">
-        <v>971</v>
       </c>
     </row>
     <row r="490" spans="1:3" x14ac:dyDescent="0.25">
@@ -10309,10 +10310,10 @@
         <v>502</v>
       </c>
       <c r="B490" t="s">
+        <v>971</v>
+      </c>
+      <c r="C490" t="s">
         <v>972</v>
-      </c>
-      <c r="C490" t="s">
-        <v>973</v>
       </c>
     </row>
     <row r="491" spans="1:3" x14ac:dyDescent="0.25">
@@ -10320,10 +10321,10 @@
         <v>503</v>
       </c>
       <c r="B491" t="s">
+        <v>973</v>
+      </c>
+      <c r="C491" t="s">
         <v>974</v>
-      </c>
-      <c r="C491" t="s">
-        <v>975</v>
       </c>
     </row>
     <row r="492" spans="1:3" x14ac:dyDescent="0.25">
@@ -10331,10 +10332,10 @@
         <v>504</v>
       </c>
       <c r="B492" t="s">
+        <v>975</v>
+      </c>
+      <c r="C492" t="s">
         <v>976</v>
-      </c>
-      <c r="C492" t="s">
-        <v>977</v>
       </c>
     </row>
     <row r="493" spans="1:3" x14ac:dyDescent="0.25">
@@ -10342,10 +10343,10 @@
         <v>505</v>
       </c>
       <c r="B493" t="s">
+        <v>977</v>
+      </c>
+      <c r="C493" t="s">
         <v>978</v>
-      </c>
-      <c r="C493" t="s">
-        <v>979</v>
       </c>
     </row>
     <row r="494" spans="1:3" x14ac:dyDescent="0.25">
@@ -10353,10 +10354,10 @@
         <v>506</v>
       </c>
       <c r="B494" t="s">
+        <v>979</v>
+      </c>
+      <c r="C494" t="s">
         <v>980</v>
-      </c>
-      <c r="C494" t="s">
-        <v>981</v>
       </c>
     </row>
     <row r="495" spans="1:3" x14ac:dyDescent="0.25">
@@ -10364,10 +10365,10 @@
         <v>507</v>
       </c>
       <c r="B495" t="s">
+        <v>981</v>
+      </c>
+      <c r="C495" t="s">
         <v>982</v>
-      </c>
-      <c r="C495" t="s">
-        <v>983</v>
       </c>
     </row>
     <row r="496" spans="1:3" x14ac:dyDescent="0.25">
@@ -10375,10 +10376,10 @@
         <v>508</v>
       </c>
       <c r="B496" t="s">
+        <v>983</v>
+      </c>
+      <c r="C496" t="s">
         <v>984</v>
-      </c>
-      <c r="C496" t="s">
-        <v>985</v>
       </c>
     </row>
     <row r="497" spans="1:3" x14ac:dyDescent="0.25">
@@ -10386,10 +10387,10 @@
         <v>509</v>
       </c>
       <c r="B497" t="s">
+        <v>985</v>
+      </c>
+      <c r="C497" t="s">
         <v>986</v>
-      </c>
-      <c r="C497" t="s">
-        <v>987</v>
       </c>
     </row>
     <row r="498" spans="1:3" x14ac:dyDescent="0.25">
@@ -10397,10 +10398,10 @@
         <v>510</v>
       </c>
       <c r="B498" t="s">
+        <v>987</v>
+      </c>
+      <c r="C498" t="s">
         <v>988</v>
-      </c>
-      <c r="C498" t="s">
-        <v>989</v>
       </c>
     </row>
     <row r="499" spans="1:3" x14ac:dyDescent="0.25">
@@ -10408,7 +10409,7 @@
         <v>511</v>
       </c>
       <c r="B499" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
     </row>
     <row r="500" spans="1:3" x14ac:dyDescent="0.25">
@@ -10416,10 +10417,10 @@
         <v>512</v>
       </c>
       <c r="B500" t="s">
+        <v>990</v>
+      </c>
+      <c r="C500" t="s">
         <v>991</v>
-      </c>
-      <c r="C500" t="s">
-        <v>992</v>
       </c>
     </row>
     <row r="501" spans="1:3" x14ac:dyDescent="0.25">
@@ -10427,10 +10428,10 @@
         <v>513</v>
       </c>
       <c r="B501" t="s">
+        <v>992</v>
+      </c>
+      <c r="C501" t="s">
         <v>993</v>
-      </c>
-      <c r="C501" t="s">
-        <v>994</v>
       </c>
     </row>
     <row r="502" spans="1:3" x14ac:dyDescent="0.25">
@@ -10438,10 +10439,10 @@
         <v>514</v>
       </c>
       <c r="B502" t="s">
+        <v>994</v>
+      </c>
+      <c r="C502" t="s">
         <v>995</v>
-      </c>
-      <c r="C502" t="s">
-        <v>996</v>
       </c>
     </row>
     <row r="503" spans="1:3" x14ac:dyDescent="0.25">
@@ -10449,10 +10450,10 @@
         <v>515</v>
       </c>
       <c r="B503" t="s">
+        <v>996</v>
+      </c>
+      <c r="C503" t="s">
         <v>997</v>
-      </c>
-      <c r="C503" t="s">
-        <v>998</v>
       </c>
     </row>
     <row r="504" spans="1:3" x14ac:dyDescent="0.25">
@@ -10460,10 +10461,10 @@
         <v>516</v>
       </c>
       <c r="B504" t="s">
+        <v>998</v>
+      </c>
+      <c r="C504" t="s">
         <v>999</v>
-      </c>
-      <c r="C504" t="s">
-        <v>1000</v>
       </c>
     </row>
     <row r="505" spans="1:3" x14ac:dyDescent="0.25">
@@ -10471,10 +10472,10 @@
         <v>517</v>
       </c>
       <c r="B505" t="s">
+        <v>1000</v>
+      </c>
+      <c r="C505" t="s">
         <v>1001</v>
-      </c>
-      <c r="C505" t="s">
-        <v>1002</v>
       </c>
     </row>
     <row r="506" spans="1:3" x14ac:dyDescent="0.25">
@@ -10482,10 +10483,10 @@
         <v>518</v>
       </c>
       <c r="B506" t="s">
+        <v>1002</v>
+      </c>
+      <c r="C506" t="s">
         <v>1003</v>
-      </c>
-      <c r="C506" t="s">
-        <v>1004</v>
       </c>
     </row>
     <row r="507" spans="1:3" x14ac:dyDescent="0.25">
@@ -10493,10 +10494,10 @@
         <v>519</v>
       </c>
       <c r="B507" t="s">
+        <v>1004</v>
+      </c>
+      <c r="C507" t="s">
         <v>1005</v>
-      </c>
-      <c r="C507" t="s">
-        <v>1006</v>
       </c>
     </row>
     <row r="508" spans="1:3" x14ac:dyDescent="0.25">
@@ -10504,10 +10505,10 @@
         <v>520</v>
       </c>
       <c r="B508" t="s">
+        <v>1006</v>
+      </c>
+      <c r="C508" t="s">
         <v>1007</v>
-      </c>
-      <c r="C508" t="s">
-        <v>1008</v>
       </c>
     </row>
     <row r="509" spans="1:3" x14ac:dyDescent="0.25">
@@ -10515,10 +10516,10 @@
         <v>521</v>
       </c>
       <c r="B509" t="s">
+        <v>1008</v>
+      </c>
+      <c r="C509" t="s">
         <v>1009</v>
-      </c>
-      <c r="C509" t="s">
-        <v>1010</v>
       </c>
     </row>
     <row r="510" spans="1:3" x14ac:dyDescent="0.25">
@@ -10526,10 +10527,10 @@
         <v>522</v>
       </c>
       <c r="B510" t="s">
+        <v>1010</v>
+      </c>
+      <c r="C510" t="s">
         <v>1011</v>
-      </c>
-      <c r="C510" t="s">
-        <v>1012</v>
       </c>
     </row>
     <row r="511" spans="1:3" x14ac:dyDescent="0.25">
@@ -10537,10 +10538,10 @@
         <v>523</v>
       </c>
       <c r="B511" t="s">
+        <v>1012</v>
+      </c>
+      <c r="C511" t="s">
         <v>1013</v>
-      </c>
-      <c r="C511" t="s">
-        <v>1014</v>
       </c>
     </row>
     <row r="512" spans="1:3" x14ac:dyDescent="0.25">
@@ -10548,10 +10549,10 @@
         <v>524</v>
       </c>
       <c r="B512" t="s">
+        <v>1014</v>
+      </c>
+      <c r="C512" t="s">
         <v>1015</v>
-      </c>
-      <c r="C512" t="s">
-        <v>1016</v>
       </c>
     </row>
     <row r="513" spans="1:3" x14ac:dyDescent="0.25">
@@ -10559,10 +10560,10 @@
         <v>525</v>
       </c>
       <c r="B513" t="s">
+        <v>1016</v>
+      </c>
+      <c r="C513" t="s">
         <v>1017</v>
-      </c>
-      <c r="C513" t="s">
-        <v>1018</v>
       </c>
     </row>
     <row r="514" spans="1:3" x14ac:dyDescent="0.25">
@@ -10570,10 +10571,10 @@
         <v>526</v>
       </c>
       <c r="B514" t="s">
+        <v>1018</v>
+      </c>
+      <c r="C514" t="s">
         <v>1019</v>
-      </c>
-      <c r="C514" t="s">
-        <v>1020</v>
       </c>
     </row>
     <row r="515" spans="1:3" x14ac:dyDescent="0.25">
@@ -10581,10 +10582,10 @@
         <v>527</v>
       </c>
       <c r="B515" t="s">
+        <v>1020</v>
+      </c>
+      <c r="C515" t="s">
         <v>1021</v>
-      </c>
-      <c r="C515" t="s">
-        <v>1022</v>
       </c>
     </row>
     <row r="516" spans="1:3" x14ac:dyDescent="0.25">
@@ -10592,10 +10593,10 @@
         <v>528</v>
       </c>
       <c r="B516" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="C516" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="517" spans="1:3" x14ac:dyDescent="0.25">
@@ -10603,10 +10604,10 @@
         <v>529</v>
       </c>
       <c r="B517" t="s">
+        <v>1023</v>
+      </c>
+      <c r="C517" t="s">
         <v>1024</v>
-      </c>
-      <c r="C517" t="s">
-        <v>1025</v>
       </c>
     </row>
     <row r="518" spans="1:3" x14ac:dyDescent="0.25">
@@ -10614,10 +10615,10 @@
         <v>530</v>
       </c>
       <c r="B518" t="s">
+        <v>1025</v>
+      </c>
+      <c r="C518" t="s">
         <v>1026</v>
-      </c>
-      <c r="C518" t="s">
-        <v>1027</v>
       </c>
     </row>
     <row r="519" spans="1:3" x14ac:dyDescent="0.25">
@@ -10625,10 +10626,10 @@
         <v>531</v>
       </c>
       <c r="B519" t="s">
+        <v>1027</v>
+      </c>
+      <c r="C519" t="s">
         <v>1028</v>
-      </c>
-      <c r="C519" t="s">
-        <v>1029</v>
       </c>
     </row>
     <row r="520" spans="1:3" x14ac:dyDescent="0.25">
@@ -10636,10 +10637,10 @@
         <v>532</v>
       </c>
       <c r="B520" t="s">
+        <v>1029</v>
+      </c>
+      <c r="C520" t="s">
         <v>1030</v>
-      </c>
-      <c r="C520" t="s">
-        <v>1031</v>
       </c>
     </row>
     <row r="521" spans="1:3" x14ac:dyDescent="0.25">
@@ -10647,10 +10648,10 @@
         <v>533</v>
       </c>
       <c r="B521" t="s">
+        <v>1031</v>
+      </c>
+      <c r="C521" t="s">
         <v>1032</v>
-      </c>
-      <c r="C521" t="s">
-        <v>1033</v>
       </c>
     </row>
     <row r="522" spans="1:3" x14ac:dyDescent="0.25">
@@ -10658,10 +10659,10 @@
         <v>534</v>
       </c>
       <c r="B522" t="s">
+        <v>1033</v>
+      </c>
+      <c r="C522" t="s">
         <v>1034</v>
-      </c>
-      <c r="C522" t="s">
-        <v>1035</v>
       </c>
     </row>
     <row r="523" spans="1:3" x14ac:dyDescent="0.25">
@@ -10669,10 +10670,10 @@
         <v>535</v>
       </c>
       <c r="B523" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C523" t="s">
         <v>1036</v>
-      </c>
-      <c r="C523" t="s">
-        <v>1037</v>
       </c>
     </row>
     <row r="524" spans="1:3" x14ac:dyDescent="0.25">
@@ -10680,10 +10681,10 @@
         <v>536</v>
       </c>
       <c r="B524" t="s">
+        <v>1037</v>
+      </c>
+      <c r="C524" t="s">
         <v>1038</v>
-      </c>
-      <c r="C524" t="s">
-        <v>1039</v>
       </c>
     </row>
     <row r="525" spans="1:3" x14ac:dyDescent="0.25">
@@ -10691,10 +10692,10 @@
         <v>537</v>
       </c>
       <c r="B525" t="s">
+        <v>1039</v>
+      </c>
+      <c r="C525" t="s">
         <v>1040</v>
-      </c>
-      <c r="C525" t="s">
-        <v>1041</v>
       </c>
     </row>
     <row r="526" spans="1:3" x14ac:dyDescent="0.25">
@@ -10702,10 +10703,10 @@
         <v>538</v>
       </c>
       <c r="B526" t="s">
+        <v>1041</v>
+      </c>
+      <c r="C526" t="s">
         <v>1042</v>
-      </c>
-      <c r="C526" t="s">
-        <v>1043</v>
       </c>
     </row>
     <row r="527" spans="1:3" x14ac:dyDescent="0.25">
@@ -10713,10 +10714,10 @@
         <v>539</v>
       </c>
       <c r="B527" t="s">
+        <v>1043</v>
+      </c>
+      <c r="C527" t="s">
         <v>1044</v>
-      </c>
-      <c r="C527" t="s">
-        <v>1045</v>
       </c>
     </row>
     <row r="528" spans="1:3" x14ac:dyDescent="0.25">
@@ -10724,10 +10725,10 @@
         <v>540</v>
       </c>
       <c r="B528" t="s">
+        <v>1045</v>
+      </c>
+      <c r="C528" t="s">
         <v>1046</v>
-      </c>
-      <c r="C528" t="s">
-        <v>1047</v>
       </c>
     </row>
     <row r="529" spans="1:3" x14ac:dyDescent="0.25">
@@ -10735,10 +10736,10 @@
         <v>542</v>
       </c>
       <c r="B529" t="s">
+        <v>1047</v>
+      </c>
+      <c r="C529" t="s">
         <v>1048</v>
-      </c>
-      <c r="C529" t="s">
-        <v>1049</v>
       </c>
     </row>
     <row r="530" spans="1:3" x14ac:dyDescent="0.25">
@@ -10746,10 +10747,10 @@
         <v>543</v>
       </c>
       <c r="B530" t="s">
+        <v>1049</v>
+      </c>
+      <c r="C530" t="s">
         <v>1050</v>
-      </c>
-      <c r="C530" t="s">
-        <v>1051</v>
       </c>
     </row>
     <row r="531" spans="1:3" x14ac:dyDescent="0.25">
@@ -10757,10 +10758,10 @@
         <v>545</v>
       </c>
       <c r="B531" t="s">
+        <v>1051</v>
+      </c>
+      <c r="C531" t="s">
         <v>1052</v>
-      </c>
-      <c r="C531" t="s">
-        <v>1053</v>
       </c>
     </row>
     <row r="532" spans="1:3" x14ac:dyDescent="0.25">
@@ -10768,10 +10769,10 @@
         <v>546</v>
       </c>
       <c r="B532" t="s">
+        <v>1053</v>
+      </c>
+      <c r="C532" t="s">
         <v>1054</v>
-      </c>
-      <c r="C532" t="s">
-        <v>1055</v>
       </c>
     </row>
     <row r="533" spans="1:3" x14ac:dyDescent="0.25">
@@ -10779,10 +10780,10 @@
         <v>547</v>
       </c>
       <c r="B533" t="s">
+        <v>1055</v>
+      </c>
+      <c r="C533" t="s">
         <v>1056</v>
-      </c>
-      <c r="C533" t="s">
-        <v>1057</v>
       </c>
     </row>
     <row r="534" spans="1:3" x14ac:dyDescent="0.25">
@@ -10790,10 +10791,10 @@
         <v>548</v>
       </c>
       <c r="B534" t="s">
+        <v>1057</v>
+      </c>
+      <c r="C534" t="s">
         <v>1058</v>
-      </c>
-      <c r="C534" t="s">
-        <v>1059</v>
       </c>
     </row>
     <row r="535" spans="1:3" x14ac:dyDescent="0.25">
@@ -10801,10 +10802,10 @@
         <v>549</v>
       </c>
       <c r="B535" t="s">
+        <v>1059</v>
+      </c>
+      <c r="C535" t="s">
         <v>1060</v>
-      </c>
-      <c r="C535" t="s">
-        <v>1061</v>
       </c>
     </row>
     <row r="536" spans="1:3" x14ac:dyDescent="0.25">
@@ -10812,10 +10813,10 @@
         <v>550</v>
       </c>
       <c r="B536" t="s">
+        <v>1061</v>
+      </c>
+      <c r="C536" t="s">
         <v>1062</v>
-      </c>
-      <c r="C536" t="s">
-        <v>1063</v>
       </c>
     </row>
     <row r="537" spans="1:3" x14ac:dyDescent="0.25">
@@ -10823,10 +10824,10 @@
         <v>551</v>
       </c>
       <c r="B537" t="s">
+        <v>1063</v>
+      </c>
+      <c r="C537" t="s">
         <v>1064</v>
-      </c>
-      <c r="C537" t="s">
-        <v>1065</v>
       </c>
     </row>
     <row r="538" spans="1:3" x14ac:dyDescent="0.25">
@@ -10834,10 +10835,10 @@
         <v>552</v>
       </c>
       <c r="B538" t="s">
+        <v>1065</v>
+      </c>
+      <c r="C538" t="s">
         <v>1066</v>
-      </c>
-      <c r="C538" t="s">
-        <v>1067</v>
       </c>
     </row>
     <row r="539" spans="1:3" x14ac:dyDescent="0.25">
@@ -10845,10 +10846,10 @@
         <v>553</v>
       </c>
       <c r="B539" t="s">
+        <v>1067</v>
+      </c>
+      <c r="C539" t="s">
         <v>1068</v>
-      </c>
-      <c r="C539" t="s">
-        <v>1069</v>
       </c>
     </row>
     <row r="540" spans="1:3" x14ac:dyDescent="0.25">
@@ -10856,10 +10857,10 @@
         <v>554</v>
       </c>
       <c r="B540" t="s">
+        <v>1069</v>
+      </c>
+      <c r="C540" t="s">
         <v>1070</v>
-      </c>
-      <c r="C540" t="s">
-        <v>1071</v>
       </c>
     </row>
     <row r="541" spans="1:3" x14ac:dyDescent="0.25">
@@ -10867,10 +10868,10 @@
         <v>555</v>
       </c>
       <c r="B541" t="s">
+        <v>1071</v>
+      </c>
+      <c r="C541" t="s">
         <v>1072</v>
-      </c>
-      <c r="C541" t="s">
-        <v>1073</v>
       </c>
     </row>
     <row r="542" spans="1:3" x14ac:dyDescent="0.25">
@@ -10878,10 +10879,10 @@
         <v>556</v>
       </c>
       <c r="B542" t="s">
+        <v>1073</v>
+      </c>
+      <c r="C542" t="s">
         <v>1074</v>
-      </c>
-      <c r="C542" t="s">
-        <v>1075</v>
       </c>
     </row>
     <row r="543" spans="1:3" x14ac:dyDescent="0.25">
@@ -10889,10 +10890,10 @@
         <v>557</v>
       </c>
       <c r="B543" t="s">
+        <v>1075</v>
+      </c>
+      <c r="C543" t="s">
         <v>1076</v>
-      </c>
-      <c r="C543" t="s">
-        <v>1077</v>
       </c>
     </row>
     <row r="544" spans="1:3" x14ac:dyDescent="0.25">
@@ -10900,10 +10901,10 @@
         <v>558</v>
       </c>
       <c r="B544" t="s">
+        <v>1077</v>
+      </c>
+      <c r="C544" t="s">
         <v>1078</v>
-      </c>
-      <c r="C544" t="s">
-        <v>1079</v>
       </c>
     </row>
     <row r="545" spans="1:3" x14ac:dyDescent="0.25">
@@ -10911,10 +10912,10 @@
         <v>559</v>
       </c>
       <c r="B545" t="s">
+        <v>1079</v>
+      </c>
+      <c r="C545" t="s">
         <v>1080</v>
-      </c>
-      <c r="C545" t="s">
-        <v>1081</v>
       </c>
     </row>
     <row r="546" spans="1:3" x14ac:dyDescent="0.25">
@@ -10922,10 +10923,10 @@
         <v>562</v>
       </c>
       <c r="B546" t="s">
+        <v>1081</v>
+      </c>
+      <c r="C546" t="s">
         <v>1082</v>
-      </c>
-      <c r="C546" t="s">
-        <v>1083</v>
       </c>
     </row>
     <row r="547" spans="1:3" x14ac:dyDescent="0.25">
@@ -10933,7 +10934,7 @@
         <v>563</v>
       </c>
       <c r="B547" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="548" spans="1:3" x14ac:dyDescent="0.25">
@@ -10941,10 +10942,10 @@
         <v>564</v>
       </c>
       <c r="B548" t="s">
+        <v>1084</v>
+      </c>
+      <c r="C548" t="s">
         <v>1085</v>
-      </c>
-      <c r="C548" t="s">
-        <v>1086</v>
       </c>
     </row>
     <row r="549" spans="1:3" x14ac:dyDescent="0.25">
@@ -10952,10 +10953,10 @@
         <v>565</v>
       </c>
       <c r="B549" t="s">
+        <v>1086</v>
+      </c>
+      <c r="C549" t="s">
         <v>1087</v>
-      </c>
-      <c r="C549" t="s">
-        <v>1088</v>
       </c>
     </row>
     <row r="550" spans="1:3" x14ac:dyDescent="0.25">
@@ -10963,10 +10964,10 @@
         <v>566</v>
       </c>
       <c r="B550" t="s">
+        <v>1088</v>
+      </c>
+      <c r="C550" t="s">
         <v>1089</v>
-      </c>
-      <c r="C550" t="s">
-        <v>1090</v>
       </c>
     </row>
     <row r="551" spans="1:3" x14ac:dyDescent="0.25">
@@ -10974,10 +10975,10 @@
         <v>567</v>
       </c>
       <c r="B551" t="s">
+        <v>1090</v>
+      </c>
+      <c r="C551" t="s">
         <v>1091</v>
-      </c>
-      <c r="C551" t="s">
-        <v>1092</v>
       </c>
     </row>
     <row r="552" spans="1:3" x14ac:dyDescent="0.25">
@@ -10985,10 +10986,10 @@
         <v>568</v>
       </c>
       <c r="B552" t="s">
+        <v>1092</v>
+      </c>
+      <c r="C552" t="s">
         <v>1093</v>
-      </c>
-      <c r="C552" t="s">
-        <v>1094</v>
       </c>
     </row>
     <row r="553" spans="1:3" x14ac:dyDescent="0.25">
@@ -10996,10 +10997,10 @@
         <v>569</v>
       </c>
       <c r="B553" t="s">
+        <v>1094</v>
+      </c>
+      <c r="C553" t="s">
         <v>1095</v>
-      </c>
-      <c r="C553" t="s">
-        <v>1096</v>
       </c>
     </row>
     <row r="554" spans="1:3" x14ac:dyDescent="0.25">
@@ -11007,10 +11008,10 @@
         <v>570</v>
       </c>
       <c r="B554" t="s">
+        <v>1096</v>
+      </c>
+      <c r="C554" t="s">
         <v>1097</v>
-      </c>
-      <c r="C554" t="s">
-        <v>1098</v>
       </c>
     </row>
     <row r="555" spans="1:3" x14ac:dyDescent="0.25">
@@ -11018,10 +11019,10 @@
         <v>571</v>
       </c>
       <c r="B555" t="s">
+        <v>1098</v>
+      </c>
+      <c r="C555" t="s">
         <v>1099</v>
-      </c>
-      <c r="C555" t="s">
-        <v>1100</v>
       </c>
     </row>
     <row r="556" spans="1:3" x14ac:dyDescent="0.25">
@@ -11029,10 +11030,10 @@
         <v>572</v>
       </c>
       <c r="B556" t="s">
+        <v>1100</v>
+      </c>
+      <c r="C556" t="s">
         <v>1101</v>
-      </c>
-      <c r="C556" t="s">
-        <v>1102</v>
       </c>
     </row>
     <row r="557" spans="1:3" x14ac:dyDescent="0.25">
@@ -11040,10 +11041,10 @@
         <v>577</v>
       </c>
       <c r="B557" t="s">
+        <v>1102</v>
+      </c>
+      <c r="C557" t="s">
         <v>1103</v>
-      </c>
-      <c r="C557" t="s">
-        <v>1104</v>
       </c>
     </row>
     <row r="558" spans="1:3" x14ac:dyDescent="0.25">
@@ -11051,10 +11052,10 @@
         <v>578</v>
       </c>
       <c r="B558" t="s">
+        <v>1104</v>
+      </c>
+      <c r="C558" t="s">
         <v>1105</v>
-      </c>
-      <c r="C558" t="s">
-        <v>1106</v>
       </c>
     </row>
     <row r="559" spans="1:3" x14ac:dyDescent="0.25">
@@ -11062,7 +11063,7 @@
         <v>579</v>
       </c>
       <c r="B559" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="560" spans="1:3" x14ac:dyDescent="0.25">
@@ -11070,10 +11071,10 @@
         <v>580</v>
       </c>
       <c r="B560" t="s">
+        <v>1107</v>
+      </c>
+      <c r="C560" t="s">
         <v>1108</v>
-      </c>
-      <c r="C560" t="s">
-        <v>1109</v>
       </c>
     </row>
     <row r="561" spans="1:3" x14ac:dyDescent="0.25">
@@ -11081,10 +11082,10 @@
         <v>581</v>
       </c>
       <c r="B561" t="s">
+        <v>1109</v>
+      </c>
+      <c r="C561" t="s">
         <v>1110</v>
-      </c>
-      <c r="C561" t="s">
-        <v>1111</v>
       </c>
     </row>
     <row r="562" spans="1:3" x14ac:dyDescent="0.25">
@@ -11092,10 +11093,10 @@
         <v>582</v>
       </c>
       <c r="B562" t="s">
+        <v>1111</v>
+      </c>
+      <c r="C562" t="s">
         <v>1112</v>
-      </c>
-      <c r="C562" t="s">
-        <v>1113</v>
       </c>
     </row>
     <row r="563" spans="1:3" x14ac:dyDescent="0.25">
@@ -11103,10 +11104,10 @@
         <v>583</v>
       </c>
       <c r="B563" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C563" t="s">
         <v>1114</v>
-      </c>
-      <c r="C563" t="s">
-        <v>1115</v>
       </c>
     </row>
     <row r="564" spans="1:3" x14ac:dyDescent="0.25">
@@ -11114,10 +11115,10 @@
         <v>584</v>
       </c>
       <c r="B564" t="s">
+        <v>1115</v>
+      </c>
+      <c r="C564" t="s">
         <v>1116</v>
-      </c>
-      <c r="C564" t="s">
-        <v>1117</v>
       </c>
     </row>
     <row r="565" spans="1:3" x14ac:dyDescent="0.25">
@@ -11125,10 +11126,10 @@
         <v>585</v>
       </c>
       <c r="B565" t="s">
+        <v>1117</v>
+      </c>
+      <c r="C565" t="s">
         <v>1118</v>
-      </c>
-      <c r="C565" t="s">
-        <v>1119</v>
       </c>
     </row>
     <row r="566" spans="1:3" x14ac:dyDescent="0.25">
@@ -11136,10 +11137,10 @@
         <v>586</v>
       </c>
       <c r="B566" t="s">
+        <v>1119</v>
+      </c>
+      <c r="C566" t="s">
         <v>1120</v>
-      </c>
-      <c r="C566" t="s">
-        <v>1121</v>
       </c>
     </row>
     <row r="567" spans="1:3" x14ac:dyDescent="0.25">
@@ -11147,10 +11148,10 @@
         <v>587</v>
       </c>
       <c r="B567" t="s">
+        <v>1121</v>
+      </c>
+      <c r="C567" t="s">
         <v>1122</v>
-      </c>
-      <c r="C567" t="s">
-        <v>1123</v>
       </c>
     </row>
     <row r="568" spans="1:3" x14ac:dyDescent="0.25">
@@ -11158,10 +11159,10 @@
         <v>588</v>
       </c>
       <c r="B568" t="s">
+        <v>1123</v>
+      </c>
+      <c r="C568" t="s">
         <v>1124</v>
-      </c>
-      <c r="C568" t="s">
-        <v>1125</v>
       </c>
     </row>
     <row r="569" spans="1:3" x14ac:dyDescent="0.25">
@@ -11169,10 +11170,10 @@
         <v>589</v>
       </c>
       <c r="B569" t="s">
+        <v>1125</v>
+      </c>
+      <c r="C569" t="s">
         <v>1126</v>
-      </c>
-      <c r="C569" t="s">
-        <v>1127</v>
       </c>
     </row>
     <row r="570" spans="1:3" x14ac:dyDescent="0.25">
@@ -11180,10 +11181,10 @@
         <v>590</v>
       </c>
       <c r="B570" t="s">
+        <v>1127</v>
+      </c>
+      <c r="C570" t="s">
         <v>1128</v>
-      </c>
-      <c r="C570" t="s">
-        <v>1129</v>
       </c>
     </row>
     <row r="571" spans="1:3" x14ac:dyDescent="0.25">
@@ -11191,10 +11192,10 @@
         <v>591</v>
       </c>
       <c r="B571" t="s">
+        <v>1129</v>
+      </c>
+      <c r="C571" t="s">
         <v>1130</v>
-      </c>
-      <c r="C571" t="s">
-        <v>1131</v>
       </c>
     </row>
     <row r="572" spans="1:3" x14ac:dyDescent="0.25">
@@ -11202,10 +11203,10 @@
         <v>592</v>
       </c>
       <c r="B572" t="s">
+        <v>1131</v>
+      </c>
+      <c r="C572" t="s">
         <v>1132</v>
-      </c>
-      <c r="C572" t="s">
-        <v>1133</v>
       </c>
     </row>
     <row r="573" spans="1:3" x14ac:dyDescent="0.25">
@@ -11213,10 +11214,10 @@
         <v>593</v>
       </c>
       <c r="B573" t="s">
+        <v>1133</v>
+      </c>
+      <c r="C573" t="s">
         <v>1134</v>
-      </c>
-      <c r="C573" t="s">
-        <v>1135</v>
       </c>
     </row>
     <row r="574" spans="1:3" x14ac:dyDescent="0.25">
@@ -11224,10 +11225,10 @@
         <v>594</v>
       </c>
       <c r="B574" t="s">
+        <v>1135</v>
+      </c>
+      <c r="C574" t="s">
         <v>1136</v>
-      </c>
-      <c r="C574" t="s">
-        <v>1137</v>
       </c>
     </row>
     <row r="575" spans="1:3" x14ac:dyDescent="0.25">
@@ -11235,10 +11236,10 @@
         <v>595</v>
       </c>
       <c r="B575" t="s">
+        <v>1137</v>
+      </c>
+      <c r="C575" t="s">
         <v>1138</v>
-      </c>
-      <c r="C575" t="s">
-        <v>1139</v>
       </c>
     </row>
     <row r="576" spans="1:3" x14ac:dyDescent="0.25">
@@ -11246,10 +11247,10 @@
         <v>596</v>
       </c>
       <c r="B576" t="s">
+        <v>1139</v>
+      </c>
+      <c r="C576" t="s">
         <v>1140</v>
-      </c>
-      <c r="C576" t="s">
-        <v>1141</v>
       </c>
     </row>
     <row r="577" spans="1:3" x14ac:dyDescent="0.25">
@@ -11257,10 +11258,10 @@
         <v>597</v>
       </c>
       <c r="B577" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="C577" t="s">
-        <v>1142</v>
+        <v>1141</v>
       </c>
     </row>
     <row r="578" spans="1:3" x14ac:dyDescent="0.25">
@@ -11268,10 +11269,10 @@
         <v>598</v>
       </c>
       <c r="B578" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="C578" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="579" spans="1:3" x14ac:dyDescent="0.25">
@@ -11279,10 +11280,10 @@
         <v>599</v>
       </c>
       <c r="B579" t="s">
+        <v>1143</v>
+      </c>
+      <c r="C579" t="s">
         <v>1144</v>
-      </c>
-      <c r="C579" t="s">
-        <v>1145</v>
       </c>
     </row>
     <row r="580" spans="1:3" x14ac:dyDescent="0.25">
@@ -11290,10 +11291,10 @@
         <v>601</v>
       </c>
       <c r="B580" t="s">
+        <v>1145</v>
+      </c>
+      <c r="C580" t="s">
         <v>1146</v>
-      </c>
-      <c r="C580" t="s">
-        <v>1147</v>
       </c>
     </row>
     <row r="581" spans="1:3" x14ac:dyDescent="0.25">
@@ -11301,10 +11302,10 @@
         <v>602</v>
       </c>
       <c r="B581" t="s">
+        <v>1147</v>
+      </c>
+      <c r="C581" t="s">
         <v>1148</v>
-      </c>
-      <c r="C581" t="s">
-        <v>1149</v>
       </c>
     </row>
     <row r="582" spans="1:3" x14ac:dyDescent="0.25">
@@ -11312,10 +11313,10 @@
         <v>604</v>
       </c>
       <c r="B582" t="s">
+        <v>1149</v>
+      </c>
+      <c r="C582" t="s">
         <v>1150</v>
-      </c>
-      <c r="C582" t="s">
-        <v>1151</v>
       </c>
     </row>
     <row r="583" spans="1:3" x14ac:dyDescent="0.25">
@@ -11323,7 +11324,7 @@
         <v>605</v>
       </c>
       <c r="C583" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
     </row>
     <row r="584" spans="1:3" x14ac:dyDescent="0.25">
@@ -11331,10 +11332,10 @@
         <v>606</v>
       </c>
       <c r="B584" t="s">
+        <v>1152</v>
+      </c>
+      <c r="C584" t="s">
         <v>1153</v>
-      </c>
-      <c r="C584" t="s">
-        <v>1154</v>
       </c>
     </row>
     <row r="585" spans="1:3" x14ac:dyDescent="0.25">
@@ -11342,10 +11343,10 @@
         <v>607</v>
       </c>
       <c r="B585" t="s">
+        <v>1154</v>
+      </c>
+      <c r="C585" t="s">
         <v>1155</v>
-      </c>
-      <c r="C585" t="s">
-        <v>1156</v>
       </c>
     </row>
     <row r="586" spans="1:3" x14ac:dyDescent="0.25">
@@ -11353,7 +11354,7 @@
         <v>609</v>
       </c>
       <c r="C586" t="s">
-        <v>1157</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="587" spans="1:3" x14ac:dyDescent="0.25">
@@ -11361,10 +11362,10 @@
         <v>612</v>
       </c>
       <c r="B587" t="s">
+        <v>1157</v>
+      </c>
+      <c r="C587" t="s">
         <v>1158</v>
-      </c>
-      <c r="C587" t="s">
-        <v>1159</v>
       </c>
     </row>
     <row r="588" spans="1:3" x14ac:dyDescent="0.25">
@@ -11372,10 +11373,10 @@
         <v>615</v>
       </c>
       <c r="B588" t="s">
+        <v>1159</v>
+      </c>
+      <c r="C588" t="s">
         <v>1160</v>
-      </c>
-      <c r="C588" t="s">
-        <v>1161</v>
       </c>
     </row>
     <row r="589" spans="1:3" x14ac:dyDescent="0.25">
@@ -11383,10 +11384,10 @@
         <v>617</v>
       </c>
       <c r="B589" t="s">
+        <v>1161</v>
+      </c>
+      <c r="C589" t="s">
         <v>1162</v>
-      </c>
-      <c r="C589" t="s">
-        <v>1163</v>
       </c>
     </row>
     <row r="590" spans="1:3" x14ac:dyDescent="0.25">
@@ -11394,10 +11395,10 @@
         <v>618</v>
       </c>
       <c r="B590" t="s">
+        <v>1163</v>
+      </c>
+      <c r="C590" t="s">
         <v>1164</v>
-      </c>
-      <c r="C590" t="s">
-        <v>1165</v>
       </c>
     </row>
     <row r="591" spans="1:3" x14ac:dyDescent="0.25">
@@ -11405,10 +11406,10 @@
         <v>625</v>
       </c>
       <c r="B591" t="s">
+        <v>1165</v>
+      </c>
+      <c r="C591" t="s">
         <v>1166</v>
-      </c>
-      <c r="C591" t="s">
-        <v>1167</v>
       </c>
     </row>
     <row r="592" spans="1:3" x14ac:dyDescent="0.25">
@@ -11416,10 +11417,10 @@
         <v>624</v>
       </c>
       <c r="B592" t="s">
+        <v>1167</v>
+      </c>
+      <c r="C592" t="s">
         <v>1168</v>
-      </c>
-      <c r="C592" t="s">
-        <v>1169</v>
       </c>
     </row>
     <row r="593" spans="1:3" x14ac:dyDescent="0.25">
@@ -11427,7 +11428,7 @@
         <v>623</v>
       </c>
       <c r="C593" t="s">
-        <v>1170</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="594" spans="1:3" x14ac:dyDescent="0.25">
@@ -11435,10 +11436,10 @@
         <v>626</v>
       </c>
       <c r="B594" t="s">
+        <v>1170</v>
+      </c>
+      <c r="C594" t="s">
         <v>1171</v>
-      </c>
-      <c r="C594" t="s">
-        <v>1172</v>
       </c>
     </row>
     <row r="595" spans="1:3" x14ac:dyDescent="0.25">
@@ -11446,10 +11447,10 @@
         <v>629</v>
       </c>
       <c r="B595" t="s">
+        <v>1172</v>
+      </c>
+      <c r="C595" t="s">
         <v>1173</v>
-      </c>
-      <c r="C595" t="s">
-        <v>1174</v>
       </c>
     </row>
     <row r="596" spans="1:3" x14ac:dyDescent="0.25">
@@ -11457,10 +11458,10 @@
         <v>630</v>
       </c>
       <c r="B596" t="s">
+        <v>1174</v>
+      </c>
+      <c r="C596" t="s">
         <v>1175</v>
-      </c>
-      <c r="C596" t="s">
-        <v>1176</v>
       </c>
     </row>
     <row r="597" spans="1:3" x14ac:dyDescent="0.25">
@@ -11468,7 +11469,7 @@
         <v>632</v>
       </c>
       <c r="C597" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="598" spans="1:3" x14ac:dyDescent="0.25">
@@ -11476,10 +11477,10 @@
         <v>633</v>
       </c>
       <c r="B598" t="s">
+        <v>1177</v>
+      </c>
+      <c r="C598" t="s">
         <v>1178</v>
-      </c>
-      <c r="C598" t="s">
-        <v>1179</v>
       </c>
     </row>
     <row r="599" spans="1:3" x14ac:dyDescent="0.25">
@@ -11487,10 +11488,10 @@
         <v>635</v>
       </c>
       <c r="B599" t="s">
+        <v>1179</v>
+      </c>
+      <c r="C599" t="s">
         <v>1180</v>
-      </c>
-      <c r="C599" t="s">
-        <v>1181</v>
       </c>
     </row>
     <row r="600" spans="1:3" x14ac:dyDescent="0.25">
@@ -11498,10 +11499,10 @@
         <v>636</v>
       </c>
       <c r="B600" t="s">
+        <v>1181</v>
+      </c>
+      <c r="C600" t="s">
         <v>1182</v>
-      </c>
-      <c r="C600" t="s">
-        <v>1183</v>
       </c>
     </row>
     <row r="601" spans="1:3" x14ac:dyDescent="0.25">
@@ -11509,7 +11510,7 @@
         <v>637</v>
       </c>
       <c r="C601" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
     </row>
     <row r="602" spans="1:3" x14ac:dyDescent="0.25">
@@ -11517,10 +11518,10 @@
         <v>642</v>
       </c>
       <c r="B602" t="s">
+        <v>1184</v>
+      </c>
+      <c r="C602" t="s">
         <v>1185</v>
-      </c>
-      <c r="C602" t="s">
-        <v>1186</v>
       </c>
     </row>
     <row r="603" spans="1:3" x14ac:dyDescent="0.25">
@@ -11528,10 +11529,10 @@
         <v>644</v>
       </c>
       <c r="B603" t="s">
+        <v>1186</v>
+      </c>
+      <c r="C603" t="s">
         <v>1187</v>
-      </c>
-      <c r="C603" t="s">
-        <v>1188</v>
       </c>
     </row>
     <row r="604" spans="1:3" x14ac:dyDescent="0.25">
@@ -11539,7 +11540,7 @@
         <v>645</v>
       </c>
       <c r="C604" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="605" spans="1:3" x14ac:dyDescent="0.25">
@@ -11547,10 +11548,10 @@
         <v>646</v>
       </c>
       <c r="B605" t="s">
+        <v>1189</v>
+      </c>
+      <c r="C605" t="s">
         <v>1190</v>
-      </c>
-      <c r="C605" t="s">
-        <v>1191</v>
       </c>
     </row>
     <row r="606" spans="1:3" x14ac:dyDescent="0.25">
@@ -11558,7 +11559,7 @@
         <v>647</v>
       </c>
       <c r="C606" t="s">
-        <v>1192</v>
+        <v>1191</v>
       </c>
     </row>
     <row r="607" spans="1:3" x14ac:dyDescent="0.25">
@@ -11566,10 +11567,10 @@
         <v>649</v>
       </c>
       <c r="B607" t="s">
+        <v>1192</v>
+      </c>
+      <c r="C607" t="s">
         <v>1193</v>
-      </c>
-      <c r="C607" t="s">
-        <v>1194</v>
       </c>
     </row>
     <row r="608" spans="1:3" x14ac:dyDescent="0.25">
@@ -11577,10 +11578,10 @@
         <v>650</v>
       </c>
       <c r="B608" t="s">
+        <v>1194</v>
+      </c>
+      <c r="C608" t="s">
         <v>1195</v>
-      </c>
-      <c r="C608" t="s">
-        <v>1196</v>
       </c>
     </row>
     <row r="609" spans="1:3" x14ac:dyDescent="0.25">
@@ -11588,10 +11589,10 @@
         <v>651</v>
       </c>
       <c r="B609" t="s">
+        <v>1196</v>
+      </c>
+      <c r="C609" t="s">
         <v>1197</v>
-      </c>
-      <c r="C609" t="s">
-        <v>1198</v>
       </c>
     </row>
     <row r="610" spans="1:3" x14ac:dyDescent="0.25">
@@ -11599,10 +11600,10 @@
         <v>653</v>
       </c>
       <c r="B610" t="s">
+        <v>1198</v>
+      </c>
+      <c r="C610" t="s">
         <v>1199</v>
-      </c>
-      <c r="C610" t="s">
-        <v>1200</v>
       </c>
     </row>
     <row r="611" spans="1:3" x14ac:dyDescent="0.25">
@@ -11610,10 +11611,10 @@
         <v>654</v>
       </c>
       <c r="B611" t="s">
+        <v>1200</v>
+      </c>
+      <c r="C611" t="s">
         <v>1201</v>
-      </c>
-      <c r="C611" t="s">
-        <v>1202</v>
       </c>
     </row>
     <row r="612" spans="1:3" x14ac:dyDescent="0.25">
@@ -11621,10 +11622,10 @@
         <v>655</v>
       </c>
       <c r="B612" t="s">
+        <v>1202</v>
+      </c>
+      <c r="C612" t="s">
         <v>1203</v>
-      </c>
-      <c r="C612" t="s">
-        <v>1204</v>
       </c>
     </row>
     <row r="613" spans="1:3" x14ac:dyDescent="0.25">
@@ -11632,7 +11633,7 @@
         <v>657</v>
       </c>
       <c r="C613" t="s">
-        <v>1205</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="614" spans="1:3" x14ac:dyDescent="0.25">
@@ -11640,10 +11641,10 @@
         <v>659</v>
       </c>
       <c r="B614" t="s">
+        <v>1205</v>
+      </c>
+      <c r="C614" t="s">
         <v>1206</v>
-      </c>
-      <c r="C614" t="s">
-        <v>1207</v>
       </c>
     </row>
     <row r="615" spans="1:3" x14ac:dyDescent="0.25">
@@ -11651,10 +11652,10 @@
         <v>660</v>
       </c>
       <c r="B615" t="s">
+        <v>1207</v>
+      </c>
+      <c r="C615" t="s">
         <v>1208</v>
-      </c>
-      <c r="C615" t="s">
-        <v>1209</v>
       </c>
     </row>
     <row r="616" spans="1:3" x14ac:dyDescent="0.25">
@@ -11662,10 +11663,10 @@
         <v>661</v>
       </c>
       <c r="B616" t="s">
+        <v>1209</v>
+      </c>
+      <c r="C616" t="s">
         <v>1210</v>
-      </c>
-      <c r="C616" t="s">
-        <v>1211</v>
       </c>
     </row>
     <row r="617" spans="1:3" x14ac:dyDescent="0.25">
@@ -11673,10 +11674,10 @@
         <v>663</v>
       </c>
       <c r="B617" t="s">
+        <v>1211</v>
+      </c>
+      <c r="C617" t="s">
         <v>1212</v>
-      </c>
-      <c r="C617" t="s">
-        <v>1213</v>
       </c>
     </row>
     <row r="618" spans="1:3" x14ac:dyDescent="0.25">
@@ -11684,10 +11685,10 @@
         <v>667</v>
       </c>
       <c r="B618" t="s">
+        <v>1213</v>
+      </c>
+      <c r="C618" t="s">
         <v>1214</v>
-      </c>
-      <c r="C618" t="s">
-        <v>1215</v>
       </c>
     </row>
     <row r="619" spans="1:3" x14ac:dyDescent="0.25">
@@ -11695,7 +11696,7 @@
         <v>669</v>
       </c>
       <c r="C619" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
     </row>
     <row r="620" spans="1:3" x14ac:dyDescent="0.25">
@@ -11703,10 +11704,10 @@
         <v>670</v>
       </c>
       <c r="B620" t="s">
+        <v>1216</v>
+      </c>
+      <c r="C620" t="s">
         <v>1217</v>
-      </c>
-      <c r="C620" t="s">
-        <v>1218</v>
       </c>
     </row>
     <row r="621" spans="1:3" x14ac:dyDescent="0.25">
@@ -11714,7 +11715,7 @@
         <v>672</v>
       </c>
       <c r="C621" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="622" spans="1:3" x14ac:dyDescent="0.25">
@@ -11722,10 +11723,10 @@
         <v>673</v>
       </c>
       <c r="B622" t="s">
+        <v>1219</v>
+      </c>
+      <c r="C622" t="s">
         <v>1220</v>
-      </c>
-      <c r="C622" t="s">
-        <v>1221</v>
       </c>
     </row>
     <row r="623" spans="1:3" x14ac:dyDescent="0.25">
@@ -11733,10 +11734,10 @@
         <v>674</v>
       </c>
       <c r="B623" t="s">
+        <v>1221</v>
+      </c>
+      <c r="C623" t="s">
         <v>1222</v>
-      </c>
-      <c r="C623" t="s">
-        <v>1223</v>
       </c>
     </row>
     <row r="624" spans="1:3" x14ac:dyDescent="0.25">
@@ -11744,10 +11745,10 @@
         <v>675</v>
       </c>
       <c r="B624" t="s">
+        <v>1223</v>
+      </c>
+      <c r="C624" t="s">
         <v>1224</v>
-      </c>
-      <c r="C624" t="s">
-        <v>1225</v>
       </c>
     </row>
     <row r="625" spans="1:3" x14ac:dyDescent="0.25">
@@ -11755,10 +11756,10 @@
         <v>680</v>
       </c>
       <c r="B625" t="s">
+        <v>1225</v>
+      </c>
+      <c r="C625" t="s">
         <v>1226</v>
-      </c>
-      <c r="C625" t="s">
-        <v>1227</v>
       </c>
     </row>
     <row r="626" spans="1:3" x14ac:dyDescent="0.25">
@@ -11766,10 +11767,10 @@
         <v>681</v>
       </c>
       <c r="B626" t="s">
+        <v>1227</v>
+      </c>
+      <c r="C626" t="s">
         <v>1228</v>
-      </c>
-      <c r="C626" t="s">
-        <v>1229</v>
       </c>
     </row>
     <row r="627" spans="1:3" x14ac:dyDescent="0.25">
@@ -11777,10 +11778,10 @@
         <v>682</v>
       </c>
       <c r="B627" t="s">
+        <v>1229</v>
+      </c>
+      <c r="C627" t="s">
         <v>1230</v>
-      </c>
-      <c r="C627" t="s">
-        <v>1231</v>
       </c>
     </row>
     <row r="628" spans="1:3" x14ac:dyDescent="0.25">
@@ -11788,10 +11789,10 @@
         <v>683</v>
       </c>
       <c r="B628" t="s">
+        <v>1231</v>
+      </c>
+      <c r="C628" t="s">
         <v>1232</v>
-      </c>
-      <c r="C628" t="s">
-        <v>1233</v>
       </c>
     </row>
     <row r="629" spans="1:3" x14ac:dyDescent="0.25">
@@ -11799,10 +11800,10 @@
         <v>684</v>
       </c>
       <c r="B629" t="s">
+        <v>1233</v>
+      </c>
+      <c r="C629" t="s">
         <v>1234</v>
-      </c>
-      <c r="C629" t="s">
-        <v>1235</v>
       </c>
     </row>
     <row r="630" spans="1:3" x14ac:dyDescent="0.25">
@@ -11810,10 +11811,10 @@
         <v>685</v>
       </c>
       <c r="B630" t="s">
+        <v>1235</v>
+      </c>
+      <c r="C630" t="s">
         <v>1236</v>
-      </c>
-      <c r="C630" t="s">
-        <v>1237</v>
       </c>
     </row>
     <row r="631" spans="1:3" x14ac:dyDescent="0.25">
@@ -11821,10 +11822,10 @@
         <v>686</v>
       </c>
       <c r="B631" t="s">
+        <v>1237</v>
+      </c>
+      <c r="C631" t="s">
         <v>1238</v>
-      </c>
-      <c r="C631" t="s">
-        <v>1239</v>
       </c>
     </row>
     <row r="632" spans="1:3" x14ac:dyDescent="0.25">
@@ -11832,10 +11833,10 @@
         <v>689</v>
       </c>
       <c r="B632" t="s">
+        <v>1239</v>
+      </c>
+      <c r="C632" t="s">
         <v>1240</v>
-      </c>
-      <c r="C632" t="s">
-        <v>1241</v>
       </c>
     </row>
     <row r="633" spans="1:3" x14ac:dyDescent="0.25">
@@ -11843,10 +11844,10 @@
         <v>697</v>
       </c>
       <c r="B633" t="s">
+        <v>1241</v>
+      </c>
+      <c r="C633" t="s">
         <v>1242</v>
-      </c>
-      <c r="C633" t="s">
-        <v>1243</v>
       </c>
     </row>
     <row r="634" spans="1:3" x14ac:dyDescent="0.25">
@@ -11854,10 +11855,10 @@
         <v>701</v>
       </c>
       <c r="B634" t="s">
+        <v>1243</v>
+      </c>
+      <c r="C634" t="s">
         <v>1244</v>
-      </c>
-      <c r="C634" t="s">
-        <v>1245</v>
       </c>
     </row>
     <row r="635" spans="1:3" x14ac:dyDescent="0.25">
@@ -11865,10 +11866,10 @@
         <v>702</v>
       </c>
       <c r="B635" t="s">
+        <v>1245</v>
+      </c>
+      <c r="C635" t="s">
         <v>1246</v>
-      </c>
-      <c r="C635" t="s">
-        <v>1247</v>
       </c>
     </row>
     <row r="636" spans="1:3" x14ac:dyDescent="0.25">
@@ -11876,10 +11877,10 @@
         <v>704</v>
       </c>
       <c r="B636" t="s">
+        <v>1247</v>
+      </c>
+      <c r="C636" t="s">
         <v>1248</v>
-      </c>
-      <c r="C636" t="s">
-        <v>1249</v>
       </c>
     </row>
     <row r="637" spans="1:3" x14ac:dyDescent="0.25">
@@ -11887,10 +11888,10 @@
         <v>705</v>
       </c>
       <c r="B637" t="s">
+        <v>1249</v>
+      </c>
+      <c r="C637" t="s">
         <v>1250</v>
-      </c>
-      <c r="C637" t="s">
-        <v>1251</v>
       </c>
     </row>
     <row r="638" spans="1:3" x14ac:dyDescent="0.25">
@@ -11898,7 +11899,7 @@
         <v>707</v>
       </c>
       <c r="C638" t="s">
-        <v>1252</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="639" spans="1:3" x14ac:dyDescent="0.25">
@@ -11906,7 +11907,7 @@
         <v>708</v>
       </c>
       <c r="C639" t="s">
-        <v>1253</v>
+        <v>1252</v>
       </c>
     </row>
     <row r="640" spans="1:3" x14ac:dyDescent="0.25">
@@ -11914,10 +11915,10 @@
         <v>710</v>
       </c>
       <c r="B640" t="s">
+        <v>1253</v>
+      </c>
+      <c r="C640" t="s">
         <v>1254</v>
-      </c>
-      <c r="C640" t="s">
-        <v>1255</v>
       </c>
     </row>
     <row r="641" spans="1:3" x14ac:dyDescent="0.25">
@@ -11925,10 +11926,10 @@
         <v>711</v>
       </c>
       <c r="B641" t="s">
+        <v>1255</v>
+      </c>
+      <c r="C641" t="s">
         <v>1256</v>
-      </c>
-      <c r="C641" t="s">
-        <v>1257</v>
       </c>
     </row>
     <row r="642" spans="1:3" x14ac:dyDescent="0.25">
@@ -11936,10 +11937,10 @@
         <v>712</v>
       </c>
       <c r="B642" t="s">
+        <v>1257</v>
+      </c>
+      <c r="C642" t="s">
         <v>1258</v>
-      </c>
-      <c r="C642" t="s">
-        <v>1259</v>
       </c>
     </row>
     <row r="643" spans="1:3" x14ac:dyDescent="0.25">
@@ -11947,10 +11948,10 @@
         <v>714</v>
       </c>
       <c r="B643" t="s">
+        <v>1259</v>
+      </c>
+      <c r="C643" t="s">
         <v>1260</v>
-      </c>
-      <c r="C643" t="s">
-        <v>1261</v>
       </c>
     </row>
     <row r="644" spans="1:3" x14ac:dyDescent="0.25">
@@ -11958,7 +11959,7 @@
         <v>715</v>
       </c>
       <c r="C644" t="s">
-        <v>1262</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="645" spans="1:3" x14ac:dyDescent="0.25">
@@ -11966,7 +11967,7 @@
         <v>716</v>
       </c>
       <c r="C645" t="s">
-        <v>1263</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="646" spans="1:3" x14ac:dyDescent="0.25">
@@ -11974,10 +11975,10 @@
         <v>717</v>
       </c>
       <c r="B646" t="s">
+        <v>1263</v>
+      </c>
+      <c r="C646" t="s">
         <v>1264</v>
-      </c>
-      <c r="C646" t="s">
-        <v>1265</v>
       </c>
     </row>
     <row r="647" spans="1:3" x14ac:dyDescent="0.25">
@@ -11985,10 +11986,10 @@
         <v>718</v>
       </c>
       <c r="B647" t="s">
+        <v>1265</v>
+      </c>
+      <c r="C647" t="s">
         <v>1266</v>
-      </c>
-      <c r="C647" t="s">
-        <v>1267</v>
       </c>
     </row>
     <row r="648" spans="1:3" x14ac:dyDescent="0.25">
@@ -11996,10 +11997,10 @@
         <v>719</v>
       </c>
       <c r="B648" t="s">
+        <v>1267</v>
+      </c>
+      <c r="C648" t="s">
         <v>1268</v>
-      </c>
-      <c r="C648" t="s">
-        <v>1269</v>
       </c>
     </row>
     <row r="649" spans="1:3" ht="19.8" x14ac:dyDescent="0.5">
@@ -12007,10 +12008,10 @@
         <v>721</v>
       </c>
       <c r="B649" t="s">
+        <v>1269</v>
+      </c>
+      <c r="C649" t="s">
         <v>1270</v>
-      </c>
-      <c r="C649" t="s">
-        <v>1271</v>
       </c>
     </row>
     <row r="650" spans="1:3" x14ac:dyDescent="0.25">
@@ -12018,10 +12019,10 @@
         <v>722</v>
       </c>
       <c r="B650" t="s">
+        <v>1271</v>
+      </c>
+      <c r="C650" t="s">
         <v>1272</v>
-      </c>
-      <c r="C650" t="s">
-        <v>1273</v>
       </c>
     </row>
     <row r="651" spans="1:3" x14ac:dyDescent="0.25">
@@ -12029,10 +12030,10 @@
         <v>723</v>
       </c>
       <c r="B651" t="s">
+        <v>1273</v>
+      </c>
+      <c r="C651" t="s">
         <v>1274</v>
-      </c>
-      <c r="C651" t="s">
-        <v>1275</v>
       </c>
     </row>
     <row r="652" spans="1:3" x14ac:dyDescent="0.25">
@@ -12040,7 +12041,7 @@
         <v>724</v>
       </c>
       <c r="C652" t="s">
-        <v>1276</v>
+        <v>1275</v>
       </c>
     </row>
     <row r="653" spans="1:3" x14ac:dyDescent="0.25">
@@ -12048,10 +12049,10 @@
         <v>725</v>
       </c>
       <c r="B653" s="2" t="s">
+        <v>1276</v>
+      </c>
+      <c r="C653" t="s">
         <v>1277</v>
-      </c>
-      <c r="C653" t="s">
-        <v>1278</v>
       </c>
     </row>
     <row r="654" spans="1:3" x14ac:dyDescent="0.25">
@@ -12059,10 +12060,10 @@
         <v>726</v>
       </c>
       <c r="B654" t="s">
+        <v>1278</v>
+      </c>
+      <c r="C654" t="s">
         <v>1279</v>
-      </c>
-      <c r="C654" t="s">
-        <v>1280</v>
       </c>
     </row>
     <row r="655" spans="1:3" x14ac:dyDescent="0.25">
@@ -12070,10 +12071,10 @@
         <v>727</v>
       </c>
       <c r="B655" t="s">
+        <v>1280</v>
+      </c>
+      <c r="C655" t="s">
         <v>1281</v>
-      </c>
-      <c r="C655" t="s">
-        <v>1282</v>
       </c>
     </row>
     <row r="656" spans="1:3" ht="19.8" x14ac:dyDescent="0.5">
@@ -12081,10 +12082,10 @@
         <v>728</v>
       </c>
       <c r="B656" t="s">
+        <v>1282</v>
+      </c>
+      <c r="C656" t="s">
         <v>1283</v>
-      </c>
-      <c r="C656" t="s">
-        <v>1284</v>
       </c>
     </row>
     <row r="657" spans="1:3" ht="19.8" x14ac:dyDescent="0.5">
@@ -12092,10 +12093,10 @@
         <v>729</v>
       </c>
       <c r="B657" t="s">
+        <v>1284</v>
+      </c>
+      <c r="C657" t="s">
         <v>1285</v>
-      </c>
-      <c r="C657" t="s">
-        <v>1286</v>
       </c>
     </row>
     <row r="658" spans="1:3" x14ac:dyDescent="0.25">
@@ -12103,10 +12104,10 @@
         <v>730</v>
       </c>
       <c r="B658" t="s">
+        <v>1286</v>
+      </c>
+      <c r="C658" t="s">
         <v>1287</v>
-      </c>
-      <c r="C658" t="s">
-        <v>1288</v>
       </c>
     </row>
     <row r="659" spans="1:3" x14ac:dyDescent="0.25">
@@ -12114,10 +12115,10 @@
         <v>731</v>
       </c>
       <c r="B659" t="s">
+        <v>1288</v>
+      </c>
+      <c r="C659" t="s">
         <v>1289</v>
-      </c>
-      <c r="C659" t="s">
-        <v>1290</v>
       </c>
     </row>
     <row r="660" spans="1:3" x14ac:dyDescent="0.25">
@@ -12125,7 +12126,7 @@
         <v>732</v>
       </c>
       <c r="C660" t="s">
-        <v>1291</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="661" spans="1:3" x14ac:dyDescent="0.25">
@@ -12133,10 +12134,10 @@
         <v>733</v>
       </c>
       <c r="B661" t="s">
+        <v>1291</v>
+      </c>
+      <c r="C661" t="s">
         <v>1292</v>
-      </c>
-      <c r="C661" t="s">
-        <v>1293</v>
       </c>
     </row>
     <row r="662" spans="1:3" x14ac:dyDescent="0.25">
@@ -12144,7 +12145,7 @@
         <v>734</v>
       </c>
       <c r="C662" t="s">
-        <v>1294</v>
+        <v>1293</v>
       </c>
     </row>
     <row r="663" spans="1:3" x14ac:dyDescent="0.25">
@@ -12152,10 +12153,10 @@
         <v>735</v>
       </c>
       <c r="B663" t="s">
+        <v>1294</v>
+      </c>
+      <c r="C663" t="s">
         <v>1295</v>
-      </c>
-      <c r="C663" t="s">
-        <v>1296</v>
       </c>
     </row>
     <row r="664" spans="1:3" x14ac:dyDescent="0.25">
@@ -12163,10 +12164,10 @@
         <v>736</v>
       </c>
       <c r="B664" t="s">
+        <v>1296</v>
+      </c>
+      <c r="C664" t="s">
         <v>1297</v>
-      </c>
-      <c r="C664" t="s">
-        <v>1298</v>
       </c>
     </row>
     <row r="665" spans="1:3" x14ac:dyDescent="0.25">
@@ -12174,10 +12175,10 @@
         <v>737</v>
       </c>
       <c r="B665" t="s">
+        <v>1298</v>
+      </c>
+      <c r="C665" t="s">
         <v>1299</v>
-      </c>
-      <c r="C665" t="s">
-        <v>1300</v>
       </c>
     </row>
     <row r="666" spans="1:3" x14ac:dyDescent="0.25">
@@ -12185,10 +12186,10 @@
         <v>738</v>
       </c>
       <c r="B666" t="s">
+        <v>1300</v>
+      </c>
+      <c r="C666" t="s">
         <v>1301</v>
-      </c>
-      <c r="C666" t="s">
-        <v>1302</v>
       </c>
     </row>
     <row r="667" spans="1:3" x14ac:dyDescent="0.25">
@@ -12196,10 +12197,10 @@
         <v>739</v>
       </c>
       <c r="B667" t="s">
+        <v>1302</v>
+      </c>
+      <c r="C667" t="s">
         <v>1303</v>
-      </c>
-      <c r="C667" t="s">
-        <v>1304</v>
       </c>
     </row>
     <row r="668" spans="1:3" x14ac:dyDescent="0.25">
@@ -12207,10 +12208,10 @@
         <v>740</v>
       </c>
       <c r="B668" t="s">
+        <v>1304</v>
+      </c>
+      <c r="C668" t="s">
         <v>1305</v>
-      </c>
-      <c r="C668" t="s">
-        <v>1306</v>
       </c>
     </row>
     <row r="669" spans="1:3" x14ac:dyDescent="0.25">
@@ -12218,10 +12219,10 @@
         <v>741</v>
       </c>
       <c r="B669" t="s">
+        <v>1306</v>
+      </c>
+      <c r="C669" t="s">
         <v>1307</v>
-      </c>
-      <c r="C669" t="s">
-        <v>1308</v>
       </c>
     </row>
     <row r="670" spans="1:3" x14ac:dyDescent="0.25">
@@ -12229,10 +12230,10 @@
         <v>742</v>
       </c>
       <c r="B670" t="s">
+        <v>1308</v>
+      </c>
+      <c r="C670" t="s">
         <v>1309</v>
-      </c>
-      <c r="C670" t="s">
-        <v>1310</v>
       </c>
     </row>
     <row r="671" spans="1:3" x14ac:dyDescent="0.25">
@@ -12240,10 +12241,10 @@
         <v>743</v>
       </c>
       <c r="B671" t="s">
+        <v>1310</v>
+      </c>
+      <c r="C671" t="s">
         <v>1311</v>
-      </c>
-      <c r="C671" t="s">
-        <v>1312</v>
       </c>
     </row>
     <row r="672" spans="1:3" x14ac:dyDescent="0.25">
@@ -12251,10 +12252,10 @@
         <v>744</v>
       </c>
       <c r="B672" t="s">
+        <v>1312</v>
+      </c>
+      <c r="C672" t="s">
         <v>1313</v>
-      </c>
-      <c r="C672" t="s">
-        <v>1314</v>
       </c>
     </row>
     <row r="673" spans="1:3" ht="19.8" x14ac:dyDescent="0.5">
@@ -12262,10 +12263,10 @@
         <v>745</v>
       </c>
       <c r="B673" s="1" t="s">
+        <v>1314</v>
+      </c>
+      <c r="C673" t="s">
         <v>1315</v>
-      </c>
-      <c r="C673" t="s">
-        <v>1316</v>
       </c>
     </row>
     <row r="674" spans="1:3" x14ac:dyDescent="0.25">
@@ -12273,10 +12274,10 @@
         <v>746</v>
       </c>
       <c r="B674" s="1" t="s">
+        <v>1316</v>
+      </c>
+      <c r="C674" t="s">
         <v>1317</v>
-      </c>
-      <c r="C674" t="s">
-        <v>1318</v>
       </c>
     </row>
     <row r="675" spans="1:3" x14ac:dyDescent="0.25">
@@ -12284,10 +12285,10 @@
         <v>747</v>
       </c>
       <c r="B675" s="1" t="s">
+        <v>1318</v>
+      </c>
+      <c r="C675" t="s">
         <v>1319</v>
-      </c>
-      <c r="C675" t="s">
-        <v>1320</v>
       </c>
     </row>
     <row r="676" spans="1:3" x14ac:dyDescent="0.25">
@@ -12295,10 +12296,10 @@
         <v>748</v>
       </c>
       <c r="B676" s="1" t="s">
+        <v>1320</v>
+      </c>
+      <c r="C676" t="s">
         <v>1321</v>
-      </c>
-      <c r="C676" t="s">
-        <v>1322</v>
       </c>
     </row>
     <row r="677" spans="1:3" x14ac:dyDescent="0.25">
@@ -12306,10 +12307,10 @@
         <v>749</v>
       </c>
       <c r="B677" s="1" t="s">
+        <v>1322</v>
+      </c>
+      <c r="C677" t="s">
         <v>1323</v>
-      </c>
-      <c r="C677" t="s">
-        <v>1324</v>
       </c>
     </row>
     <row r="678" spans="1:3" x14ac:dyDescent="0.25">
@@ -12318,7 +12319,7 @@
       </c>
       <c r="B678" s="1"/>
       <c r="C678" t="s">
-        <v>1325</v>
+        <v>1324</v>
       </c>
     </row>
     <row r="679" spans="1:3" x14ac:dyDescent="0.25">
@@ -12327,7 +12328,7 @@
       </c>
       <c r="B679" s="1"/>
       <c r="C679" t="s">
-        <v>1326</v>
+        <v>1325</v>
       </c>
     </row>
     <row r="680" spans="1:3" x14ac:dyDescent="0.25">
@@ -12335,10 +12336,10 @@
         <v>753</v>
       </c>
       <c r="B680" s="1" t="s">
+        <v>1326</v>
+      </c>
+      <c r="C680" t="s">
         <v>1327</v>
-      </c>
-      <c r="C680" t="s">
-        <v>1328</v>
       </c>
     </row>
     <row r="681" spans="1:3" x14ac:dyDescent="0.25">
@@ -12346,10 +12347,10 @@
         <v>755</v>
       </c>
       <c r="B681" s="1" t="s">
+        <v>1328</v>
+      </c>
+      <c r="C681" t="s">
         <v>1329</v>
-      </c>
-      <c r="C681" t="s">
-        <v>1330</v>
       </c>
     </row>
     <row r="682" spans="1:3" x14ac:dyDescent="0.25">
@@ -12357,10 +12358,10 @@
         <v>756</v>
       </c>
       <c r="B682" s="1" t="s">
+        <v>1330</v>
+      </c>
+      <c r="C682" t="s">
         <v>1331</v>
-      </c>
-      <c r="C682" t="s">
-        <v>1332</v>
       </c>
     </row>
     <row r="683" spans="1:3" x14ac:dyDescent="0.25">
@@ -12368,10 +12369,10 @@
         <v>757</v>
       </c>
       <c r="B683" s="1" t="s">
+        <v>1332</v>
+      </c>
+      <c r="C683" t="s">
         <v>1333</v>
-      </c>
-      <c r="C683" t="s">
-        <v>1334</v>
       </c>
     </row>
     <row r="684" spans="1:3" x14ac:dyDescent="0.25">
@@ -12379,10 +12380,10 @@
         <v>758</v>
       </c>
       <c r="B684" s="1" t="s">
+        <v>1334</v>
+      </c>
+      <c r="C684" t="s">
         <v>1335</v>
-      </c>
-      <c r="C684" t="s">
-        <v>1336</v>
       </c>
     </row>
     <row r="685" spans="1:3" x14ac:dyDescent="0.25">
@@ -12390,10 +12391,10 @@
         <v>759</v>
       </c>
       <c r="B685" s="1" t="s">
+        <v>1336</v>
+      </c>
+      <c r="C685" t="s">
         <v>1337</v>
-      </c>
-      <c r="C685" t="s">
-        <v>1338</v>
       </c>
     </row>
     <row r="686" spans="1:3" x14ac:dyDescent="0.25">
@@ -12401,10 +12402,10 @@
         <v>760</v>
       </c>
       <c r="B686" s="1" t="s">
+        <v>1338</v>
+      </c>
+      <c r="C686" t="s">
         <v>1339</v>
-      </c>
-      <c r="C686" t="s">
-        <v>1340</v>
       </c>
     </row>
     <row r="687" spans="1:3" ht="19.8" x14ac:dyDescent="0.5">
@@ -12412,10 +12413,10 @@
         <v>761</v>
       </c>
       <c r="B687" s="1" t="s">
+        <v>1340</v>
+      </c>
+      <c r="C687" t="s">
         <v>1341</v>
-      </c>
-      <c r="C687" t="s">
-        <v>1342</v>
       </c>
     </row>
     <row r="688" spans="1:3" ht="19.2" x14ac:dyDescent="0.45">
@@ -12423,10 +12424,10 @@
         <v>762</v>
       </c>
       <c r="B688" s="1" t="s">
+        <v>1342</v>
+      </c>
+      <c r="C688" t="s">
         <v>1343</v>
-      </c>
-      <c r="C688" t="s">
-        <v>1344</v>
       </c>
     </row>
     <row r="689" spans="1:3" ht="19.2" x14ac:dyDescent="0.45">
@@ -12434,10 +12435,10 @@
         <v>763</v>
       </c>
       <c r="B689" s="1" t="s">
+        <v>1344</v>
+      </c>
+      <c r="C689" t="s">
         <v>1345</v>
-      </c>
-      <c r="C689" t="s">
-        <v>1346</v>
       </c>
     </row>
     <row r="690" spans="1:3" x14ac:dyDescent="0.25">
@@ -12445,10 +12446,10 @@
         <v>764</v>
       </c>
       <c r="B690" s="1" t="s">
+        <v>1346</v>
+      </c>
+      <c r="C690" t="s">
         <v>1347</v>
-      </c>
-      <c r="C690" t="s">
-        <v>1348</v>
       </c>
     </row>
     <row r="691" spans="1:3" x14ac:dyDescent="0.25">
@@ -12456,10 +12457,10 @@
         <v>765</v>
       </c>
       <c r="B691" s="1" t="s">
+        <v>1348</v>
+      </c>
+      <c r="C691" t="s">
         <v>1349</v>
-      </c>
-      <c r="C691" t="s">
-        <v>1350</v>
       </c>
     </row>
     <row r="692" spans="1:3" x14ac:dyDescent="0.25">
@@ -12468,7 +12469,7 @@
       </c>
       <c r="B692" s="1"/>
       <c r="C692" t="s">
-        <v>1351</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="693" spans="1:3" x14ac:dyDescent="0.25">
@@ -12476,10 +12477,10 @@
         <v>767</v>
       </c>
       <c r="B693" s="1" t="s">
+        <v>1351</v>
+      </c>
+      <c r="C693" t="s">
         <v>1352</v>
-      </c>
-      <c r="C693" t="s">
-        <v>1353</v>
       </c>
     </row>
     <row r="694" spans="1:3" x14ac:dyDescent="0.25">
@@ -12488,7 +12489,7 @@
       </c>
       <c r="B694" s="1"/>
       <c r="C694" t="s">
-        <v>1354</v>
+        <v>1353</v>
       </c>
     </row>
     <row r="695" spans="1:3" x14ac:dyDescent="0.25">
@@ -12496,10 +12497,10 @@
         <v>769</v>
       </c>
       <c r="B695" s="1" t="s">
+        <v>1354</v>
+      </c>
+      <c r="C695" t="s">
         <v>1355</v>
-      </c>
-      <c r="C695" t="s">
-        <v>1356</v>
       </c>
     </row>
     <row r="696" spans="1:3" x14ac:dyDescent="0.25">
@@ -12507,10 +12508,10 @@
         <v>772</v>
       </c>
       <c r="B696" s="1" t="s">
+        <v>1356</v>
+      </c>
+      <c r="C696" t="s">
         <v>1357</v>
-      </c>
-      <c r="C696" t="s">
-        <v>1358</v>
       </c>
     </row>
     <row r="697" spans="1:3" x14ac:dyDescent="0.25">
@@ -12519,7 +12520,7 @@
       </c>
       <c r="B697" s="1"/>
       <c r="C697" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
     </row>
     <row r="698" spans="1:3" x14ac:dyDescent="0.25">
@@ -12528,7 +12529,7 @@
       </c>
       <c r="B698" s="1"/>
       <c r="C698" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
     </row>
     <row r="699" spans="1:3" x14ac:dyDescent="0.25">
@@ -12537,7 +12538,7 @@
       </c>
       <c r="B699" s="1"/>
       <c r="C699" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
     </row>
     <row r="700" spans="1:3" x14ac:dyDescent="0.25">
@@ -12546,7 +12547,7 @@
       </c>
       <c r="B700" s="1"/>
       <c r="C700" t="s">
-        <v>1362</v>
+        <v>1361</v>
       </c>
     </row>
     <row r="701" spans="1:3" x14ac:dyDescent="0.25">
@@ -12555,7 +12556,7 @@
       </c>
       <c r="B701" s="1"/>
       <c r="C701" t="s">
-        <v>1363</v>
+        <v>1362</v>
       </c>
     </row>
     <row r="702" spans="1:3" x14ac:dyDescent="0.25">
@@ -12564,7 +12565,7 @@
       </c>
       <c r="B702" s="1"/>
       <c r="C702" t="s">
-        <v>1364</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="703" spans="1:3" x14ac:dyDescent="0.25">
@@ -12573,7 +12574,7 @@
       </c>
       <c r="B703" s="1"/>
       <c r="C703" t="s">
-        <v>1365</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="704" spans="1:3" x14ac:dyDescent="0.25">
@@ -12582,7 +12583,7 @@
       </c>
       <c r="B704" s="1"/>
       <c r="C704" t="s">
-        <v>1366</v>
+        <v>1365</v>
       </c>
     </row>
     <row r="705" spans="1:3" x14ac:dyDescent="0.25">
@@ -12591,7 +12592,7 @@
       </c>
       <c r="B705" s="1"/>
       <c r="C705" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="706" spans="1:3" x14ac:dyDescent="0.25">
@@ -12599,7 +12600,7 @@
         <v>785</v>
       </c>
       <c r="C706" t="s">
-        <v>1368</v>
+        <v>1367</v>
       </c>
     </row>
     <row r="707" spans="1:3" x14ac:dyDescent="0.25">
@@ -12607,7 +12608,7 @@
         <v>787</v>
       </c>
       <c r="C707" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
     </row>
     <row r="708" spans="1:3" x14ac:dyDescent="0.25">
@@ -12615,7 +12616,7 @@
         <v>788</v>
       </c>
       <c r="C708" t="s">
-        <v>1370</v>
+        <v>1369</v>
       </c>
     </row>
     <row r="709" spans="1:3" x14ac:dyDescent="0.25">
@@ -12623,7 +12624,7 @@
         <v>790</v>
       </c>
       <c r="C709" t="s">
-        <v>1371</v>
+        <v>1370</v>
       </c>
     </row>
     <row r="710" spans="1:3" x14ac:dyDescent="0.25">
@@ -12631,7 +12632,7 @@
         <v>791</v>
       </c>
       <c r="C710" t="s">
-        <v>1372</v>
+        <v>1371</v>
       </c>
     </row>
     <row r="711" spans="1:3" x14ac:dyDescent="0.25">
@@ -12639,7 +12640,7 @@
         <v>792</v>
       </c>
       <c r="C711" t="s">
-        <v>1373</v>
+        <v>1372</v>
       </c>
     </row>
     <row r="712" spans="1:3" x14ac:dyDescent="0.25">
@@ -12647,7 +12648,7 @@
         <v>794</v>
       </c>
       <c r="C712" t="s">
-        <v>1374</v>
+        <v>1373</v>
       </c>
     </row>
     <row r="713" spans="1:3" x14ac:dyDescent="0.25">
@@ -12655,7 +12656,7 @@
         <v>795</v>
       </c>
       <c r="C713" t="s">
-        <v>1375</v>
+        <v>1374</v>
       </c>
     </row>
     <row r="714" spans="1:3" x14ac:dyDescent="0.25">
@@ -12663,7 +12664,7 @@
         <v>796</v>
       </c>
       <c r="C714" t="s">
-        <v>1376</v>
+        <v>1375</v>
       </c>
     </row>
     <row r="715" spans="1:3" x14ac:dyDescent="0.25">
@@ -12671,7 +12672,7 @@
         <v>797</v>
       </c>
       <c r="C715" t="s">
-        <v>1377</v>
+        <v>1376</v>
       </c>
     </row>
     <row r="716" spans="1:3" x14ac:dyDescent="0.25">
@@ -12679,7 +12680,7 @@
         <v>798</v>
       </c>
       <c r="C716" t="s">
-        <v>1378</v>
+        <v>1377</v>
       </c>
     </row>
     <row r="717" spans="1:3" x14ac:dyDescent="0.25">
@@ -12687,7 +12688,7 @@
         <v>799</v>
       </c>
       <c r="C717" t="s">
-        <v>1379</v>
+        <v>1378</v>
       </c>
     </row>
     <row r="718" spans="1:3" x14ac:dyDescent="0.25">
@@ -12695,7 +12696,7 @@
         <v>800</v>
       </c>
       <c r="C718" t="s">
-        <v>1380</v>
+        <v>1379</v>
       </c>
     </row>
     <row r="719" spans="1:3" x14ac:dyDescent="0.25">
@@ -12708,7 +12709,7 @@
         <v>802</v>
       </c>
       <c r="C720" t="s">
-        <v>1381</v>
+        <v>1380</v>
       </c>
     </row>
     <row r="721" spans="1:3" ht="16.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -12716,7 +12717,7 @@
         <v>803</v>
       </c>
       <c r="C721" t="s">
-        <v>1382</v>
+        <v>1381</v>
       </c>
     </row>
     <row r="722" spans="1:3" ht="16.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -12724,7 +12725,7 @@
         <v>804</v>
       </c>
       <c r="C722" t="s">
-        <v>1383</v>
+        <v>1382</v>
       </c>
     </row>
     <row r="723" spans="1:3" ht="16.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -12732,7 +12733,7 @@
         <v>805</v>
       </c>
       <c r="C723" s="3" t="s">
-        <v>1387</v>
+        <v>1386</v>
       </c>
     </row>
     <row r="724" spans="1:3" ht="16.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -12740,7 +12741,7 @@
         <v>806</v>
       </c>
       <c r="C724" s="3" t="s">
-        <v>1388</v>
+        <v>1387</v>
       </c>
     </row>
     <row r="725" spans="1:3" ht="16.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -12748,7 +12749,7 @@
         <v>807</v>
       </c>
       <c r="C725" s="3" t="s">
-        <v>1389</v>
+        <v>1388</v>
       </c>
     </row>
     <row r="726" spans="1:3" ht="16.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -12756,7 +12757,7 @@
         <v>808</v>
       </c>
       <c r="C726" s="3" t="s">
-        <v>1390</v>
+        <v>1389</v>
       </c>
     </row>
     <row r="727" spans="1:3" ht="16.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -12764,7 +12765,7 @@
         <v>809</v>
       </c>
       <c r="C727" s="3" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="728" spans="1:3" ht="16.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -12772,7 +12773,7 @@
         <v>810</v>
       </c>
       <c r="C728" s="3" t="s">
-        <v>1392</v>
+        <v>1391</v>
       </c>
     </row>
     <row r="729" spans="1:3" ht="16.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -12780,7 +12781,7 @@
         <v>811</v>
       </c>
       <c r="C729" s="3" t="s">
-        <v>1394</v>
+        <v>1393</v>
       </c>
     </row>
     <row r="730" spans="1:3" ht="16.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -12788,7 +12789,7 @@
         <v>812</v>
       </c>
       <c r="C730" s="3" t="s">
-        <v>1395</v>
+        <v>1394</v>
       </c>
     </row>
     <row r="731" spans="1:3" ht="16.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -12796,7 +12797,7 @@
         <v>813</v>
       </c>
       <c r="C731" s="3" t="s">
-        <v>1396</v>
+        <v>1395</v>
       </c>
     </row>
     <row r="732" spans="1:3" ht="16.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -12804,7 +12805,7 @@
         <v>814</v>
       </c>
       <c r="C732" s="3" t="s">
-        <v>1397</v>
+        <v>1396</v>
       </c>
     </row>
     <row r="733" spans="1:3" ht="16.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -12812,7 +12813,7 @@
         <v>815</v>
       </c>
       <c r="C733" s="3" t="s">
-        <v>1398</v>
+        <v>1397</v>
       </c>
     </row>
     <row r="734" spans="1:3" ht="16.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -12820,7 +12821,7 @@
         <v>816</v>
       </c>
       <c r="C734" s="3" t="s">
-        <v>1386</v>
+        <v>1385</v>
       </c>
     </row>
     <row r="735" spans="1:3" ht="16.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -12828,7 +12829,7 @@
         <v>817</v>
       </c>
       <c r="C735" s="3" t="s">
-        <v>1399</v>
+        <v>1398</v>
       </c>
     </row>
     <row r="736" spans="1:3" ht="16.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -12836,7 +12837,7 @@
         <v>818</v>
       </c>
       <c r="C736" s="3" t="s">
-        <v>1400</v>
+        <v>1399</v>
       </c>
     </row>
     <row r="737" spans="1:3" ht="16.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -12844,7 +12845,7 @@
         <v>819</v>
       </c>
       <c r="C737" s="3" t="s">
-        <v>1401</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="738" spans="1:3" ht="16.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -12852,7 +12853,7 @@
         <v>820</v>
       </c>
       <c r="C738" s="3" t="s">
-        <v>1402</v>
+        <v>1401</v>
       </c>
     </row>
     <row r="739" spans="1:3" x14ac:dyDescent="0.25">
@@ -12860,10 +12861,10 @@
         <v>10001</v>
       </c>
       <c r="B739" t="s">
+        <v>1383</v>
+      </c>
+      <c r="C739" t="s">
         <v>1384</v>
-      </c>
-      <c r="C739" t="s">
-        <v>1385</v>
       </c>
     </row>
     <row r="740" spans="1:3" x14ac:dyDescent="0.25">
@@ -12871,10 +12872,10 @@
         <v>10003</v>
       </c>
       <c r="B740" t="s">
+        <v>1354</v>
+      </c>
+      <c r="C740" t="s">
         <v>1355</v>
-      </c>
-      <c r="C740" t="s">
-        <v>1356</v>
       </c>
     </row>
   </sheetData>

--- a/nickname_song.xlsx
+++ b/nickname_song.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Coding\Tsugu-Backend\config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0C8B657-974B-4F68-9323-E90BEB8A1E70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9ED74584-BC84-4AC6-AFC9-43ABD06D997C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2124" yWindow="1536" windowWidth="23040" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1413" uniqueCount="1403">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2826" uniqueCount="1403">
   <si>
     <t>Id</t>
   </si>
@@ -4373,9 +4373,6 @@
     <t>漫画平行,cp平行,平行世界</t>
   </si>
   <si>
-    <t>gcsp,游戏改变者,改变游戏者,gc</t>
-  </si>
-  <si>
     <t>灼热小太阳平行,灼热平行,火焰弹平行,炽热平行</t>
   </si>
   <si>
@@ -4502,6 +4499,10 @@
   </si>
   <si>
     <t>二重虹,ppp2章,二重之虹,俩彩虹,两彩虹,双彩虹,双重彩虹</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>gcsp,游戏改变者,改变游戏者,gc,三文鱼,鲑鱼</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -6103,7 +6104,7 @@
         <v>213</v>
       </c>
       <c r="C107" s="3" t="s">
-        <v>1392</v>
+        <v>1391</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.25">
@@ -6180,7 +6181,7 @@
         <v>226</v>
       </c>
       <c r="C114" s="3" t="s">
-        <v>1402</v>
+        <v>1401</v>
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.25">
@@ -12582,8 +12583,8 @@
         <v>782</v>
       </c>
       <c r="B704" s="1"/>
-      <c r="C704" t="s">
-        <v>1365</v>
+      <c r="C704" s="3" t="s">
+        <v>1402</v>
       </c>
     </row>
     <row r="705" spans="1:3" x14ac:dyDescent="0.25">
@@ -12592,7 +12593,7 @@
       </c>
       <c r="B705" s="1"/>
       <c r="C705" t="s">
-        <v>1366</v>
+        <v>1365</v>
       </c>
     </row>
     <row r="706" spans="1:3" x14ac:dyDescent="0.25">
@@ -12600,7 +12601,7 @@
         <v>785</v>
       </c>
       <c r="C706" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="707" spans="1:3" x14ac:dyDescent="0.25">
@@ -12608,7 +12609,7 @@
         <v>787</v>
       </c>
       <c r="C707" t="s">
-        <v>1368</v>
+        <v>1367</v>
       </c>
     </row>
     <row r="708" spans="1:3" x14ac:dyDescent="0.25">
@@ -12616,7 +12617,7 @@
         <v>788</v>
       </c>
       <c r="C708" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
     </row>
     <row r="709" spans="1:3" x14ac:dyDescent="0.25">
@@ -12624,7 +12625,7 @@
         <v>790</v>
       </c>
       <c r="C709" t="s">
-        <v>1370</v>
+        <v>1369</v>
       </c>
     </row>
     <row r="710" spans="1:3" x14ac:dyDescent="0.25">
@@ -12632,7 +12633,7 @@
         <v>791</v>
       </c>
       <c r="C710" t="s">
-        <v>1371</v>
+        <v>1370</v>
       </c>
     </row>
     <row r="711" spans="1:3" x14ac:dyDescent="0.25">
@@ -12640,7 +12641,7 @@
         <v>792</v>
       </c>
       <c r="C711" t="s">
-        <v>1372</v>
+        <v>1371</v>
       </c>
     </row>
     <row r="712" spans="1:3" x14ac:dyDescent="0.25">
@@ -12648,7 +12649,7 @@
         <v>794</v>
       </c>
       <c r="C712" t="s">
-        <v>1373</v>
+        <v>1372</v>
       </c>
     </row>
     <row r="713" spans="1:3" x14ac:dyDescent="0.25">
@@ -12656,7 +12657,7 @@
         <v>795</v>
       </c>
       <c r="C713" t="s">
-        <v>1374</v>
+        <v>1373</v>
       </c>
     </row>
     <row r="714" spans="1:3" x14ac:dyDescent="0.25">
@@ -12664,7 +12665,7 @@
         <v>796</v>
       </c>
       <c r="C714" t="s">
-        <v>1375</v>
+        <v>1374</v>
       </c>
     </row>
     <row r="715" spans="1:3" x14ac:dyDescent="0.25">
@@ -12672,7 +12673,7 @@
         <v>797</v>
       </c>
       <c r="C715" t="s">
-        <v>1376</v>
+        <v>1375</v>
       </c>
     </row>
     <row r="716" spans="1:3" x14ac:dyDescent="0.25">
@@ -12680,7 +12681,7 @@
         <v>798</v>
       </c>
       <c r="C716" t="s">
-        <v>1377</v>
+        <v>1376</v>
       </c>
     </row>
     <row r="717" spans="1:3" x14ac:dyDescent="0.25">
@@ -12688,7 +12689,7 @@
         <v>799</v>
       </c>
       <c r="C717" t="s">
-        <v>1378</v>
+        <v>1377</v>
       </c>
     </row>
     <row r="718" spans="1:3" x14ac:dyDescent="0.25">
@@ -12696,7 +12697,7 @@
         <v>800</v>
       </c>
       <c r="C718" t="s">
-        <v>1379</v>
+        <v>1378</v>
       </c>
     </row>
     <row r="719" spans="1:3" x14ac:dyDescent="0.25">
@@ -12709,7 +12710,7 @@
         <v>802</v>
       </c>
       <c r="C720" t="s">
-        <v>1380</v>
+        <v>1379</v>
       </c>
     </row>
     <row r="721" spans="1:3" ht="16.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -12717,7 +12718,7 @@
         <v>803</v>
       </c>
       <c r="C721" t="s">
-        <v>1381</v>
+        <v>1380</v>
       </c>
     </row>
     <row r="722" spans="1:3" ht="16.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -12725,7 +12726,7 @@
         <v>804</v>
       </c>
       <c r="C722" t="s">
-        <v>1382</v>
+        <v>1381</v>
       </c>
     </row>
     <row r="723" spans="1:3" ht="16.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -12733,7 +12734,7 @@
         <v>805</v>
       </c>
       <c r="C723" s="3" t="s">
-        <v>1386</v>
+        <v>1385</v>
       </c>
     </row>
     <row r="724" spans="1:3" ht="16.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -12741,7 +12742,7 @@
         <v>806</v>
       </c>
       <c r="C724" s="3" t="s">
-        <v>1387</v>
+        <v>1386</v>
       </c>
     </row>
     <row r="725" spans="1:3" ht="16.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -12749,7 +12750,7 @@
         <v>807</v>
       </c>
       <c r="C725" s="3" t="s">
-        <v>1388</v>
+        <v>1387</v>
       </c>
     </row>
     <row r="726" spans="1:3" ht="16.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -12757,7 +12758,7 @@
         <v>808</v>
       </c>
       <c r="C726" s="3" t="s">
-        <v>1389</v>
+        <v>1388</v>
       </c>
     </row>
     <row r="727" spans="1:3" ht="16.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -12765,7 +12766,7 @@
         <v>809</v>
       </c>
       <c r="C727" s="3" t="s">
-        <v>1390</v>
+        <v>1389</v>
       </c>
     </row>
     <row r="728" spans="1:3" ht="16.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -12773,7 +12774,7 @@
         <v>810</v>
       </c>
       <c r="C728" s="3" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="729" spans="1:3" ht="16.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -12781,7 +12782,7 @@
         <v>811</v>
       </c>
       <c r="C729" s="3" t="s">
-        <v>1393</v>
+        <v>1392</v>
       </c>
     </row>
     <row r="730" spans="1:3" ht="16.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -12789,7 +12790,7 @@
         <v>812</v>
       </c>
       <c r="C730" s="3" t="s">
-        <v>1394</v>
+        <v>1393</v>
       </c>
     </row>
     <row r="731" spans="1:3" ht="16.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -12797,7 +12798,7 @@
         <v>813</v>
       </c>
       <c r="C731" s="3" t="s">
-        <v>1395</v>
+        <v>1394</v>
       </c>
     </row>
     <row r="732" spans="1:3" ht="16.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -12805,7 +12806,7 @@
         <v>814</v>
       </c>
       <c r="C732" s="3" t="s">
-        <v>1396</v>
+        <v>1395</v>
       </c>
     </row>
     <row r="733" spans="1:3" ht="16.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -12813,7 +12814,7 @@
         <v>815</v>
       </c>
       <c r="C733" s="3" t="s">
-        <v>1397</v>
+        <v>1396</v>
       </c>
     </row>
     <row r="734" spans="1:3" ht="16.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -12821,7 +12822,7 @@
         <v>816</v>
       </c>
       <c r="C734" s="3" t="s">
-        <v>1385</v>
+        <v>1384</v>
       </c>
     </row>
     <row r="735" spans="1:3" ht="16.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -12829,7 +12830,7 @@
         <v>817</v>
       </c>
       <c r="C735" s="3" t="s">
-        <v>1398</v>
+        <v>1397</v>
       </c>
     </row>
     <row r="736" spans="1:3" ht="16.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -12837,7 +12838,7 @@
         <v>818</v>
       </c>
       <c r="C736" s="3" t="s">
-        <v>1399</v>
+        <v>1398</v>
       </c>
     </row>
     <row r="737" spans="1:3" ht="16.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -12845,7 +12846,7 @@
         <v>819</v>
       </c>
       <c r="C737" s="3" t="s">
-        <v>1400</v>
+        <v>1399</v>
       </c>
     </row>
     <row r="738" spans="1:3" ht="16.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -12853,7 +12854,7 @@
         <v>820</v>
       </c>
       <c r="C738" s="3" t="s">
-        <v>1401</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="739" spans="1:3" x14ac:dyDescent="0.25">
@@ -12861,10 +12862,10 @@
         <v>10001</v>
       </c>
       <c r="B739" t="s">
+        <v>1382</v>
+      </c>
+      <c r="C739" t="s">
         <v>1383</v>
-      </c>
-      <c r="C739" t="s">
-        <v>1384</v>
       </c>
     </row>
     <row r="740" spans="1:3" x14ac:dyDescent="0.25">

--- a/nickname_song.xlsx
+++ b/nickname_song.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30430"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Coding\Tsugu-Backend\config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9ED74584-BC84-4AC6-AFC9-43ABD06D997C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B11EDC78-15FC-417A-B381-902AEC5A281C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="30612" yWindow="3012" windowWidth="13176" windowHeight="22536" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2826" uniqueCount="1403">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1413" uniqueCount="1403">
   <si>
     <t>Id</t>
   </si>
@@ -153,37 +153,6 @@
     <t>シュガーソングとビターステップ</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>糖歌,血界战线,</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Emoji"/>
-        <family val="2"/>
-      </rPr>
-      <t>🍬</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>,糖,32分,糖车</t>
-    </r>
-  </si>
-  <si>
     <t>いーあるふぁんくらぶ</t>
   </si>
   <si>
@@ -517,9 +486,6 @@
     <t>世界は恋に落ちている</t>
   </si>
   <si>
-    <t>青春之旅,世界坠入爱河,honeyworks,世界恋落</t>
-  </si>
-  <si>
     <t>す、好きなんかじゃない！</t>
   </si>
   <si>
@@ -535,9 +501,6 @@
     <t>恋は渾沌の隷也</t>
   </si>
   <si>
-    <t>激萌萝莉,奈亚子,三只佩奇,恋混沌,恋爱混沌</t>
-  </si>
-  <si>
     <t>プライド革命</t>
   </si>
   <si>
@@ -559,21 +522,12 @@
     <t>君じゃなきゃダメみたい</t>
   </si>
   <si>
-    <t>月刊少女,洗你大衣,搓衣板,32分</t>
-  </si>
-  <si>
     <t>残酷な天使のテーゼ</t>
   </si>
   <si>
-    <t>残酷天使,残纲,eva</t>
-  </si>
-  <si>
     <t>Dragon Night</t>
   </si>
   <si>
-    <t>龙夜,313combo,313,农业</t>
-  </si>
-  <si>
     <t>Redo</t>
   </si>
   <si>
@@ -997,9 +951,6 @@
     <t>名前のない怪物</t>
   </si>
   <si>
-    <t>无名怪物,没有名字的怪物,心理测量者</t>
-  </si>
-  <si>
     <t>回レ！雪月花</t>
   </si>
   <si>
@@ -1177,9 +1128,6 @@
     <t>午夜の待ち合わせ</t>
   </si>
   <si>
-    <t>野良神,午夜待合</t>
-  </si>
-  <si>
     <t>チェリボム</t>
   </si>
   <si>
@@ -1612,9 +1560,6 @@
     <t>秒針を噛む</t>
   </si>
   <si>
-    <t>咬秒针,咬住秒针,真夜中,秒针</t>
-  </si>
-  <si>
     <t>RED RED RED</t>
   </si>
   <si>
@@ -1708,9 +1653,6 @@
     <t>青と夏</t>
   </si>
   <si>
-    <t>青夏,绿苹果</t>
-  </si>
-  <si>
     <t>恋しさと せつなさと 心強さと</t>
   </si>
   <si>
@@ -1822,9 +1764,6 @@
     <t>好き！雪！本気マジック</t>
   </si>
   <si>
-    <t>卧槽!下雪了!牛逼啊!,喜欢!雪!真实的魔法!,卧槽！下雪了！牛逼啊！,喜欢！雪！真实的魔法！,好雪本气,草！雪！牛逼！,卧槽下雪了牛逼啊</t>
-  </si>
-  <si>
     <t>SAVIOR OF SONG</t>
   </si>
   <si>
@@ -1894,9 +1833,6 @@
     <t>夜に駆ける</t>
   </si>
   <si>
-    <t>夜驱,夜跑,夜奔,试图把我激怒,yoasobi,夜游,夜驅,向夜晚奔去,向着夜晚奔去</t>
-  </si>
-  <si>
     <t>イエスタデイ</t>
   </si>
   <si>
@@ -2006,9 +1942,6 @@
   </si>
   <si>
     <t>ラムのラブソング</t>
-  </si>
-  <si>
-    <t>拉姆情歌,拉姆恋歌</t>
   </si>
   <si>
     <t>overtuRe</t>
@@ -4503,6 +4436,79 @@
   </si>
   <si>
     <t>gcsp,游戏改变者,改变游戏者,gc,三文鱼,鲑鱼</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>月刊少女,洗你大衣,搓衣板,32分,似乎非你不可</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>青春之旅,世界坠入爱河,honeyworks,世界恋落,我的世界已坠入爱河,我的世界已经坠入爱河</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>龙夜,313combo,313,农业,龙之夜</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>残酷天使,残纲,eva,残酷天使的行动纲领,残酷天使行动纲领</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>青夏,绿苹果,青之夏</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>野良神,午夜待合,午夜相会</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>夜驱,夜跑,夜奔,试图把我激怒,yoasobi,夜游,夜驅,向夜晚奔去,向着夜晚奔去,奔向黑夜</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>拉姆情歌,拉姆恋歌,拉姆的爱之歌</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>无名怪物,没有名字的怪物,心理测量者,无名的怪物</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>糖歌,血界战线,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>🍬</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>,糖,32分,糖车,甜蜜情歌和苦涩舞步</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>激萌萝莉,奈亚子,三只佩奇,恋混沌,恋爱混沌,恋爱乃混沌之奴隶也</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>卧槽!下雪了!牛逼啊!,喜欢!雪!真实的魔法!,卧槽！下雪了！牛逼啊！,喜欢！雪！真实的魔法！,好雪本气,草！雪！牛逼！,卧槽下雪了牛逼啊,喜欢！雪！真实的魔法</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>咬秒针,咬住秒针,真夜中,秒针,噬咬秒针</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -4921,7 +4927,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C740"/>
+  <dimension ref="A1:C752"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.69921875" customWidth="1"/>
@@ -4970,8 +4976,8 @@
       <c r="B4" t="s">
         <v>7</v>
       </c>
-      <c r="C4" t="s">
-        <v>8</v>
+      <c r="C4" t="str">
+        <v>薄饼香呼呼,薄饼,跃动' Shuffle</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -5058,8 +5064,8 @@
       <c r="B12" t="s">
         <v>23</v>
       </c>
-      <c r="C12" t="s">
-        <v>24</v>
+      <c r="C12" t="str">
+        <v>走你,走始,致刚开始奔跑的你,致刚刚开始奔跑的你</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
@@ -5124,8 +5130,8 @@
       <c r="B18" t="s">
         <v>35</v>
       </c>
-      <c r="C18" t="s">
-        <v>36</v>
+      <c r="C18" t="str">
+        <v>未闻花名,那朵花,secret base,秘密基地,秘密基地 ~你所给予之物~</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
@@ -5146,8 +5152,8 @@
       <c r="B20" t="s">
         <v>39</v>
       </c>
-      <c r="C20" t="s">
-        <v>40</v>
+      <c r="C20" s="3" t="s">
+        <v>1399</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
@@ -5155,10 +5161,10 @@
         <v>21</v>
       </c>
       <c r="B21" t="s">
+        <v>40</v>
+      </c>
+      <c r="C21" t="s">
         <v>41</v>
-      </c>
-      <c r="C21" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
@@ -5166,10 +5172,10 @@
         <v>22</v>
       </c>
       <c r="B22" t="s">
+        <v>42</v>
+      </c>
+      <c r="C22" t="s">
         <v>43</v>
-      </c>
-      <c r="C22" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
@@ -5177,10 +5183,10 @@
         <v>24</v>
       </c>
       <c r="B23" t="s">
+        <v>44</v>
+      </c>
+      <c r="C23" t="s">
         <v>45</v>
-      </c>
-      <c r="C23" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
@@ -5188,10 +5194,10 @@
         <v>25</v>
       </c>
       <c r="B24" t="s">
-        <v>47</v>
-      </c>
-      <c r="C24" t="s">
-        <v>48</v>
+        <v>46</v>
+      </c>
+      <c r="C24" t="str">
+        <v>krkr,信鸽,无论闪耀还是梦想~歌之少女~</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
@@ -5199,10 +5205,10 @@
         <v>26</v>
       </c>
       <c r="B25" t="s">
+        <v>48</v>
+      </c>
+      <c r="C25" t="s">
         <v>49</v>
-      </c>
-      <c r="C25" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
@@ -5210,10 +5216,10 @@
         <v>27</v>
       </c>
       <c r="B26" t="s">
+        <v>50</v>
+      </c>
+      <c r="C26" t="s">
         <v>51</v>
-      </c>
-      <c r="C26" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
@@ -5221,10 +5227,10 @@
         <v>28</v>
       </c>
       <c r="B27" t="s">
+        <v>52</v>
+      </c>
+      <c r="C27" t="s">
         <v>53</v>
-      </c>
-      <c r="C27" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
@@ -5232,10 +5238,10 @@
         <v>29</v>
       </c>
       <c r="B28" t="s">
+        <v>54</v>
+      </c>
+      <c r="C28" t="s">
         <v>55</v>
-      </c>
-      <c r="C28" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
@@ -5243,10 +5249,10 @@
         <v>30</v>
       </c>
       <c r="B29" t="s">
+        <v>56</v>
+      </c>
+      <c r="C29" t="s">
         <v>57</v>
-      </c>
-      <c r="C29" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
@@ -5254,10 +5260,10 @@
         <v>31</v>
       </c>
       <c r="B30" t="s">
+        <v>58</v>
+      </c>
+      <c r="C30" t="s">
         <v>59</v>
-      </c>
-      <c r="C30" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
@@ -5265,10 +5271,10 @@
         <v>32</v>
       </c>
       <c r="B31" t="s">
-        <v>61</v>
-      </c>
-      <c r="C31" t="s">
-        <v>62</v>
+        <v>60</v>
+      </c>
+      <c r="C31" t="str">
+        <v>修车,shuwa,修哇修哇,修瓦,泡沫般的梦想</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
@@ -5276,10 +5282,10 @@
         <v>33</v>
       </c>
       <c r="B32" t="s">
+        <v>62</v>
+      </c>
+      <c r="C32" t="s">
         <v>63</v>
-      </c>
-      <c r="C32" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
@@ -5287,10 +5293,10 @@
         <v>34</v>
       </c>
       <c r="B33" t="s">
+        <v>64</v>
+      </c>
+      <c r="C33" t="s">
         <v>65</v>
-      </c>
-      <c r="C33" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
@@ -5298,10 +5304,10 @@
         <v>35</v>
       </c>
       <c r="B34" t="s">
-        <v>67</v>
-      </c>
-      <c r="C34" t="s">
-        <v>68</v>
+        <v>66</v>
+      </c>
+      <c r="C34" t="str">
+        <v>orchestra,管弦乐团,笑容管弦乐,笑容的管弦乐</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
@@ -5309,10 +5315,10 @@
         <v>36</v>
       </c>
       <c r="B35" t="s">
+        <v>68</v>
+      </c>
+      <c r="C35" t="s">
         <v>69</v>
-      </c>
-      <c r="C35" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
@@ -5320,10 +5326,10 @@
         <v>37</v>
       </c>
       <c r="B36" t="s">
+        <v>70</v>
+      </c>
+      <c r="C36" t="s">
         <v>71</v>
-      </c>
-      <c r="C36" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
@@ -5331,10 +5337,10 @@
         <v>40</v>
       </c>
       <c r="B37" t="s">
+        <v>72</v>
+      </c>
+      <c r="C37" t="s">
         <v>73</v>
-      </c>
-      <c r="C37" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
@@ -5342,10 +5348,10 @@
         <v>41</v>
       </c>
       <c r="B38" t="s">
+        <v>74</v>
+      </c>
+      <c r="C38" t="s">
         <v>75</v>
-      </c>
-      <c r="C38" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
@@ -5353,10 +5359,10 @@
         <v>42</v>
       </c>
       <c r="B39" t="s">
+        <v>76</v>
+      </c>
+      <c r="C39" t="s">
         <v>77</v>
-      </c>
-      <c r="C39" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
@@ -5364,10 +5370,10 @@
         <v>43</v>
       </c>
       <c r="B40" t="s">
-        <v>79</v>
-      </c>
-      <c r="C40" t="s">
-        <v>80</v>
+        <v>78</v>
+      </c>
+      <c r="C40" t="str">
+        <v>向前,速食面,勇往直前,前进吧!</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
@@ -5375,10 +5381,10 @@
         <v>44</v>
       </c>
       <c r="B41" t="s">
+        <v>80</v>
+      </c>
+      <c r="C41" t="s">
         <v>81</v>
-      </c>
-      <c r="C41" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
@@ -5386,10 +5392,10 @@
         <v>45</v>
       </c>
       <c r="B42" t="s">
+        <v>82</v>
+      </c>
+      <c r="C42" t="s">
         <v>83</v>
-      </c>
-      <c r="C42" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
@@ -5397,10 +5403,10 @@
         <v>46</v>
       </c>
       <c r="B43" t="s">
+        <v>84</v>
+      </c>
+      <c r="C43" t="s">
         <v>85</v>
-      </c>
-      <c r="C43" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
@@ -5408,10 +5414,10 @@
         <v>47</v>
       </c>
       <c r="B44" t="s">
+        <v>86</v>
+      </c>
+      <c r="C44" t="s">
         <v>87</v>
-      </c>
-      <c r="C44" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
@@ -5419,10 +5425,10 @@
         <v>48</v>
       </c>
       <c r="B45" t="s">
+        <v>88</v>
+      </c>
+      <c r="C45" t="s">
         <v>89</v>
-      </c>
-      <c r="C45" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
@@ -5430,10 +5436,10 @@
         <v>49</v>
       </c>
       <c r="B46" t="s">
+        <v>90</v>
+      </c>
+      <c r="C46" t="s">
         <v>91</v>
-      </c>
-      <c r="C46" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
@@ -5441,10 +5447,10 @@
         <v>50</v>
       </c>
       <c r="B47" t="s">
+        <v>92</v>
+      </c>
+      <c r="C47" t="s">
         <v>93</v>
-      </c>
-      <c r="C47" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
@@ -5452,10 +5458,10 @@
         <v>51</v>
       </c>
       <c r="B48" t="s">
+        <v>94</v>
+      </c>
+      <c r="C48" t="s">
         <v>95</v>
-      </c>
-      <c r="C48" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
@@ -5463,10 +5469,10 @@
         <v>52</v>
       </c>
       <c r="B49" t="s">
+        <v>96</v>
+      </c>
+      <c r="C49" t="s">
         <v>97</v>
-      </c>
-      <c r="C49" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
@@ -5474,10 +5480,10 @@
         <v>53</v>
       </c>
       <c r="B50" t="s">
-        <v>99</v>
-      </c>
-      <c r="C50" t="s">
-        <v>100</v>
+        <v>98</v>
+      </c>
+      <c r="C50" t="str">
+        <v>蔷薇辉石,yuki,锁手三纵,温暖的蔷薇辉石</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
@@ -5485,10 +5491,10 @@
         <v>54</v>
       </c>
       <c r="B51" t="s">
+        <v>100</v>
+      </c>
+      <c r="C51" t="s">
         <v>101</v>
-      </c>
-      <c r="C51" t="s">
-        <v>102</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
@@ -5496,10 +5502,10 @@
         <v>55</v>
       </c>
       <c r="B52" t="s">
+        <v>102</v>
+      </c>
+      <c r="C52" t="s">
         <v>103</v>
-      </c>
-      <c r="C52" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
@@ -5507,10 +5513,10 @@
         <v>56</v>
       </c>
       <c r="B53" t="s">
-        <v>105</v>
-      </c>
-      <c r="C53" t="s">
-        <v>106</v>
+        <v>104</v>
+      </c>
+      <c r="C53" t="str">
+        <v>热色星火,星石,热色,頂点へ 狂い咲け,热色,热色Star Mine</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
@@ -5518,10 +5524,10 @@
         <v>57</v>
       </c>
       <c r="B54" t="s">
+        <v>106</v>
+      </c>
+      <c r="C54" t="s">
         <v>107</v>
-      </c>
-      <c r="C54" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
@@ -5529,10 +5535,10 @@
         <v>58</v>
       </c>
       <c r="B55" t="s">
+        <v>108</v>
+      </c>
+      <c r="C55" t="s">
         <v>109</v>
-      </c>
-      <c r="C55" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
@@ -5540,10 +5546,10 @@
         <v>59</v>
       </c>
       <c r="B56" t="s">
+        <v>110</v>
+      </c>
+      <c r="C56" t="s">
         <v>111</v>
-      </c>
-      <c r="C56" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
@@ -5551,10 +5557,10 @@
         <v>60</v>
       </c>
       <c r="B57" t="s">
+        <v>112</v>
+      </c>
+      <c r="C57" t="s">
         <v>113</v>
-      </c>
-      <c r="C57" t="s">
-        <v>114</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
@@ -5562,10 +5568,10 @@
         <v>61</v>
       </c>
       <c r="B58" t="s">
+        <v>114</v>
+      </c>
+      <c r="C58" t="s">
         <v>115</v>
-      </c>
-      <c r="C58" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
@@ -5573,10 +5579,10 @@
         <v>62</v>
       </c>
       <c r="B59" t="s">
+        <v>116</v>
+      </c>
+      <c r="C59" t="s">
         <v>117</v>
-      </c>
-      <c r="C59" t="s">
-        <v>118</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
@@ -5584,10 +5590,10 @@
         <v>63</v>
       </c>
       <c r="B60" t="s">
+        <v>118</v>
+      </c>
+      <c r="C60" t="s">
         <v>119</v>
-      </c>
-      <c r="C60" t="s">
-        <v>120</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
@@ -5595,10 +5601,10 @@
         <v>64</v>
       </c>
       <c r="B61" t="s">
-        <v>121</v>
-      </c>
-      <c r="C61" t="s">
-        <v>122</v>
+        <v>120</v>
+      </c>
+      <c r="C61" t="str">
+        <v>八月的伊芙,八月的if,八月,八月的遐想</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
@@ -5606,10 +5612,10 @@
         <v>65</v>
       </c>
       <c r="B62" t="s">
-        <v>123</v>
-      </c>
-      <c r="C62" t="s">
-        <v>124</v>
+        <v>122</v>
+      </c>
+      <c r="C62" t="str">
+        <v>capriccio,狂骚曲,你开头gr了,hey-day,Hey-day随想曲</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
@@ -5617,10 +5623,10 @@
         <v>66</v>
       </c>
       <c r="B63" t="s">
+        <v>124</v>
+      </c>
+      <c r="C63" t="s">
         <v>125</v>
-      </c>
-      <c r="C63" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
@@ -5628,10 +5634,10 @@
         <v>67</v>
       </c>
       <c r="B64" t="s">
+        <v>126</v>
+      </c>
+      <c r="C64" t="s">
         <v>127</v>
-      </c>
-      <c r="C64" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
@@ -5639,10 +5645,10 @@
         <v>68</v>
       </c>
       <c r="B65" t="s">
+        <v>128</v>
+      </c>
+      <c r="C65" t="s">
         <v>129</v>
-      </c>
-      <c r="C65" t="s">
-        <v>130</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
@@ -5650,10 +5656,10 @@
         <v>69</v>
       </c>
       <c r="B66" t="s">
-        <v>131</v>
-      </c>
-      <c r="C66" t="s">
-        <v>132</v>
+        <v>130</v>
+      </c>
+      <c r="C66" t="str">
+        <v>打碟,搓碟,天线宝宝,绿条,yo,哟,世界无限延伸Treasure！</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
@@ -5661,10 +5667,10 @@
         <v>70</v>
       </c>
       <c r="B67" t="s">
-        <v>133</v>
-      </c>
-      <c r="C67" t="s">
-        <v>134</v>
+        <v>132</v>
+      </c>
+      <c r="C67" t="str">
+        <v>无人岛,survivor,永不言弃的求生者</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
@@ -5672,10 +5678,10 @@
         <v>71</v>
       </c>
       <c r="B68" t="s">
+        <v>134</v>
+      </c>
+      <c r="C68" t="s">
         <v>135</v>
-      </c>
-      <c r="C68" t="s">
-        <v>136</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
@@ -5683,10 +5689,10 @@
         <v>72</v>
       </c>
       <c r="B69" t="s">
+        <v>136</v>
+      </c>
+      <c r="C69" t="s">
         <v>137</v>
-      </c>
-      <c r="C69" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
@@ -5694,10 +5700,10 @@
         <v>73</v>
       </c>
       <c r="B70" t="s">
+        <v>138</v>
+      </c>
+      <c r="C70" t="s">
         <v>139</v>
-      </c>
-      <c r="C70" t="s">
-        <v>140</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
@@ -5705,10 +5711,10 @@
         <v>74</v>
       </c>
       <c r="B71" t="s">
+        <v>140</v>
+      </c>
+      <c r="C71" t="s">
         <v>141</v>
-      </c>
-      <c r="C71" t="s">
-        <v>142</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
@@ -5716,10 +5722,10 @@
         <v>75</v>
       </c>
       <c r="B72" t="s">
+        <v>142</v>
+      </c>
+      <c r="C72" t="s">
         <v>143</v>
-      </c>
-      <c r="C72" t="s">
-        <v>144</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
@@ -5727,10 +5733,10 @@
         <v>76</v>
       </c>
       <c r="B73" t="s">
+        <v>144</v>
+      </c>
+      <c r="C73" t="s">
         <v>145</v>
-      </c>
-      <c r="C73" t="s">
-        <v>146</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
@@ -5738,10 +5744,10 @@
         <v>77</v>
       </c>
       <c r="B74" t="s">
+        <v>146</v>
+      </c>
+      <c r="C74" t="s">
         <v>147</v>
-      </c>
-      <c r="C74" t="s">
-        <v>148</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
@@ -5749,10 +5755,10 @@
         <v>78</v>
       </c>
       <c r="B75" t="s">
+        <v>148</v>
+      </c>
+      <c r="C75" t="s">
         <v>149</v>
-      </c>
-      <c r="C75" t="s">
-        <v>150</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
@@ -5760,10 +5766,10 @@
         <v>79</v>
       </c>
       <c r="B76" t="s">
-        <v>151</v>
-      </c>
-      <c r="C76" t="s">
-        <v>152</v>
+        <v>150</v>
+      </c>
+      <c r="C76" s="3" t="s">
+        <v>1391</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
@@ -5771,10 +5777,10 @@
         <v>80</v>
       </c>
       <c r="B77" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C77" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
@@ -5782,10 +5788,10 @@
         <v>81</v>
       </c>
       <c r="B78" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C78" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.25">
@@ -5793,10 +5799,10 @@
         <v>82</v>
       </c>
       <c r="B79" t="s">
-        <v>157</v>
-      </c>
-      <c r="C79" t="s">
-        <v>158</v>
+        <v>155</v>
+      </c>
+      <c r="C79" s="3" t="s">
+        <v>1400</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.25">
@@ -5804,10 +5810,10 @@
         <v>83</v>
       </c>
       <c r="B80" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="C80" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
@@ -5815,10 +5821,10 @@
         <v>84</v>
       </c>
       <c r="B81" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="C81" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.25">
@@ -5826,10 +5832,10 @@
         <v>85</v>
       </c>
       <c r="B82" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="C82" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.25">
@@ -5837,10 +5843,10 @@
         <v>86</v>
       </c>
       <c r="B83" t="s">
-        <v>165</v>
-      </c>
-      <c r="C83" t="s">
-        <v>166</v>
+        <v>162</v>
+      </c>
+      <c r="C83" s="3" t="str">
+        <v>月刊少女,洗你大衣,搓衣板,32分,似乎非你不可,非你莫属</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.25">
@@ -5848,10 +5854,10 @@
         <v>87</v>
       </c>
       <c r="B84" t="s">
-        <v>167</v>
-      </c>
-      <c r="C84" t="s">
-        <v>168</v>
+        <v>163</v>
+      </c>
+      <c r="C84" s="3" t="s">
+        <v>1393</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.25">
@@ -5859,10 +5865,10 @@
         <v>88</v>
       </c>
       <c r="B85" t="s">
-        <v>169</v>
-      </c>
-      <c r="C85" t="s">
-        <v>170</v>
+        <v>164</v>
+      </c>
+      <c r="C85" s="3" t="s">
+        <v>1392</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.25">
@@ -5870,10 +5876,10 @@
         <v>89</v>
       </c>
       <c r="B86" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="C86" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.25">
@@ -5881,10 +5887,10 @@
         <v>90</v>
       </c>
       <c r="B87" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="C87" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.25">
@@ -5892,10 +5898,10 @@
         <v>91</v>
       </c>
       <c r="B88" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="C88" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.25">
@@ -5903,10 +5909,10 @@
         <v>92</v>
       </c>
       <c r="B89" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="C89" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.25">
@@ -5914,10 +5920,10 @@
         <v>93</v>
       </c>
       <c r="B90" t="s">
-        <v>179</v>
-      </c>
-      <c r="C90" t="s">
-        <v>180</v>
+        <v>173</v>
+      </c>
+      <c r="C90" t="str">
+        <v>大哥上楼梯,yolo,斜楼梯,时光不再来</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.25">
@@ -5925,10 +5931,10 @@
         <v>94</v>
       </c>
       <c r="B91" t="s">
-        <v>181</v>
-      </c>
-      <c r="C91" t="s">
-        <v>182</v>
+        <v>175</v>
+      </c>
+      <c r="C91" t="str">
+        <v>企鹅进行曲,相羽爱奈进行曲,i83进行曲,花音可爱捏,行进曲,跌跌撞撞进行曲</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.25">
@@ -5936,10 +5942,10 @@
         <v>95</v>
       </c>
       <c r="B92" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="C92" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.25">
@@ -5947,10 +5953,10 @@
         <v>96</v>
       </c>
       <c r="B93" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="C93" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.25">
@@ -5958,10 +5964,10 @@
         <v>97</v>
       </c>
       <c r="B94" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="C94" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.25">
@@ -5969,10 +5975,10 @@
         <v>100</v>
       </c>
       <c r="B95" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="C95" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.25">
@@ -5980,10 +5986,10 @@
         <v>101</v>
       </c>
       <c r="B96" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="C96" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.25">
@@ -5991,10 +5997,10 @@
         <v>104</v>
       </c>
       <c r="B97" t="s">
-        <v>193</v>
-      </c>
-      <c r="C97" t="s">
-        <v>194</v>
+        <v>187</v>
+      </c>
+      <c r="C97" t="str">
+        <v>pp2,引牛之主,再来,再一次 闪耀,再次闪耀,再度闪耀,再一次 绽放光芒</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.25">
@@ -6002,10 +6008,10 @@
         <v>105</v>
       </c>
       <c r="B98" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="C98" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.25">
@@ -6013,10 +6019,10 @@
         <v>106</v>
       </c>
       <c r="B99" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="C99" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.25">
@@ -6024,10 +6030,10 @@
         <v>107</v>
       </c>
       <c r="B100" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="C100" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.25">
@@ -6035,10 +6041,10 @@
         <v>108</v>
       </c>
       <c r="B101" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="C101" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.25">
@@ -6046,10 +6052,10 @@
         <v>109</v>
       </c>
       <c r="B102" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="C102" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.25">
@@ -6057,10 +6063,10 @@
         <v>110</v>
       </c>
       <c r="B103" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="C103" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.25">
@@ -6068,10 +6074,10 @@
         <v>111</v>
       </c>
       <c r="B104" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="C104" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.25">
@@ -6079,10 +6085,10 @@
         <v>112</v>
       </c>
       <c r="B105" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="C105" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.25">
@@ -6090,10 +6096,10 @@
         <v>113</v>
       </c>
       <c r="B106" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="C106" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.25">
@@ -6101,10 +6107,10 @@
         <v>115</v>
       </c>
       <c r="B107" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="C107" s="3" t="s">
-        <v>1391</v>
+        <v>1378</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.25">
@@ -6112,10 +6118,10 @@
         <v>116</v>
       </c>
       <c r="B108" t="s">
-        <v>214</v>
+        <v>208</v>
       </c>
       <c r="C108" t="s">
-        <v>215</v>
+        <v>209</v>
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.25">
@@ -6123,10 +6129,10 @@
         <v>117</v>
       </c>
       <c r="B109" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="C109" t="s">
-        <v>217</v>
+        <v>211</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.25">
@@ -6134,10 +6140,10 @@
         <v>118</v>
       </c>
       <c r="B110" t="s">
-        <v>218</v>
-      </c>
-      <c r="C110" t="s">
-        <v>219</v>
+        <v>212</v>
+      </c>
+      <c r="C110" t="str">
+        <v>na,r2,米歇尔,neo,新视角</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.25">
@@ -6145,10 +6151,10 @@
         <v>119</v>
       </c>
       <c r="B111" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="C111" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.25">
@@ -6156,10 +6162,10 @@
         <v>120</v>
       </c>
       <c r="B112" t="s">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="C112" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.25">
@@ -6167,10 +6173,10 @@
         <v>121</v>
       </c>
       <c r="B113" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="C113" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.25">
@@ -6178,10 +6184,10 @@
         <v>122</v>
       </c>
       <c r="B114" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="C114" s="3" t="s">
-        <v>1401</v>
+        <v>1388</v>
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.25">
@@ -6189,10 +6195,10 @@
         <v>123</v>
       </c>
       <c r="B115" t="s">
-        <v>227</v>
-      </c>
-      <c r="C115" t="s">
-        <v>228</v>
+        <v>221</v>
+      </c>
+      <c r="C115" t="str">
+        <v>呼哇呼哇,梦色三明治,fuwafuwa,轻飘飘☆梦色三明治</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.25">
@@ -6200,10 +6206,10 @@
         <v>124</v>
       </c>
       <c r="B116" t="s">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="C116" t="s">
-        <v>230</v>
+        <v>224</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.25">
@@ -6211,10 +6217,10 @@
         <v>125</v>
       </c>
       <c r="B117" t="s">
-        <v>231</v>
-      </c>
-      <c r="C117" t="s">
-        <v>232</v>
+        <v>225</v>
+      </c>
+      <c r="C117" t="str">
+        <v>atz,a2z,阿三风,你行八行,武士道,天下统一,天下统一A to Z☆</v>
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.25">
@@ -6222,10 +6228,10 @@
         <v>126</v>
       </c>
       <c r="B118" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="C118" t="s">
-        <v>234</v>
+        <v>228</v>
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.25">
@@ -6233,10 +6239,10 @@
         <v>127</v>
       </c>
       <c r="B119" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="C119" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.25">
@@ -6244,10 +6250,10 @@
         <v>128</v>
       </c>
       <c r="B120" t="s">
-        <v>237</v>
-      </c>
-      <c r="C120" t="s">
-        <v>238</v>
+        <v>231</v>
+      </c>
+      <c r="C120" t="str">
+        <v>希腊奶,各位群友晚上好,lzn,六兆年,六兆年一夜物语,六兆年零一夜物语</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.25">
@@ -6255,10 +6261,10 @@
         <v>129</v>
       </c>
       <c r="B121" t="s">
-        <v>239</v>
+        <v>233</v>
       </c>
       <c r="C121" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.25">
@@ -6266,10 +6272,10 @@
         <v>130</v>
       </c>
       <c r="B122" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
       <c r="C122" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.25">
@@ -6277,10 +6283,10 @@
         <v>131</v>
       </c>
       <c r="B123" t="s">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="C123" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.25">
@@ -6288,10 +6294,10 @@
         <v>132</v>
       </c>
       <c r="B124" t="s">
-        <v>245</v>
-      </c>
-      <c r="C124" t="s">
-        <v>246</v>
+        <v>239</v>
+      </c>
+      <c r="C124" t="str">
+        <v>旧宝岛,万万岁,highfive,击掌与冒险</v>
       </c>
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.25">
@@ -6299,10 +6305,10 @@
         <v>133</v>
       </c>
       <c r="B125" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="C125" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.25">
@@ -6310,10 +6316,10 @@
         <v>134</v>
       </c>
       <c r="B126" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="C126" t="s">
-        <v>250</v>
+        <v>244</v>
       </c>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.25">
@@ -6321,10 +6327,10 @@
         <v>135</v>
       </c>
       <c r="B127" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="C127" t="s">
-        <v>252</v>
+        <v>246</v>
       </c>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.25">
@@ -6332,10 +6338,10 @@
         <v>136</v>
       </c>
       <c r="B128" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="C128" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.25">
@@ -6343,10 +6349,10 @@
         <v>137</v>
       </c>
       <c r="B129" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="C129" t="s">
-        <v>256</v>
+        <v>250</v>
       </c>
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.25">
@@ -6354,10 +6360,10 @@
         <v>138</v>
       </c>
       <c r="B130" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="C130" t="s">
-        <v>258</v>
+        <v>252</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.25">
@@ -6365,10 +6371,10 @@
         <v>139</v>
       </c>
       <c r="B131" t="s">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="C131" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.25">
@@ -6376,10 +6382,10 @@
         <v>140</v>
       </c>
       <c r="B132" t="s">
-        <v>261</v>
+        <v>255</v>
       </c>
       <c r="C132" t="s">
-        <v>262</v>
+        <v>256</v>
       </c>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.25">
@@ -6387,10 +6393,10 @@
         <v>141</v>
       </c>
       <c r="B133" t="s">
-        <v>263</v>
+        <v>257</v>
       </c>
       <c r="C133" t="s">
-        <v>264</v>
+        <v>258</v>
       </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.25">
@@ -6398,10 +6404,10 @@
         <v>142</v>
       </c>
       <c r="B134" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="C134" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.25">
@@ -6409,10 +6415,10 @@
         <v>143</v>
       </c>
       <c r="B135" t="s">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="C135" t="s">
-        <v>268</v>
+        <v>262</v>
       </c>
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.25">
@@ -6420,10 +6426,10 @@
         <v>144</v>
       </c>
       <c r="B136" t="s">
-        <v>269</v>
-      </c>
-      <c r="C136" t="s">
-        <v>270</v>
+        <v>263</v>
+      </c>
+      <c r="C136" t="str">
+        <v>ag2,与天色相连</v>
       </c>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.25">
@@ -6431,10 +6437,10 @@
         <v>145</v>
       </c>
       <c r="B137" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="C137" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.25">
@@ -6442,10 +6448,10 @@
         <v>146</v>
       </c>
       <c r="B138" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="C138" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.25">
@@ -6453,10 +6459,10 @@
         <v>147</v>
       </c>
       <c r="B139" t="s">
-        <v>275</v>
+        <v>269</v>
       </c>
       <c r="C139" t="s">
-        <v>276</v>
+        <v>270</v>
       </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.25">
@@ -6464,10 +6470,10 @@
         <v>148</v>
       </c>
       <c r="B140" t="s">
-        <v>277</v>
-      </c>
-      <c r="C140" t="s">
-        <v>278</v>
+        <v>271</v>
+      </c>
+      <c r="C140" t="str">
+        <v>绝对宣言,俏皮可爱,卡手宣言,七个大个,俏皮新键,绝对宣言～Recital～</v>
       </c>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.25">
@@ -6475,10 +6481,10 @@
         <v>149</v>
       </c>
       <c r="B141" t="s">
-        <v>279</v>
+        <v>273</v>
       </c>
       <c r="C141" t="s">
-        <v>280</v>
+        <v>274</v>
       </c>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.25">
@@ -6486,10 +6492,10 @@
         <v>150</v>
       </c>
       <c r="B142" t="s">
-        <v>281</v>
-      </c>
-      <c r="C142" t="s">
-        <v>282</v>
+        <v>275</v>
+      </c>
+      <c r="C142" t="str">
+        <v>hhw2,没你不行,非你不可,没有你不行,没你可不行,没有你可不行,没你不可,少了你可不行呢!</v>
       </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.25">
@@ -6497,10 +6503,10 @@
         <v>151</v>
       </c>
       <c r="B143" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="C143" t="s">
-        <v>284</v>
+        <v>278</v>
       </c>
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.25">
@@ -6508,10 +6514,10 @@
         <v>152</v>
       </c>
       <c r="B144" t="s">
-        <v>285</v>
+        <v>279</v>
       </c>
       <c r="C144" t="s">
-        <v>286</v>
+        <v>280</v>
       </c>
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.25">
@@ -6519,10 +6525,10 @@
         <v>153</v>
       </c>
       <c r="B145" t="s">
-        <v>287</v>
-      </c>
-      <c r="C145" t="s">
-        <v>288</v>
+        <v>281</v>
+      </c>
+      <c r="C145" t="str">
+        <v>爬,PA,热忱,热枕,热忱颂扬曲</v>
       </c>
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.25">
@@ -6530,10 +6536,10 @@
         <v>154</v>
       </c>
       <c r="B146" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="C146" t="s">
-        <v>290</v>
+        <v>284</v>
       </c>
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.25">
@@ -6541,10 +6547,10 @@
         <v>155</v>
       </c>
       <c r="B147" t="s">
-        <v>291</v>
+        <v>285</v>
       </c>
       <c r="C147" t="s">
-        <v>292</v>
+        <v>286</v>
       </c>
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.25">
@@ -6552,10 +6558,10 @@
         <v>156</v>
       </c>
       <c r="B148" t="s">
-        <v>293</v>
-      </c>
-      <c r="C148" t="s">
-        <v>294</v>
+        <v>287</v>
+      </c>
+      <c r="C148" t="str">
+        <v>小号兰,rambling memory,隆隆作响的记忆</v>
       </c>
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.25">
@@ -6563,10 +6569,10 @@
         <v>157</v>
       </c>
       <c r="B149" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="C149" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.25">
@@ -6574,10 +6580,10 @@
         <v>158</v>
       </c>
       <c r="B150" t="s">
-        <v>297</v>
-      </c>
-      <c r="C150" t="s">
-        <v>298</v>
+        <v>291</v>
+      </c>
+      <c r="C150" t="str">
+        <v>羁绊歌,kzn,kizuna music,kznmusic,羁绊,友谊的华丽乐章</v>
       </c>
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.25">
@@ -6585,10 +6591,10 @@
         <v>159</v>
       </c>
       <c r="B151" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="C151" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.25">
@@ -6596,10 +6602,10 @@
         <v>160</v>
       </c>
       <c r="B152" t="s">
-        <v>301</v>
+        <v>295</v>
       </c>
       <c r="C152" t="s">
-        <v>302</v>
+        <v>296</v>
       </c>
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.25">
@@ -6607,10 +6613,10 @@
         <v>161</v>
       </c>
       <c r="B153" t="s">
-        <v>303</v>
+        <v>297</v>
       </c>
       <c r="C153" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.25">
@@ -6618,10 +6624,10 @@
         <v>162</v>
       </c>
       <c r="B154" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="C154" t="s">
-        <v>306</v>
+        <v>300</v>
       </c>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.25">
@@ -6629,10 +6635,10 @@
         <v>163</v>
       </c>
       <c r="B155" t="s">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="C155" t="s">
-        <v>308</v>
+        <v>302</v>
       </c>
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.25">
@@ -6640,10 +6646,10 @@
         <v>164</v>
       </c>
       <c r="B156" t="s">
-        <v>309</v>
+        <v>303</v>
       </c>
       <c r="C156" t="s">
-        <v>310</v>
+        <v>304</v>
       </c>
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.25">
@@ -6651,10 +6657,10 @@
         <v>165</v>
       </c>
       <c r="B157" t="s">
-        <v>311</v>
-      </c>
-      <c r="C157" t="s">
-        <v>312</v>
+        <v>305</v>
+      </c>
+      <c r="C157" s="3" t="s">
+        <v>1398</v>
       </c>
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.25">
@@ -6662,10 +6668,10 @@
         <v>166</v>
       </c>
       <c r="B158" t="s">
-        <v>313</v>
+        <v>306</v>
       </c>
       <c r="C158" t="s">
-        <v>314</v>
+        <v>307</v>
       </c>
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.25">
@@ -6673,10 +6679,10 @@
         <v>167</v>
       </c>
       <c r="B159" t="s">
-        <v>315</v>
+        <v>308</v>
       </c>
       <c r="C159" t="s">
-        <v>316</v>
+        <v>309</v>
       </c>
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.25">
@@ -6684,10 +6690,10 @@
         <v>168</v>
       </c>
       <c r="B160" t="s">
-        <v>317</v>
+        <v>310</v>
       </c>
       <c r="C160" t="s">
-        <v>318</v>
+        <v>311</v>
       </c>
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.25">
@@ -6695,10 +6701,10 @@
         <v>169</v>
       </c>
       <c r="B161" t="s">
-        <v>319</v>
-      </c>
-      <c r="C161" t="s">
-        <v>320</v>
+        <v>312</v>
+      </c>
+      <c r="C161" t="str">
+        <v>日,mayadays,拥抱的日子</v>
       </c>
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.25">
@@ -6706,10 +6712,10 @@
         <v>170</v>
       </c>
       <c r="B162" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="C162" t="s">
-        <v>322</v>
+        <v>315</v>
       </c>
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.25">
@@ -6717,10 +6723,10 @@
         <v>171</v>
       </c>
       <c r="B163" t="s">
-        <v>323</v>
-      </c>
-      <c r="C163" t="s">
-        <v>324</v>
+        <v>316</v>
+      </c>
+      <c r="C163" t="str">
+        <v>皮卡燐燐,BPM230,太阳公公当空照,光彩照人 灿烂无比♪</v>
       </c>
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.25">
@@ -6728,10 +6734,10 @@
         <v>172</v>
       </c>
       <c r="B164" t="s">
-        <v>325</v>
+        <v>318</v>
       </c>
       <c r="C164" t="s">
-        <v>326</v>
+        <v>319</v>
       </c>
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.25">
@@ -6739,10 +6745,10 @@
         <v>173</v>
       </c>
       <c r="B165" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="C165" t="s">
-        <v>328</v>
+        <v>321</v>
       </c>
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.25">
@@ -6750,10 +6756,10 @@
         <v>174</v>
       </c>
       <c r="B166" t="s">
-        <v>329</v>
+        <v>322</v>
       </c>
       <c r="C166" t="s">
-        <v>330</v>
+        <v>323</v>
       </c>
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.25">
@@ -6761,10 +6767,10 @@
         <v>175</v>
       </c>
       <c r="B167" t="s">
-        <v>331</v>
+        <v>324</v>
       </c>
       <c r="C167" t="s">
-        <v>332</v>
+        <v>325</v>
       </c>
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.25">
@@ -6772,10 +6778,10 @@
         <v>176</v>
       </c>
       <c r="B168" t="s">
-        <v>333</v>
+        <v>326</v>
       </c>
       <c r="C168" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
     </row>
     <row r="169" spans="1:3" x14ac:dyDescent="0.25">
@@ -6783,10 +6789,10 @@
         <v>177</v>
       </c>
       <c r="B169" t="s">
-        <v>335</v>
+        <v>328</v>
       </c>
       <c r="C169" t="s">
-        <v>336</v>
+        <v>329</v>
       </c>
     </row>
     <row r="170" spans="1:3" x14ac:dyDescent="0.25">
@@ -6794,10 +6800,10 @@
         <v>178</v>
       </c>
       <c r="B170" t="s">
-        <v>337</v>
+        <v>330</v>
       </c>
       <c r="C170" t="s">
-        <v>338</v>
+        <v>331</v>
       </c>
     </row>
     <row r="171" spans="1:3" x14ac:dyDescent="0.25">
@@ -6805,10 +6811,10 @@
         <v>179</v>
       </c>
       <c r="B171" t="s">
-        <v>339</v>
-      </c>
-      <c r="C171" t="s">
-        <v>340</v>
+        <v>332</v>
+      </c>
+      <c r="C171" t="str">
+        <v>滑稽团,樱花大战,檄！帝国华击团</v>
       </c>
     </row>
     <row r="172" spans="1:3" x14ac:dyDescent="0.25">
@@ -6816,10 +6822,10 @@
         <v>180</v>
       </c>
       <c r="B172" t="s">
-        <v>341</v>
-      </c>
-      <c r="C172" t="s">
-        <v>342</v>
+        <v>334</v>
+      </c>
+      <c r="C172" t="str">
+        <v>多惠专用曲目,回归,回归之歌</v>
       </c>
     </row>
     <row r="173" spans="1:3" x14ac:dyDescent="0.25">
@@ -6827,10 +6833,10 @@
         <v>181</v>
       </c>
       <c r="B173" t="s">
-        <v>343</v>
+        <v>336</v>
       </c>
       <c r="C173" t="s">
-        <v>344</v>
+        <v>337</v>
       </c>
     </row>
     <row r="174" spans="1:3" x14ac:dyDescent="0.25">
@@ -6838,10 +6844,10 @@
         <v>182</v>
       </c>
       <c r="B174" t="s">
-        <v>345</v>
-      </c>
-      <c r="C174" t="s">
-        <v>346</v>
+        <v>338</v>
+      </c>
+      <c r="C174" t="str">
+        <v>加油追梦人,dg,追梦人出发！</v>
       </c>
     </row>
     <row r="175" spans="1:3" x14ac:dyDescent="0.25">
@@ -6849,10 +6855,10 @@
         <v>183</v>
       </c>
       <c r="B175" t="s">
-        <v>347</v>
+        <v>340</v>
       </c>
       <c r="C175" t="s">
-        <v>348</v>
+        <v>341</v>
       </c>
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.25">
@@ -6860,10 +6866,10 @@
         <v>184</v>
       </c>
       <c r="B176" t="s">
-        <v>349</v>
-      </c>
-      <c r="C176" t="s">
-        <v>350</v>
+        <v>342</v>
+      </c>
+      <c r="C176" t="str">
+        <v>oym,定滑纵连,各就各位</v>
       </c>
     </row>
     <row r="177" spans="1:3" x14ac:dyDescent="0.25">
@@ -6871,10 +6877,10 @@
         <v>185</v>
       </c>
       <c r="B177" t="s">
-        <v>351</v>
+        <v>344</v>
       </c>
       <c r="C177" t="s">
-        <v>352</v>
+        <v>345</v>
       </c>
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.25">
@@ -6882,10 +6888,10 @@
         <v>186</v>
       </c>
       <c r="B178" t="s">
-        <v>353</v>
-      </c>
-      <c r="C178" t="s">
-        <v>354</v>
+        <v>346</v>
+      </c>
+      <c r="C178" t="str">
+        <v>Q花,九枚花,下个路口见,kyumai flower,cmf,可爱而坚强的花</v>
       </c>
     </row>
     <row r="179" spans="1:3" x14ac:dyDescent="0.25">
@@ -6893,10 +6899,10 @@
         <v>187</v>
       </c>
       <c r="B179" t="s">
-        <v>355</v>
+        <v>348</v>
       </c>
       <c r="C179" t="s">
-        <v>356</v>
+        <v>349</v>
       </c>
     </row>
     <row r="180" spans="1:3" x14ac:dyDescent="0.25">
@@ -6904,10 +6910,10 @@
         <v>188</v>
       </c>
       <c r="B180" t="s">
-        <v>357</v>
+        <v>350</v>
       </c>
       <c r="C180" t="s">
-        <v>358</v>
+        <v>351</v>
       </c>
     </row>
     <row r="181" spans="1:3" x14ac:dyDescent="0.25">
@@ -6915,10 +6921,10 @@
         <v>189</v>
       </c>
       <c r="B181" t="s">
-        <v>359</v>
-      </c>
-      <c r="C181" t="s">
-        <v>360</v>
+        <v>352</v>
+      </c>
+      <c r="C181" t="str">
+        <v>娃哈哈,sing a song,哇哈哈,唱首欢笑的歌</v>
       </c>
     </row>
     <row r="182" spans="1:3" x14ac:dyDescent="0.25">
@@ -6926,10 +6932,10 @@
         <v>190</v>
       </c>
       <c r="B182" t="s">
-        <v>361</v>
+        <v>354</v>
       </c>
       <c r="C182" t="s">
-        <v>362</v>
+        <v>355</v>
       </c>
     </row>
     <row r="183" spans="1:3" x14ac:dyDescent="0.25">
@@ -6937,10 +6943,10 @@
         <v>191</v>
       </c>
       <c r="B183" t="s">
-        <v>363</v>
+        <v>356</v>
       </c>
       <c r="C183" t="s">
-        <v>364</v>
+        <v>357</v>
       </c>
     </row>
     <row r="184" spans="1:3" x14ac:dyDescent="0.25">
@@ -6948,10 +6954,10 @@
         <v>192</v>
       </c>
       <c r="B184" t="s">
-        <v>365</v>
+        <v>358</v>
       </c>
       <c r="C184" t="s">
-        <v>366</v>
+        <v>359</v>
       </c>
     </row>
     <row r="185" spans="1:3" x14ac:dyDescent="0.25">
@@ -6959,10 +6965,10 @@
         <v>193</v>
       </c>
       <c r="B185" t="s">
-        <v>367</v>
-      </c>
-      <c r="C185" t="s">
-        <v>368</v>
+        <v>360</v>
+      </c>
+      <c r="C185" t="str">
+        <v>地底人,摩尔,期待不已meets trip</v>
       </c>
     </row>
     <row r="186" spans="1:3" x14ac:dyDescent="0.25">
@@ -6970,10 +6976,10 @@
         <v>194</v>
       </c>
       <c r="B186" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="C186" t="s">
-        <v>370</v>
+        <v>363</v>
       </c>
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.25">
@@ -6981,10 +6987,10 @@
         <v>195</v>
       </c>
       <c r="B187" t="s">
-        <v>371</v>
-      </c>
-      <c r="C187" t="s">
-        <v>372</v>
+        <v>364</v>
+      </c>
+      <c r="C187" s="3" t="s">
+        <v>1395</v>
       </c>
     </row>
     <row r="188" spans="1:3" x14ac:dyDescent="0.25">
@@ -6992,10 +6998,10 @@
         <v>196</v>
       </c>
       <c r="B188" t="s">
-        <v>373</v>
+        <v>365</v>
       </c>
       <c r="C188" t="s">
-        <v>374</v>
+        <v>366</v>
       </c>
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.25">
@@ -7003,10 +7009,10 @@
         <v>197</v>
       </c>
       <c r="B189" t="s">
-        <v>375</v>
-      </c>
-      <c r="C189" t="s">
-        <v>376</v>
+        <v>367</v>
+      </c>
+      <c r="C189" t="str">
+        <v>niconico,にこにこ,rusmiling,微笑×微笑=Hyper Smile Power!</v>
       </c>
     </row>
     <row r="190" spans="1:3" x14ac:dyDescent="0.25">
@@ -7014,10 +7020,10 @@
         <v>198</v>
       </c>
       <c r="B190" t="s">
-        <v>377</v>
-      </c>
-      <c r="C190" t="s">
-        <v>378</v>
+        <v>369</v>
+      </c>
+      <c r="C190" t="str">
+        <v>春拟,春物op,拟春</v>
       </c>
     </row>
     <row r="191" spans="1:3" x14ac:dyDescent="0.25">
@@ -7025,10 +7031,10 @@
         <v>199</v>
       </c>
       <c r="B191" t="s">
-        <v>379</v>
-      </c>
-      <c r="C191" t="s">
-        <v>380</v>
+        <v>371</v>
+      </c>
+      <c r="C191" t="str">
+        <v>少歌,discovery,发现！</v>
       </c>
     </row>
     <row r="192" spans="1:3" x14ac:dyDescent="0.25">
@@ -7036,10 +7042,10 @@
         <v>200</v>
       </c>
       <c r="B192" t="s">
-        <v>381</v>
+        <v>373</v>
       </c>
       <c r="C192" t="s">
-        <v>382</v>
+        <v>374</v>
       </c>
     </row>
     <row r="193" spans="1:3" x14ac:dyDescent="0.25">
@@ -7047,10 +7053,10 @@
         <v>201</v>
       </c>
       <c r="B193" t="s">
-        <v>383</v>
+        <v>375</v>
       </c>
       <c r="C193" t="s">
-        <v>384</v>
+        <v>376</v>
       </c>
     </row>
     <row r="194" spans="1:3" x14ac:dyDescent="0.25">
@@ -7058,10 +7064,10 @@
         <v>202</v>
       </c>
       <c r="B194" t="s">
-        <v>385</v>
+        <v>377</v>
       </c>
       <c r="C194" t="s">
-        <v>386</v>
+        <v>378</v>
       </c>
     </row>
     <row r="195" spans="1:3" x14ac:dyDescent="0.25">
@@ -7069,10 +7075,10 @@
         <v>203</v>
       </c>
       <c r="B195" t="s">
-        <v>387</v>
+        <v>379</v>
       </c>
       <c r="C195" t="s">
-        <v>388</v>
+        <v>380</v>
       </c>
     </row>
     <row r="196" spans="1:3" x14ac:dyDescent="0.25">
@@ -7080,10 +7086,10 @@
         <v>204</v>
       </c>
       <c r="B196" t="s">
-        <v>389</v>
+        <v>381</v>
       </c>
       <c r="C196" t="s">
-        <v>390</v>
+        <v>382</v>
       </c>
     </row>
     <row r="197" spans="1:3" x14ac:dyDescent="0.25">
@@ -7091,10 +7097,10 @@
         <v>205</v>
       </c>
       <c r="B197" t="s">
-        <v>391</v>
+        <v>383</v>
       </c>
       <c r="C197" t="s">
-        <v>392</v>
+        <v>384</v>
       </c>
     </row>
     <row r="198" spans="1:3" x14ac:dyDescent="0.25">
@@ -7102,10 +7108,10 @@
         <v>206</v>
       </c>
       <c r="B198" t="s">
-        <v>393</v>
+        <v>385</v>
       </c>
       <c r="C198" t="s">
-        <v>394</v>
+        <v>386</v>
       </c>
     </row>
     <row r="199" spans="1:3" x14ac:dyDescent="0.25">
@@ -7113,10 +7119,10 @@
         <v>207</v>
       </c>
       <c r="B199" t="s">
-        <v>395</v>
+        <v>387</v>
       </c>
       <c r="C199" t="s">
-        <v>396</v>
+        <v>388</v>
       </c>
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.25">
@@ -7124,10 +7130,10 @@
         <v>208</v>
       </c>
       <c r="B200" t="s">
-        <v>397</v>
-      </c>
-      <c r="C200" t="s">
-        <v>398</v>
+        <v>389</v>
+      </c>
+      <c r="C200" t="str">
+        <v>上海八二一,上海821,上海甜心</v>
       </c>
     </row>
     <row r="201" spans="1:3" x14ac:dyDescent="0.25">
@@ -7135,10 +7141,10 @@
         <v>209</v>
       </c>
       <c r="B201" t="s">
-        <v>399</v>
+        <v>391</v>
       </c>
       <c r="C201" t="s">
-        <v>400</v>
+        <v>392</v>
       </c>
     </row>
     <row r="202" spans="1:3" x14ac:dyDescent="0.25">
@@ -7146,10 +7152,10 @@
         <v>210</v>
       </c>
       <c r="B202" t="s">
-        <v>401</v>
-      </c>
-      <c r="C202" t="s">
-        <v>402</v>
+        <v>393</v>
+      </c>
+      <c r="C202" t="str">
+        <v>常夏,pp泳装,炎热永恒的夏天！</v>
       </c>
     </row>
     <row r="203" spans="1:3" x14ac:dyDescent="0.25">
@@ -7157,10 +7163,10 @@
         <v>211</v>
       </c>
       <c r="B203" t="s">
-        <v>403</v>
-      </c>
-      <c r="C203" t="s">
-        <v>404</v>
+        <v>395</v>
+      </c>
+      <c r="C203" t="str">
+        <v>切沙漏,悲伤沙漏,悲伤的沙漏</v>
       </c>
     </row>
     <row r="204" spans="1:3" x14ac:dyDescent="0.25">
@@ -7168,10 +7174,10 @@
         <v>212</v>
       </c>
       <c r="B204" t="s">
-        <v>405</v>
+        <v>397</v>
       </c>
       <c r="C204" t="s">
-        <v>406</v>
+        <v>398</v>
       </c>
     </row>
     <row r="205" spans="1:3" x14ac:dyDescent="0.25">
@@ -7179,10 +7185,10 @@
         <v>213</v>
       </c>
       <c r="B205" t="s">
-        <v>407</v>
+        <v>399</v>
       </c>
       <c r="C205" t="s">
-        <v>408</v>
+        <v>400</v>
       </c>
     </row>
     <row r="206" spans="1:3" x14ac:dyDescent="0.25">
@@ -7190,10 +7196,10 @@
         <v>214</v>
       </c>
       <c r="B206" t="s">
-        <v>409</v>
+        <v>401</v>
       </c>
       <c r="C206" t="s">
-        <v>410</v>
+        <v>402</v>
       </c>
     </row>
     <row r="207" spans="1:3" x14ac:dyDescent="0.25">
@@ -7201,10 +7207,10 @@
         <v>215</v>
       </c>
       <c r="B207" t="s">
-        <v>411</v>
+        <v>403</v>
       </c>
       <c r="C207" t="s">
-        <v>412</v>
+        <v>404</v>
       </c>
     </row>
     <row r="208" spans="1:3" x14ac:dyDescent="0.25">
@@ -7212,10 +7218,10 @@
         <v>217</v>
       </c>
       <c r="B208" t="s">
-        <v>413</v>
+        <v>405</v>
       </c>
       <c r="C208" t="s">
-        <v>414</v>
+        <v>406</v>
       </c>
     </row>
     <row r="209" spans="1:3" x14ac:dyDescent="0.25">
@@ -7223,10 +7229,10 @@
         <v>218</v>
       </c>
       <c r="B209" t="s">
-        <v>415</v>
+        <v>407</v>
       </c>
       <c r="C209" t="s">
-        <v>416</v>
+        <v>408</v>
       </c>
     </row>
     <row r="210" spans="1:3" x14ac:dyDescent="0.25">
@@ -7234,10 +7240,10 @@
         <v>219</v>
       </c>
       <c r="B210" t="s">
-        <v>417</v>
+        <v>409</v>
       </c>
       <c r="C210" t="s">
-        <v>418</v>
+        <v>410</v>
       </c>
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.25">
@@ -7245,10 +7251,10 @@
         <v>220</v>
       </c>
       <c r="B211" t="s">
-        <v>419</v>
+        <v>411</v>
       </c>
       <c r="C211" t="s">
-        <v>420</v>
+        <v>412</v>
       </c>
     </row>
     <row r="212" spans="1:3" x14ac:dyDescent="0.25">
@@ -7256,10 +7262,10 @@
         <v>221</v>
       </c>
       <c r="B212" t="s">
-        <v>421</v>
+        <v>413</v>
       </c>
       <c r="C212" t="s">
-        <v>422</v>
+        <v>414</v>
       </c>
     </row>
     <row r="213" spans="1:3" x14ac:dyDescent="0.25">
@@ -7267,10 +7273,10 @@
         <v>222</v>
       </c>
       <c r="B213" t="s">
-        <v>423</v>
+        <v>415</v>
       </c>
       <c r="C213" t="s">
-        <v>424</v>
+        <v>416</v>
       </c>
     </row>
     <row r="214" spans="1:3" x14ac:dyDescent="0.25">
@@ -7278,10 +7284,10 @@
         <v>223</v>
       </c>
       <c r="B214" t="s">
-        <v>425</v>
+        <v>417</v>
       </c>
       <c r="C214" t="s">
-        <v>426</v>
+        <v>418</v>
       </c>
     </row>
     <row r="215" spans="1:3" x14ac:dyDescent="0.25">
@@ -7289,10 +7295,10 @@
         <v>224</v>
       </c>
       <c r="B215" t="s">
-        <v>427</v>
+        <v>419</v>
       </c>
       <c r="C215" t="s">
-        <v>428</v>
+        <v>420</v>
       </c>
     </row>
     <row r="216" spans="1:3" x14ac:dyDescent="0.25">
@@ -7300,10 +7306,10 @@
         <v>225</v>
       </c>
       <c r="B216" t="s">
-        <v>429</v>
+        <v>421</v>
       </c>
       <c r="C216" t="s">
-        <v>430</v>
+        <v>422</v>
       </c>
     </row>
     <row r="217" spans="1:3" x14ac:dyDescent="0.25">
@@ -7311,10 +7317,10 @@
         <v>226</v>
       </c>
       <c r="B217" t="s">
-        <v>431</v>
-      </c>
-      <c r="C217" t="s">
-        <v>432</v>
+        <v>423</v>
+      </c>
+      <c r="C217" t="str">
+        <v>u咩u咩,梦想梦想Gradation</v>
       </c>
     </row>
     <row r="218" spans="1:3" x14ac:dyDescent="0.25">
@@ -7322,10 +7328,10 @@
         <v>227</v>
       </c>
       <c r="B218" t="s">
-        <v>433</v>
+        <v>425</v>
       </c>
       <c r="C218" t="s">
-        <v>434</v>
+        <v>426</v>
       </c>
     </row>
     <row r="219" spans="1:3" x14ac:dyDescent="0.25">
@@ -7333,10 +7339,10 @@
         <v>228</v>
       </c>
       <c r="B219" t="s">
-        <v>435</v>
+        <v>427</v>
       </c>
       <c r="C219" t="s">
-        <v>436</v>
+        <v>428</v>
       </c>
     </row>
     <row r="220" spans="1:3" x14ac:dyDescent="0.25">
@@ -7344,10 +7350,10 @@
         <v>229</v>
       </c>
       <c r="B220" t="s">
-        <v>437</v>
+        <v>429</v>
       </c>
       <c r="C220" t="s">
-        <v>438</v>
+        <v>430</v>
       </c>
     </row>
     <row r="221" spans="1:3" x14ac:dyDescent="0.25">
@@ -7355,10 +7361,10 @@
         <v>230</v>
       </c>
       <c r="B221" t="s">
-        <v>439</v>
+        <v>431</v>
       </c>
       <c r="C221" t="s">
-        <v>440</v>
+        <v>432</v>
       </c>
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.25">
@@ -7366,10 +7372,10 @@
         <v>231</v>
       </c>
       <c r="B222" t="s">
-        <v>441</v>
+        <v>433</v>
       </c>
       <c r="C222" t="s">
-        <v>442</v>
+        <v>434</v>
       </c>
     </row>
     <row r="223" spans="1:3" x14ac:dyDescent="0.25">
@@ -7377,10 +7383,10 @@
         <v>232</v>
       </c>
       <c r="B223" t="s">
-        <v>443</v>
-      </c>
-      <c r="C223" t="s">
-        <v>444</v>
+        <v>435</v>
+      </c>
+      <c r="C223" t="str">
+        <v>印尼虾,initial,最初</v>
       </c>
     </row>
     <row r="224" spans="1:3" x14ac:dyDescent="0.25">
@@ -7388,10 +7394,10 @@
         <v>233</v>
       </c>
       <c r="B224" t="s">
-        <v>445</v>
+        <v>437</v>
       </c>
       <c r="C224" t="s">
-        <v>446</v>
+        <v>438</v>
       </c>
     </row>
     <row r="225" spans="1:3" x14ac:dyDescent="0.25">
@@ -7399,10 +7405,10 @@
         <v>234</v>
       </c>
       <c r="B225" t="s">
-        <v>447</v>
+        <v>439</v>
       </c>
       <c r="C225" t="s">
-        <v>448</v>
+        <v>440</v>
       </c>
     </row>
     <row r="226" spans="1:3" x14ac:dyDescent="0.25">
@@ -7410,10 +7416,10 @@
         <v>235</v>
       </c>
       <c r="B226" t="s">
-        <v>449</v>
+        <v>441</v>
       </c>
       <c r="C226" t="s">
-        <v>450</v>
+        <v>442</v>
       </c>
     </row>
     <row r="227" spans="1:3" x14ac:dyDescent="0.25">
@@ -7421,10 +7427,10 @@
         <v>236</v>
       </c>
       <c r="B227" t="s">
-        <v>451</v>
+        <v>443</v>
       </c>
       <c r="C227" t="s">
-        <v>452</v>
+        <v>444</v>
       </c>
     </row>
     <row r="228" spans="1:3" x14ac:dyDescent="0.25">
@@ -7432,10 +7438,10 @@
         <v>237</v>
       </c>
       <c r="B228" t="s">
-        <v>453</v>
+        <v>445</v>
       </c>
       <c r="C228" t="s">
-        <v>454</v>
+        <v>446</v>
       </c>
     </row>
     <row r="229" spans="1:3" x14ac:dyDescent="0.25">
@@ -7443,10 +7449,10 @@
         <v>238</v>
       </c>
       <c r="B229" t="s">
-        <v>455</v>
-      </c>
-      <c r="C229" t="s">
-        <v>456</v>
+        <v>447</v>
+      </c>
+      <c r="C229" t="str">
+        <v>花舞少女,花踊,花舞,花涌,随花起舞</v>
       </c>
     </row>
     <row r="230" spans="1:3" x14ac:dyDescent="0.25">
@@ -7454,10 +7460,10 @@
         <v>239</v>
       </c>
       <c r="B230" t="s">
-        <v>457</v>
-      </c>
-      <c r="C230" t="s">
-        <v>458</v>
+        <v>449</v>
+      </c>
+      <c r="C230" t="str">
+        <v>梦击,梦击拔,梦撃拔,梦jb,梦击碎,击穿梦想,邦邦上河图,瞬间,梦想的一击,击穿梦想的瞬间！</v>
       </c>
     </row>
     <row r="231" spans="1:3" x14ac:dyDescent="0.25">
@@ -7465,10 +7471,10 @@
         <v>240</v>
       </c>
       <c r="B231" t="s">
-        <v>459</v>
+        <v>451</v>
       </c>
       <c r="C231" t="s">
-        <v>460</v>
+        <v>452</v>
       </c>
     </row>
     <row r="232" spans="1:3" x14ac:dyDescent="0.25">
@@ -7476,10 +7482,10 @@
         <v>241</v>
       </c>
       <c r="B232" t="s">
-        <v>461</v>
+        <v>453</v>
       </c>
       <c r="C232" t="s">
-        <v>462</v>
+        <v>454</v>
       </c>
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.25">
@@ -7487,10 +7493,10 @@
         <v>242</v>
       </c>
       <c r="B233" t="s">
-        <v>463</v>
+        <v>455</v>
       </c>
       <c r="C233" t="s">
-        <v>464</v>
+        <v>456</v>
       </c>
     </row>
     <row r="234" spans="1:3" x14ac:dyDescent="0.25">
@@ -7498,10 +7504,10 @@
         <v>243</v>
       </c>
       <c r="B234" t="s">
-        <v>465</v>
+        <v>457</v>
       </c>
       <c r="C234" t="s">
-        <v>466</v>
+        <v>458</v>
       </c>
     </row>
     <row r="235" spans="1:3" x14ac:dyDescent="0.25">
@@ -7509,10 +7515,10 @@
         <v>244</v>
       </c>
       <c r="B235" t="s">
-        <v>467</v>
+        <v>459</v>
       </c>
       <c r="C235" t="s">
-        <v>468</v>
+        <v>460</v>
       </c>
     </row>
     <row r="236" spans="1:3" x14ac:dyDescent="0.25">
@@ -7520,10 +7526,10 @@
         <v>245</v>
       </c>
       <c r="B236" t="s">
-        <v>469</v>
+        <v>461</v>
       </c>
       <c r="C236" t="s">
-        <v>470</v>
+        <v>462</v>
       </c>
     </row>
     <row r="237" spans="1:3" x14ac:dyDescent="0.25">
@@ -7531,10 +7537,10 @@
         <v>246</v>
       </c>
       <c r="B237" t="s">
-        <v>471</v>
+        <v>463</v>
       </c>
       <c r="C237" t="s">
-        <v>472</v>
+        <v>464</v>
       </c>
     </row>
     <row r="238" spans="1:3" x14ac:dyDescent="0.25">
@@ -7542,10 +7548,10 @@
         <v>247</v>
       </c>
       <c r="B238" t="s">
-        <v>473</v>
+        <v>465</v>
       </c>
       <c r="C238" t="s">
-        <v>474</v>
+        <v>466</v>
       </c>
     </row>
     <row r="239" spans="1:3" x14ac:dyDescent="0.25">
@@ -7553,10 +7559,10 @@
         <v>248</v>
       </c>
       <c r="B239" t="s">
-        <v>475</v>
+        <v>467</v>
       </c>
       <c r="C239" t="s">
-        <v>476</v>
+        <v>468</v>
       </c>
     </row>
     <row r="240" spans="1:3" x14ac:dyDescent="0.25">
@@ -7564,10 +7570,10 @@
         <v>249</v>
       </c>
       <c r="B240" t="s">
-        <v>477</v>
+        <v>469</v>
       </c>
       <c r="C240" t="s">
-        <v>478</v>
+        <v>470</v>
       </c>
     </row>
     <row r="241" spans="1:3" x14ac:dyDescent="0.25">
@@ -7575,10 +7581,10 @@
         <v>250</v>
       </c>
       <c r="B241" t="s">
-        <v>479</v>
+        <v>471</v>
       </c>
       <c r="C241" t="s">
-        <v>480</v>
+        <v>472</v>
       </c>
     </row>
     <row r="242" spans="1:3" x14ac:dyDescent="0.25">
@@ -7586,10 +7592,10 @@
         <v>251</v>
       </c>
       <c r="B242" t="s">
-        <v>481</v>
+        <v>473</v>
       </c>
       <c r="C242" t="s">
-        <v>482</v>
+        <v>474</v>
       </c>
     </row>
     <row r="243" spans="1:3" x14ac:dyDescent="0.25">
@@ -7597,10 +7603,10 @@
         <v>252</v>
       </c>
       <c r="B243" t="s">
-        <v>483</v>
+        <v>475</v>
       </c>
       <c r="C243" t="s">
-        <v>484</v>
+        <v>476</v>
       </c>
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.25">
@@ -7608,10 +7614,10 @@
         <v>253</v>
       </c>
       <c r="B244" t="s">
-        <v>485</v>
+        <v>477</v>
       </c>
       <c r="C244" t="s">
-        <v>486</v>
+        <v>478</v>
       </c>
     </row>
     <row r="245" spans="1:3" x14ac:dyDescent="0.25">
@@ -7619,10 +7625,10 @@
         <v>254</v>
       </c>
       <c r="B245" t="s">
-        <v>487</v>
+        <v>479</v>
       </c>
       <c r="C245" t="s">
-        <v>488</v>
+        <v>480</v>
       </c>
     </row>
     <row r="246" spans="1:3" x14ac:dyDescent="0.25">
@@ -7630,10 +7636,10 @@
         <v>255</v>
       </c>
       <c r="B246" t="s">
-        <v>489</v>
+        <v>481</v>
       </c>
       <c r="C246" t="s">
-        <v>490</v>
+        <v>482</v>
       </c>
     </row>
     <row r="247" spans="1:3" x14ac:dyDescent="0.25">
@@ -7641,10 +7647,10 @@
         <v>256</v>
       </c>
       <c r="B247" t="s">
-        <v>491</v>
+        <v>483</v>
       </c>
       <c r="C247" t="s">
-        <v>492</v>
+        <v>484</v>
       </c>
     </row>
     <row r="248" spans="1:3" x14ac:dyDescent="0.25">
@@ -7652,10 +7658,10 @@
         <v>257</v>
       </c>
       <c r="B248" t="s">
-        <v>493</v>
+        <v>485</v>
       </c>
       <c r="C248" t="s">
-        <v>494</v>
+        <v>486</v>
       </c>
     </row>
     <row r="249" spans="1:3" x14ac:dyDescent="0.25">
@@ -7663,10 +7669,10 @@
         <v>258</v>
       </c>
       <c r="B249" t="s">
-        <v>495</v>
+        <v>487</v>
       </c>
       <c r="C249" t="s">
-        <v>496</v>
+        <v>488</v>
       </c>
     </row>
     <row r="250" spans="1:3" x14ac:dyDescent="0.25">
@@ -7674,10 +7680,10 @@
         <v>259</v>
       </c>
       <c r="B250" t="s">
-        <v>497</v>
+        <v>489</v>
       </c>
       <c r="C250" t="s">
-        <v>498</v>
+        <v>490</v>
       </c>
     </row>
     <row r="251" spans="1:3" x14ac:dyDescent="0.25">
@@ -7685,10 +7691,10 @@
         <v>260</v>
       </c>
       <c r="B251" t="s">
-        <v>499</v>
+        <v>491</v>
       </c>
       <c r="C251" t="s">
-        <v>500</v>
+        <v>492</v>
       </c>
     </row>
     <row r="252" spans="1:3" x14ac:dyDescent="0.25">
@@ -7696,10 +7702,10 @@
         <v>261</v>
       </c>
       <c r="B252" t="s">
-        <v>501</v>
+        <v>493</v>
       </c>
       <c r="C252" t="s">
-        <v>501</v>
+        <v>493</v>
       </c>
     </row>
     <row r="253" spans="1:3" x14ac:dyDescent="0.25">
@@ -7707,10 +7713,10 @@
         <v>262</v>
       </c>
       <c r="B253" t="s">
-        <v>502</v>
+        <v>494</v>
       </c>
       <c r="C253" t="s">
-        <v>503</v>
+        <v>495</v>
       </c>
     </row>
     <row r="254" spans="1:3" x14ac:dyDescent="0.25">
@@ -7718,10 +7724,10 @@
         <v>263</v>
       </c>
       <c r="B254" t="s">
-        <v>504</v>
+        <v>496</v>
       </c>
       <c r="C254" t="s">
-        <v>505</v>
+        <v>497</v>
       </c>
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.25">
@@ -7729,10 +7735,10 @@
         <v>264</v>
       </c>
       <c r="B255" t="s">
-        <v>506</v>
+        <v>498</v>
       </c>
       <c r="C255" t="s">
-        <v>507</v>
+        <v>499</v>
       </c>
     </row>
     <row r="256" spans="1:3" x14ac:dyDescent="0.25">
@@ -7740,10 +7746,10 @@
         <v>265</v>
       </c>
       <c r="B256" t="s">
-        <v>508</v>
-      </c>
-      <c r="C256" t="s">
-        <v>509</v>
+        <v>500</v>
+      </c>
+      <c r="C256" t="str">
+        <v>未来列车,火车,驶向未来的列车</v>
       </c>
     </row>
     <row r="257" spans="1:3" x14ac:dyDescent="0.25">
@@ -7751,10 +7757,10 @@
         <v>266</v>
       </c>
       <c r="B257" t="s">
-        <v>510</v>
+        <v>502</v>
       </c>
       <c r="C257" t="s">
-        <v>511</v>
+        <v>503</v>
       </c>
     </row>
     <row r="258" spans="1:3" x14ac:dyDescent="0.25">
@@ -7762,10 +7768,10 @@
         <v>267</v>
       </c>
       <c r="B258" t="s">
-        <v>512</v>
+        <v>504</v>
       </c>
       <c r="C258" t="s">
-        <v>513</v>
+        <v>505</v>
       </c>
     </row>
     <row r="259" spans="1:3" x14ac:dyDescent="0.25">
@@ -7773,10 +7779,10 @@
         <v>268</v>
       </c>
       <c r="B259" t="s">
-        <v>514</v>
+        <v>506</v>
       </c>
       <c r="C259" t="s">
-        <v>515</v>
+        <v>507</v>
       </c>
     </row>
     <row r="260" spans="1:3" x14ac:dyDescent="0.25">
@@ -7784,10 +7790,10 @@
         <v>269</v>
       </c>
       <c r="B260" t="s">
-        <v>516</v>
-      </c>
-      <c r="C260" t="s">
-        <v>517</v>
+        <v>508</v>
+      </c>
+      <c r="C260" s="3" t="s">
+        <v>1402</v>
       </c>
     </row>
     <row r="261" spans="1:3" x14ac:dyDescent="0.25">
@@ -7795,10 +7801,10 @@
         <v>270</v>
       </c>
       <c r="B261" t="s">
-        <v>518</v>
+        <v>509</v>
       </c>
       <c r="C261" t="s">
-        <v>519</v>
+        <v>510</v>
       </c>
     </row>
     <row r="262" spans="1:3" x14ac:dyDescent="0.25">
@@ -7806,10 +7812,10 @@
         <v>271</v>
       </c>
       <c r="B262" t="s">
-        <v>520</v>
+        <v>511</v>
       </c>
       <c r="C262" t="s">
-        <v>521</v>
+        <v>512</v>
       </c>
     </row>
     <row r="263" spans="1:3" x14ac:dyDescent="0.25">
@@ -7817,10 +7823,10 @@
         <v>272</v>
       </c>
       <c r="B263" t="s">
-        <v>522</v>
-      </c>
-      <c r="C263" t="s">
-        <v>523</v>
+        <v>513</v>
+      </c>
+      <c r="C263" t="str">
+        <v>孤夜,一个人,一个人的夜,独自一人的夜</v>
       </c>
     </row>
     <row r="264" spans="1:3" x14ac:dyDescent="0.25">
@@ -7828,10 +7834,10 @@
         <v>274</v>
       </c>
       <c r="B264" t="s">
-        <v>524</v>
+        <v>515</v>
       </c>
       <c r="C264" t="s">
-        <v>525</v>
+        <v>516</v>
       </c>
     </row>
     <row r="265" spans="1:3" x14ac:dyDescent="0.25">
@@ -7839,10 +7845,10 @@
         <v>275</v>
       </c>
       <c r="B265" t="s">
-        <v>526</v>
+        <v>517</v>
       </c>
       <c r="C265" t="s">
-        <v>527</v>
+        <v>518</v>
       </c>
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.25">
@@ -7850,10 +7856,10 @@
         <v>276</v>
       </c>
       <c r="B266" t="s">
-        <v>528</v>
+        <v>519</v>
       </c>
       <c r="C266" t="s">
-        <v>529</v>
+        <v>520</v>
       </c>
     </row>
     <row r="267" spans="1:3" x14ac:dyDescent="0.25">
@@ -7861,10 +7867,10 @@
         <v>277</v>
       </c>
       <c r="B267" t="s">
-        <v>530</v>
+        <v>521</v>
       </c>
       <c r="C267" t="s">
-        <v>531</v>
+        <v>522</v>
       </c>
     </row>
     <row r="268" spans="1:3" x14ac:dyDescent="0.25">
@@ -7872,10 +7878,10 @@
         <v>278</v>
       </c>
       <c r="B268" t="s">
-        <v>532</v>
+        <v>523</v>
       </c>
       <c r="C268" t="s">
-        <v>533</v>
+        <v>524</v>
       </c>
     </row>
     <row r="269" spans="1:3" x14ac:dyDescent="0.25">
@@ -7883,10 +7889,10 @@
         <v>279</v>
       </c>
       <c r="B269" t="s">
-        <v>534</v>
-      </c>
-      <c r="C269" t="s">
-        <v>535</v>
+        <v>525</v>
+      </c>
+      <c r="C269" t="str">
+        <v>foh,希望之火,希望之焰</v>
       </c>
     </row>
     <row r="270" spans="1:3" x14ac:dyDescent="0.25">
@@ -7894,10 +7900,10 @@
         <v>280</v>
       </c>
       <c r="B270" t="s">
-        <v>536</v>
+        <v>527</v>
       </c>
       <c r="C270" t="s">
-        <v>537</v>
+        <v>528</v>
       </c>
     </row>
     <row r="271" spans="1:3" x14ac:dyDescent="0.25">
@@ -7905,10 +7911,10 @@
         <v>281</v>
       </c>
       <c r="B271" t="s">
-        <v>538</v>
+        <v>529</v>
       </c>
       <c r="C271" t="s">
-        <v>539</v>
+        <v>530</v>
       </c>
     </row>
     <row r="272" spans="1:3" x14ac:dyDescent="0.25">
@@ -7916,10 +7922,10 @@
         <v>282</v>
       </c>
       <c r="B272" t="s">
-        <v>540</v>
+        <v>531</v>
       </c>
       <c r="C272" t="s">
-        <v>541</v>
+        <v>532</v>
       </c>
     </row>
     <row r="273" spans="1:3" x14ac:dyDescent="0.25">
@@ -7927,10 +7933,10 @@
         <v>283</v>
       </c>
       <c r="B273" t="s">
-        <v>542</v>
+        <v>533</v>
       </c>
       <c r="C273" t="s">
-        <v>543</v>
+        <v>534</v>
       </c>
     </row>
     <row r="274" spans="1:3" x14ac:dyDescent="0.25">
@@ -7938,10 +7944,10 @@
         <v>284</v>
       </c>
       <c r="B274" t="s">
-        <v>544</v>
+        <v>535</v>
       </c>
       <c r="C274" t="s">
-        <v>545</v>
+        <v>536</v>
       </c>
     </row>
     <row r="275" spans="1:3" x14ac:dyDescent="0.25">
@@ -7949,10 +7955,10 @@
         <v>285</v>
       </c>
       <c r="B275" t="s">
-        <v>546</v>
+        <v>537</v>
       </c>
       <c r="C275" t="s">
-        <v>547</v>
+        <v>538</v>
       </c>
     </row>
     <row r="276" spans="1:3" x14ac:dyDescent="0.25">
@@ -7960,10 +7966,10 @@
         <v>286</v>
       </c>
       <c r="B276" t="s">
-        <v>548</v>
-      </c>
-      <c r="C276" t="s">
-        <v>549</v>
+        <v>539</v>
+      </c>
+      <c r="C276" s="3" t="s">
+        <v>1394</v>
       </c>
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.25">
@@ -7971,10 +7977,10 @@
         <v>287</v>
       </c>
       <c r="B277" t="s">
-        <v>550</v>
-      </c>
-      <c r="C277" t="s">
-        <v>551</v>
+        <v>540</v>
+      </c>
+      <c r="C277" t="str">
+        <v>恋心强,街头霸王,小室,爱恋 心痛 坚强</v>
       </c>
     </row>
     <row r="278" spans="1:3" x14ac:dyDescent="0.25">
@@ -7982,10 +7988,10 @@
         <v>288</v>
       </c>
       <c r="B278" t="s">
-        <v>552</v>
+        <v>542</v>
       </c>
       <c r="C278" t="s">
-        <v>553</v>
+        <v>543</v>
       </c>
     </row>
     <row r="279" spans="1:3" x14ac:dyDescent="0.25">
@@ -7993,10 +7999,10 @@
         <v>289</v>
       </c>
       <c r="B279" t="s">
-        <v>554</v>
+        <v>544</v>
       </c>
       <c r="C279" t="s">
-        <v>555</v>
+        <v>545</v>
       </c>
     </row>
     <row r="280" spans="1:3" x14ac:dyDescent="0.25">
@@ -8004,10 +8010,10 @@
         <v>290</v>
       </c>
       <c r="B280" t="s">
-        <v>556</v>
+        <v>546</v>
       </c>
       <c r="C280" t="s">
-        <v>557</v>
+        <v>547</v>
       </c>
     </row>
     <row r="281" spans="1:3" x14ac:dyDescent="0.25">
@@ -8015,10 +8021,10 @@
         <v>291</v>
       </c>
       <c r="B281" t="s">
-        <v>558</v>
+        <v>548</v>
       </c>
       <c r="C281" t="s">
-        <v>559</v>
+        <v>549</v>
       </c>
     </row>
     <row r="282" spans="1:3" x14ac:dyDescent="0.25">
@@ -8026,10 +8032,10 @@
         <v>292</v>
       </c>
       <c r="B282" t="s">
-        <v>560</v>
+        <v>550</v>
       </c>
       <c r="C282" t="s">
-        <v>561</v>
+        <v>551</v>
       </c>
     </row>
     <row r="283" spans="1:3" x14ac:dyDescent="0.25">
@@ -8037,10 +8043,10 @@
         <v>293</v>
       </c>
       <c r="B283" t="s">
-        <v>562</v>
+        <v>552</v>
       </c>
       <c r="C283" t="s">
-        <v>563</v>
+        <v>553</v>
       </c>
     </row>
     <row r="284" spans="1:3" x14ac:dyDescent="0.25">
@@ -8048,10 +8054,10 @@
         <v>294</v>
       </c>
       <c r="B284" t="s">
-        <v>564</v>
+        <v>554</v>
       </c>
       <c r="C284" t="s">
-        <v>565</v>
+        <v>555</v>
       </c>
     </row>
     <row r="285" spans="1:3" x14ac:dyDescent="0.25">
@@ -8059,10 +8065,10 @@
         <v>295</v>
       </c>
       <c r="B285" t="s">
-        <v>566</v>
+        <v>556</v>
       </c>
       <c r="C285" t="s">
-        <v>567</v>
+        <v>557</v>
       </c>
     </row>
     <row r="286" spans="1:3" x14ac:dyDescent="0.25">
@@ -8070,10 +8076,10 @@
         <v>296</v>
       </c>
       <c r="B286" t="s">
-        <v>568</v>
+        <v>558</v>
       </c>
       <c r="C286" t="s">
-        <v>569</v>
+        <v>559</v>
       </c>
     </row>
     <row r="287" spans="1:3" x14ac:dyDescent="0.25">
@@ -8081,10 +8087,10 @@
         <v>297</v>
       </c>
       <c r="B287" t="s">
-        <v>570</v>
-      </c>
-      <c r="C287" t="s">
-        <v>571</v>
+        <v>560</v>
+      </c>
+      <c r="C287" t="str">
+        <v>小魔女,光吉猛修,小魔女嘉年华！！</v>
       </c>
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.25">
@@ -8092,10 +8098,10 @@
         <v>298</v>
       </c>
       <c r="B288" t="s">
-        <v>572</v>
+        <v>562</v>
       </c>
       <c r="C288" t="s">
-        <v>573</v>
+        <v>563</v>
       </c>
     </row>
     <row r="289" spans="1:3" x14ac:dyDescent="0.25">
@@ -8103,10 +8109,10 @@
         <v>299</v>
       </c>
       <c r="B289" t="s">
-        <v>574</v>
+        <v>564</v>
       </c>
       <c r="C289" t="s">
-        <v>575</v>
+        <v>565</v>
       </c>
     </row>
     <row r="290" spans="1:3" x14ac:dyDescent="0.25">
@@ -8114,10 +8120,10 @@
         <v>300</v>
       </c>
       <c r="B290" t="s">
-        <v>576</v>
+        <v>566</v>
       </c>
       <c r="C290" t="s">
-        <v>577</v>
+        <v>567</v>
       </c>
     </row>
     <row r="291" spans="1:3" x14ac:dyDescent="0.25">
@@ -8125,10 +8131,10 @@
         <v>301</v>
       </c>
       <c r="B291" t="s">
-        <v>578</v>
+        <v>568</v>
       </c>
       <c r="C291" t="s">
-        <v>579</v>
+        <v>569</v>
       </c>
     </row>
     <row r="292" spans="1:3" x14ac:dyDescent="0.25">
@@ -8136,10 +8142,10 @@
         <v>302</v>
       </c>
       <c r="B292" t="s">
-        <v>580</v>
+        <v>570</v>
       </c>
       <c r="C292" t="s">
-        <v>581</v>
+        <v>571</v>
       </c>
     </row>
     <row r="293" spans="1:3" x14ac:dyDescent="0.25">
@@ -8147,10 +8153,10 @@
         <v>303</v>
       </c>
       <c r="B293" t="s">
-        <v>582</v>
+        <v>572</v>
       </c>
       <c r="C293" t="s">
-        <v>583</v>
+        <v>573</v>
       </c>
     </row>
     <row r="294" spans="1:3" x14ac:dyDescent="0.25">
@@ -8158,10 +8164,10 @@
         <v>304</v>
       </c>
       <c r="B294" t="s">
-        <v>584</v>
+        <v>574</v>
       </c>
       <c r="C294" t="s">
-        <v>585</v>
+        <v>575</v>
       </c>
     </row>
     <row r="295" spans="1:3" x14ac:dyDescent="0.25">
@@ -8169,10 +8175,10 @@
         <v>305</v>
       </c>
       <c r="B295" t="s">
-        <v>586</v>
-      </c>
-      <c r="C295" t="s">
-        <v>587</v>
+        <v>576</v>
+      </c>
+      <c r="C295" s="3" t="s">
+        <v>1401</v>
       </c>
     </row>
     <row r="296" spans="1:3" x14ac:dyDescent="0.25">
@@ -8180,10 +8186,10 @@
         <v>306</v>
       </c>
       <c r="B296" t="s">
-        <v>588</v>
+        <v>577</v>
       </c>
       <c r="C296" t="s">
-        <v>589</v>
+        <v>578</v>
       </c>
     </row>
     <row r="297" spans="1:3" x14ac:dyDescent="0.25">
@@ -8191,10 +8197,10 @@
         <v>307</v>
       </c>
       <c r="B297" t="s">
-        <v>590</v>
+        <v>579</v>
       </c>
       <c r="C297" t="s">
-        <v>591</v>
+        <v>580</v>
       </c>
     </row>
     <row r="298" spans="1:3" x14ac:dyDescent="0.25">
@@ -8202,10 +8208,10 @@
         <v>308</v>
       </c>
       <c r="B298" t="s">
-        <v>592</v>
+        <v>581</v>
       </c>
       <c r="C298" t="s">
-        <v>593</v>
+        <v>582</v>
       </c>
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.25">
@@ -8213,10 +8219,10 @@
         <v>309</v>
       </c>
       <c r="B299" t="s">
-        <v>594</v>
+        <v>583</v>
       </c>
       <c r="C299" t="s">
-        <v>595</v>
+        <v>584</v>
       </c>
     </row>
     <row r="300" spans="1:3" x14ac:dyDescent="0.25">
@@ -8224,10 +8230,10 @@
         <v>310</v>
       </c>
       <c r="B300" t="s">
-        <v>596</v>
+        <v>585</v>
       </c>
       <c r="C300" t="s">
-        <v>597</v>
+        <v>586</v>
       </c>
     </row>
     <row r="301" spans="1:3" x14ac:dyDescent="0.25">
@@ -8235,10 +8241,10 @@
         <v>311</v>
       </c>
       <c r="B301" t="s">
-        <v>598</v>
+        <v>587</v>
       </c>
       <c r="C301" t="s">
-        <v>599</v>
+        <v>588</v>
       </c>
     </row>
     <row r="302" spans="1:3" x14ac:dyDescent="0.25">
@@ -8246,10 +8252,10 @@
         <v>312</v>
       </c>
       <c r="B302" t="s">
-        <v>600</v>
+        <v>589</v>
       </c>
       <c r="C302" t="s">
-        <v>601</v>
+        <v>590</v>
       </c>
     </row>
     <row r="303" spans="1:3" x14ac:dyDescent="0.25">
@@ -8257,10 +8263,10 @@
         <v>313</v>
       </c>
       <c r="B303" t="s">
-        <v>602</v>
+        <v>591</v>
       </c>
       <c r="C303" t="s">
-        <v>603</v>
+        <v>592</v>
       </c>
     </row>
     <row r="304" spans="1:3" x14ac:dyDescent="0.25">
@@ -8268,10 +8274,10 @@
         <v>314</v>
       </c>
       <c r="B304" t="s">
-        <v>604</v>
+        <v>593</v>
       </c>
       <c r="C304" t="s">
-        <v>605</v>
+        <v>594</v>
       </c>
     </row>
     <row r="305" spans="1:3" x14ac:dyDescent="0.25">
@@ -8279,10 +8285,10 @@
         <v>315</v>
       </c>
       <c r="B305" t="s">
-        <v>606</v>
+        <v>595</v>
       </c>
       <c r="C305" t="s">
-        <v>607</v>
+        <v>596</v>
       </c>
     </row>
     <row r="306" spans="1:3" x14ac:dyDescent="0.25">
@@ -8290,10 +8296,10 @@
         <v>316</v>
       </c>
       <c r="B306" t="s">
-        <v>608</v>
+        <v>597</v>
       </c>
       <c r="C306" t="s">
-        <v>609</v>
+        <v>598</v>
       </c>
     </row>
     <row r="307" spans="1:3" x14ac:dyDescent="0.25">
@@ -8301,10 +8307,10 @@
         <v>317</v>
       </c>
       <c r="B307" t="s">
-        <v>610</v>
-      </c>
-      <c r="C307" t="s">
-        <v>611</v>
+        <v>599</v>
+      </c>
+      <c r="C307" s="3" t="s">
+        <v>1396</v>
       </c>
     </row>
     <row r="308" spans="1:3" x14ac:dyDescent="0.25">
@@ -8312,10 +8318,10 @@
         <v>318</v>
       </c>
       <c r="B308" t="s">
-        <v>612</v>
+        <v>600</v>
       </c>
       <c r="C308" t="s">
-        <v>613</v>
+        <v>601</v>
       </c>
     </row>
     <row r="309" spans="1:3" x14ac:dyDescent="0.25">
@@ -8323,10 +8329,10 @@
         <v>319</v>
       </c>
       <c r="B309" t="s">
-        <v>614</v>
-      </c>
-      <c r="C309" t="s">
-        <v>615</v>
+        <v>602</v>
+      </c>
+      <c r="C309" t="str">
+        <v>武士之心,银魂,slih,武士之魂</v>
       </c>
     </row>
     <row r="310" spans="1:3" x14ac:dyDescent="0.25">
@@ -8334,10 +8340,10 @@
         <v>320</v>
       </c>
       <c r="B310" t="s">
-        <v>616</v>
+        <v>604</v>
       </c>
       <c r="C310" t="s">
-        <v>617</v>
+        <v>605</v>
       </c>
     </row>
     <row r="311" spans="1:3" x14ac:dyDescent="0.25">
@@ -8345,10 +8351,10 @@
         <v>321</v>
       </c>
       <c r="B311" t="s">
-        <v>618</v>
+        <v>606</v>
       </c>
       <c r="C311" t="s">
-        <v>619</v>
+        <v>607</v>
       </c>
     </row>
     <row r="312" spans="1:3" x14ac:dyDescent="0.25">
@@ -8356,10 +8362,10 @@
         <v>322</v>
       </c>
       <c r="B312" t="s">
-        <v>620</v>
+        <v>608</v>
       </c>
       <c r="C312" t="s">
-        <v>621</v>
+        <v>609</v>
       </c>
     </row>
     <row r="313" spans="1:3" x14ac:dyDescent="0.25">
@@ -8367,10 +8373,10 @@
         <v>323</v>
       </c>
       <c r="B313" t="s">
-        <v>622</v>
+        <v>610</v>
       </c>
       <c r="C313" t="s">
-        <v>623</v>
+        <v>611</v>
       </c>
     </row>
     <row r="314" spans="1:3" x14ac:dyDescent="0.25">
@@ -8378,10 +8384,10 @@
         <v>324</v>
       </c>
       <c r="B314" t="s">
-        <v>624</v>
+        <v>612</v>
       </c>
       <c r="C314" t="s">
-        <v>625</v>
+        <v>613</v>
       </c>
     </row>
     <row r="315" spans="1:3" x14ac:dyDescent="0.25">
@@ -8389,10 +8395,10 @@
         <v>325</v>
       </c>
       <c r="B315" t="s">
-        <v>626</v>
+        <v>614</v>
       </c>
       <c r="C315" t="s">
-        <v>627</v>
+        <v>615</v>
       </c>
     </row>
     <row r="316" spans="1:3" x14ac:dyDescent="0.25">
@@ -8400,10 +8406,10 @@
         <v>326</v>
       </c>
       <c r="B316" t="s">
-        <v>628</v>
+        <v>616</v>
       </c>
       <c r="C316" t="s">
-        <v>629</v>
+        <v>617</v>
       </c>
     </row>
     <row r="317" spans="1:3" x14ac:dyDescent="0.25">
@@ -8411,10 +8417,10 @@
         <v>327</v>
       </c>
       <c r="B317" t="s">
-        <v>630</v>
+        <v>618</v>
       </c>
       <c r="C317" t="s">
-        <v>631</v>
+        <v>619</v>
       </c>
     </row>
     <row r="318" spans="1:3" x14ac:dyDescent="0.25">
@@ -8422,10 +8428,10 @@
         <v>328</v>
       </c>
       <c r="B318" t="s">
-        <v>632</v>
+        <v>620</v>
       </c>
       <c r="C318" t="s">
-        <v>633</v>
+        <v>621</v>
       </c>
     </row>
     <row r="319" spans="1:3" x14ac:dyDescent="0.25">
@@ -8433,10 +8439,10 @@
         <v>329</v>
       </c>
       <c r="B319" t="s">
-        <v>634</v>
+        <v>622</v>
       </c>
       <c r="C319" t="s">
-        <v>635</v>
+        <v>623</v>
       </c>
     </row>
     <row r="320" spans="1:3" x14ac:dyDescent="0.25">
@@ -8444,10 +8450,10 @@
         <v>330</v>
       </c>
       <c r="B320" t="s">
-        <v>636</v>
+        <v>624</v>
       </c>
       <c r="C320" t="s">
-        <v>637</v>
+        <v>625</v>
       </c>
     </row>
     <row r="321" spans="1:3" x14ac:dyDescent="0.25">
@@ -8455,10 +8461,10 @@
         <v>331</v>
       </c>
       <c r="B321" t="s">
-        <v>638</v>
+        <v>626</v>
       </c>
       <c r="C321" t="s">
-        <v>639</v>
+        <v>627</v>
       </c>
     </row>
     <row r="322" spans="1:3" x14ac:dyDescent="0.25">
@@ -8466,10 +8472,10 @@
         <v>332</v>
       </c>
       <c r="B322" t="s">
-        <v>640</v>
+        <v>628</v>
       </c>
       <c r="C322" t="s">
-        <v>641</v>
+        <v>629</v>
       </c>
     </row>
     <row r="323" spans="1:3" x14ac:dyDescent="0.25">
@@ -8477,10 +8483,10 @@
         <v>333</v>
       </c>
       <c r="B323" t="s">
-        <v>642</v>
+        <v>630</v>
       </c>
       <c r="C323" t="s">
-        <v>643</v>
+        <v>631</v>
       </c>
     </row>
     <row r="324" spans="1:3" x14ac:dyDescent="0.25">
@@ -8488,10 +8494,10 @@
         <v>334</v>
       </c>
       <c r="B324" t="s">
-        <v>644</v>
+        <v>632</v>
       </c>
       <c r="C324" t="s">
-        <v>645</v>
+        <v>633</v>
       </c>
     </row>
     <row r="325" spans="1:3" x14ac:dyDescent="0.25">
@@ -8499,10 +8505,10 @@
         <v>335</v>
       </c>
       <c r="B325" t="s">
-        <v>646</v>
+        <v>634</v>
       </c>
       <c r="C325" t="s">
-        <v>647</v>
+        <v>635</v>
       </c>
     </row>
     <row r="326" spans="1:3" x14ac:dyDescent="0.25">
@@ -8510,10 +8516,10 @@
         <v>336</v>
       </c>
       <c r="B326" t="s">
-        <v>648</v>
-      </c>
-      <c r="C326" t="s">
-        <v>649</v>
+        <v>636</v>
+      </c>
+      <c r="C326" s="3" t="s">
+        <v>1397</v>
       </c>
     </row>
     <row r="327" spans="1:3" x14ac:dyDescent="0.25">
@@ -8521,10 +8527,10 @@
         <v>337</v>
       </c>
       <c r="B327" t="s">
-        <v>650</v>
+        <v>637</v>
       </c>
       <c r="C327" t="s">
-        <v>651</v>
+        <v>638</v>
       </c>
     </row>
     <row r="328" spans="1:3" x14ac:dyDescent="0.25">
@@ -8532,10 +8538,10 @@
         <v>338</v>
       </c>
       <c r="B328" t="s">
-        <v>652</v>
+        <v>639</v>
       </c>
       <c r="C328" t="s">
-        <v>653</v>
+        <v>640</v>
       </c>
     </row>
     <row r="329" spans="1:3" x14ac:dyDescent="0.25">
@@ -8543,10 +8549,10 @@
         <v>339</v>
       </c>
       <c r="B329" t="s">
-        <v>654</v>
+        <v>641</v>
       </c>
       <c r="C329" t="s">
-        <v>655</v>
+        <v>642</v>
       </c>
     </row>
     <row r="330" spans="1:3" x14ac:dyDescent="0.25">
@@ -8554,10 +8560,10 @@
         <v>340</v>
       </c>
       <c r="B330" t="s">
-        <v>656</v>
+        <v>643</v>
       </c>
       <c r="C330" t="s">
-        <v>657</v>
+        <v>644</v>
       </c>
     </row>
     <row r="331" spans="1:3" x14ac:dyDescent="0.25">
@@ -8565,10 +8571,10 @@
         <v>341</v>
       </c>
       <c r="B331" t="s">
-        <v>658</v>
+        <v>645</v>
       </c>
       <c r="C331" t="s">
-        <v>659</v>
+        <v>646</v>
       </c>
     </row>
     <row r="332" spans="1:3" x14ac:dyDescent="0.25">
@@ -8576,10 +8582,10 @@
         <v>342</v>
       </c>
       <c r="B332" t="s">
-        <v>660</v>
+        <v>647</v>
       </c>
       <c r="C332" t="s">
-        <v>661</v>
+        <v>648</v>
       </c>
     </row>
     <row r="333" spans="1:3" x14ac:dyDescent="0.25">
@@ -8587,10 +8593,10 @@
         <v>343</v>
       </c>
       <c r="B333" t="s">
-        <v>662</v>
+        <v>649</v>
       </c>
       <c r="C333" t="s">
-        <v>663</v>
+        <v>650</v>
       </c>
     </row>
     <row r="334" spans="1:3" x14ac:dyDescent="0.25">
@@ -8598,10 +8604,10 @@
         <v>344</v>
       </c>
       <c r="B334" t="s">
-        <v>664</v>
+        <v>651</v>
       </c>
       <c r="C334" t="s">
-        <v>665</v>
+        <v>652</v>
       </c>
     </row>
     <row r="335" spans="1:3" x14ac:dyDescent="0.25">
@@ -8609,10 +8615,10 @@
         <v>345</v>
       </c>
       <c r="B335" t="s">
-        <v>666</v>
+        <v>653</v>
       </c>
       <c r="C335" t="s">
-        <v>667</v>
+        <v>654</v>
       </c>
     </row>
     <row r="336" spans="1:3" x14ac:dyDescent="0.25">
@@ -8620,10 +8626,10 @@
         <v>346</v>
       </c>
       <c r="B336" t="s">
-        <v>668</v>
-      </c>
-      <c r="C336" t="s">
-        <v>669</v>
+        <v>655</v>
+      </c>
+      <c r="C336" t="str">
+        <v>r3,齐颂,齐声高歌,蜜雪冰城,一齐歌诵</v>
       </c>
     </row>
     <row r="337" spans="1:3" x14ac:dyDescent="0.25">
@@ -8631,10 +8637,10 @@
         <v>347</v>
       </c>
       <c r="B337" t="s">
-        <v>670</v>
+        <v>657</v>
       </c>
       <c r="C337" t="s">
-        <v>671</v>
+        <v>658</v>
       </c>
     </row>
     <row r="338" spans="1:3" x14ac:dyDescent="0.25">
@@ -8642,10 +8648,10 @@
         <v>348</v>
       </c>
       <c r="B338" t="s">
-        <v>672</v>
+        <v>659</v>
       </c>
       <c r="C338" t="s">
-        <v>673</v>
+        <v>660</v>
       </c>
     </row>
     <row r="339" spans="1:3" x14ac:dyDescent="0.25">
@@ -8653,10 +8659,10 @@
         <v>349</v>
       </c>
       <c r="B339" t="s">
-        <v>674</v>
+        <v>661</v>
       </c>
       <c r="C339" t="s">
-        <v>675</v>
+        <v>662</v>
       </c>
     </row>
     <row r="340" spans="1:3" x14ac:dyDescent="0.25">
@@ -8664,10 +8670,10 @@
         <v>350</v>
       </c>
       <c r="B340" t="s">
-        <v>676</v>
+        <v>663</v>
       </c>
       <c r="C340" t="s">
-        <v>677</v>
+        <v>664</v>
       </c>
     </row>
     <row r="341" spans="1:3" x14ac:dyDescent="0.25">
@@ -8675,10 +8681,10 @@
         <v>351</v>
       </c>
       <c r="B341" t="s">
-        <v>678</v>
+        <v>665</v>
       </c>
       <c r="C341" t="s">
-        <v>679</v>
+        <v>666</v>
       </c>
     </row>
     <row r="342" spans="1:3" x14ac:dyDescent="0.25">
@@ -8686,10 +8692,10 @@
         <v>352</v>
       </c>
       <c r="B342" t="s">
-        <v>680</v>
+        <v>667</v>
       </c>
       <c r="C342" t="s">
-        <v>681</v>
+        <v>668</v>
       </c>
     </row>
     <row r="343" spans="1:3" x14ac:dyDescent="0.25">
@@ -8697,10 +8703,10 @@
         <v>353</v>
       </c>
       <c r="B343" t="s">
-        <v>682</v>
-      </c>
-      <c r="C343" t="s">
-        <v>683</v>
+        <v>669</v>
+      </c>
+      <c r="C343" t="str">
+        <v>绊色,我们奏响的合奏曲是,羁绊色的合奏</v>
       </c>
     </row>
     <row r="344" spans="1:3" x14ac:dyDescent="0.25">
@@ -8708,10 +8714,10 @@
         <v>354</v>
       </c>
       <c r="B344" t="s">
-        <v>684</v>
+        <v>671</v>
       </c>
       <c r="C344" t="s">
-        <v>685</v>
+        <v>672</v>
       </c>
     </row>
     <row r="345" spans="1:3" x14ac:dyDescent="0.25">
@@ -8719,10 +8725,10 @@
         <v>355</v>
       </c>
       <c r="B345" t="s">
-        <v>686</v>
-      </c>
-      <c r="C345" t="s">
-        <v>687</v>
+        <v>673</v>
+      </c>
+      <c r="C345" t="str">
+        <v>竞宴,喜宴,囍宴,婚后高歌曲,对山歌,山歌,美竹兰你就是个（）,美竹兰你就是个(),红紫,竞演,竞宴Red×Violet</v>
       </c>
     </row>
     <row r="346" spans="1:3" x14ac:dyDescent="0.25">
@@ -8730,10 +8736,10 @@
         <v>356</v>
       </c>
       <c r="B346" t="s">
-        <v>688</v>
+        <v>675</v>
       </c>
       <c r="C346" t="s">
-        <v>689</v>
+        <v>676</v>
       </c>
     </row>
     <row r="347" spans="1:3" x14ac:dyDescent="0.25">
@@ -8741,10 +8747,10 @@
         <v>357</v>
       </c>
       <c r="B347" t="s">
-        <v>690</v>
-      </c>
-      <c r="C347" t="s">
-        <v>691</v>
+        <v>677</v>
+      </c>
+      <c r="C347" t="str">
+        <v>重金属儿歌,rashappy,电子核儿歌,这也能27,rashapeople,女孩的快乐力量</v>
       </c>
     </row>
     <row r="348" spans="1:3" x14ac:dyDescent="0.25">
@@ -8752,10 +8758,10 @@
         <v>358</v>
       </c>
       <c r="B348" t="s">
-        <v>692</v>
+        <v>679</v>
       </c>
       <c r="C348" t="s">
-        <v>693</v>
+        <v>680</v>
       </c>
     </row>
     <row r="349" spans="1:3" x14ac:dyDescent="0.25">
@@ -8763,10 +8769,10 @@
         <v>359</v>
       </c>
       <c r="B349" t="s">
-        <v>694</v>
+        <v>681</v>
       </c>
       <c r="C349" t="s">
-        <v>695</v>
+        <v>682</v>
       </c>
     </row>
     <row r="350" spans="1:3" x14ac:dyDescent="0.25">
@@ -8774,10 +8780,10 @@
         <v>360</v>
       </c>
       <c r="B350" t="s">
-        <v>696</v>
-      </c>
-      <c r="C350" t="s">
-        <v>697</v>
+        <v>683</v>
+      </c>
+      <c r="C350" t="str">
+        <v>突击莉莉,土鸡莉莉,sw,神圣世界,神圣的世界</v>
       </c>
     </row>
     <row r="351" spans="1:3" x14ac:dyDescent="0.25">
@@ -8785,10 +8791,10 @@
         <v>361</v>
       </c>
       <c r="B351" t="s">
-        <v>698</v>
+        <v>685</v>
       </c>
       <c r="C351" t="s">
-        <v>699</v>
+        <v>686</v>
       </c>
     </row>
     <row r="352" spans="1:3" x14ac:dyDescent="0.25">
@@ -8796,10 +8802,10 @@
         <v>362</v>
       </c>
       <c r="B352" t="s">
-        <v>700</v>
-      </c>
-      <c r="C352" t="s">
-        <v>701</v>
+        <v>687</v>
+      </c>
+      <c r="C352" t="str">
+        <v>恐怖马戏团,万圣,hhw万圣,与你闪耀的庆典</v>
       </c>
     </row>
     <row r="353" spans="1:3" x14ac:dyDescent="0.25">
@@ -8807,10 +8813,10 @@
         <v>363</v>
       </c>
       <c r="B353" t="s">
-        <v>702</v>
+        <v>689</v>
       </c>
       <c r="C353" t="s">
-        <v>703</v>
+        <v>690</v>
       </c>
     </row>
     <row r="354" spans="1:3" x14ac:dyDescent="0.25">
@@ -8818,10 +8824,10 @@
         <v>364</v>
       </c>
       <c r="B354" t="s">
-        <v>704</v>
+        <v>691</v>
       </c>
       <c r="C354" t="s">
-        <v>705</v>
+        <v>692</v>
       </c>
     </row>
     <row r="355" spans="1:3" x14ac:dyDescent="0.25">
@@ -8829,10 +8835,10 @@
         <v>365</v>
       </c>
       <c r="B355" t="s">
-        <v>706</v>
-      </c>
-      <c r="C355" t="s">
-        <v>707</v>
+        <v>693</v>
+      </c>
+      <c r="C355" t="str">
+        <v>m2,夜飞,伴夜飞翔</v>
       </c>
     </row>
     <row r="356" spans="1:3" x14ac:dyDescent="0.25">
@@ -8840,10 +8846,10 @@
         <v>366</v>
       </c>
       <c r="B356" t="s">
-        <v>708</v>
+        <v>695</v>
       </c>
       <c r="C356" t="s">
-        <v>709</v>
+        <v>696</v>
       </c>
     </row>
     <row r="357" spans="1:3" x14ac:dyDescent="0.25">
@@ -8851,10 +8857,10 @@
         <v>367</v>
       </c>
       <c r="B357" t="s">
-        <v>710</v>
+        <v>697</v>
       </c>
       <c r="C357" t="s">
-        <v>711</v>
+        <v>698</v>
       </c>
     </row>
     <row r="358" spans="1:3" x14ac:dyDescent="0.25">
@@ -8862,10 +8868,10 @@
         <v>368</v>
       </c>
       <c r="B358" t="s">
-        <v>712</v>
+        <v>699</v>
       </c>
       <c r="C358" t="s">
-        <v>713</v>
+        <v>700</v>
       </c>
     </row>
     <row r="359" spans="1:3" x14ac:dyDescent="0.25">
@@ -8873,10 +8879,10 @@
         <v>369</v>
       </c>
       <c r="B359" t="s">
-        <v>714</v>
+        <v>701</v>
       </c>
       <c r="C359" t="s">
-        <v>715</v>
+        <v>702</v>
       </c>
     </row>
     <row r="360" spans="1:3" x14ac:dyDescent="0.25">
@@ -8884,10 +8890,10 @@
         <v>370</v>
       </c>
       <c r="B360" t="s">
-        <v>716</v>
-      </c>
-      <c r="C360" t="s">
-        <v>717</v>
+        <v>703</v>
+      </c>
+      <c r="C360" t="str">
+        <v>万岁,怕死怕累,人生万岁,趴趴累,啪啪累,怕怕累,人生！万万岁！</v>
       </c>
     </row>
     <row r="361" spans="1:3" x14ac:dyDescent="0.25">
@@ -8895,10 +8901,10 @@
         <v>371</v>
       </c>
       <c r="B361" t="s">
-        <v>718</v>
+        <v>705</v>
       </c>
       <c r="C361" t="s">
-        <v>719</v>
+        <v>706</v>
       </c>
     </row>
     <row r="362" spans="1:3" x14ac:dyDescent="0.25">
@@ -8906,10 +8912,10 @@
         <v>372</v>
       </c>
       <c r="B362" t="s">
-        <v>720</v>
+        <v>707</v>
       </c>
       <c r="C362" t="s">
-        <v>721</v>
+        <v>708</v>
       </c>
     </row>
     <row r="363" spans="1:3" x14ac:dyDescent="0.25">
@@ -8917,10 +8923,10 @@
         <v>373</v>
       </c>
       <c r="B363" t="s">
-        <v>722</v>
+        <v>709</v>
       </c>
       <c r="C363" t="s">
-        <v>723</v>
+        <v>710</v>
       </c>
     </row>
     <row r="364" spans="1:3" x14ac:dyDescent="0.25">
@@ -8928,10 +8934,10 @@
         <v>374</v>
       </c>
       <c r="B364" t="s">
-        <v>724</v>
+        <v>711</v>
       </c>
       <c r="C364" t="s">
-        <v>725</v>
+        <v>712</v>
       </c>
     </row>
     <row r="365" spans="1:3" x14ac:dyDescent="0.25">
@@ -8939,10 +8945,10 @@
         <v>375</v>
       </c>
       <c r="B365" t="s">
-        <v>726</v>
+        <v>713</v>
       </c>
       <c r="C365" t="s">
-        <v>727</v>
+        <v>714</v>
       </c>
     </row>
     <row r="366" spans="1:3" x14ac:dyDescent="0.25">
@@ -8950,10 +8956,10 @@
         <v>376</v>
       </c>
       <c r="B366" t="s">
-        <v>728</v>
+        <v>715</v>
       </c>
       <c r="C366" t="s">
-        <v>729</v>
+        <v>716</v>
       </c>
     </row>
     <row r="367" spans="1:3" x14ac:dyDescent="0.25">
@@ -8961,10 +8967,10 @@
         <v>377</v>
       </c>
       <c r="B367" t="s">
-        <v>730</v>
+        <v>717</v>
       </c>
       <c r="C367" t="s">
-        <v>731</v>
+        <v>718</v>
       </c>
     </row>
     <row r="368" spans="1:3" x14ac:dyDescent="0.25">
@@ -8972,10 +8978,10 @@
         <v>378</v>
       </c>
       <c r="B368" t="s">
-        <v>732</v>
+        <v>719</v>
       </c>
       <c r="C368" t="s">
-        <v>733</v>
+        <v>720</v>
       </c>
     </row>
     <row r="369" spans="1:3" x14ac:dyDescent="0.25">
@@ -8983,10 +8989,10 @@
         <v>379</v>
       </c>
       <c r="B369" t="s">
-        <v>734</v>
+        <v>721</v>
       </c>
       <c r="C369" t="s">
-        <v>735</v>
+        <v>722</v>
       </c>
     </row>
     <row r="370" spans="1:3" x14ac:dyDescent="0.25">
@@ -8994,10 +9000,10 @@
         <v>380</v>
       </c>
       <c r="B370" t="s">
-        <v>736</v>
+        <v>723</v>
       </c>
       <c r="C370" t="s">
-        <v>737</v>
+        <v>724</v>
       </c>
     </row>
     <row r="371" spans="1:3" x14ac:dyDescent="0.25">
@@ -9005,10 +9011,10 @@
         <v>381</v>
       </c>
       <c r="B371" t="s">
-        <v>738</v>
+        <v>725</v>
       </c>
       <c r="C371" t="s">
-        <v>739</v>
+        <v>726</v>
       </c>
     </row>
     <row r="372" spans="1:3" x14ac:dyDescent="0.25">
@@ -9016,10 +9022,10 @@
         <v>382</v>
       </c>
       <c r="B372" t="s">
-        <v>740</v>
+        <v>727</v>
       </c>
       <c r="C372" t="s">
-        <v>741</v>
+        <v>728</v>
       </c>
     </row>
     <row r="373" spans="1:3" x14ac:dyDescent="0.25">
@@ -9027,10 +9033,10 @@
         <v>383</v>
       </c>
       <c r="B373" t="s">
-        <v>742</v>
+        <v>729</v>
       </c>
       <c r="C373" t="s">
-        <v>743</v>
+        <v>730</v>
       </c>
     </row>
     <row r="374" spans="1:3" x14ac:dyDescent="0.25">
@@ -9038,10 +9044,10 @@
         <v>384</v>
       </c>
       <c r="B374" t="s">
-        <v>744</v>
+        <v>731</v>
       </c>
       <c r="C374" t="s">
-        <v>745</v>
+        <v>732</v>
       </c>
     </row>
     <row r="375" spans="1:3" x14ac:dyDescent="0.25">
@@ -9049,10 +9055,10 @@
         <v>385</v>
       </c>
       <c r="B375" t="s">
-        <v>746</v>
+        <v>733</v>
       </c>
       <c r="C375" t="s">
-        <v>747</v>
+        <v>734</v>
       </c>
     </row>
     <row r="376" spans="1:3" x14ac:dyDescent="0.25">
@@ -9060,10 +9066,10 @@
         <v>386</v>
       </c>
       <c r="B376" t="s">
-        <v>748</v>
+        <v>735</v>
       </c>
       <c r="C376" t="s">
-        <v>749</v>
+        <v>736</v>
       </c>
     </row>
     <row r="377" spans="1:3" x14ac:dyDescent="0.25">
@@ -9071,10 +9077,10 @@
         <v>387</v>
       </c>
       <c r="B377" t="s">
-        <v>750</v>
+        <v>737</v>
       </c>
       <c r="C377" t="s">
-        <v>751</v>
+        <v>738</v>
       </c>
     </row>
     <row r="378" spans="1:3" x14ac:dyDescent="0.25">
@@ -9082,10 +9088,10 @@
         <v>388</v>
       </c>
       <c r="B378" t="s">
-        <v>752</v>
+        <v>739</v>
       </c>
       <c r="C378" t="s">
-        <v>753</v>
+        <v>740</v>
       </c>
     </row>
     <row r="379" spans="1:3" x14ac:dyDescent="0.25">
@@ -9093,10 +9099,10 @@
         <v>389</v>
       </c>
       <c r="B379" t="s">
-        <v>754</v>
+        <v>741</v>
       </c>
       <c r="C379" t="s">
-        <v>755</v>
+        <v>742</v>
       </c>
     </row>
     <row r="380" spans="1:3" x14ac:dyDescent="0.25">
@@ -9104,10 +9110,10 @@
         <v>390</v>
       </c>
       <c r="B380" t="s">
-        <v>756</v>
+        <v>743</v>
       </c>
       <c r="C380" t="s">
-        <v>757</v>
+        <v>744</v>
       </c>
     </row>
     <row r="381" spans="1:3" x14ac:dyDescent="0.25">
@@ -9115,10 +9121,10 @@
         <v>391</v>
       </c>
       <c r="B381" t="s">
-        <v>758</v>
+        <v>745</v>
       </c>
       <c r="C381" t="s">
-        <v>759</v>
+        <v>746</v>
       </c>
     </row>
     <row r="382" spans="1:3" x14ac:dyDescent="0.25">
@@ -9126,10 +9132,10 @@
         <v>392</v>
       </c>
       <c r="B382" t="s">
-        <v>760</v>
+        <v>747</v>
       </c>
       <c r="C382" t="s">
-        <v>761</v>
+        <v>748</v>
       </c>
     </row>
     <row r="383" spans="1:3" x14ac:dyDescent="0.25">
@@ -9137,10 +9143,10 @@
         <v>393</v>
       </c>
       <c r="B383" t="s">
-        <v>762</v>
-      </c>
-      <c r="C383" t="s">
-        <v>763</v>
+        <v>749</v>
+      </c>
+      <c r="C383" t="str">
+        <v>怪盗2,出现啦,大怪盗,哈批,哈罗哈皮,小贼船,贼船2,贼床2,海盗床2,海盗船2,现身！大怪盗哈罗海皮！</v>
       </c>
     </row>
     <row r="384" spans="1:3" x14ac:dyDescent="0.25">
@@ -9148,10 +9154,10 @@
         <v>394</v>
       </c>
       <c r="B384" t="s">
-        <v>764</v>
+        <v>751</v>
       </c>
       <c r="C384" t="s">
-        <v>765</v>
+        <v>752</v>
       </c>
     </row>
     <row r="385" spans="1:3" x14ac:dyDescent="0.25">
@@ -9159,10 +9165,10 @@
         <v>395</v>
       </c>
       <c r="B385" t="s">
-        <v>766</v>
+        <v>753</v>
       </c>
       <c r="C385" t="s">
-        <v>767</v>
+        <v>754</v>
       </c>
     </row>
     <row r="386" spans="1:3" x14ac:dyDescent="0.25">
@@ -9170,10 +9176,10 @@
         <v>396</v>
       </c>
       <c r="B386" t="s">
-        <v>768</v>
+        <v>755</v>
       </c>
       <c r="C386" t="s">
-        <v>769</v>
+        <v>756</v>
       </c>
     </row>
     <row r="387" spans="1:3" x14ac:dyDescent="0.25">
@@ -9181,10 +9187,10 @@
         <v>397</v>
       </c>
       <c r="B387" t="s">
-        <v>770</v>
+        <v>757</v>
       </c>
       <c r="C387" t="s">
-        <v>771</v>
+        <v>758</v>
       </c>
     </row>
     <row r="388" spans="1:3" x14ac:dyDescent="0.25">
@@ -9192,10 +9198,10 @@
         <v>398</v>
       </c>
       <c r="B388" t="s">
-        <v>772</v>
-      </c>
-      <c r="C388" t="s">
-        <v>773</v>
+        <v>759</v>
+      </c>
+      <c r="C388" t="str">
+        <v>五蝶进窗,一步一个脚印</v>
       </c>
     </row>
     <row r="389" spans="1:3" x14ac:dyDescent="0.25">
@@ -9203,10 +9209,10 @@
         <v>399</v>
       </c>
       <c r="B389" t="s">
-        <v>774</v>
+        <v>761</v>
       </c>
       <c r="C389" t="s">
-        <v>775</v>
+        <v>762</v>
       </c>
     </row>
     <row r="390" spans="1:3" x14ac:dyDescent="0.25">
@@ -9214,10 +9220,10 @@
         <v>400</v>
       </c>
       <c r="B390" t="s">
-        <v>776</v>
+        <v>763</v>
       </c>
       <c r="C390" t="s">
-        <v>777</v>
+        <v>764</v>
       </c>
     </row>
     <row r="391" spans="1:3" x14ac:dyDescent="0.25">
@@ -9225,10 +9231,10 @@
         <v>401</v>
       </c>
       <c r="B391" t="s">
-        <v>778</v>
+        <v>765</v>
       </c>
       <c r="C391" t="s">
-        <v>779</v>
+        <v>766</v>
       </c>
     </row>
     <row r="392" spans="1:3" ht="19.2" x14ac:dyDescent="0.45">
@@ -9236,10 +9242,10 @@
         <v>402</v>
       </c>
       <c r="B392" t="s">
-        <v>780</v>
+        <v>767</v>
       </c>
       <c r="C392" t="s">
-        <v>781</v>
+        <v>768</v>
       </c>
     </row>
     <row r="393" spans="1:3" x14ac:dyDescent="0.25">
@@ -9247,10 +9253,10 @@
         <v>403</v>
       </c>
       <c r="B393" t="s">
-        <v>782</v>
+        <v>769</v>
       </c>
       <c r="C393" t="s">
-        <v>783</v>
+        <v>770</v>
       </c>
     </row>
     <row r="394" spans="1:3" x14ac:dyDescent="0.25">
@@ -9258,10 +9264,10 @@
         <v>404</v>
       </c>
       <c r="B394" t="s">
-        <v>784</v>
+        <v>771</v>
       </c>
       <c r="C394" t="s">
-        <v>785</v>
+        <v>772</v>
       </c>
     </row>
     <row r="395" spans="1:3" x14ac:dyDescent="0.25">
@@ -9269,10 +9275,10 @@
         <v>405</v>
       </c>
       <c r="B395" t="s">
-        <v>786</v>
+        <v>773</v>
       </c>
       <c r="C395" t="s">
-        <v>787</v>
+        <v>774</v>
       </c>
     </row>
     <row r="396" spans="1:3" x14ac:dyDescent="0.25">
@@ -9280,10 +9286,10 @@
         <v>406</v>
       </c>
       <c r="B396" t="s">
-        <v>788</v>
+        <v>775</v>
       </c>
       <c r="C396" t="s">
-        <v>789</v>
+        <v>776</v>
       </c>
     </row>
     <row r="397" spans="1:3" x14ac:dyDescent="0.25">
@@ -9291,10 +9297,10 @@
         <v>407</v>
       </c>
       <c r="B397" t="s">
-        <v>790</v>
+        <v>777</v>
       </c>
       <c r="C397" t="s">
-        <v>791</v>
+        <v>778</v>
       </c>
     </row>
     <row r="398" spans="1:3" x14ac:dyDescent="0.25">
@@ -9302,10 +9308,10 @@
         <v>408</v>
       </c>
       <c r="B398" t="s">
-        <v>792</v>
+        <v>779</v>
       </c>
       <c r="C398" t="s">
-        <v>793</v>
+        <v>780</v>
       </c>
     </row>
     <row r="399" spans="1:3" x14ac:dyDescent="0.25">
@@ -9313,10 +9319,10 @@
         <v>409</v>
       </c>
       <c r="B399" t="s">
-        <v>794</v>
+        <v>781</v>
       </c>
       <c r="C399" t="s">
-        <v>795</v>
+        <v>782</v>
       </c>
     </row>
     <row r="400" spans="1:3" x14ac:dyDescent="0.25">
@@ -9324,10 +9330,10 @@
         <v>410</v>
       </c>
       <c r="B400" t="s">
-        <v>796</v>
+        <v>783</v>
       </c>
       <c r="C400" t="s">
-        <v>797</v>
+        <v>784</v>
       </c>
     </row>
     <row r="401" spans="1:3" x14ac:dyDescent="0.25">
@@ -9335,10 +9341,10 @@
         <v>411</v>
       </c>
       <c r="B401" t="s">
-        <v>798</v>
+        <v>785</v>
       </c>
       <c r="C401" t="s">
-        <v>799</v>
+        <v>786</v>
       </c>
     </row>
     <row r="402" spans="1:3" x14ac:dyDescent="0.25">
@@ -9346,10 +9352,10 @@
         <v>412</v>
       </c>
       <c r="B402" t="s">
-        <v>800</v>
+        <v>787</v>
       </c>
       <c r="C402" t="s">
-        <v>801</v>
+        <v>788</v>
       </c>
     </row>
     <row r="403" spans="1:3" x14ac:dyDescent="0.25">
@@ -9357,10 +9363,10 @@
         <v>413</v>
       </c>
       <c r="B403" t="s">
-        <v>802</v>
+        <v>789</v>
       </c>
       <c r="C403" t="s">
-        <v>803</v>
+        <v>790</v>
       </c>
     </row>
     <row r="404" spans="1:3" x14ac:dyDescent="0.25">
@@ -9368,10 +9374,10 @@
         <v>414</v>
       </c>
       <c r="B404" t="s">
-        <v>804</v>
+        <v>791</v>
       </c>
       <c r="C404" t="s">
-        <v>805</v>
+        <v>792</v>
       </c>
     </row>
     <row r="405" spans="1:3" x14ac:dyDescent="0.25">
@@ -9379,10 +9385,10 @@
         <v>415</v>
       </c>
       <c r="B405" t="s">
-        <v>806</v>
+        <v>793</v>
       </c>
       <c r="C405" t="s">
-        <v>807</v>
+        <v>794</v>
       </c>
     </row>
     <row r="406" spans="1:3" x14ac:dyDescent="0.25">
@@ -9390,10 +9396,10 @@
         <v>416</v>
       </c>
       <c r="B406" t="s">
-        <v>808</v>
+        <v>795</v>
       </c>
       <c r="C406" t="s">
-        <v>809</v>
+        <v>796</v>
       </c>
     </row>
     <row r="407" spans="1:3" x14ac:dyDescent="0.25">
@@ -9401,10 +9407,10 @@
         <v>417</v>
       </c>
       <c r="B407" t="s">
-        <v>810</v>
+        <v>797</v>
       </c>
       <c r="C407" t="s">
-        <v>811</v>
+        <v>798</v>
       </c>
     </row>
     <row r="408" spans="1:3" x14ac:dyDescent="0.25">
@@ -9412,10 +9418,10 @@
         <v>418</v>
       </c>
       <c r="B408" t="s">
-        <v>812</v>
-      </c>
-      <c r="C408" t="s">
-        <v>813</v>
+        <v>799</v>
+      </c>
+      <c r="C408" t="str">
+        <v>青空狂想曲,小林家的龙女仆,妹抖龙,舅舅爷,弟媳,六舅,啊那个郭德纲,微辣猪,蓝天的狂想曲</v>
       </c>
     </row>
     <row r="409" spans="1:3" x14ac:dyDescent="0.25">
@@ -9423,10 +9429,10 @@
         <v>419</v>
       </c>
       <c r="B409" t="s">
-        <v>814</v>
+        <v>801</v>
       </c>
       <c r="C409" t="s">
-        <v>815</v>
+        <v>802</v>
       </c>
     </row>
     <row r="410" spans="1:3" x14ac:dyDescent="0.25">
@@ -9434,10 +9440,10 @@
         <v>420</v>
       </c>
       <c r="B410" t="s">
-        <v>816</v>
+        <v>803</v>
       </c>
       <c r="C410" t="s">
-        <v>817</v>
+        <v>804</v>
       </c>
     </row>
     <row r="411" spans="1:3" x14ac:dyDescent="0.25">
@@ -9445,10 +9451,10 @@
         <v>421</v>
       </c>
       <c r="B411" t="s">
-        <v>818</v>
+        <v>805</v>
       </c>
       <c r="C411" t="s">
-        <v>819</v>
+        <v>806</v>
       </c>
     </row>
     <row r="412" spans="1:3" x14ac:dyDescent="0.25">
@@ -9456,10 +9462,10 @@
         <v>422</v>
       </c>
       <c r="B412" t="s">
-        <v>820</v>
+        <v>807</v>
       </c>
       <c r="C412" t="s">
-        <v>821</v>
+        <v>808</v>
       </c>
     </row>
     <row r="413" spans="1:3" x14ac:dyDescent="0.25">
@@ -9467,10 +9473,10 @@
         <v>423</v>
       </c>
       <c r="B413" t="s">
-        <v>822</v>
+        <v>809</v>
       </c>
       <c r="C413" t="s">
-        <v>823</v>
+        <v>810</v>
       </c>
     </row>
     <row r="414" spans="1:3" x14ac:dyDescent="0.25">
@@ -9478,10 +9484,10 @@
         <v>424</v>
       </c>
       <c r="B414" t="s">
-        <v>824</v>
+        <v>811</v>
       </c>
       <c r="C414" t="s">
-        <v>825</v>
+        <v>812</v>
       </c>
     </row>
     <row r="415" spans="1:3" x14ac:dyDescent="0.25">
@@ -9489,10 +9495,10 @@
         <v>425</v>
       </c>
       <c r="B415" t="s">
-        <v>826</v>
+        <v>813</v>
       </c>
       <c r="C415" t="s">
-        <v>827</v>
+        <v>814</v>
       </c>
     </row>
     <row r="416" spans="1:3" x14ac:dyDescent="0.25">
@@ -9500,10 +9506,10 @@
         <v>426</v>
       </c>
       <c r="B416" t="s">
-        <v>828</v>
+        <v>815</v>
       </c>
       <c r="C416" t="s">
-        <v>829</v>
+        <v>816</v>
       </c>
     </row>
     <row r="417" spans="1:3" x14ac:dyDescent="0.25">
@@ -9511,10 +9517,10 @@
         <v>427</v>
       </c>
       <c r="B417" t="s">
-        <v>830</v>
+        <v>817</v>
       </c>
       <c r="C417" t="s">
-        <v>831</v>
+        <v>818</v>
       </c>
     </row>
     <row r="418" spans="1:3" x14ac:dyDescent="0.25">
@@ -9522,10 +9528,10 @@
         <v>428</v>
       </c>
       <c r="B418" t="s">
-        <v>832</v>
+        <v>819</v>
       </c>
       <c r="C418" t="s">
-        <v>833</v>
+        <v>820</v>
       </c>
     </row>
     <row r="419" spans="1:3" x14ac:dyDescent="0.25">
@@ -9533,10 +9539,10 @@
         <v>429</v>
       </c>
       <c r="B419" t="s">
-        <v>834</v>
+        <v>821</v>
       </c>
       <c r="C419" t="s">
-        <v>835</v>
+        <v>822</v>
       </c>
     </row>
     <row r="420" spans="1:3" x14ac:dyDescent="0.25">
@@ -9544,10 +9550,10 @@
         <v>430</v>
       </c>
       <c r="B420" t="s">
-        <v>836</v>
+        <v>823</v>
       </c>
       <c r="C420" t="s">
-        <v>837</v>
+        <v>824</v>
       </c>
     </row>
     <row r="421" spans="1:3" x14ac:dyDescent="0.25">
@@ -9555,10 +9561,10 @@
         <v>431</v>
       </c>
       <c r="B421" t="s">
-        <v>838</v>
+        <v>825</v>
       </c>
       <c r="C421" t="s">
-        <v>839</v>
+        <v>826</v>
       </c>
     </row>
     <row r="422" spans="1:3" x14ac:dyDescent="0.25">
@@ -9566,10 +9572,10 @@
         <v>432</v>
       </c>
       <c r="B422" t="s">
-        <v>840</v>
+        <v>827</v>
       </c>
       <c r="C422" t="s">
-        <v>841</v>
+        <v>828</v>
       </c>
     </row>
     <row r="423" spans="1:3" x14ac:dyDescent="0.25">
@@ -9577,10 +9583,10 @@
         <v>433</v>
       </c>
       <c r="B423" t="s">
-        <v>842</v>
+        <v>829</v>
       </c>
       <c r="C423" t="s">
-        <v>843</v>
+        <v>830</v>
       </c>
     </row>
     <row r="424" spans="1:3" x14ac:dyDescent="0.25">
@@ -9588,10 +9594,10 @@
         <v>434</v>
       </c>
       <c r="B424" t="s">
-        <v>844</v>
+        <v>831</v>
       </c>
       <c r="C424" t="s">
-        <v>845</v>
+        <v>832</v>
       </c>
     </row>
     <row r="425" spans="1:3" x14ac:dyDescent="0.25">
@@ -9599,10 +9605,10 @@
         <v>435</v>
       </c>
       <c r="B425" t="s">
-        <v>846</v>
-      </c>
-      <c r="C425" t="s">
-        <v>847</v>
+        <v>833</v>
+      </c>
+      <c r="C425" t="str">
+        <v>morfonication,寄边日日,寄边,sunny sunny,能够依靠的晴天</v>
       </c>
     </row>
     <row r="426" spans="1:3" x14ac:dyDescent="0.25">
@@ -9610,10 +9616,10 @@
         <v>436</v>
       </c>
       <c r="B426" t="s">
-        <v>848</v>
+        <v>835</v>
       </c>
       <c r="C426" t="s">
-        <v>849</v>
+        <v>836</v>
       </c>
     </row>
     <row r="427" spans="1:3" x14ac:dyDescent="0.25">
@@ -9621,10 +9627,10 @@
         <v>437</v>
       </c>
       <c r="B427" t="s">
-        <v>850</v>
+        <v>837</v>
       </c>
       <c r="C427" t="s">
-        <v>851</v>
+        <v>838</v>
       </c>
     </row>
     <row r="428" spans="1:3" x14ac:dyDescent="0.25">
@@ -9632,10 +9638,10 @@
         <v>438</v>
       </c>
       <c r="B428" t="s">
-        <v>852</v>
+        <v>839</v>
       </c>
       <c r="C428" t="s">
-        <v>789</v>
+        <v>776</v>
       </c>
     </row>
     <row r="429" spans="1:3" x14ac:dyDescent="0.25">
@@ -9643,10 +9649,10 @@
         <v>439</v>
       </c>
       <c r="B429" t="s">
-        <v>853</v>
+        <v>840</v>
       </c>
       <c r="C429" t="s">
-        <v>854</v>
+        <v>841</v>
       </c>
     </row>
     <row r="430" spans="1:3" x14ac:dyDescent="0.25">
@@ -9654,10 +9660,10 @@
         <v>440</v>
       </c>
       <c r="B430" t="s">
-        <v>855</v>
+        <v>842</v>
       </c>
       <c r="C430" t="s">
-        <v>856</v>
+        <v>843</v>
       </c>
     </row>
     <row r="431" spans="1:3" x14ac:dyDescent="0.25">
@@ -9665,10 +9671,10 @@
         <v>441</v>
       </c>
       <c r="B431" t="s">
-        <v>857</v>
+        <v>844</v>
       </c>
       <c r="C431" t="s">
-        <v>858</v>
+        <v>845</v>
       </c>
     </row>
     <row r="432" spans="1:3" x14ac:dyDescent="0.25">
@@ -9676,10 +9682,10 @@
         <v>442</v>
       </c>
       <c r="B432" t="s">
-        <v>859</v>
+        <v>846</v>
       </c>
       <c r="C432" t="s">
-        <v>860</v>
+        <v>847</v>
       </c>
     </row>
     <row r="433" spans="1:3" x14ac:dyDescent="0.25">
@@ -9687,10 +9693,10 @@
         <v>443</v>
       </c>
       <c r="B433" t="s">
-        <v>861</v>
+        <v>848</v>
       </c>
       <c r="C433" t="s">
-        <v>862</v>
+        <v>849</v>
       </c>
     </row>
     <row r="434" spans="1:3" x14ac:dyDescent="0.25">
@@ -9698,10 +9704,10 @@
         <v>444</v>
       </c>
       <c r="B434" t="s">
-        <v>863</v>
+        <v>850</v>
       </c>
       <c r="C434" t="s">
-        <v>864</v>
+        <v>851</v>
       </c>
     </row>
     <row r="435" spans="1:3" x14ac:dyDescent="0.25">
@@ -9709,10 +9715,10 @@
         <v>445</v>
       </c>
       <c r="B435" t="s">
-        <v>865</v>
+        <v>852</v>
       </c>
       <c r="C435" t="s">
-        <v>866</v>
+        <v>853</v>
       </c>
     </row>
     <row r="436" spans="1:3" x14ac:dyDescent="0.25">
@@ -9720,10 +9726,10 @@
         <v>446</v>
       </c>
       <c r="B436" t="s">
-        <v>867</v>
+        <v>854</v>
       </c>
       <c r="C436" t="s">
-        <v>868</v>
+        <v>855</v>
       </c>
     </row>
     <row r="437" spans="1:3" x14ac:dyDescent="0.25">
@@ -9731,10 +9737,10 @@
         <v>447</v>
       </c>
       <c r="B437" t="s">
-        <v>869</v>
+        <v>856</v>
       </c>
       <c r="C437" t="s">
-        <v>870</v>
+        <v>857</v>
       </c>
     </row>
     <row r="438" spans="1:3" x14ac:dyDescent="0.25">
@@ -9742,10 +9748,10 @@
         <v>448</v>
       </c>
       <c r="B438" t="s">
-        <v>871</v>
+        <v>858</v>
       </c>
       <c r="C438" t="s">
-        <v>872</v>
+        <v>859</v>
       </c>
     </row>
     <row r="439" spans="1:3" x14ac:dyDescent="0.25">
@@ -9753,10 +9759,10 @@
         <v>449</v>
       </c>
       <c r="B439" t="s">
-        <v>873</v>
+        <v>860</v>
       </c>
       <c r="C439" t="s">
-        <v>874</v>
+        <v>861</v>
       </c>
     </row>
     <row r="440" spans="1:3" x14ac:dyDescent="0.25">
@@ -9764,10 +9770,10 @@
         <v>450</v>
       </c>
       <c r="B440" t="s">
-        <v>875</v>
+        <v>862</v>
       </c>
       <c r="C440" t="s">
-        <v>876</v>
+        <v>863</v>
       </c>
     </row>
     <row r="441" spans="1:3" x14ac:dyDescent="0.25">
@@ -9775,10 +9781,10 @@
         <v>451</v>
       </c>
       <c r="B441" t="s">
-        <v>877</v>
+        <v>864</v>
       </c>
       <c r="C441" t="s">
-        <v>878</v>
+        <v>865</v>
       </c>
     </row>
     <row r="442" spans="1:3" x14ac:dyDescent="0.25">
@@ -9786,10 +9792,10 @@
         <v>452</v>
       </c>
       <c r="B442" t="s">
-        <v>879</v>
+        <v>866</v>
       </c>
       <c r="C442" t="s">
-        <v>880</v>
+        <v>867</v>
       </c>
     </row>
     <row r="443" spans="1:3" x14ac:dyDescent="0.25">
@@ -9797,10 +9803,10 @@
         <v>453</v>
       </c>
       <c r="B443" t="s">
-        <v>881</v>
+        <v>868</v>
       </c>
       <c r="C443" t="s">
-        <v>882</v>
+        <v>869</v>
       </c>
     </row>
     <row r="444" spans="1:3" x14ac:dyDescent="0.25">
@@ -9808,10 +9814,10 @@
         <v>455</v>
       </c>
       <c r="B444" t="s">
-        <v>883</v>
-      </c>
-      <c r="C444" t="s">
-        <v>884</v>
+        <v>870</v>
+      </c>
+      <c r="C444" t="str">
+        <v>史莱姆,无名故事,轴交互采小提琴,无名物语</v>
       </c>
     </row>
     <row r="445" spans="1:3" x14ac:dyDescent="0.25">
@@ -9819,10 +9825,10 @@
         <v>456</v>
       </c>
       <c r="B445" t="s">
-        <v>885</v>
+        <v>872</v>
       </c>
       <c r="C445" t="s">
-        <v>886</v>
+        <v>873</v>
       </c>
     </row>
     <row r="446" spans="1:3" x14ac:dyDescent="0.25">
@@ -9830,10 +9836,10 @@
         <v>457</v>
       </c>
       <c r="B446" t="s">
-        <v>887</v>
+        <v>874</v>
       </c>
       <c r="C446" t="s">
-        <v>888</v>
+        <v>875</v>
       </c>
     </row>
     <row r="447" spans="1:3" x14ac:dyDescent="0.25">
@@ -9841,10 +9847,10 @@
         <v>458</v>
       </c>
       <c r="B447" t="s">
-        <v>889</v>
+        <v>876</v>
       </c>
       <c r="C447" t="s">
-        <v>890</v>
+        <v>877</v>
       </c>
     </row>
     <row r="448" spans="1:3" x14ac:dyDescent="0.25">
@@ -9852,10 +9858,10 @@
         <v>459</v>
       </c>
       <c r="B448" t="s">
-        <v>891</v>
+        <v>878</v>
       </c>
       <c r="C448" t="s">
-        <v>892</v>
+        <v>879</v>
       </c>
     </row>
     <row r="449" spans="1:3" x14ac:dyDescent="0.25">
@@ -9863,10 +9869,10 @@
         <v>460</v>
       </c>
       <c r="B449" t="s">
-        <v>893</v>
-      </c>
-      <c r="C449" t="s">
-        <v>894</v>
+        <v>880</v>
+      </c>
+      <c r="C449" t="str">
+        <v>Are you ready?,好了吗,笑容，准备好了吗？？？</v>
       </c>
     </row>
     <row r="450" spans="1:3" x14ac:dyDescent="0.25">
@@ -9874,10 +9880,10 @@
         <v>461</v>
       </c>
       <c r="B450" t="s">
-        <v>895</v>
+        <v>882</v>
       </c>
       <c r="C450" t="s">
-        <v>896</v>
+        <v>883</v>
       </c>
     </row>
     <row r="451" spans="1:3" x14ac:dyDescent="0.25">
@@ -9885,10 +9891,10 @@
         <v>462</v>
       </c>
       <c r="B451" t="s">
-        <v>754</v>
+        <v>741</v>
       </c>
       <c r="C451" t="s">
-        <v>897</v>
+        <v>884</v>
       </c>
     </row>
     <row r="452" spans="1:3" x14ac:dyDescent="0.25">
@@ -9896,10 +9902,10 @@
         <v>463</v>
       </c>
       <c r="B452" t="s">
-        <v>898</v>
+        <v>885</v>
       </c>
       <c r="C452" t="s">
-        <v>899</v>
+        <v>886</v>
       </c>
     </row>
     <row r="453" spans="1:3" x14ac:dyDescent="0.25">
@@ -9907,10 +9913,10 @@
         <v>464</v>
       </c>
       <c r="B453" t="s">
-        <v>900</v>
+        <v>887</v>
       </c>
       <c r="C453" t="s">
-        <v>901</v>
+        <v>888</v>
       </c>
     </row>
     <row r="454" spans="1:3" x14ac:dyDescent="0.25">
@@ -9918,10 +9924,10 @@
         <v>465</v>
       </c>
       <c r="B454" t="s">
-        <v>902</v>
+        <v>889</v>
       </c>
       <c r="C454" t="s">
-        <v>903</v>
+        <v>890</v>
       </c>
     </row>
     <row r="455" spans="1:3" x14ac:dyDescent="0.25">
@@ -9929,10 +9935,10 @@
         <v>466</v>
       </c>
       <c r="B455" t="s">
-        <v>904</v>
+        <v>891</v>
       </c>
       <c r="C455" t="s">
-        <v>905</v>
+        <v>892</v>
       </c>
     </row>
     <row r="456" spans="1:3" x14ac:dyDescent="0.25">
@@ -9940,10 +9946,10 @@
         <v>467</v>
       </c>
       <c r="B456" t="s">
-        <v>796</v>
+        <v>783</v>
       </c>
       <c r="C456" t="s">
-        <v>906</v>
+        <v>893</v>
       </c>
     </row>
     <row r="457" spans="1:3" x14ac:dyDescent="0.25">
@@ -9951,10 +9957,10 @@
         <v>468</v>
       </c>
       <c r="B457" t="s">
-        <v>907</v>
+        <v>894</v>
       </c>
       <c r="C457" t="s">
-        <v>908</v>
+        <v>895</v>
       </c>
     </row>
     <row r="458" spans="1:3" x14ac:dyDescent="0.25">
@@ -9962,10 +9968,10 @@
         <v>469</v>
       </c>
       <c r="B458" t="s">
-        <v>909</v>
+        <v>896</v>
       </c>
       <c r="C458" t="s">
-        <v>910</v>
+        <v>897</v>
       </c>
     </row>
     <row r="459" spans="1:3" x14ac:dyDescent="0.25">
@@ -9973,10 +9979,10 @@
         <v>470</v>
       </c>
       <c r="B459" t="s">
-        <v>911</v>
-      </c>
-      <c r="C459" t="s">
-        <v>912</v>
+        <v>898</v>
+      </c>
+      <c r="C459" t="str">
+        <v>ig,点燃光芒</v>
       </c>
     </row>
     <row r="460" spans="1:3" x14ac:dyDescent="0.25">
@@ -9984,7 +9990,7 @@
         <v>471</v>
       </c>
       <c r="B460" t="s">
-        <v>913</v>
+        <v>900</v>
       </c>
     </row>
     <row r="461" spans="1:3" x14ac:dyDescent="0.25">
@@ -9992,10 +9998,10 @@
         <v>472</v>
       </c>
       <c r="B461" t="s">
-        <v>914</v>
-      </c>
-      <c r="C461" t="s">
-        <v>915</v>
+        <v>901</v>
+      </c>
+      <c r="C461" t="str">
+        <v>加帕里,兽娘动物园,欢迎来到加帕里公园</v>
       </c>
     </row>
     <row r="462" spans="1:3" x14ac:dyDescent="0.25">
@@ -10003,10 +10009,10 @@
         <v>473</v>
       </c>
       <c r="B462" t="s">
-        <v>916</v>
+        <v>903</v>
       </c>
       <c r="C462" t="s">
-        <v>917</v>
+        <v>904</v>
       </c>
     </row>
     <row r="463" spans="1:3" x14ac:dyDescent="0.25">
@@ -10014,10 +10020,10 @@
         <v>474</v>
       </c>
       <c r="B463" t="s">
-        <v>918</v>
+        <v>905</v>
       </c>
       <c r="C463" t="s">
-        <v>919</v>
+        <v>906</v>
       </c>
     </row>
     <row r="464" spans="1:3" x14ac:dyDescent="0.25">
@@ -10025,10 +10031,10 @@
         <v>475</v>
       </c>
       <c r="B464" t="s">
-        <v>920</v>
+        <v>907</v>
       </c>
       <c r="C464" t="s">
-        <v>921</v>
+        <v>908</v>
       </c>
     </row>
     <row r="465" spans="1:3" x14ac:dyDescent="0.25">
@@ -10036,10 +10042,10 @@
         <v>476</v>
       </c>
       <c r="B465" t="s">
-        <v>922</v>
+        <v>909</v>
       </c>
       <c r="C465" t="s">
-        <v>923</v>
+        <v>910</v>
       </c>
     </row>
     <row r="466" spans="1:3" x14ac:dyDescent="0.25">
@@ -10047,10 +10053,10 @@
         <v>477</v>
       </c>
       <c r="B466" t="s">
-        <v>924</v>
+        <v>911</v>
       </c>
       <c r="C466" t="s">
-        <v>925</v>
+        <v>912</v>
       </c>
     </row>
     <row r="467" spans="1:3" x14ac:dyDescent="0.25">
@@ -10058,10 +10064,10 @@
         <v>478</v>
       </c>
       <c r="B467" t="s">
-        <v>926</v>
+        <v>913</v>
       </c>
       <c r="C467" t="s">
-        <v>927</v>
+        <v>914</v>
       </c>
     </row>
     <row r="468" spans="1:3" x14ac:dyDescent="0.25">
@@ -10069,10 +10075,10 @@
         <v>479</v>
       </c>
       <c r="B468" t="s">
-        <v>928</v>
+        <v>915</v>
       </c>
       <c r="C468" t="s">
-        <v>929</v>
+        <v>916</v>
       </c>
     </row>
     <row r="469" spans="1:3" x14ac:dyDescent="0.25">
@@ -10080,10 +10086,10 @@
         <v>480</v>
       </c>
       <c r="B469" t="s">
-        <v>930</v>
+        <v>917</v>
       </c>
       <c r="C469" t="s">
-        <v>931</v>
+        <v>918</v>
       </c>
     </row>
     <row r="470" spans="1:3" x14ac:dyDescent="0.25">
@@ -10091,10 +10097,10 @@
         <v>481</v>
       </c>
       <c r="B470" t="s">
-        <v>932</v>
+        <v>919</v>
       </c>
       <c r="C470" t="s">
-        <v>933</v>
+        <v>920</v>
       </c>
     </row>
     <row r="471" spans="1:3" x14ac:dyDescent="0.25">
@@ -10102,10 +10108,10 @@
         <v>482</v>
       </c>
       <c r="B471" t="s">
-        <v>934</v>
+        <v>921</v>
       </c>
       <c r="C471" t="s">
-        <v>935</v>
+        <v>922</v>
       </c>
     </row>
     <row r="472" spans="1:3" x14ac:dyDescent="0.25">
@@ -10113,10 +10119,10 @@
         <v>483</v>
       </c>
       <c r="B472" t="s">
-        <v>936</v>
-      </c>
-      <c r="C472" t="s">
-        <v>937</v>
+        <v>923</v>
+      </c>
+      <c r="C472" t="str">
+        <v>像神一样啊,嘟嘟噜嘟嘟嘟噜嘿,你游vocal最高音,god-ish,神样,像神一样呐</v>
       </c>
     </row>
     <row r="473" spans="1:3" ht="19.2" x14ac:dyDescent="0.45">
@@ -10124,10 +10130,10 @@
         <v>484</v>
       </c>
       <c r="B473" t="s">
-        <v>938</v>
+        <v>925</v>
       </c>
       <c r="C473" t="s">
-        <v>939</v>
+        <v>926</v>
       </c>
     </row>
     <row r="474" spans="1:3" x14ac:dyDescent="0.25">
@@ -10135,10 +10141,10 @@
         <v>485</v>
       </c>
       <c r="B474" t="s">
-        <v>940</v>
+        <v>927</v>
       </c>
       <c r="C474" t="s">
-        <v>941</v>
+        <v>928</v>
       </c>
     </row>
     <row r="475" spans="1:3" x14ac:dyDescent="0.25">
@@ -10146,10 +10152,10 @@
         <v>486</v>
       </c>
       <c r="B475" t="s">
-        <v>942</v>
+        <v>929</v>
       </c>
       <c r="C475" t="s">
-        <v>943</v>
+        <v>930</v>
       </c>
     </row>
     <row r="476" spans="1:3" x14ac:dyDescent="0.25">
@@ -10157,10 +10163,10 @@
         <v>487</v>
       </c>
       <c r="B476" t="s">
-        <v>944</v>
+        <v>931</v>
       </c>
       <c r="C476" t="s">
-        <v>945</v>
+        <v>932</v>
       </c>
     </row>
     <row r="477" spans="1:3" x14ac:dyDescent="0.25">
@@ -10168,10 +10174,10 @@
         <v>488</v>
       </c>
       <c r="B477" t="s">
-        <v>946</v>
+        <v>933</v>
       </c>
       <c r="C477" t="s">
-        <v>947</v>
+        <v>934</v>
       </c>
     </row>
     <row r="478" spans="1:3" x14ac:dyDescent="0.25">
@@ -10179,10 +10185,10 @@
         <v>489</v>
       </c>
       <c r="B478" t="s">
-        <v>948</v>
+        <v>935</v>
       </c>
       <c r="C478" t="s">
-        <v>948</v>
+        <v>935</v>
       </c>
     </row>
     <row r="479" spans="1:3" x14ac:dyDescent="0.25">
@@ -10190,10 +10196,10 @@
         <v>490</v>
       </c>
       <c r="B479" t="s">
-        <v>949</v>
-      </c>
-      <c r="C479" t="s">
-        <v>950</v>
+        <v>936</v>
+      </c>
+      <c r="C479" t="str">
+        <v>在新的季节里,全新的季节,新季节,在这崭新的季节里</v>
       </c>
     </row>
     <row r="480" spans="1:3" x14ac:dyDescent="0.25">
@@ -10201,10 +10207,10 @@
         <v>491</v>
       </c>
       <c r="B480" t="s">
-        <v>951</v>
+        <v>938</v>
       </c>
       <c r="C480" t="s">
-        <v>952</v>
+        <v>939</v>
       </c>
     </row>
     <row r="481" spans="1:3" x14ac:dyDescent="0.25">
@@ -10212,10 +10218,10 @@
         <v>492</v>
       </c>
       <c r="B481" t="s">
-        <v>953</v>
+        <v>940</v>
       </c>
       <c r="C481" t="s">
-        <v>954</v>
+        <v>941</v>
       </c>
     </row>
     <row r="482" spans="1:3" x14ac:dyDescent="0.25">
@@ -10223,10 +10229,10 @@
         <v>493</v>
       </c>
       <c r="B482" t="s">
-        <v>955</v>
+        <v>942</v>
       </c>
       <c r="C482" t="s">
-        <v>956</v>
+        <v>943</v>
       </c>
     </row>
     <row r="483" spans="1:3" x14ac:dyDescent="0.25">
@@ -10234,10 +10240,10 @@
         <v>494</v>
       </c>
       <c r="B483" t="s">
-        <v>957</v>
+        <v>944</v>
       </c>
       <c r="C483" t="s">
-        <v>958</v>
+        <v>945</v>
       </c>
     </row>
     <row r="484" spans="1:3" x14ac:dyDescent="0.25">
@@ -10245,10 +10251,10 @@
         <v>496</v>
       </c>
       <c r="B484" t="s">
-        <v>959</v>
+        <v>946</v>
       </c>
       <c r="C484" t="s">
-        <v>960</v>
+        <v>947</v>
       </c>
     </row>
     <row r="485" spans="1:3" x14ac:dyDescent="0.25">
@@ -10256,10 +10262,10 @@
         <v>497</v>
       </c>
       <c r="B485" t="s">
-        <v>961</v>
+        <v>948</v>
       </c>
       <c r="C485" t="s">
-        <v>962</v>
+        <v>949</v>
       </c>
     </row>
     <row r="486" spans="1:3" x14ac:dyDescent="0.25">
@@ -10267,10 +10273,10 @@
         <v>498</v>
       </c>
       <c r="B486" t="s">
-        <v>963</v>
+        <v>950</v>
       </c>
       <c r="C486" t="s">
-        <v>964</v>
+        <v>951</v>
       </c>
     </row>
     <row r="487" spans="1:3" x14ac:dyDescent="0.25">
@@ -10278,10 +10284,10 @@
         <v>499</v>
       </c>
       <c r="B487" t="s">
-        <v>965</v>
+        <v>952</v>
       </c>
       <c r="C487" t="s">
-        <v>966</v>
+        <v>953</v>
       </c>
     </row>
     <row r="488" spans="1:3" x14ac:dyDescent="0.25">
@@ -10289,10 +10295,10 @@
         <v>500</v>
       </c>
       <c r="B488" t="s">
-        <v>967</v>
-      </c>
-      <c r="C488" t="s">
-        <v>968</v>
+        <v>954</v>
+      </c>
+      <c r="C488" t="str">
+        <v>天使梯,天梯,al,羽阶</v>
       </c>
     </row>
     <row r="489" spans="1:3" x14ac:dyDescent="0.25">
@@ -10300,10 +10306,10 @@
         <v>501</v>
       </c>
       <c r="B489" t="s">
-        <v>969</v>
+        <v>956</v>
       </c>
       <c r="C489" t="s">
-        <v>970</v>
+        <v>957</v>
       </c>
     </row>
     <row r="490" spans="1:3" x14ac:dyDescent="0.25">
@@ -10311,10 +10317,10 @@
         <v>502</v>
       </c>
       <c r="B490" t="s">
-        <v>971</v>
+        <v>958</v>
       </c>
       <c r="C490" t="s">
-        <v>972</v>
+        <v>959</v>
       </c>
     </row>
     <row r="491" spans="1:3" x14ac:dyDescent="0.25">
@@ -10322,10 +10328,10 @@
         <v>503</v>
       </c>
       <c r="B491" t="s">
-        <v>973</v>
+        <v>960</v>
       </c>
       <c r="C491" t="s">
-        <v>974</v>
+        <v>961</v>
       </c>
     </row>
     <row r="492" spans="1:3" x14ac:dyDescent="0.25">
@@ -10333,10 +10339,10 @@
         <v>504</v>
       </c>
       <c r="B492" t="s">
-        <v>975</v>
-      </c>
-      <c r="C492" t="s">
-        <v>976</v>
+        <v>962</v>
+      </c>
+      <c r="C492" t="str">
+        <v>Let'have fun!,你也一起尽情・享受・吧♪</v>
       </c>
     </row>
     <row r="493" spans="1:3" x14ac:dyDescent="0.25">
@@ -10344,10 +10350,10 @@
         <v>505</v>
       </c>
       <c r="B493" t="s">
-        <v>977</v>
+        <v>964</v>
       </c>
       <c r="C493" t="s">
-        <v>978</v>
+        <v>965</v>
       </c>
     </row>
     <row r="494" spans="1:3" x14ac:dyDescent="0.25">
@@ -10355,10 +10361,10 @@
         <v>506</v>
       </c>
       <c r="B494" t="s">
-        <v>979</v>
+        <v>966</v>
       </c>
       <c r="C494" t="s">
-        <v>980</v>
+        <v>967</v>
       </c>
     </row>
     <row r="495" spans="1:3" x14ac:dyDescent="0.25">
@@ -10366,10 +10372,10 @@
         <v>507</v>
       </c>
       <c r="B495" t="s">
-        <v>981</v>
+        <v>968</v>
       </c>
       <c r="C495" t="s">
-        <v>982</v>
+        <v>969</v>
       </c>
     </row>
     <row r="496" spans="1:3" x14ac:dyDescent="0.25">
@@ -10377,10 +10383,10 @@
         <v>508</v>
       </c>
       <c r="B496" t="s">
-        <v>983</v>
+        <v>970</v>
       </c>
       <c r="C496" t="s">
-        <v>984</v>
+        <v>971</v>
       </c>
     </row>
     <row r="497" spans="1:3" x14ac:dyDescent="0.25">
@@ -10388,10 +10394,10 @@
         <v>509</v>
       </c>
       <c r="B497" t="s">
-        <v>985</v>
+        <v>972</v>
       </c>
       <c r="C497" t="s">
-        <v>986</v>
+        <v>973</v>
       </c>
     </row>
     <row r="498" spans="1:3" x14ac:dyDescent="0.25">
@@ -10399,10 +10405,10 @@
         <v>510</v>
       </c>
       <c r="B498" t="s">
-        <v>987</v>
+        <v>974</v>
       </c>
       <c r="C498" t="s">
-        <v>988</v>
+        <v>975</v>
       </c>
     </row>
     <row r="499" spans="1:3" x14ac:dyDescent="0.25">
@@ -10410,7 +10416,7 @@
         <v>511</v>
       </c>
       <c r="B499" t="s">
-        <v>989</v>
+        <v>976</v>
       </c>
     </row>
     <row r="500" spans="1:3" x14ac:dyDescent="0.25">
@@ -10418,10 +10424,10 @@
         <v>512</v>
       </c>
       <c r="B500" t="s">
-        <v>990</v>
+        <v>977</v>
       </c>
       <c r="C500" t="s">
-        <v>991</v>
+        <v>978</v>
       </c>
     </row>
     <row r="501" spans="1:3" x14ac:dyDescent="0.25">
@@ -10429,10 +10435,10 @@
         <v>513</v>
       </c>
       <c r="B501" t="s">
-        <v>992</v>
+        <v>979</v>
       </c>
       <c r="C501" t="s">
-        <v>993</v>
+        <v>980</v>
       </c>
     </row>
     <row r="502" spans="1:3" x14ac:dyDescent="0.25">
@@ -10440,10 +10446,10 @@
         <v>514</v>
       </c>
       <c r="B502" t="s">
-        <v>994</v>
+        <v>981</v>
       </c>
       <c r="C502" t="s">
-        <v>995</v>
+        <v>982</v>
       </c>
     </row>
     <row r="503" spans="1:3" x14ac:dyDescent="0.25">
@@ -10451,10 +10457,10 @@
         <v>515</v>
       </c>
       <c r="B503" t="s">
-        <v>996</v>
+        <v>983</v>
       </c>
       <c r="C503" t="s">
-        <v>997</v>
+        <v>984</v>
       </c>
     </row>
     <row r="504" spans="1:3" x14ac:dyDescent="0.25">
@@ -10462,10 +10468,10 @@
         <v>516</v>
       </c>
       <c r="B504" t="s">
-        <v>998</v>
+        <v>985</v>
       </c>
       <c r="C504" t="s">
-        <v>999</v>
+        <v>986</v>
       </c>
     </row>
     <row r="505" spans="1:3" x14ac:dyDescent="0.25">
@@ -10473,10 +10479,10 @@
         <v>517</v>
       </c>
       <c r="B505" t="s">
-        <v>1000</v>
+        <v>987</v>
       </c>
       <c r="C505" t="s">
-        <v>1001</v>
+        <v>988</v>
       </c>
     </row>
     <row r="506" spans="1:3" x14ac:dyDescent="0.25">
@@ -10484,10 +10490,10 @@
         <v>518</v>
       </c>
       <c r="B506" t="s">
-        <v>1002</v>
+        <v>989</v>
       </c>
       <c r="C506" t="s">
-        <v>1003</v>
+        <v>990</v>
       </c>
     </row>
     <row r="507" spans="1:3" x14ac:dyDescent="0.25">
@@ -10495,10 +10501,10 @@
         <v>519</v>
       </c>
       <c r="B507" t="s">
-        <v>1004</v>
+        <v>991</v>
       </c>
       <c r="C507" t="s">
-        <v>1005</v>
+        <v>992</v>
       </c>
     </row>
     <row r="508" spans="1:3" x14ac:dyDescent="0.25">
@@ -10506,10 +10512,10 @@
         <v>520</v>
       </c>
       <c r="B508" t="s">
-        <v>1006</v>
-      </c>
-      <c r="C508" t="s">
-        <v>1007</v>
+        <v>993</v>
+      </c>
+      <c r="C508" t="str">
+        <v>ever sky blue,永恒的蓝天</v>
       </c>
     </row>
     <row r="509" spans="1:3" x14ac:dyDescent="0.25">
@@ -10517,10 +10523,10 @@
         <v>521</v>
       </c>
       <c r="B509" t="s">
-        <v>1008</v>
+        <v>995</v>
       </c>
       <c r="C509" t="s">
-        <v>1009</v>
+        <v>996</v>
       </c>
     </row>
     <row r="510" spans="1:3" x14ac:dyDescent="0.25">
@@ -10528,10 +10534,10 @@
         <v>522</v>
       </c>
       <c r="B510" t="s">
-        <v>1010</v>
+        <v>997</v>
       </c>
       <c r="C510" t="s">
-        <v>1011</v>
+        <v>998</v>
       </c>
     </row>
     <row r="511" spans="1:3" x14ac:dyDescent="0.25">
@@ -10539,10 +10545,10 @@
         <v>523</v>
       </c>
       <c r="B511" t="s">
-        <v>1012</v>
+        <v>999</v>
       </c>
       <c r="C511" t="s">
-        <v>1013</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="512" spans="1:3" x14ac:dyDescent="0.25">
@@ -10550,10 +10556,10 @@
         <v>524</v>
       </c>
       <c r="B512" t="s">
-        <v>1014</v>
-      </c>
-      <c r="C512" t="s">
-        <v>1015</v>
+        <v>1001</v>
+      </c>
+      <c r="C512" t="str">
+        <v>我超原,五个笑容◯全力以赴！</v>
       </c>
     </row>
     <row r="513" spans="1:3" x14ac:dyDescent="0.25">
@@ -10561,10 +10567,10 @@
         <v>525</v>
       </c>
       <c r="B513" t="s">
-        <v>1016</v>
+        <v>1003</v>
       </c>
       <c r="C513" t="s">
-        <v>1017</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="514" spans="1:3" x14ac:dyDescent="0.25">
@@ -10572,10 +10578,10 @@
         <v>526</v>
       </c>
       <c r="B514" t="s">
-        <v>1018</v>
+        <v>1005</v>
       </c>
       <c r="C514" t="s">
-        <v>1019</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="515" spans="1:3" x14ac:dyDescent="0.25">
@@ -10583,10 +10589,10 @@
         <v>527</v>
       </c>
       <c r="B515" t="s">
-        <v>1020</v>
+        <v>1007</v>
       </c>
       <c r="C515" t="s">
-        <v>1021</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="516" spans="1:3" x14ac:dyDescent="0.25">
@@ -10594,10 +10600,10 @@
         <v>528</v>
       </c>
       <c r="B516" t="s">
-        <v>730</v>
+        <v>717</v>
       </c>
       <c r="C516" t="s">
-        <v>1022</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="517" spans="1:3" x14ac:dyDescent="0.25">
@@ -10605,10 +10611,10 @@
         <v>529</v>
       </c>
       <c r="B517" t="s">
-        <v>1023</v>
+        <v>1010</v>
       </c>
       <c r="C517" t="s">
-        <v>1024</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="518" spans="1:3" x14ac:dyDescent="0.25">
@@ -10616,10 +10622,10 @@
         <v>530</v>
       </c>
       <c r="B518" t="s">
-        <v>1025</v>
+        <v>1012</v>
       </c>
       <c r="C518" t="s">
-        <v>1026</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="519" spans="1:3" x14ac:dyDescent="0.25">
@@ -10627,10 +10633,10 @@
         <v>531</v>
       </c>
       <c r="B519" t="s">
-        <v>1027</v>
+        <v>1014</v>
       </c>
       <c r="C519" t="s">
-        <v>1028</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="520" spans="1:3" x14ac:dyDescent="0.25">
@@ -10638,10 +10644,10 @@
         <v>532</v>
       </c>
       <c r="B520" t="s">
-        <v>1029</v>
+        <v>1016</v>
       </c>
       <c r="C520" t="s">
-        <v>1030</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="521" spans="1:3" x14ac:dyDescent="0.25">
@@ -10649,10 +10655,10 @@
         <v>533</v>
       </c>
       <c r="B521" t="s">
-        <v>1031</v>
-      </c>
-      <c r="C521" t="s">
-        <v>1032</v>
+        <v>1018</v>
+      </c>
+      <c r="C521" t="str">
+        <v>这么可爱真是抱歉呢,pp缺主唱,可爱,这么可爱真是抱歉</v>
       </c>
     </row>
     <row r="522" spans="1:3" x14ac:dyDescent="0.25">
@@ -10660,10 +10666,10 @@
         <v>534</v>
       </c>
       <c r="B522" t="s">
-        <v>1033</v>
+        <v>1020</v>
       </c>
       <c r="C522" t="s">
-        <v>1034</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="523" spans="1:3" x14ac:dyDescent="0.25">
@@ -10671,10 +10677,10 @@
         <v>535</v>
       </c>
       <c r="B523" t="s">
-        <v>1035</v>
+        <v>1022</v>
       </c>
       <c r="C523" t="s">
-        <v>1036</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="524" spans="1:3" x14ac:dyDescent="0.25">
@@ -10682,10 +10688,10 @@
         <v>536</v>
       </c>
       <c r="B524" t="s">
-        <v>1037</v>
+        <v>1024</v>
       </c>
       <c r="C524" t="s">
-        <v>1038</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="525" spans="1:3" x14ac:dyDescent="0.25">
@@ -10693,10 +10699,10 @@
         <v>537</v>
       </c>
       <c r="B525" t="s">
-        <v>1039</v>
+        <v>1026</v>
       </c>
       <c r="C525" t="s">
-        <v>1040</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="526" spans="1:3" x14ac:dyDescent="0.25">
@@ -10704,10 +10710,10 @@
         <v>538</v>
       </c>
       <c r="B526" t="s">
-        <v>1041</v>
+        <v>1028</v>
       </c>
       <c r="C526" t="s">
-        <v>1042</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="527" spans="1:3" x14ac:dyDescent="0.25">
@@ -10715,10 +10721,10 @@
         <v>539</v>
       </c>
       <c r="B527" t="s">
-        <v>1043</v>
+        <v>1030</v>
       </c>
       <c r="C527" t="s">
-        <v>1044</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="528" spans="1:3" x14ac:dyDescent="0.25">
@@ -10726,10 +10732,10 @@
         <v>540</v>
       </c>
       <c r="B528" t="s">
-        <v>1045</v>
+        <v>1032</v>
       </c>
       <c r="C528" t="s">
-        <v>1046</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="529" spans="1:3" x14ac:dyDescent="0.25">
@@ -10737,10 +10743,10 @@
         <v>542</v>
       </c>
       <c r="B529" t="s">
-        <v>1047</v>
+        <v>1034</v>
       </c>
       <c r="C529" t="s">
-        <v>1048</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="530" spans="1:3" x14ac:dyDescent="0.25">
@@ -10748,10 +10754,10 @@
         <v>543</v>
       </c>
       <c r="B530" t="s">
-        <v>1049</v>
+        <v>1036</v>
       </c>
       <c r="C530" t="s">
-        <v>1050</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="531" spans="1:3" x14ac:dyDescent="0.25">
@@ -10759,10 +10765,10 @@
         <v>545</v>
       </c>
       <c r="B531" t="s">
-        <v>1051</v>
+        <v>1038</v>
       </c>
       <c r="C531" t="s">
-        <v>1052</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="532" spans="1:3" x14ac:dyDescent="0.25">
@@ -10770,10 +10776,10 @@
         <v>546</v>
       </c>
       <c r="B532" t="s">
-        <v>1053</v>
+        <v>1040</v>
       </c>
       <c r="C532" t="s">
-        <v>1054</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="533" spans="1:3" x14ac:dyDescent="0.25">
@@ -10781,10 +10787,10 @@
         <v>547</v>
       </c>
       <c r="B533" t="s">
-        <v>1055</v>
+        <v>1042</v>
       </c>
       <c r="C533" t="s">
-        <v>1056</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="534" spans="1:3" x14ac:dyDescent="0.25">
@@ -10792,10 +10798,10 @@
         <v>548</v>
       </c>
       <c r="B534" t="s">
-        <v>1057</v>
+        <v>1044</v>
       </c>
       <c r="C534" t="s">
-        <v>1058</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="535" spans="1:3" x14ac:dyDescent="0.25">
@@ -10803,10 +10809,10 @@
         <v>549</v>
       </c>
       <c r="B535" t="s">
-        <v>1059</v>
+        <v>1046</v>
       </c>
       <c r="C535" t="s">
-        <v>1060</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="536" spans="1:3" x14ac:dyDescent="0.25">
@@ -10814,10 +10820,10 @@
         <v>550</v>
       </c>
       <c r="B536" t="s">
-        <v>1061</v>
+        <v>1048</v>
       </c>
       <c r="C536" t="s">
-        <v>1062</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="537" spans="1:3" x14ac:dyDescent="0.25">
@@ -10825,10 +10831,10 @@
         <v>551</v>
       </c>
       <c r="B537" t="s">
-        <v>1063</v>
+        <v>1050</v>
       </c>
       <c r="C537" t="s">
-        <v>1064</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="538" spans="1:3" x14ac:dyDescent="0.25">
@@ -10836,10 +10842,10 @@
         <v>552</v>
       </c>
       <c r="B538" t="s">
-        <v>1065</v>
+        <v>1052</v>
       </c>
       <c r="C538" t="s">
-        <v>1066</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="539" spans="1:3" x14ac:dyDescent="0.25">
@@ -10847,10 +10853,10 @@
         <v>553</v>
       </c>
       <c r="B539" t="s">
-        <v>1067</v>
+        <v>1054</v>
       </c>
       <c r="C539" t="s">
-        <v>1068</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="540" spans="1:3" x14ac:dyDescent="0.25">
@@ -10858,10 +10864,10 @@
         <v>554</v>
       </c>
       <c r="B540" t="s">
-        <v>1069</v>
+        <v>1056</v>
       </c>
       <c r="C540" t="s">
-        <v>1070</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="541" spans="1:3" x14ac:dyDescent="0.25">
@@ -10869,10 +10875,10 @@
         <v>555</v>
       </c>
       <c r="B541" t="s">
-        <v>1071</v>
+        <v>1058</v>
       </c>
       <c r="C541" t="s">
-        <v>1072</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="542" spans="1:3" x14ac:dyDescent="0.25">
@@ -10880,10 +10886,10 @@
         <v>556</v>
       </c>
       <c r="B542" t="s">
-        <v>1073</v>
+        <v>1060</v>
       </c>
       <c r="C542" t="s">
-        <v>1074</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="543" spans="1:3" x14ac:dyDescent="0.25">
@@ -10891,10 +10897,10 @@
         <v>557</v>
       </c>
       <c r="B543" t="s">
-        <v>1075</v>
+        <v>1062</v>
       </c>
       <c r="C543" t="s">
-        <v>1076</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="544" spans="1:3" x14ac:dyDescent="0.25">
@@ -10902,10 +10908,10 @@
         <v>558</v>
       </c>
       <c r="B544" t="s">
-        <v>1077</v>
+        <v>1064</v>
       </c>
       <c r="C544" t="s">
-        <v>1078</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="545" spans="1:3" x14ac:dyDescent="0.25">
@@ -10913,10 +10919,10 @@
         <v>559</v>
       </c>
       <c r="B545" t="s">
-        <v>1079</v>
+        <v>1066</v>
       </c>
       <c r="C545" t="s">
-        <v>1080</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="546" spans="1:3" x14ac:dyDescent="0.25">
@@ -10924,10 +10930,10 @@
         <v>562</v>
       </c>
       <c r="B546" t="s">
-        <v>1081</v>
+        <v>1068</v>
       </c>
       <c r="C546" t="s">
-        <v>1082</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="547" spans="1:3" x14ac:dyDescent="0.25">
@@ -10935,7 +10941,7 @@
         <v>563</v>
       </c>
       <c r="B547" t="s">
-        <v>1083</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="548" spans="1:3" x14ac:dyDescent="0.25">
@@ -10943,10 +10949,10 @@
         <v>564</v>
       </c>
       <c r="B548" t="s">
-        <v>1084</v>
+        <v>1071</v>
       </c>
       <c r="C548" t="s">
-        <v>1085</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="549" spans="1:3" x14ac:dyDescent="0.25">
@@ -10954,10 +10960,10 @@
         <v>565</v>
       </c>
       <c r="B549" t="s">
-        <v>1086</v>
+        <v>1073</v>
       </c>
       <c r="C549" t="s">
-        <v>1087</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="550" spans="1:3" x14ac:dyDescent="0.25">
@@ -10965,10 +10971,10 @@
         <v>566</v>
       </c>
       <c r="B550" t="s">
-        <v>1088</v>
-      </c>
-      <c r="C550" t="s">
-        <v>1089</v>
+        <v>1075</v>
+      </c>
+      <c r="C550" t="str">
+        <v>我是最强,海贼王,最强,我就是最强的</v>
       </c>
     </row>
     <row r="551" spans="1:3" x14ac:dyDescent="0.25">
@@ -10976,10 +10982,10 @@
         <v>567</v>
       </c>
       <c r="B551" t="s">
-        <v>1090</v>
+        <v>1077</v>
       </c>
       <c r="C551" t="s">
-        <v>1091</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="552" spans="1:3" x14ac:dyDescent="0.25">
@@ -10987,10 +10993,10 @@
         <v>568</v>
       </c>
       <c r="B552" t="s">
-        <v>1092</v>
+        <v>1079</v>
       </c>
       <c r="C552" t="s">
-        <v>1093</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="553" spans="1:3" x14ac:dyDescent="0.25">
@@ -10998,10 +11004,10 @@
         <v>569</v>
       </c>
       <c r="B553" t="s">
-        <v>1094</v>
+        <v>1081</v>
       </c>
       <c r="C553" t="s">
-        <v>1095</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="554" spans="1:3" x14ac:dyDescent="0.25">
@@ -11009,10 +11015,10 @@
         <v>570</v>
       </c>
       <c r="B554" t="s">
-        <v>1096</v>
+        <v>1083</v>
       </c>
       <c r="C554" t="s">
-        <v>1097</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="555" spans="1:3" x14ac:dyDescent="0.25">
@@ -11020,10 +11026,10 @@
         <v>571</v>
       </c>
       <c r="B555" t="s">
-        <v>1098</v>
+        <v>1085</v>
       </c>
       <c r="C555" t="s">
-        <v>1099</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="556" spans="1:3" x14ac:dyDescent="0.25">
@@ -11031,10 +11037,10 @@
         <v>572</v>
       </c>
       <c r="B556" t="s">
-        <v>1100</v>
+        <v>1087</v>
       </c>
       <c r="C556" t="s">
-        <v>1101</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="557" spans="1:3" x14ac:dyDescent="0.25">
@@ -11042,10 +11048,10 @@
         <v>577</v>
       </c>
       <c r="B557" t="s">
-        <v>1102</v>
+        <v>1089</v>
       </c>
       <c r="C557" t="s">
-        <v>1103</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="558" spans="1:3" x14ac:dyDescent="0.25">
@@ -11053,10 +11059,10 @@
         <v>578</v>
       </c>
       <c r="B558" t="s">
-        <v>1104</v>
+        <v>1091</v>
       </c>
       <c r="C558" t="s">
-        <v>1105</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="559" spans="1:3" x14ac:dyDescent="0.25">
@@ -11064,7 +11070,7 @@
         <v>579</v>
       </c>
       <c r="B559" t="s">
-        <v>1106</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="560" spans="1:3" x14ac:dyDescent="0.25">
@@ -11072,10 +11078,10 @@
         <v>580</v>
       </c>
       <c r="B560" t="s">
-        <v>1107</v>
+        <v>1094</v>
       </c>
       <c r="C560" t="s">
-        <v>1108</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="561" spans="1:3" x14ac:dyDescent="0.25">
@@ -11083,10 +11089,10 @@
         <v>581</v>
       </c>
       <c r="B561" t="s">
-        <v>1109</v>
-      </c>
-      <c r="C561" t="s">
-        <v>1110</v>
+        <v>1096</v>
+      </c>
+      <c r="C561" t="str">
+        <v>苍穹,向着苍穹之路</v>
       </c>
     </row>
     <row r="562" spans="1:3" x14ac:dyDescent="0.25">
@@ -11094,10 +11100,10 @@
         <v>582</v>
       </c>
       <c r="B562" t="s">
-        <v>1111</v>
+        <v>1098</v>
       </c>
       <c r="C562" t="s">
-        <v>1112</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="563" spans="1:3" x14ac:dyDescent="0.25">
@@ -11105,10 +11111,10 @@
         <v>583</v>
       </c>
       <c r="B563" t="s">
-        <v>1113</v>
+        <v>1100</v>
       </c>
       <c r="C563" t="s">
-        <v>1114</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="564" spans="1:3" x14ac:dyDescent="0.25">
@@ -11116,10 +11122,10 @@
         <v>584</v>
       </c>
       <c r="B564" t="s">
-        <v>1115</v>
+        <v>1102</v>
       </c>
       <c r="C564" t="s">
-        <v>1116</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="565" spans="1:3" x14ac:dyDescent="0.25">
@@ -11127,10 +11133,10 @@
         <v>585</v>
       </c>
       <c r="B565" t="s">
-        <v>1117</v>
+        <v>1104</v>
       </c>
       <c r="C565" t="s">
-        <v>1118</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="566" spans="1:3" x14ac:dyDescent="0.25">
@@ -11138,10 +11144,10 @@
         <v>586</v>
       </c>
       <c r="B566" t="s">
-        <v>1119</v>
-      </c>
-      <c r="C566" t="s">
-        <v>1120</v>
+        <v>1106</v>
+      </c>
+      <c r="C566" t="str">
+        <v>wb,誓言,wbsp,纯真振翅,纯真振翅膀,纯真震翅膀,誓言振翅膀,誓言的振翅</v>
       </c>
     </row>
     <row r="567" spans="1:3" x14ac:dyDescent="0.25">
@@ -11149,10 +11155,10 @@
         <v>587</v>
       </c>
       <c r="B567" t="s">
-        <v>1121</v>
+        <v>1108</v>
       </c>
       <c r="C567" t="s">
-        <v>1122</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="568" spans="1:3" x14ac:dyDescent="0.25">
@@ -11160,10 +11166,10 @@
         <v>588</v>
       </c>
       <c r="B568" t="s">
-        <v>1123</v>
+        <v>1110</v>
       </c>
       <c r="C568" t="s">
-        <v>1124</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="569" spans="1:3" x14ac:dyDescent="0.25">
@@ -11171,10 +11177,10 @@
         <v>589</v>
       </c>
       <c r="B569" t="s">
-        <v>1125</v>
+        <v>1112</v>
       </c>
       <c r="C569" t="s">
-        <v>1126</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="570" spans="1:3" x14ac:dyDescent="0.25">
@@ -11182,10 +11188,10 @@
         <v>590</v>
       </c>
       <c r="B570" t="s">
-        <v>1127</v>
+        <v>1114</v>
       </c>
       <c r="C570" t="s">
-        <v>1128</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="571" spans="1:3" x14ac:dyDescent="0.25">
@@ -11193,10 +11199,10 @@
         <v>591</v>
       </c>
       <c r="B571" t="s">
-        <v>1129</v>
+        <v>1116</v>
       </c>
       <c r="C571" t="s">
-        <v>1130</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="572" spans="1:3" x14ac:dyDescent="0.25">
@@ -11204,10 +11210,10 @@
         <v>592</v>
       </c>
       <c r="B572" t="s">
-        <v>1131</v>
+        <v>1118</v>
       </c>
       <c r="C572" t="s">
-        <v>1132</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="573" spans="1:3" x14ac:dyDescent="0.25">
@@ -11215,10 +11221,10 @@
         <v>593</v>
       </c>
       <c r="B573" t="s">
-        <v>1133</v>
+        <v>1120</v>
       </c>
       <c r="C573" t="s">
-        <v>1134</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="574" spans="1:3" x14ac:dyDescent="0.25">
@@ -11226,10 +11232,10 @@
         <v>594</v>
       </c>
       <c r="B574" t="s">
-        <v>1135</v>
+        <v>1122</v>
       </c>
       <c r="C574" t="s">
-        <v>1136</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="575" spans="1:3" x14ac:dyDescent="0.25">
@@ -11237,10 +11243,10 @@
         <v>595</v>
       </c>
       <c r="B575" t="s">
-        <v>1137</v>
+        <v>1124</v>
       </c>
       <c r="C575" t="s">
-        <v>1138</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="576" spans="1:3" x14ac:dyDescent="0.25">
@@ -11248,10 +11254,10 @@
         <v>596</v>
       </c>
       <c r="B576" t="s">
-        <v>1139</v>
+        <v>1126</v>
       </c>
       <c r="C576" t="s">
-        <v>1140</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="577" spans="1:3" x14ac:dyDescent="0.25">
@@ -11259,10 +11265,10 @@
         <v>597</v>
       </c>
       <c r="B577" t="s">
-        <v>942</v>
+        <v>929</v>
       </c>
       <c r="C577" t="s">
-        <v>1141</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="578" spans="1:3" x14ac:dyDescent="0.25">
@@ -11270,10 +11276,10 @@
         <v>598</v>
       </c>
       <c r="B578" t="s">
-        <v>944</v>
+        <v>931</v>
       </c>
       <c r="C578" t="s">
-        <v>1142</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="579" spans="1:3" x14ac:dyDescent="0.25">
@@ -11281,10 +11287,10 @@
         <v>599</v>
       </c>
       <c r="B579" t="s">
-        <v>1143</v>
+        <v>1130</v>
       </c>
       <c r="C579" t="s">
-        <v>1144</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="580" spans="1:3" x14ac:dyDescent="0.25">
@@ -11292,10 +11298,10 @@
         <v>601</v>
       </c>
       <c r="B580" t="s">
-        <v>1145</v>
-      </c>
-      <c r="C580" t="s">
-        <v>1146</v>
+        <v>1132</v>
+      </c>
+      <c r="C580" t="str">
+        <v>两翼,雨翼,双翼的光辉</v>
       </c>
     </row>
     <row r="581" spans="1:3" x14ac:dyDescent="0.25">
@@ -11303,10 +11309,10 @@
         <v>602</v>
       </c>
       <c r="B581" t="s">
-        <v>1147</v>
+        <v>1134</v>
       </c>
       <c r="C581" t="s">
-        <v>1148</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="582" spans="1:3" x14ac:dyDescent="0.25">
@@ -11314,18 +11320,21 @@
         <v>604</v>
       </c>
       <c r="B582" t="s">
-        <v>1149</v>
+        <v>1136</v>
       </c>
       <c r="C582" t="s">
-        <v>1150</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="583" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A583">
         <v>605</v>
       </c>
+      <c r="B583" t="str">
+        <v>メランコリックララバイ</v>
+      </c>
       <c r="C583" t="s">
-        <v>1151</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="584" spans="1:3" x14ac:dyDescent="0.25">
@@ -11333,10 +11342,10 @@
         <v>606</v>
       </c>
       <c r="B584" t="s">
-        <v>1152</v>
+        <v>1139</v>
       </c>
       <c r="C584" t="s">
-        <v>1153</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="585" spans="1:3" x14ac:dyDescent="0.25">
@@ -11344,18 +11353,21 @@
         <v>607</v>
       </c>
       <c r="B585" t="s">
-        <v>1154</v>
-      </c>
-      <c r="C585" t="s">
-        <v>1155</v>
+        <v>1141</v>
+      </c>
+      <c r="C585" t="str">
+        <v>桑巴Happy~!,桑巴乐嗨皮！</v>
       </c>
     </row>
     <row r="586" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A586">
         <v>609</v>
       </c>
+      <c r="B586" t="str">
+        <v>Floral Haven</v>
+      </c>
       <c r="C586" t="s">
-        <v>1156</v>
+        <v>1143</v>
       </c>
     </row>
     <row r="587" spans="1:3" x14ac:dyDescent="0.25">
@@ -11363,10 +11375,10 @@
         <v>612</v>
       </c>
       <c r="B587" t="s">
-        <v>1157</v>
+        <v>1144</v>
       </c>
       <c r="C587" t="s">
-        <v>1158</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="588" spans="1:3" x14ac:dyDescent="0.25">
@@ -11374,10 +11386,10 @@
         <v>615</v>
       </c>
       <c r="B588" t="s">
-        <v>1159</v>
+        <v>1146</v>
       </c>
       <c r="C588" t="s">
-        <v>1160</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="589" spans="1:3" x14ac:dyDescent="0.25">
@@ -11385,10 +11397,10 @@
         <v>617</v>
       </c>
       <c r="B589" t="s">
-        <v>1161</v>
+        <v>1148</v>
       </c>
       <c r="C589" t="s">
-        <v>1162</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="590" spans="1:3" x14ac:dyDescent="0.25">
@@ -11396,10 +11408,10 @@
         <v>618</v>
       </c>
       <c r="B590" t="s">
-        <v>1163</v>
-      </c>
-      <c r="C590" t="s">
-        <v>1164</v>
+        <v>1150</v>
+      </c>
+      <c r="C590" t="str">
+        <v>花冠,基石之花冠</v>
       </c>
     </row>
     <row r="591" spans="1:3" x14ac:dyDescent="0.25">
@@ -11407,10 +11419,10 @@
         <v>625</v>
       </c>
       <c r="B591" t="s">
-        <v>1165</v>
+        <v>1152</v>
       </c>
       <c r="C591" t="s">
-        <v>1166</v>
+        <v>1153</v>
       </c>
     </row>
     <row r="592" spans="1:3" x14ac:dyDescent="0.25">
@@ -11418,18 +11430,21 @@
         <v>624</v>
       </c>
       <c r="B592" t="s">
-        <v>1167</v>
+        <v>1154</v>
       </c>
       <c r="C592" t="s">
-        <v>1168</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="593" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A593">
         <v>623</v>
       </c>
+      <c r="B593" t="str">
+        <v>Bad Kids All Bet</v>
+      </c>
       <c r="C593" t="s">
-        <v>1169</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="594" spans="1:3" x14ac:dyDescent="0.25">
@@ -11437,10 +11452,10 @@
         <v>626</v>
       </c>
       <c r="B594" t="s">
-        <v>1170</v>
+        <v>1157</v>
       </c>
       <c r="C594" t="s">
-        <v>1171</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="595" spans="1:3" x14ac:dyDescent="0.25">
@@ -11448,10 +11463,10 @@
         <v>629</v>
       </c>
       <c r="B595" t="s">
-        <v>1172</v>
+        <v>1159</v>
       </c>
       <c r="C595" t="s">
-        <v>1173</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="596" spans="1:3" x14ac:dyDescent="0.25">
@@ -11459,18 +11474,21 @@
         <v>630</v>
       </c>
       <c r="B596" t="s">
-        <v>1174</v>
+        <v>1161</v>
       </c>
       <c r="C596" t="s">
-        <v>1175</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="597" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A597">
         <v>632</v>
       </c>
-      <c r="C597" t="s">
-        <v>1176</v>
+      <c r="B597" t="str">
+        <v>カゲロウデイズ</v>
+      </c>
+      <c r="C597" t="str">
+        <v>阳炎,阳炎眩乱</v>
       </c>
     </row>
     <row r="598" spans="1:3" x14ac:dyDescent="0.25">
@@ -11478,10 +11496,10 @@
         <v>633</v>
       </c>
       <c r="B598" t="s">
-        <v>1177</v>
-      </c>
-      <c r="C598" t="s">
-        <v>1178</v>
+        <v>1164</v>
+      </c>
+      <c r="C598" t="str">
+        <v>杂沓,杂踏,雑踏,gbcop,熙熙攘攘,gbc,糟蹋,踏街,羊杂,熙熙攘攘，我们的城市</v>
       </c>
     </row>
     <row r="599" spans="1:3" x14ac:dyDescent="0.25">
@@ -11489,10 +11507,10 @@
         <v>635</v>
       </c>
       <c r="B599" t="s">
-        <v>1179</v>
+        <v>1166</v>
       </c>
       <c r="C599" t="s">
-        <v>1180</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="600" spans="1:3" x14ac:dyDescent="0.25">
@@ -11500,18 +11518,21 @@
         <v>636</v>
       </c>
       <c r="B600" t="s">
-        <v>1181</v>
-      </c>
-      <c r="C600" t="s">
-        <v>1182</v>
+        <v>1168</v>
+      </c>
+      <c r="C600" t="str">
+        <v>毛二力,モニカ,蝶万圣曲,蒂里卡莫尼卡里拉</v>
       </c>
     </row>
     <row r="601" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A601">
         <v>637</v>
       </c>
-      <c r="C601" t="s">
-        <v>1183</v>
+      <c r="B601" t="str">
+        <v>サインはB</v>
+      </c>
+      <c r="C601" t="str">
+        <v>信号B,信号 B,标志是B,B标志,B信号,我推的孩子B,我推B,我推2,暗号是B</v>
       </c>
     </row>
     <row r="602" spans="1:3" x14ac:dyDescent="0.25">
@@ -11519,10 +11540,10 @@
         <v>642</v>
       </c>
       <c r="B602" t="s">
-        <v>1184</v>
+        <v>1171</v>
       </c>
       <c r="C602" t="s">
-        <v>1185</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="603" spans="1:3" x14ac:dyDescent="0.25">
@@ -11530,18 +11551,21 @@
         <v>644</v>
       </c>
       <c r="B603" t="s">
-        <v>1186</v>
-      </c>
-      <c r="C603" t="s">
-        <v>1187</v>
+        <v>1173</v>
+      </c>
+      <c r="C603" t="str">
+        <v>遥之彼方,遥彼方,羊叫,遥远的彼方</v>
       </c>
     </row>
     <row r="604" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A604">
         <v>645</v>
       </c>
+      <c r="B604" t="str">
+        <v>ホワイト ノスタルジア</v>
+      </c>
       <c r="C604" t="s">
-        <v>1188</v>
+        <v>1175</v>
       </c>
     </row>
     <row r="605" spans="1:3" x14ac:dyDescent="0.25">
@@ -11549,18 +11573,21 @@
         <v>646</v>
       </c>
       <c r="B605" t="s">
-        <v>1189</v>
+        <v>1176</v>
       </c>
       <c r="C605" t="s">
-        <v>1190</v>
+        <v>1177</v>
       </c>
     </row>
     <row r="606" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A606">
         <v>647</v>
       </c>
+      <c r="B606" t="str">
+        <v>VIVID FIRST TIME</v>
+      </c>
       <c r="C606" t="s">
-        <v>1191</v>
+        <v>1178</v>
       </c>
     </row>
     <row r="607" spans="1:3" x14ac:dyDescent="0.25">
@@ -11568,10 +11595,10 @@
         <v>649</v>
       </c>
       <c r="B607" t="s">
-        <v>1192</v>
+        <v>1179</v>
       </c>
       <c r="C607" t="s">
-        <v>1193</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="608" spans="1:3" x14ac:dyDescent="0.25">
@@ -11579,10 +11606,10 @@
         <v>650</v>
       </c>
       <c r="B608" t="s">
-        <v>1194</v>
-      </c>
-      <c r="C608" t="s">
-        <v>1195</v>
+        <v>1181</v>
+      </c>
+      <c r="C608" t="str">
+        <v>还不够,tarinal,trainal,远远不够</v>
       </c>
     </row>
     <row r="609" spans="1:3" x14ac:dyDescent="0.25">
@@ -11590,10 +11617,10 @@
         <v>651</v>
       </c>
       <c r="B609" t="s">
-        <v>1196</v>
+        <v>1183</v>
       </c>
       <c r="C609" t="s">
-        <v>1197</v>
+        <v>1184</v>
       </c>
     </row>
     <row r="610" spans="1:3" x14ac:dyDescent="0.25">
@@ -11601,10 +11628,10 @@
         <v>653</v>
       </c>
       <c r="B610" t="s">
-        <v>1198</v>
+        <v>1185</v>
       </c>
       <c r="C610" t="s">
-        <v>1199</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="611" spans="1:3" x14ac:dyDescent="0.25">
@@ -11612,10 +11639,10 @@
         <v>654</v>
       </c>
       <c r="B611" t="s">
-        <v>1200</v>
-      </c>
-      <c r="C611" t="s">
-        <v>1201</v>
+        <v>1187</v>
+      </c>
+      <c r="C611" t="str">
+        <v>暴风雨,风暴,临时,最临时,纵使风雨</v>
       </c>
     </row>
     <row r="612" spans="1:3" x14ac:dyDescent="0.25">
@@ -11623,18 +11650,21 @@
         <v>655</v>
       </c>
       <c r="B612" t="s">
-        <v>1202</v>
-      </c>
-      <c r="C612" t="s">
-        <v>1203</v>
+        <v>1189</v>
+      </c>
+      <c r="C612" t="str">
+        <v>鹿乃子,鹿色时光</v>
       </c>
     </row>
     <row r="613" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A613">
         <v>657</v>
       </c>
+      <c r="B613" t="str">
+        <v>悪魔の子</v>
+      </c>
       <c r="C613" t="s">
-        <v>1204</v>
+        <v>1191</v>
       </c>
     </row>
     <row r="614" spans="1:3" x14ac:dyDescent="0.25">
@@ -11642,10 +11672,10 @@
         <v>659</v>
       </c>
       <c r="B614" t="s">
-        <v>1205</v>
+        <v>1192</v>
       </c>
       <c r="C614" t="s">
-        <v>1206</v>
+        <v>1193</v>
       </c>
     </row>
     <row r="615" spans="1:3" x14ac:dyDescent="0.25">
@@ -11653,10 +11683,10 @@
         <v>660</v>
       </c>
       <c r="B615" t="s">
-        <v>1207</v>
+        <v>1194</v>
       </c>
       <c r="C615" t="s">
-        <v>1208</v>
+        <v>1195</v>
       </c>
     </row>
     <row r="616" spans="1:3" x14ac:dyDescent="0.25">
@@ -11664,10 +11694,10 @@
         <v>661</v>
       </c>
       <c r="B616" t="s">
-        <v>1209</v>
+        <v>1196</v>
       </c>
       <c r="C616" t="s">
-        <v>1210</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="617" spans="1:3" x14ac:dyDescent="0.25">
@@ -11675,10 +11705,10 @@
         <v>663</v>
       </c>
       <c r="B617" t="s">
-        <v>1211</v>
-      </c>
-      <c r="C617" t="s">
-        <v>1212</v>
+        <v>1198</v>
+      </c>
+      <c r="C617" t="str">
+        <v>乌托邦,stu,驶向乌托邦</v>
       </c>
     </row>
     <row r="618" spans="1:3" x14ac:dyDescent="0.25">
@@ -11686,18 +11716,21 @@
         <v>667</v>
       </c>
       <c r="B618" t="s">
-        <v>1213</v>
+        <v>1200</v>
       </c>
       <c r="C618" t="s">
-        <v>1214</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="619" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A619">
         <v>669</v>
       </c>
+      <c r="B619" t="str">
+        <v>とっておきAnswer</v>
+      </c>
       <c r="C619" t="s">
-        <v>1215</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="620" spans="1:3" x14ac:dyDescent="0.25">
@@ -11705,18 +11738,21 @@
         <v>670</v>
       </c>
       <c r="B620" t="s">
-        <v>1216</v>
+        <v>1203</v>
       </c>
       <c r="C620" t="s">
-        <v>1217</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="621" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A621">
         <v>672</v>
       </c>
+      <c r="B621" t="str">
+        <v>HOWLING AMBITION</v>
+      </c>
       <c r="C621" t="s">
-        <v>1218</v>
+        <v>1205</v>
       </c>
     </row>
     <row r="622" spans="1:3" x14ac:dyDescent="0.25">
@@ -11724,10 +11760,10 @@
         <v>673</v>
       </c>
       <c r="B622" t="s">
-        <v>1219</v>
+        <v>1206</v>
       </c>
       <c r="C622" t="s">
-        <v>1220</v>
+        <v>1207</v>
       </c>
     </row>
     <row r="623" spans="1:3" x14ac:dyDescent="0.25">
@@ -11735,10 +11771,10 @@
         <v>674</v>
       </c>
       <c r="B623" t="s">
-        <v>1221</v>
+        <v>1208</v>
       </c>
       <c r="C623" t="s">
-        <v>1222</v>
+        <v>1209</v>
       </c>
     </row>
     <row r="624" spans="1:3" x14ac:dyDescent="0.25">
@@ -11746,10 +11782,10 @@
         <v>675</v>
       </c>
       <c r="B624" t="s">
-        <v>1223</v>
-      </c>
-      <c r="C624" t="s">
-        <v>1224</v>
+        <v>1210</v>
+      </c>
+      <c r="C624" t="str">
+        <v>最上级,最上层,最上等的可爱！</v>
       </c>
     </row>
     <row r="625" spans="1:3" x14ac:dyDescent="0.25">
@@ -11757,10 +11793,10 @@
         <v>680</v>
       </c>
       <c r="B625" t="s">
-        <v>1225</v>
-      </c>
-      <c r="C625" t="s">
-        <v>1226</v>
+        <v>1212</v>
+      </c>
+      <c r="C625" t="str">
+        <v>心脏,如果能成为谁的心脏的话</v>
       </c>
     </row>
     <row r="626" spans="1:3" x14ac:dyDescent="0.25">
@@ -11768,10 +11804,10 @@
         <v>681</v>
       </c>
       <c r="B626" t="s">
-        <v>1227</v>
+        <v>1214</v>
       </c>
       <c r="C626" t="s">
-        <v>1228</v>
+        <v>1215</v>
       </c>
     </row>
     <row r="627" spans="1:3" x14ac:dyDescent="0.25">
@@ -11779,10 +11815,10 @@
         <v>682</v>
       </c>
       <c r="B627" t="s">
-        <v>1229</v>
+        <v>1216</v>
       </c>
       <c r="C627" t="s">
-        <v>1230</v>
+        <v>1217</v>
       </c>
     </row>
     <row r="628" spans="1:3" x14ac:dyDescent="0.25">
@@ -11790,10 +11826,10 @@
         <v>683</v>
       </c>
       <c r="B628" t="s">
-        <v>1231</v>
+        <v>1218</v>
       </c>
       <c r="C628" t="s">
-        <v>1232</v>
+        <v>1219</v>
       </c>
     </row>
     <row r="629" spans="1:3" x14ac:dyDescent="0.25">
@@ -11801,10 +11837,10 @@
         <v>684</v>
       </c>
       <c r="B629" t="s">
-        <v>1233</v>
+        <v>1220</v>
       </c>
       <c r="C629" t="s">
-        <v>1234</v>
+        <v>1221</v>
       </c>
     </row>
     <row r="630" spans="1:3" x14ac:dyDescent="0.25">
@@ -11812,10 +11848,10 @@
         <v>685</v>
       </c>
       <c r="B630" t="s">
-        <v>1235</v>
+        <v>1222</v>
       </c>
       <c r="C630" t="s">
-        <v>1236</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="631" spans="1:3" x14ac:dyDescent="0.25">
@@ -11823,10 +11859,10 @@
         <v>686</v>
       </c>
       <c r="B631" t="s">
-        <v>1237</v>
+        <v>1224</v>
       </c>
       <c r="C631" t="s">
-        <v>1238</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="632" spans="1:3" x14ac:dyDescent="0.25">
@@ -11834,10 +11870,10 @@
         <v>689</v>
       </c>
       <c r="B632" t="s">
-        <v>1239</v>
+        <v>1226</v>
       </c>
       <c r="C632" t="s">
-        <v>1240</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="633" spans="1:3" x14ac:dyDescent="0.25">
@@ -11845,10 +11881,10 @@
         <v>697</v>
       </c>
       <c r="B633" t="s">
-        <v>1241</v>
+        <v>1228</v>
       </c>
       <c r="C633" t="s">
-        <v>1242</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="634" spans="1:3" x14ac:dyDescent="0.25">
@@ -11856,10 +11892,10 @@
         <v>701</v>
       </c>
       <c r="B634" t="s">
-        <v>1243</v>
+        <v>1230</v>
       </c>
       <c r="C634" t="s">
-        <v>1244</v>
+        <v>1231</v>
       </c>
     </row>
     <row r="635" spans="1:3" x14ac:dyDescent="0.25">
@@ -11867,10 +11903,10 @@
         <v>702</v>
       </c>
       <c r="B635" t="s">
-        <v>1245</v>
+        <v>1232</v>
       </c>
       <c r="C635" t="s">
-        <v>1246</v>
+        <v>1233</v>
       </c>
     </row>
     <row r="636" spans="1:3" x14ac:dyDescent="0.25">
@@ -11878,10 +11914,10 @@
         <v>704</v>
       </c>
       <c r="B636" t="s">
-        <v>1247</v>
+        <v>1234</v>
       </c>
       <c r="C636" t="s">
-        <v>1248</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="637" spans="1:3" x14ac:dyDescent="0.25">
@@ -11889,26 +11925,32 @@
         <v>705</v>
       </c>
       <c r="B637" t="s">
-        <v>1249</v>
+        <v>1236</v>
       </c>
       <c r="C637" t="s">
-        <v>1250</v>
+        <v>1237</v>
       </c>
     </row>
     <row r="638" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A638">
         <v>707</v>
       </c>
+      <c r="B638" t="str">
+        <v>つよがるガール feat. もっさ</v>
+      </c>
       <c r="C638" t="s">
-        <v>1251</v>
+        <v>1238</v>
       </c>
     </row>
     <row r="639" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A639">
         <v>708</v>
       </c>
+      <c r="B639" t="str">
+        <v>Feathered Dreams</v>
+      </c>
       <c r="C639" t="s">
-        <v>1252</v>
+        <v>1239</v>
       </c>
     </row>
     <row r="640" spans="1:3" x14ac:dyDescent="0.25">
@@ -11916,10 +11958,10 @@
         <v>710</v>
       </c>
       <c r="B640" t="s">
-        <v>1253</v>
+        <v>1240</v>
       </c>
       <c r="C640" t="s">
-        <v>1254</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="641" spans="1:3" x14ac:dyDescent="0.25">
@@ -11927,10 +11969,10 @@
         <v>711</v>
       </c>
       <c r="B641" t="s">
-        <v>1255</v>
+        <v>1242</v>
       </c>
       <c r="C641" t="s">
-        <v>1256</v>
+        <v>1243</v>
       </c>
     </row>
     <row r="642" spans="1:3" x14ac:dyDescent="0.25">
@@ -11938,10 +11980,10 @@
         <v>712</v>
       </c>
       <c r="B642" t="s">
-        <v>1257</v>
+        <v>1244</v>
       </c>
       <c r="C642" t="s">
-        <v>1258</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="643" spans="1:3" x14ac:dyDescent="0.25">
@@ -11949,26 +11991,32 @@
         <v>714</v>
       </c>
       <c r="B643" t="s">
-        <v>1259</v>
+        <v>1246</v>
       </c>
       <c r="C643" t="s">
-        <v>1260</v>
+        <v>1247</v>
       </c>
     </row>
     <row r="644" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A644">
         <v>715</v>
       </c>
+      <c r="B644" t="str">
+        <v>残痕字</v>
+      </c>
       <c r="C644" t="s">
-        <v>1261</v>
+        <v>1248</v>
       </c>
     </row>
     <row r="645" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A645">
         <v>716</v>
       </c>
+      <c r="B645" t="str">
+        <v>アイワナムチュー</v>
+      </c>
       <c r="C645" t="s">
-        <v>1262</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="646" spans="1:3" x14ac:dyDescent="0.25">
@@ -11976,10 +12024,10 @@
         <v>717</v>
       </c>
       <c r="B646" t="s">
-        <v>1263</v>
+        <v>1250</v>
       </c>
       <c r="C646" t="s">
-        <v>1264</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="647" spans="1:3" x14ac:dyDescent="0.25">
@@ -11987,10 +12035,10 @@
         <v>718</v>
       </c>
       <c r="B647" t="s">
-        <v>1265</v>
+        <v>1252</v>
       </c>
       <c r="C647" t="s">
-        <v>1266</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="648" spans="1:3" x14ac:dyDescent="0.25">
@@ -11998,10 +12046,10 @@
         <v>719</v>
       </c>
       <c r="B648" t="s">
-        <v>1267</v>
+        <v>1254</v>
       </c>
       <c r="C648" t="s">
-        <v>1268</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="649" spans="1:3" ht="19.8" x14ac:dyDescent="0.5">
@@ -12009,10 +12057,10 @@
         <v>721</v>
       </c>
       <c r="B649" t="s">
-        <v>1269</v>
+        <v>1256</v>
       </c>
       <c r="C649" t="s">
-        <v>1270</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="650" spans="1:3" x14ac:dyDescent="0.25">
@@ -12020,10 +12068,10 @@
         <v>722</v>
       </c>
       <c r="B650" t="s">
-        <v>1271</v>
+        <v>1258</v>
       </c>
       <c r="C650" t="s">
-        <v>1272</v>
+        <v>1259</v>
       </c>
     </row>
     <row r="651" spans="1:3" x14ac:dyDescent="0.25">
@@ -12031,18 +12079,21 @@
         <v>723</v>
       </c>
       <c r="B651" t="s">
-        <v>1273</v>
+        <v>1260</v>
       </c>
       <c r="C651" t="s">
-        <v>1274</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="652" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A652">
         <v>724</v>
       </c>
-      <c r="C652" t="s">
-        <v>1275</v>
+      <c r="B652" t="str">
+        <v>Resonant Strings</v>
+      </c>
+      <c r="C652" t="str">
+        <v>rs,共鸣之弦</v>
       </c>
     </row>
     <row r="653" spans="1:3" x14ac:dyDescent="0.25">
@@ -12050,10 +12101,10 @@
         <v>725</v>
       </c>
       <c r="B653" s="2" t="s">
-        <v>1276</v>
+        <v>1263</v>
       </c>
       <c r="C653" t="s">
-        <v>1277</v>
+        <v>1264</v>
       </c>
     </row>
     <row r="654" spans="1:3" x14ac:dyDescent="0.25">
@@ -12061,10 +12112,10 @@
         <v>726</v>
       </c>
       <c r="B654" t="s">
-        <v>1278</v>
+        <v>1265</v>
       </c>
       <c r="C654" t="s">
-        <v>1279</v>
+        <v>1266</v>
       </c>
     </row>
     <row r="655" spans="1:3" x14ac:dyDescent="0.25">
@@ -12072,10 +12123,10 @@
         <v>727</v>
       </c>
       <c r="B655" t="s">
-        <v>1280</v>
+        <v>1267</v>
       </c>
       <c r="C655" t="s">
-        <v>1281</v>
+        <v>1268</v>
       </c>
     </row>
     <row r="656" spans="1:3" ht="19.8" x14ac:dyDescent="0.5">
@@ -12083,10 +12134,10 @@
         <v>728</v>
       </c>
       <c r="B656" t="s">
-        <v>1282</v>
+        <v>1269</v>
       </c>
       <c r="C656" t="s">
-        <v>1283</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="657" spans="1:3" ht="19.8" x14ac:dyDescent="0.5">
@@ -12094,10 +12145,10 @@
         <v>729</v>
       </c>
       <c r="B657" t="s">
-        <v>1284</v>
+        <v>1271</v>
       </c>
       <c r="C657" t="s">
-        <v>1285</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="658" spans="1:3" x14ac:dyDescent="0.25">
@@ -12105,10 +12156,10 @@
         <v>730</v>
       </c>
       <c r="B658" t="s">
-        <v>1286</v>
+        <v>1273</v>
       </c>
       <c r="C658" t="s">
-        <v>1287</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="659" spans="1:3" x14ac:dyDescent="0.25">
@@ -12116,18 +12167,21 @@
         <v>731</v>
       </c>
       <c r="B659" t="s">
-        <v>1288</v>
+        <v>1275</v>
       </c>
       <c r="C659" t="s">
-        <v>1289</v>
+        <v>1276</v>
       </c>
     </row>
     <row r="660" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A660">
         <v>732</v>
       </c>
+      <c r="B660" t="str">
+        <v>Fallen</v>
+      </c>
       <c r="C660" t="s">
-        <v>1290</v>
+        <v>1277</v>
       </c>
     </row>
     <row r="661" spans="1:3" x14ac:dyDescent="0.25">
@@ -12135,18 +12189,21 @@
         <v>733</v>
       </c>
       <c r="B661" t="s">
-        <v>1291</v>
+        <v>1278</v>
       </c>
       <c r="C661" t="s">
-        <v>1292</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="662" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A662">
         <v>734</v>
       </c>
+      <c r="B662" t="str">
+        <v>POP IN 2</v>
+      </c>
       <c r="C662" t="s">
-        <v>1293</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="663" spans="1:3" x14ac:dyDescent="0.25">
@@ -12154,10 +12211,10 @@
         <v>735</v>
       </c>
       <c r="B663" t="s">
-        <v>1294</v>
+        <v>1281</v>
       </c>
       <c r="C663" t="s">
-        <v>1295</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="664" spans="1:3" x14ac:dyDescent="0.25">
@@ -12165,10 +12222,10 @@
         <v>736</v>
       </c>
       <c r="B664" t="s">
-        <v>1296</v>
+        <v>1283</v>
       </c>
       <c r="C664" t="s">
-        <v>1297</v>
+        <v>1284</v>
       </c>
     </row>
     <row r="665" spans="1:3" x14ac:dyDescent="0.25">
@@ -12176,10 +12233,10 @@
         <v>737</v>
       </c>
       <c r="B665" t="s">
-        <v>1298</v>
+        <v>1285</v>
       </c>
       <c r="C665" t="s">
-        <v>1299</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="666" spans="1:3" x14ac:dyDescent="0.25">
@@ -12187,10 +12244,10 @@
         <v>738</v>
       </c>
       <c r="B666" t="s">
-        <v>1300</v>
+        <v>1287</v>
       </c>
       <c r="C666" t="s">
-        <v>1301</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="667" spans="1:3" x14ac:dyDescent="0.25">
@@ -12198,10 +12255,10 @@
         <v>739</v>
       </c>
       <c r="B667" t="s">
-        <v>1302</v>
+        <v>1289</v>
       </c>
       <c r="C667" t="s">
-        <v>1303</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="668" spans="1:3" x14ac:dyDescent="0.25">
@@ -12209,10 +12266,10 @@
         <v>740</v>
       </c>
       <c r="B668" t="s">
-        <v>1304</v>
+        <v>1291</v>
       </c>
       <c r="C668" t="s">
-        <v>1305</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="669" spans="1:3" x14ac:dyDescent="0.25">
@@ -12220,10 +12277,10 @@
         <v>741</v>
       </c>
       <c r="B669" t="s">
-        <v>1306</v>
-      </c>
-      <c r="C669" t="s">
-        <v>1307</v>
+        <v>1293</v>
+      </c>
+      <c r="C669" t="str">
+        <v>世界中的青空,世界中青空,世界中的清空,世界清空,世青空,世清空,收集全世界的蓝天,汇聚全世界的蔚蓝天空</v>
       </c>
     </row>
     <row r="670" spans="1:3" x14ac:dyDescent="0.25">
@@ -12231,10 +12288,10 @@
         <v>742</v>
       </c>
       <c r="B670" t="s">
-        <v>1308</v>
+        <v>1295</v>
       </c>
       <c r="C670" t="s">
-        <v>1309</v>
+        <v>1296</v>
       </c>
     </row>
     <row r="671" spans="1:3" x14ac:dyDescent="0.25">
@@ -12242,10 +12299,10 @@
         <v>743</v>
       </c>
       <c r="B671" t="s">
-        <v>1310</v>
+        <v>1297</v>
       </c>
       <c r="C671" t="s">
-        <v>1311</v>
+        <v>1298</v>
       </c>
     </row>
     <row r="672" spans="1:3" x14ac:dyDescent="0.25">
@@ -12253,10 +12310,10 @@
         <v>744</v>
       </c>
       <c r="B672" t="s">
-        <v>1312</v>
+        <v>1299</v>
       </c>
       <c r="C672" t="s">
-        <v>1313</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="673" spans="1:3" ht="19.8" x14ac:dyDescent="0.5">
@@ -12264,10 +12321,10 @@
         <v>745</v>
       </c>
       <c r="B673" s="1" t="s">
-        <v>1314</v>
-      </c>
-      <c r="C673" t="s">
-        <v>1315</v>
+        <v>1301</v>
+      </c>
+      <c r="C673" t="str">
+        <v>桃色片想,三丽鸥,桃色单恋</v>
       </c>
     </row>
     <row r="674" spans="1:3" x14ac:dyDescent="0.25">
@@ -12275,10 +12332,10 @@
         <v>746</v>
       </c>
       <c r="B674" s="1" t="s">
-        <v>1316</v>
+        <v>1303</v>
       </c>
       <c r="C674" t="s">
-        <v>1317</v>
+        <v>1304</v>
       </c>
     </row>
     <row r="675" spans="1:3" x14ac:dyDescent="0.25">
@@ -12286,10 +12343,10 @@
         <v>747</v>
       </c>
       <c r="B675" s="1" t="s">
-        <v>1318</v>
+        <v>1305</v>
       </c>
       <c r="C675" t="s">
-        <v>1319</v>
+        <v>1306</v>
       </c>
     </row>
     <row r="676" spans="1:3" x14ac:dyDescent="0.25">
@@ -12297,10 +12354,10 @@
         <v>748</v>
       </c>
       <c r="B676" s="1" t="s">
-        <v>1320</v>
+        <v>1307</v>
       </c>
       <c r="C676" t="s">
-        <v>1321</v>
+        <v>1308</v>
       </c>
     </row>
     <row r="677" spans="1:3" x14ac:dyDescent="0.25">
@@ -12308,28 +12365,32 @@
         <v>749</v>
       </c>
       <c r="B677" s="1" t="s">
-        <v>1322</v>
+        <v>1309</v>
       </c>
       <c r="C677" t="s">
-        <v>1323</v>
+        <v>1310</v>
       </c>
     </row>
     <row r="678" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A678">
         <v>750</v>
       </c>
-      <c r="B678" s="1"/>
+      <c r="B678" s="1" t="str">
+        <v>スマイリーキャロル</v>
+      </c>
       <c r="C678" t="s">
-        <v>1324</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="679" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A679">
         <v>751</v>
       </c>
-      <c r="B679" s="1"/>
+      <c r="B679" s="1" t="str">
+        <v>ミラクルペイント</v>
+      </c>
       <c r="C679" t="s">
-        <v>1325</v>
+        <v>1312</v>
       </c>
     </row>
     <row r="680" spans="1:3" x14ac:dyDescent="0.25">
@@ -12337,10 +12398,10 @@
         <v>753</v>
       </c>
       <c r="B680" s="1" t="s">
-        <v>1326</v>
+        <v>1313</v>
       </c>
       <c r="C680" t="s">
-        <v>1327</v>
+        <v>1314</v>
       </c>
     </row>
     <row r="681" spans="1:3" x14ac:dyDescent="0.25">
@@ -12348,10 +12409,10 @@
         <v>755</v>
       </c>
       <c r="B681" s="1" t="s">
-        <v>1328</v>
+        <v>1315</v>
       </c>
       <c r="C681" t="s">
-        <v>1329</v>
+        <v>1316</v>
       </c>
     </row>
     <row r="682" spans="1:3" x14ac:dyDescent="0.25">
@@ -12359,10 +12420,10 @@
         <v>756</v>
       </c>
       <c r="B682" s="1" t="s">
-        <v>1330</v>
+        <v>1317</v>
       </c>
       <c r="C682" t="s">
-        <v>1331</v>
+        <v>1318</v>
       </c>
     </row>
     <row r="683" spans="1:3" x14ac:dyDescent="0.25">
@@ -12370,10 +12431,10 @@
         <v>757</v>
       </c>
       <c r="B683" s="1" t="s">
-        <v>1332</v>
+        <v>1319</v>
       </c>
       <c r="C683" t="s">
-        <v>1333</v>
+        <v>1320</v>
       </c>
     </row>
     <row r="684" spans="1:3" x14ac:dyDescent="0.25">
@@ -12381,10 +12442,10 @@
         <v>758</v>
       </c>
       <c r="B684" s="1" t="s">
-        <v>1334</v>
+        <v>1321</v>
       </c>
       <c r="C684" t="s">
-        <v>1335</v>
+        <v>1322</v>
       </c>
     </row>
     <row r="685" spans="1:3" x14ac:dyDescent="0.25">
@@ -12392,10 +12453,10 @@
         <v>759</v>
       </c>
       <c r="B685" s="1" t="s">
-        <v>1336</v>
+        <v>1323</v>
       </c>
       <c r="C685" t="s">
-        <v>1337</v>
+        <v>1324</v>
       </c>
     </row>
     <row r="686" spans="1:3" x14ac:dyDescent="0.25">
@@ -12403,10 +12464,10 @@
         <v>760</v>
       </c>
       <c r="B686" s="1" t="s">
-        <v>1338</v>
+        <v>1325</v>
       </c>
       <c r="C686" t="s">
-        <v>1339</v>
+        <v>1326</v>
       </c>
     </row>
     <row r="687" spans="1:3" ht="19.8" x14ac:dyDescent="0.5">
@@ -12414,10 +12475,10 @@
         <v>761</v>
       </c>
       <c r="B687" s="1" t="s">
-        <v>1340</v>
+        <v>1327</v>
       </c>
       <c r="C687" t="s">
-        <v>1341</v>
+        <v>1328</v>
       </c>
     </row>
     <row r="688" spans="1:3" ht="19.2" x14ac:dyDescent="0.45">
@@ -12425,10 +12486,10 @@
         <v>762</v>
       </c>
       <c r="B688" s="1" t="s">
-        <v>1342</v>
+        <v>1329</v>
       </c>
       <c r="C688" t="s">
-        <v>1343</v>
+        <v>1330</v>
       </c>
     </row>
     <row r="689" spans="1:3" ht="19.2" x14ac:dyDescent="0.45">
@@ -12436,10 +12497,10 @@
         <v>763</v>
       </c>
       <c r="B689" s="1" t="s">
-        <v>1344</v>
+        <v>1331</v>
       </c>
       <c r="C689" t="s">
-        <v>1345</v>
+        <v>1332</v>
       </c>
     </row>
     <row r="690" spans="1:3" x14ac:dyDescent="0.25">
@@ -12447,10 +12508,10 @@
         <v>764</v>
       </c>
       <c r="B690" s="1" t="s">
-        <v>1346</v>
+        <v>1333</v>
       </c>
       <c r="C690" t="s">
-        <v>1347</v>
+        <v>1334</v>
       </c>
     </row>
     <row r="691" spans="1:3" x14ac:dyDescent="0.25">
@@ -12458,19 +12519,21 @@
         <v>765</v>
       </c>
       <c r="B691" s="1" t="s">
-        <v>1348</v>
-      </c>
-      <c r="C691" t="s">
-        <v>1349</v>
+        <v>1335</v>
+      </c>
+      <c r="C691" t="str">
+        <v>start,拉帮结派,拉邦结派,ll,梦想☆启程</v>
       </c>
     </row>
     <row r="692" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A692">
         <v>766</v>
       </c>
-      <c r="B692" s="1"/>
+      <c r="B692" s="1" t="str">
+        <v>RUNAWAY STAR</v>
+      </c>
       <c r="C692" t="s">
-        <v>1350</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="693" spans="1:3" x14ac:dyDescent="0.25">
@@ -12478,19 +12541,21 @@
         <v>767</v>
       </c>
       <c r="B693" s="1" t="s">
-        <v>1351</v>
+        <v>1338</v>
       </c>
       <c r="C693" t="s">
-        <v>1352</v>
+        <v>1339</v>
       </c>
     </row>
     <row r="694" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A694">
         <v>768</v>
       </c>
-      <c r="B694" s="1"/>
+      <c r="B694" s="1" t="str">
+        <v>どきどきデエト</v>
+      </c>
       <c r="C694" t="s">
-        <v>1353</v>
+        <v>1340</v>
       </c>
     </row>
     <row r="695" spans="1:3" x14ac:dyDescent="0.25">
@@ -12498,10 +12563,10 @@
         <v>769</v>
       </c>
       <c r="B695" s="1" t="s">
-        <v>1354</v>
+        <v>1341</v>
       </c>
       <c r="C695" t="s">
-        <v>1355</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="696" spans="1:3" x14ac:dyDescent="0.25">
@@ -12509,352 +12574,469 @@
         <v>772</v>
       </c>
       <c r="B696" s="1" t="s">
-        <v>1356</v>
+        <v>1343</v>
       </c>
       <c r="C696" t="s">
-        <v>1357</v>
+        <v>1344</v>
       </c>
     </row>
     <row r="697" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A697">
         <v>773</v>
       </c>
-      <c r="B697" s="1"/>
+      <c r="B697" s="1" t="str">
+        <v>かぽーんっと極楽☆ 湯〜とぴあ！</v>
+      </c>
       <c r="C697" t="s">
-        <v>1358</v>
+        <v>1345</v>
       </c>
     </row>
     <row r="698" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A698">
         <v>774</v>
       </c>
-      <c r="B698" s="1"/>
+      <c r="B698" s="1" t="str">
+        <v>MATSURI BAYASHI</v>
+      </c>
       <c r="C698" t="s">
-        <v>1359</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="699" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A699">
         <v>776</v>
       </c>
-      <c r="B699" s="1"/>
+      <c r="B699" s="1" t="str">
+        <v>DAY×DAY</v>
+      </c>
       <c r="C699" t="s">
-        <v>1360</v>
+        <v>1347</v>
       </c>
     </row>
     <row r="700" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A700">
         <v>779</v>
       </c>
-      <c r="B700" s="1"/>
+      <c r="B700" s="1" t="str">
+        <v>金曜日のおはよう</v>
+      </c>
       <c r="C700" t="s">
-        <v>1361</v>
+        <v>1348</v>
       </c>
     </row>
     <row r="701" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A701">
         <v>780</v>
       </c>
-      <c r="B701" s="1"/>
+      <c r="B701" s="1" t="str">
+        <v>許婚っきゅん</v>
+      </c>
       <c r="C701" t="s">
-        <v>1362</v>
+        <v>1349</v>
       </c>
     </row>
     <row r="702" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A702">
         <v>781</v>
       </c>
-      <c r="B702" s="1"/>
+      <c r="B702" s="1" t="str">
+        <v>過去を喰らう</v>
+      </c>
       <c r="C702" t="s">
-        <v>1363</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="703" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A703">
         <v>783</v>
       </c>
-      <c r="B703" s="1"/>
+      <c r="B703" s="1" t="str">
+        <v>COMIC PANIC!!!(パラレルver.)</v>
+      </c>
       <c r="C703" t="s">
-        <v>1364</v>
+        <v>1351</v>
       </c>
     </row>
     <row r="704" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A704">
         <v>782</v>
       </c>
-      <c r="B704" s="1"/>
+      <c r="B704" s="1" t="str">
+        <v>Game Changer</v>
+      </c>
       <c r="C704" s="3" t="s">
-        <v>1402</v>
+        <v>1389</v>
       </c>
     </row>
     <row r="705" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A705">
         <v>784</v>
       </c>
-      <c r="B705" s="1"/>
+      <c r="B705" s="1" t="str">
+        <v>灼熱 Bonfire!(パラレルver.)</v>
+      </c>
       <c r="C705" t="s">
-        <v>1365</v>
+        <v>1352</v>
       </c>
     </row>
     <row r="706" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A706">
         <v>785</v>
       </c>
+      <c r="B706" t="str">
+        <v>Painting New Dawn</v>
+      </c>
       <c r="C706" t="s">
-        <v>1366</v>
+        <v>1353</v>
       </c>
     </row>
     <row r="707" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A707">
         <v>787</v>
       </c>
+      <c r="B707" t="str">
+        <v>ヒカリへ</v>
+      </c>
       <c r="C707" t="s">
-        <v>1367</v>
+        <v>1354</v>
       </c>
     </row>
     <row r="708" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A708">
         <v>788</v>
       </c>
+      <c r="B708" t="str">
+        <v>証は赫く</v>
+      </c>
       <c r="C708" t="s">
-        <v>1368</v>
+        <v>1355</v>
       </c>
     </row>
     <row r="709" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A709">
         <v>790</v>
       </c>
+      <c r="B709" t="str">
+        <v>ときめきエクスペリエンス！ (月島まりなver.)</v>
+      </c>
       <c r="C709" t="s">
-        <v>1369</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="710" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A710">
         <v>791</v>
       </c>
+      <c r="B710" t="str">
+        <v>絶対零度</v>
+      </c>
       <c r="C710" t="s">
-        <v>1370</v>
+        <v>1357</v>
       </c>
     </row>
     <row r="711" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A711">
         <v>792</v>
       </c>
+      <c r="B711" t="str">
+        <v>舞台に立って</v>
+      </c>
       <c r="C711" t="s">
-        <v>1371</v>
+        <v>1358</v>
       </c>
     </row>
     <row r="712" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A712">
         <v>794</v>
       </c>
+      <c r="B712" t="str">
+        <v>超最強</v>
+      </c>
       <c r="C712" t="s">
-        <v>1372</v>
+        <v>1359</v>
       </c>
     </row>
     <row r="713" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A713">
         <v>795</v>
       </c>
+      <c r="B713" t="str">
+        <v>ランデヴー</v>
+      </c>
       <c r="C713" t="s">
-        <v>1373</v>
+        <v>1360</v>
       </c>
     </row>
     <row r="714" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A714">
         <v>796</v>
       </c>
+      <c r="B714" t="str">
+        <v>無路矢</v>
+      </c>
       <c r="C714" t="s">
-        <v>1374</v>
+        <v>1361</v>
       </c>
     </row>
     <row r="715" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A715">
         <v>797</v>
       </c>
+      <c r="B715" t="str">
+        <v>ココロのちず</v>
+      </c>
       <c r="C715" t="s">
-        <v>1375</v>
+        <v>1362</v>
       </c>
     </row>
     <row r="716" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A716">
         <v>798</v>
       </c>
+      <c r="B716" t="str">
+        <v>胡蝶翔る星月夜</v>
+      </c>
       <c r="C716" t="s">
-        <v>1376</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="717" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A717">
         <v>799</v>
       </c>
+      <c r="B717" t="str">
+        <v>Come to see YOU!!</v>
+      </c>
       <c r="C717" t="s">
-        <v>1377</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="718" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A718">
         <v>800</v>
       </c>
+      <c r="B718" t="str">
+        <v>ほれぼれっ☆すまいるゴール！</v>
+      </c>
       <c r="C718" t="s">
-        <v>1378</v>
+        <v>1365</v>
       </c>
     </row>
     <row r="719" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A719">
         <v>801</v>
       </c>
+      <c r="B719" t="str">
+        <v>Amore</v>
+      </c>
     </row>
     <row r="720" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A720">
         <v>802</v>
       </c>
+      <c r="B720" t="str">
+        <v>who we aRe</v>
+      </c>
       <c r="C720" t="s">
-        <v>1379</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="721" spans="1:3" ht="16.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A721">
         <v>803</v>
       </c>
+      <c r="B721" t="str">
+        <v>Wings of the Lights</v>
+      </c>
       <c r="C721" t="s">
-        <v>1380</v>
+        <v>1367</v>
       </c>
     </row>
     <row r="722" spans="1:3" ht="16.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A722">
         <v>804</v>
       </c>
+      <c r="B722" t="str">
+        <v>スターラブレイション</v>
+      </c>
       <c r="C722" t="s">
-        <v>1381</v>
+        <v>1368</v>
       </c>
     </row>
     <row r="723" spans="1:3" ht="16.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A723">
         <v>805</v>
       </c>
+      <c r="B723" t="str">
+        <v>夕影と歌う この先も</v>
+      </c>
       <c r="C723" s="3" t="s">
-        <v>1385</v>
+        <v>1372</v>
       </c>
     </row>
     <row r="724" spans="1:3" ht="16.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A724">
         <v>806</v>
       </c>
+      <c r="B724" t="str">
+        <v>Rainbow of Dreams</v>
+      </c>
       <c r="C724" s="3" t="s">
-        <v>1386</v>
+        <v>1373</v>
       </c>
     </row>
     <row r="725" spans="1:3" ht="16.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A725">
         <v>807</v>
       </c>
+      <c r="B725" t="str">
+        <v>ポニーテールとシュシュ</v>
+      </c>
       <c r="C725" s="3" t="s">
-        <v>1387</v>
+        <v>1374</v>
       </c>
     </row>
     <row r="726" spans="1:3" ht="16.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A726">
         <v>808</v>
       </c>
+      <c r="B726" t="str">
+        <v>I AM WHO I AM</v>
+      </c>
       <c r="C726" s="3" t="s">
-        <v>1388</v>
+        <v>1375</v>
       </c>
     </row>
     <row r="727" spans="1:3" ht="16.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A727">
         <v>809</v>
       </c>
+      <c r="B727" t="str">
+        <v>SUMMER SONG</v>
+      </c>
       <c r="C727" s="3" t="s">
-        <v>1389</v>
+        <v>1376</v>
       </c>
     </row>
     <row r="728" spans="1:3" ht="16.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A728">
         <v>810</v>
       </c>
+      <c r="B728" t="str">
+        <v>好き・スキ・だいすき〜ズっ！</v>
+      </c>
       <c r="C728" s="3" t="s">
-        <v>1390</v>
+        <v>1377</v>
       </c>
     </row>
     <row r="729" spans="1:3" ht="16.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A729">
         <v>811</v>
       </c>
+      <c r="B729" t="str">
+        <v>私の心はチョココロネ(パラレルver.)</v>
+      </c>
       <c r="C729" s="3" t="s">
-        <v>1392</v>
+        <v>1379</v>
       </c>
     </row>
     <row r="730" spans="1:3" ht="16.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A730">
         <v>812</v>
       </c>
+      <c r="B730" t="str">
+        <v>Resound the Way</v>
+      </c>
       <c r="C730" s="3" t="s">
-        <v>1393</v>
+        <v>1380</v>
       </c>
     </row>
     <row r="731" spans="1:3" ht="16.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A731">
         <v>813</v>
       </c>
+      <c r="B731" t="str">
+        <v>この蒼き闇と光</v>
+      </c>
       <c r="C731" s="3" t="s">
-        <v>1394</v>
+        <v>1381</v>
       </c>
     </row>
     <row r="732" spans="1:3" ht="16.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A732">
         <v>814</v>
       </c>
+      <c r="B732" t="str">
+        <v>勇侠青春謳</v>
+      </c>
       <c r="C732" s="3" t="s">
-        <v>1395</v>
+        <v>1382</v>
       </c>
     </row>
     <row r="733" spans="1:3" ht="16.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A733">
         <v>815</v>
       </c>
+      <c r="B733" t="str">
+        <v>盛れ！ミ・アモーレ</v>
+      </c>
       <c r="C733" s="3" t="s">
-        <v>1396</v>
+        <v>1383</v>
       </c>
     </row>
     <row r="734" spans="1:3" ht="16.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A734">
         <v>816</v>
       </c>
+      <c r="B734" t="str">
+        <v>浪漫飛行</v>
+      </c>
       <c r="C734" s="3" t="s">
-        <v>1384</v>
+        <v>1371</v>
       </c>
     </row>
     <row r="735" spans="1:3" ht="16.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A735">
         <v>817</v>
       </c>
+      <c r="B735" t="str">
+        <v>千の翼</v>
+      </c>
       <c r="C735" s="3" t="s">
-        <v>1397</v>
+        <v>1384</v>
       </c>
     </row>
     <row r="736" spans="1:3" ht="16.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A736">
         <v>818</v>
       </c>
+      <c r="B736" t="str">
+        <v>けっかおーらい</v>
+      </c>
       <c r="C736" s="3" t="s">
-        <v>1398</v>
+        <v>1385</v>
       </c>
     </row>
     <row r="737" spans="1:3" ht="16.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A737">
         <v>819</v>
       </c>
+      <c r="B737" t="str">
+        <v>悲しみなんて笑い飛ばせ</v>
+      </c>
       <c r="C737" s="3" t="s">
-        <v>1399</v>
+        <v>1386</v>
       </c>
     </row>
     <row r="738" spans="1:3" ht="16.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A738">
         <v>820</v>
       </c>
+      <c r="B738" t="str">
+        <v>オー！リバル</v>
+      </c>
       <c r="C738" s="3" t="s">
-        <v>1400</v>
+        <v>1387</v>
       </c>
     </row>
     <row r="739" spans="1:3" x14ac:dyDescent="0.25">
@@ -12862,10 +13044,10 @@
         <v>10001</v>
       </c>
       <c r="B739" t="s">
-        <v>1382</v>
+        <v>1369</v>
       </c>
       <c r="C739" t="s">
-        <v>1383</v>
+        <v>1370</v>
       </c>
     </row>
     <row r="740" spans="1:3" x14ac:dyDescent="0.25">
@@ -12873,10 +13055,142 @@
         <v>10003</v>
       </c>
       <c r="B740" t="s">
-        <v>1354</v>
+        <v>1341</v>
       </c>
       <c r="C740" t="s">
-        <v>1355</v>
+        <v>1342</v>
+      </c>
+    </row>
+    <row r="741" spans="1:3">
+      <c r="A741" t="n">
+        <v>454</v>
+      </c>
+      <c r="B741" t="str">
+        <v>だから、ひとりじゃない</v>
+      </c>
+      <c r="C741" t="str">
+        <v>所以，不是一个人</v>
+      </c>
+    </row>
+    <row r="742" spans="1:3">
+      <c r="A742" t="n">
+        <v>614</v>
+      </c>
+      <c r="B742" t="str">
+        <v>雨上がり、キミと</v>
+      </c>
+      <c r="C742" t="str">
+        <v>雨后，与你</v>
+      </c>
+    </row>
+    <row r="743" spans="1:3">
+      <c r="A743" t="n">
+        <v>600</v>
+      </c>
+      <c r="B743" t="str">
+        <v>むすんでわらって</v>
+      </c>
+      <c r="C743" t="str">
+        <v>结缘笑颜</v>
+      </c>
+    </row>
+    <row r="744" spans="1:3">
+      <c r="A744" t="n">
+        <v>664</v>
+      </c>
+      <c r="B744" t="str">
+        <v>れっつ・スマイル・すとり〜みんぐっ♪</v>
+      </c>
+      <c r="C744" t="str">
+        <v>一直·微笑·大家～♪</v>
+      </c>
+    </row>
+    <row r="745" spans="1:3">
+      <c r="A745" t="n">
+        <v>641</v>
+      </c>
+      <c r="B745" t="str">
+        <v>ハイタッチ／＼びりーばーず☆</v>
+      </c>
+      <c r="C745" t="str">
+        <v>击掌／＼比里巴斯</v>
+      </c>
+    </row>
+    <row r="746" spans="1:3">
+      <c r="A746" t="n">
+        <v>621</v>
+      </c>
+      <c r="B746" t="str">
+        <v>With〜きみとわたしたちの物語〜</v>
+      </c>
+      <c r="C746" t="str">
+        <v>With～你和我们的故事～</v>
+      </c>
+    </row>
+    <row r="747" spans="1:3">
+      <c r="A747" t="n">
+        <v>692</v>
+      </c>
+      <c r="B747" t="str">
+        <v>Portray Empathy</v>
+      </c>
+      <c r="C747" t="str">
+        <v>描绘共情</v>
+      </c>
+    </row>
+    <row r="748" spans="1:3">
+      <c r="A748" t="n">
+        <v>694</v>
+      </c>
+      <c r="B748" t="str">
+        <v>Y.O.L.O！！！！！(パスパレver.)</v>
+      </c>
+      <c r="C748" t="str">
+        <v>人生只有一次!!!!!(PasPale版）</v>
+      </c>
+    </row>
+    <row r="749" spans="1:3">
+      <c r="A749" t="n">
+        <v>703</v>
+      </c>
+      <c r="B749" t="str">
+        <v>Polyphonyscape</v>
+      </c>
+      <c r="C749" t="str">
+        <v>异律同景</v>
+      </c>
+    </row>
+    <row r="750" spans="1:3">
+      <c r="A750" t="n">
+        <v>775</v>
+      </c>
+      <c r="B750" t="str">
+        <v>メロウ</v>
+      </c>
+      <c r="C750" t="str">
+        <v>柔和的</v>
+      </c>
+    </row>
+    <row r="751" spans="1:3">
+      <c r="A751" t="n">
+        <v>666</v>
+      </c>
+      <c r="B751" t="str">
+        <v>花笑みのデュオ</v>
+      </c>
+      <c r="C751" t="str">
+        <v>花之微笑的二重奏</v>
+      </c>
+    </row>
+    <row r="752" spans="1:3">
+      <c r="A752" t="n">
+        <v>616</v>
+      </c>
+      <c r="B752" t="str">
+        <v>Sage der Rosen</v>
+      </c>
+      <c r="C752" t="str">
+        <v>玫瑰的传说</v>
       </c>
     </row>
   </sheetData>
@@ -12884,7 +13198,7 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200"/>
   <ignoredErrors>
-    <ignoredError sqref="A32:C35 A36:B36 A37:C37 A1:C1 A121:C127 A120:B120 A739:B739 A315:B315 A316:C317 A352:C352 A351:B351 A594:C594 A575 A574:B574 A460:C462 A459:B459 A627:B627 A235:C242 A247:B247 A248:C249 A234:B234 A95:C96 A146:C149 A145:B145 A541:C549 A540:B540 A55:C55 A558:C564 A29:C29 A28:B28 A579:C579 A308:C312 A307:B307 A53:B54 A457:C458 A516:C516 A93:B94 A554:C554 A553:B553 A346:C348 A345:B345 A52:C52 A51:B51 A72:C76 A70:B70 A163:C166 A162:B162 A378:C378 A377:B377 A630:C632 A258:C259 A257:B257 A7:C7 A573:C573 A567:C568 A566 A616:C616 A21:C22 A20:B20 A420:C420 A119:C119 A118:B118 A115:C117 A287:C293 A418:B419 A80:C82 A79:B79 A504:C504 A503 A151:C151 A150:B150 A481:C482 A480:B480 A520:C520 A517:B519 A532:C535 A625:B625 A576:B578 A513:B515 A501:C502 A454:C454 A424:C424 A14:C14 A12:B13 A2:B6 A582:C582 A580:B580 A450:C450 A449:B449 A552:C552 A550:B551 A539:C539 A508:C508 A509:B510 A511:C512 A505:B507 A466:C466 A448:C448 A447:B447 A433:C440 A432:B432 A425:B425 A403:C405 A401:B402 A281:C284 A269:C270 A268:B268 A261:C267 A260:B260 A252:C253 A250:B251 A231:C233 A229:B230 A108:C109 A107:B107 A59:C62 A155:C157 A154:B154 A129:C129 A128:B128 A71 A9:C11 A8:B8 A602:C602 A382:C382 A383:B383 A384:C384 A379:B381 A451:B453 A523:C524 A521:B522 A470:C471 A469:B469 A455:B456 A100:C106 A99:B99 A40:C42 A16:C16 A15:B15 A565:B565 A555:B557 A478:C479 A477:B477 A408:C411 A407:B407 A387:C389 A385:B386 A328:C331 A327 A297:C306 A44:C50 A43:B43 A609:C610 A605:B605 A598:B598 A354:C360 A353:B353 A463:B465 A350:C350 A349:B349 A475:C476 A473 A86:C90 A85:B85 A30:B31 A38:B39 A171:C177 A170:B170 A612:C612 A590:C590 A587:B587 A569:B572 A24:C27 A23:B23 A499:B500 A414:C417 A412:A413 C412:C413 A406 A375:C376 A374:B374 A279:B280 A536:B538 A474:B474 A618:B618 A595:B595 A134:C141 A133:B133 A314:C314 A313:B313 A209:C209 A208:B208 A421:B423 A488:C498 A487:B487 A285:B286 A168:C169 A167:B167 A391:C391 A390:B390 A393:C398 A392 A622:B623 A426:C428 A608:B608 A113:B114 A340:C341 A338:B339 A294:B296 A468:C468 A467:B467 A225:C228 A224:B224 A530:B531 A131:C132 A130:B130 A272:C278 A271:B271 A526:C529 A525:B525 A56:B58 A255:C256 A254:B254 A153:C153 A152:B152 A212:C219 A210:B211 A343:C344 A342:B342 A98:C98 A97:B97 A599:C599 A199:C199 A198:B198 A362:C373 A361:B361 A84:C84 A83:B83 A143:C144 A142:B142 A183:C189 A181:B182 A442:C446 A441:B441 A19:C19 A17:B18 A485:C486 A483:B484 A65:C69 A63:B64 A320:C326 A318:B319 A179:C180 A178:B178 A111:C112 A110:B110 A400:C400 A399:B399 A221:C223 A220:B220 A159:C161 A158:B158 A333:C333 A332:B332 A430:C431 A429:B429 A472:B472 A191:C197 A190:B190 A589:B589 A201:C207 A200:B200 A92:C92 A91:B91 A335:C337 A334:B334 A600 A244:C246 A243:B243 A78:C78 A77:B77" numberStoredAsText="1"/>
+    <ignoredError sqref="A32:C35 A36:B36 A37:C37 A1:C1 A121:C127 A120:B120 A739:B739 A315:B315 A316:C317 A352:C352 A351:B351 A594:C594 A575 A574:B574 A460:C462 A459:B459 A627:B627 A235:C242 A247:B247 A248:C249 A234:B234 A95:C96 A146:C149 A145:B145 A541:C549 A540:B540 A55:C55 A558:C564 A29:C29 A28:B28 A579:C579 A308:C312 A307:B307 A53:B54 A457:C458 A516:C516 A93:B94 A554:C554 A553:B553 A346:C348 A345:B345 A52:C52 A51:B51 A72:C75 A70:B70 A163:C166 A162:B162 A378:C378 A377:B377 A630:C632 A258:C259 A257:B257 A7:C7 A573:C573 A567:C568 A566 A616:C616 A21:C22 A20:B20 A420:C420 A119:C119 A118:B118 A115:C117 A287:C293 A418:B419 A80:C82 A79:B79 A504:C504 A503 A151:C151 A150:B150 A481:C482 A480:B480 A520:C520 A517:B519 A532:C535 A625:B625 A576:B578 A513:B515 A501:C502 A454:C454 A424:C424 A14:C14 A12:B13 A2:B6 A582:C582 A580:B580 A450:C450 A449:B449 A552:C552 A550:B551 A539:C539 A508:C508 A509:B510 A511:C512 A505:B507 A466:C466 A448:C448 A447:B447 A433:C440 A432:B432 A425:B425 A403:C405 A401:B402 A281:C284 A269:C270 A268:B268 A261:C267 A260:B260 A252:C253 A250:B251 A231:C233 A229:B230 A108:C109 A107:B107 A59:C62 A155:C156 A154:B154 A129:C129 A128:B128 A71 A9:C11 A8:B8 A602:C602 A382:C382 A383:B383 A384:C384 A379:B381 A451:B453 A523:C524 A521:B522 A470:C471 A469:B469 A455:B456 A100:C106 A99:B99 A40:C42 A16:C16 A15:B15 A565:B565 A555:B557 A478:C479 A477:B477 A408:C411 A407:B407 A387:C389 A385:B386 A328:C331 A327 A297:C306 A44:C50 A43:B43 A609:C610 A605:B605 A598:B598 A354:C360 A353:B353 A463:B465 A350:C350 A349:B349 A475:C476 A473 A86:C90 A85:B85 A30:B31 A38:B39 A171:C177 A170:B170 A612:C612 A590:C590 A587:B587 A569:B572 A24:C27 A23:B23 A499:B500 A414:C417 A412:A413 C412:C413 A406 A375:C376 A374:B374 A279:B280 A536:B538 A474:B474 A618:B618 A595:B595 A134:C141 A133:B133 A314:C314 A313:B313 A209:C209 A208:B208 A421:B423 A488:C498 A487:B487 A285:B286 A168:C169 A167:B167 A391:C391 A390:B390 A393:C398 A392 A622:B623 A426:C428 A608:B608 A113:B114 A340:C341 A338:B339 A294:B296 A468:C468 A467:B467 A225:C228 A224:B224 A530:B531 A131:C132 A130:B130 A272:C275 A271:B271 A526:C529 A525:B525 A56:B58 A255:C256 A254:B254 A153:C153 A152:B152 A212:C219 A210:B211 A343:C344 A342:B342 A98:C98 A97:B97 A599:C599 A199:C199 A198:B198 A362:C373 A361:B361 A84:B84 A83:B83 A143:C144 A142:B142 A183:C186 A181:B182 A442:C446 A441:B441 A19:C19 A17:B18 A485:C486 A483:B484 A65:C69 A63:B64 A320:C325 A318:B319 A179:C180 A178:B178 A111:C112 A110:B110 A400:C400 A399:B399 A221:C223 A220:B220 A159:C161 A158:B158 A333:C333 A332:B332 A430:C431 A429:B429 A472:B472 A191:C197 A190:B190 A589:B589 A201:C207 A200:B200 A92:C92 A91:B91 A335:C337 A334:B334 A600 A244:C246 A243:B243 A78:C78 A77:B77 A76:B76 A277:C278 A276:B276 A188:C189 A187:B187 A326:B326 A157:B157" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>